--- a/UKMLA_Keyword_Cluster_Sheet.xlsx
+++ b/UKMLA_Keyword_Cluster_Sheet.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Keyword Cluster Sheet'!$A$1:$J$65</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Keyword Cluster Sheet'!$A$1:$J$72</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -470,7 +470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J65"/>
+  <dimension ref="A1:J72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2968,28 +2968,32 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Good Medical Practice UKMLA</t>
+          <t>how to become a doctor in UK from India</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>how to practice medicine in UK; medical acronyms; medical students; UKMLA for international medical graduates; UKMLA mock exam practice</t>
+          <t>how to become a doctor in UK; UKMLA India; how to become a doctor in UK from Nigeria; how to become a doctor in UK from Pakistan; how to apply for UKMLA from India</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Professional Practice &amp; Safety</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr"/>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Good Medical Practice and the UKMLA: What the GMC Expects</t>
+          <t>How to Become a Doctor in the UK from India: The Complete UKMLA Route</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>/news#good-medical-practice-ukmla</t>
+          <t>/news#how-to-become-a-doctor-in-uk-from-india</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -3004,40 +3008,44 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>Growing (3 posts)</t>
+          <t>Established (6 posts)</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>30 June 2026</t>
+          <t>01 July 2026</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>patient safety UKMLA</t>
+          <t>UKMLA question bank</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>1. Patient Presentations; The official GMC MLA Content Map listing core patient presentations, conditions, and practical procedures</t>
+          <t>best question bank for UKMLA; best question bank for UKMLA UK students; UKMLA question bank free for students; UKMLA AKT question bank free; UKMLA mock</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Professional Practice &amp; Safety</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr"/>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Preparation</t>
+        </is>
+      </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting</t>
+          <t>UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>/news#patient-safety-ukmla-prescribing-errors</t>
+          <t>/news#ukmla-question-bank-and-mock-tests</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -3052,292 +3060,296 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>Growing (3 posts)</t>
+          <t>Established (6 posts)</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>30 June 2026</t>
+          <t>01 July 2026</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>safeguarding UKMLA</t>
+          <t>UKMLA for Nigerian doctors</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>ukmla guide; UKMLA pharmacology revision; about ukmla guide; contact ukmla guide; img guide</t>
+          <t>UKMLA for GP doctors in UK; UKMLA eligibility for Indian doctors; UKMLA fees for doctors 2026; UKMLA for Indian doctors; UKMLA for Pakistani doctors</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-for-nigerian-doctors</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>Established (6 posts)</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>01 July 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA for Pakistani doctors</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA for GP doctors in UK; UKMLA eligibility for Indian doctors; UKMLA fees for doctors 2026; UKMLA for Indian doctors; UKMLA for Nigerian doctors</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-for-pakistani-doctors</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>Established (6 posts)</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>01 July 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA vs NEET PG</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA exam for Indian medical graduates; UKMLA for international medical graduates; UKMLA for Caribbean medical graduates; international medical graduates; UKMLA for Indian doctors</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA vs PLAB</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-vs-neet-pg</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>Established (6 posts)</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>01 July 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA vs USMLE</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA vs USMLE which is easier; UKMLA exam; what is the UKMLA exam; The Exam; UKMLA vs USMLE cost and difficulty</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA vs PLAB</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-vs-usmle-comparison</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>Established (6 posts)</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>01 July 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>Good Medical Practice UKMLA</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>how to practice medicine in UK; medical acronyms; medical students; UKMLA for international medical graduates; UKMLA mock exam practice</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
           <t>Professional Practice &amp; Safety</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr"/>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>Safeguarding Adults and Children: A UKMLA Revision Guide</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>/news#safeguarding-ukmla-revision</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="inlineStr">
-        <is>
-          <t>Informational</t>
-        </is>
-      </c>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="I51" s="2" t="inlineStr">
+      <c r="D55" s="2" t="inlineStr"/>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>Good Medical Practice and the UKMLA: What the GMC Expects</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>/news#good-medical-practice-ukmla</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
         <is>
           <t>Growing (3 posts)</t>
         </is>
       </c>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>30 June 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="4" t="inlineStr">
-        <is>
-          <t>UKMLA for IMG</t>
-        </is>
-      </c>
-      <c r="B52" s="5" t="inlineStr">
-        <is>
-          <t>UKMLA for international medical graduates; UKMLA eligibility; UKMLA exam for UK medical students; UKMLA eligibility for international medical graduates</t>
-        </is>
-      </c>
-      <c r="C52" s="4" t="inlineStr">
-        <is>
-          <t>Registration &amp; Eligibility</t>
-        </is>
-      </c>
-      <c r="D52" s="4" t="inlineStr">
-        <is>
-          <t>Eligibility</t>
-        </is>
-      </c>
-      <c r="E52" s="4" t="inlineStr">
-        <is>
-          <t>Eligibility</t>
-        </is>
-      </c>
-      <c r="F52" s="4" t="inlineStr">
-        <is>
-          <t>/eligibility</t>
-        </is>
-      </c>
-      <c r="G52" s="4" t="inlineStr">
-        <is>
-          <t>Informational</t>
-        </is>
-      </c>
-      <c r="H52" s="4" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="I52" s="4" t="inlineStr">
-        <is>
-          <t>Established (6 posts)</t>
-        </is>
-      </c>
-      <c r="J52" s="4" t="inlineStr">
-        <is>
-          <t>N/A (static page)</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="4" t="inlineStr">
-        <is>
-          <t>Fees</t>
-        </is>
-      </c>
-      <c r="B53" s="5" t="inlineStr"/>
-      <c r="C53" s="4" t="inlineStr">
-        <is>
-          <t>Registration &amp; Eligibility</t>
-        </is>
-      </c>
-      <c r="D53" s="4" t="inlineStr">
-        <is>
-          <t>Fees</t>
-        </is>
-      </c>
-      <c r="E53" s="4" t="inlineStr">
-        <is>
-          <t>Fees</t>
-        </is>
-      </c>
-      <c r="F53" s="4" t="inlineStr">
-        <is>
-          <t>/fees</t>
-        </is>
-      </c>
-      <c r="G53" s="4" t="inlineStr">
-        <is>
-          <t>Commercial</t>
-        </is>
-      </c>
-      <c r="H53" s="4" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="I53" s="4" t="inlineStr">
-        <is>
-          <t>Established (6 posts)</t>
-        </is>
-      </c>
-      <c r="J53" s="4" t="inlineStr">
-        <is>
-          <t>N/A (static page)</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="4" t="inlineStr">
-        <is>
-          <t>UKMLA dates</t>
-        </is>
-      </c>
-      <c r="B54" s="5" t="inlineStr"/>
-      <c r="C54" s="4" t="inlineStr">
-        <is>
-          <t>Registration &amp; Eligibility</t>
-        </is>
-      </c>
-      <c r="D54" s="4" t="inlineStr">
-        <is>
-          <t>Key Dates</t>
-        </is>
-      </c>
-      <c r="E54" s="4" t="inlineStr">
-        <is>
-          <t>Key Dates</t>
-        </is>
-      </c>
-      <c r="F54" s="4" t="inlineStr">
-        <is>
-          <t>/key-dates</t>
-        </is>
-      </c>
-      <c r="G54" s="4" t="inlineStr">
-        <is>
-          <t>Transactional</t>
-        </is>
-      </c>
-      <c r="H54" s="4" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="I54" s="4" t="inlineStr">
-        <is>
-          <t>Established (6 posts)</t>
-        </is>
-      </c>
-      <c r="J54" s="4" t="inlineStr">
-        <is>
-          <t>N/A (static page)</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="4" t="inlineStr">
-        <is>
-          <t>UKMLA registration</t>
-        </is>
-      </c>
-      <c r="B55" s="5" t="inlineStr">
-        <is>
-          <t>UKMLA booking; English language requirement for UKMLA; UKMLA registration process GMC</t>
-        </is>
-      </c>
-      <c r="C55" s="4" t="inlineStr">
-        <is>
-          <t>Registration &amp; Eligibility</t>
-        </is>
-      </c>
-      <c r="D55" s="4" t="inlineStr">
-        <is>
-          <t>Registration Guide</t>
-        </is>
-      </c>
-      <c r="E55" s="4" t="inlineStr">
-        <is>
-          <t>Registration Guide</t>
-        </is>
-      </c>
-      <c r="F55" s="4" t="inlineStr">
-        <is>
-          <t>/registration-guide</t>
-        </is>
-      </c>
-      <c r="G55" s="4" t="inlineStr">
-        <is>
-          <t>Informational</t>
-        </is>
-      </c>
-      <c r="H55" s="4" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="I55" s="4" t="inlineStr">
-        <is>
-          <t>Established (6 posts)</t>
-        </is>
-      </c>
-      <c r="J55" s="4" t="inlineStr">
-        <is>
-          <t>N/A (static page)</t>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>30 June 2026</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>UKMLA disability access adjustments</t>
+          <t>patient safety UKMLA</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>ukmla guide; Reasonable Adjustments; reasonable adjustments gmc; about ukmla guide; contact ukmla guide</t>
+          <t>1. Patient Presentations; The official GMC MLA Content Map listing core patient presentations, conditions, and practical procedures</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Registration &amp; Eligibility</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>Appeals and Resits</t>
-        </is>
-      </c>
+          <t>Professional Practice &amp; Safety</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr"/>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide</t>
+          <t>Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>/news#disability-access-ukmla-guide</t>
+          <t>/news#patient-safety-ukmla-prescribing-errors</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -3352,7 +3364,7 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>Established (6 posts)</t>
+          <t>Growing (3 posts)</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -3364,392 +3376,384 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>safeguarding UKMLA</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>ukmla guide; UKMLA pharmacology revision; about ukmla guide; contact ukmla guide; img guide</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Professional Practice &amp; Safety</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr"/>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>Safeguarding Adults and Children: A UKMLA Revision Guide</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>/news#safeguarding-ukmla-revision</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>Growing (3 posts)</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>30 June 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>UKMLA for IMG</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="inlineStr">
+        <is>
+          <t>UKMLA for international medical graduates; UKMLA eligibility; UKMLA exam for UK medical students; UKMLA eligibility for international medical graduates</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>Registration &amp; Eligibility</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>/eligibility</t>
+        </is>
+      </c>
+      <c r="G58" s="4" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H58" s="4" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I58" s="4" t="inlineStr">
+        <is>
+          <t>Established (7 posts)</t>
+        </is>
+      </c>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>N/A (static page)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>Fees</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr"/>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>Registration &amp; Eligibility</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>Fees</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>Fees</t>
+        </is>
+      </c>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>/fees</t>
+        </is>
+      </c>
+      <c r="G59" s="4" t="inlineStr">
+        <is>
+          <t>Commercial</t>
+        </is>
+      </c>
+      <c r="H59" s="4" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I59" s="4" t="inlineStr">
+        <is>
+          <t>Established (7 posts)</t>
+        </is>
+      </c>
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t>N/A (static page)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>UKMLA dates</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="inlineStr"/>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>Registration &amp; Eligibility</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>Key Dates</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>Key Dates</t>
+        </is>
+      </c>
+      <c r="F60" s="4" t="inlineStr">
+        <is>
+          <t>/key-dates</t>
+        </is>
+      </c>
+      <c r="G60" s="4" t="inlineStr">
+        <is>
+          <t>Transactional</t>
+        </is>
+      </c>
+      <c r="H60" s="4" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I60" s="4" t="inlineStr">
+        <is>
+          <t>Established (7 posts)</t>
+        </is>
+      </c>
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t>N/A (static page)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>UKMLA registration</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>UKMLA booking; English language requirement for UKMLA; UKMLA registration process GMC</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>Registration &amp; Eligibility</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t>Registration Guide</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>Registration Guide</t>
+        </is>
+      </c>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t>/registration-guide</t>
+        </is>
+      </c>
+      <c r="G61" s="4" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H61" s="4" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I61" s="4" t="inlineStr">
+        <is>
+          <t>Established (7 posts)</t>
+        </is>
+      </c>
+      <c r="J61" s="4" t="inlineStr">
+        <is>
+          <t>N/A (static page)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA disability access adjustments</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>ukmla guide; Reasonable Adjustments; reasonable adjustments gmc; about ukmla guide; contact ukmla guide</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Registration &amp; Eligibility</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>Appeals and Resits</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>/news#disability-access-ukmla-guide</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>Established (7 posts)</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>30 June 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
           <t>how to register for PLAB 1</t>
         </is>
       </c>
-      <c r="B57" s="3" t="inlineStr">
+      <c r="B63" s="3" t="inlineStr">
         <is>
           <t>PLAB vs UKMLA; plab 1; plab 2; UKMLA vs PLAB; is UKMLA replacing PLAB</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
+      <c r="C63" s="2" t="inlineStr">
         <is>
           <t>Registration &amp; Eligibility</t>
         </is>
       </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Registration Guide</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>How to Register for PLAB 1: A Step-by-Step Guide for IMGs</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>/news#how-to-register-plab-1</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr">
-        <is>
-          <t>Informational</t>
-        </is>
-      </c>
-      <c r="H57" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="I57" s="2" t="inlineStr">
-        <is>
-          <t>Established (6 posts)</t>
-        </is>
-      </c>
-      <c r="J57" s="2" t="inlineStr">
-        <is>
-          <t>30 June 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>UKMLA eligibility</t>
-        </is>
-      </c>
-      <c r="B58" s="3" t="inlineStr">
-        <is>
-          <t>Eligibility; UKMLA exam; what is the UKMLA exam; The Exam; UKMLA Eligibility Pathways</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>Registration &amp; Eligibility</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>Eligibility</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>UKMLA Eligibility: Who Can Sit the Exam?</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>/news#ukmla-eligibility-who-can-sit</t>
-        </is>
-      </c>
-      <c r="G58" s="2" t="inlineStr">
-        <is>
-          <t>Informational</t>
-        </is>
-      </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="I58" s="2" t="inlineStr">
-        <is>
-          <t>Established (6 posts)</t>
-        </is>
-      </c>
-      <c r="J58" s="2" t="inlineStr">
-        <is>
-          <t>30 June 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>UKMLA fees</t>
-        </is>
-      </c>
-      <c r="B59" s="3" t="inlineStr">
-        <is>
-          <t>UKMLA fees for doctors 2026; UKMLA cost; UKMLA Fees and Costs 2026; UKMLA exam fees for IMG; UKMLA fees in Indian rupees</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>Registration &amp; Eligibility</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
-        <is>
-          <t>Fees</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="inlineStr">
-        <is>
-          <t>UKMLA Fees: The Complete 2026 Cost Breakdown</t>
-        </is>
-      </c>
-      <c r="F59" s="2" t="inlineStr">
-        <is>
-          <t>/news#ukmla-fees-explained</t>
-        </is>
-      </c>
-      <c r="G59" s="2" t="inlineStr">
-        <is>
-          <t>Informational</t>
-        </is>
-      </c>
-      <c r="H59" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="I59" s="2" t="inlineStr">
-        <is>
-          <t>Established (6 posts)</t>
-        </is>
-      </c>
-      <c r="J59" s="2" t="inlineStr">
-        <is>
-          <t>30 June 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>UKMLA key dates</t>
-        </is>
-      </c>
-      <c r="B60" s="3" t="inlineStr">
-        <is>
-          <t>UKMLA dates; Key Dates; Key Dates &amp; Timeline; UKMLA exam dates 2026; UKMLA exam dates and fees</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>Registration &amp; Eligibility</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t>Key Dates</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>UKMLA Key Dates and Sitting Schedule: What to Know</t>
-        </is>
-      </c>
-      <c r="F60" s="2" t="inlineStr">
-        <is>
-          <t>/news#ukmla-key-dates-sitting-schedule</t>
-        </is>
-      </c>
-      <c r="G60" s="2" t="inlineStr">
-        <is>
-          <t>Transactional</t>
-        </is>
-      </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="I60" s="2" t="inlineStr">
-        <is>
-          <t>Established (6 posts)</t>
-        </is>
-      </c>
-      <c r="J60" s="2" t="inlineStr">
-        <is>
-          <t>30 June 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>UKMLA resits</t>
-        </is>
-      </c>
-      <c r="B61" s="3" t="inlineStr">
-        <is>
-          <t>Appeals &amp; Resits; UKMLA Appeals, Resits &amp; Reasonable Adjustments; Appeals, Resits &amp; Reasonable Adjustments; Attempt Limits and Retake Rules; plab attempt limits</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>Registration &amp; Eligibility</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
-        <is>
-          <t>Appeals and Resits</t>
-        </is>
-      </c>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t>UKMLA Resits: Rules, Limits, and How to Bounce Back</t>
-        </is>
-      </c>
-      <c r="F61" s="2" t="inlineStr">
-        <is>
-          <t>/news#ukmla-resits-rules-limits</t>
-        </is>
-      </c>
-      <c r="G61" s="2" t="inlineStr">
-        <is>
-          <t>Informational</t>
-        </is>
-      </c>
-      <c r="H61" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="I61" s="2" t="inlineStr">
-        <is>
-          <t>Established (6 posts)</t>
-        </is>
-      </c>
-      <c r="J61" s="2" t="inlineStr">
-        <is>
-          <t>30 June 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="4" t="inlineStr">
-        <is>
-          <t>Appeals and Resits</t>
-        </is>
-      </c>
-      <c r="B62" s="5" t="inlineStr"/>
-      <c r="C62" s="4" t="inlineStr">
-        <is>
-          <t>Results &amp; Scoring</t>
-        </is>
-      </c>
-      <c r="D62" s="4" t="inlineStr">
-        <is>
-          <t>Appeals and Resits</t>
-        </is>
-      </c>
-      <c r="E62" s="4" t="inlineStr">
-        <is>
-          <t>Appeals and Resits</t>
-        </is>
-      </c>
-      <c r="F62" s="4" t="inlineStr">
-        <is>
-          <t>/appeals-and-resits</t>
-        </is>
-      </c>
-      <c r="G62" s="4" t="inlineStr">
-        <is>
-          <t>Informational</t>
-        </is>
-      </c>
-      <c r="H62" s="4" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="I62" s="4" t="inlineStr">
-        <is>
-          <t>Needs More Support (1 post)</t>
-        </is>
-      </c>
-      <c r="J62" s="4" t="inlineStr">
-        <is>
-          <t>N/A (static page)</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="4" t="inlineStr">
-        <is>
-          <t>UKMLA results</t>
-        </is>
-      </c>
-      <c r="B63" s="5" t="inlineStr">
-        <is>
-          <t>UKMLA pass mark; UKMLA pass rate for IMG; UKMLA results release date</t>
-        </is>
-      </c>
-      <c r="C63" s="4" t="inlineStr">
-        <is>
-          <t>Results &amp; Scoring</t>
-        </is>
-      </c>
-      <c r="D63" s="4" t="inlineStr">
-        <is>
-          <t>Results and Scoring</t>
-        </is>
-      </c>
-      <c r="E63" s="4" t="inlineStr">
-        <is>
-          <t>Results and Scoring</t>
-        </is>
-      </c>
-      <c r="F63" s="4" t="inlineStr">
-        <is>
-          <t>/results-and-scoring</t>
-        </is>
-      </c>
-      <c r="G63" s="4" t="inlineStr">
-        <is>
-          <t>Informational</t>
-        </is>
-      </c>
-      <c r="H63" s="4" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="I63" s="4" t="inlineStr">
-        <is>
-          <t>Needs More Support (1 post)</t>
-        </is>
-      </c>
-      <c r="J63" s="4" t="inlineStr">
-        <is>
-          <t>N/A (static page)</t>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>Established (7 posts)</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>30 June 2026</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>UKMLA results feedback</t>
+          <t>UKMLA eligibility</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>UKMLA results; Results &amp; Data; Results &amp; Scoring; UKMLA results timeline 2026; UKMLA results release date</t>
+          <t>Eligibility; UKMLA exam; what is the UKMLA exam; The Exam; UKMLA Eligibility Pathways</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Results &amp; Scoring</t>
+          <t>Registration &amp; Eligibility</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Results and Scoring</t>
+          <t>Eligibility</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>UKMLA Results: How to Interpret Your Feedback Report</t>
+          <t>UKMLA Eligibility: Who Can Sit the Exam?</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-results-feedback-report</t>
+          <t>/news#ukmla-eligibility-who-can-sit</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -3764,7 +3768,7 @@
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>Needs More Support (1 post)</t>
+          <t>Established (7 posts)</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -3776,53 +3780,413 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>UKMLA exam fees for IMG</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA exam; UKMLA fees; UKMLA for IMG; what is the UKMLA exam; The Exam</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Registration &amp; Eligibility</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>Fees</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-fees-for-img-2026</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>Established (7 posts)</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>01 July 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA fees</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA fees for doctors 2026; UKMLA cost; UKMLA Fees and Costs 2026; UKMLA exam fees for IMG; UKMLA fees in Indian rupees</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Registration &amp; Eligibility</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Fees</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA Fees: The Complete 2026 Cost Breakdown</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-fees-explained</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>Established (7 posts)</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>30 June 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA key dates</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA dates; Key Dates; Key Dates &amp; Timeline; UKMLA exam dates 2026; UKMLA exam dates and fees</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Registration &amp; Eligibility</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>Key Dates</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA Key Dates and Sitting Schedule: What to Know</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-key-dates-sitting-schedule</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>Transactional</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>Established (7 posts)</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>30 June 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA resits</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>Appeals &amp; Resits; UKMLA Appeals, Resits &amp; Reasonable Adjustments; Appeals, Resits &amp; Reasonable Adjustments; Attempt Limits and Retake Rules; plab attempt limits</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Registration &amp; Eligibility</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>Appeals and Resits</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA Resits: Rules, Limits, and How to Bounce Back</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-resits-rules-limits</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>Established (7 posts)</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>30 June 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>Appeals and Resits</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="inlineStr"/>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>Results &amp; Scoring</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="inlineStr">
+        <is>
+          <t>Appeals and Resits</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>Appeals and Resits</t>
+        </is>
+      </c>
+      <c r="F69" s="4" t="inlineStr">
+        <is>
+          <t>/appeals-and-resits</t>
+        </is>
+      </c>
+      <c r="G69" s="4" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H69" s="4" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I69" s="4" t="inlineStr">
+        <is>
+          <t>Needs More Support (1 post)</t>
+        </is>
+      </c>
+      <c r="J69" s="4" t="inlineStr">
+        <is>
+          <t>N/A (static page)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>UKMLA results</t>
+        </is>
+      </c>
+      <c r="B70" s="5" t="inlineStr">
+        <is>
+          <t>UKMLA pass mark; UKMLA pass rate for IMG; UKMLA results release date</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>Results &amp; Scoring</t>
+        </is>
+      </c>
+      <c r="D70" s="4" t="inlineStr">
+        <is>
+          <t>Results and Scoring</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>Results and Scoring</t>
+        </is>
+      </c>
+      <c r="F70" s="4" t="inlineStr">
+        <is>
+          <t>/results-and-scoring</t>
+        </is>
+      </c>
+      <c r="G70" s="4" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H70" s="4" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I70" s="4" t="inlineStr">
+        <is>
+          <t>Needs More Support (1 post)</t>
+        </is>
+      </c>
+      <c r="J70" s="4" t="inlineStr">
+        <is>
+          <t>N/A (static page)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA results feedback</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA results; Results &amp; Data; Results &amp; Scoring; UKMLA results timeline 2026; UKMLA results release date</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Results &amp; Scoring</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>Results and Scoring</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA Results: How to Interpret Your Feedback Report</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-results-feedback-report</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>Needs More Support (1 post)</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>30 June 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
           <t>Foundation Programme after UKMLA</t>
         </is>
       </c>
-      <c r="B65" s="3" t="inlineStr">
+      <c r="B72" s="3" t="inlineStr">
         <is>
           <t>UKMLA for academic foundation programme; UKMLA after MBBS; UKMLA after MBBS in India; UKMLA and foundation year application; UKMLA fail foundation year impact</t>
         </is>
       </c>
-      <c r="C65" s="2" t="inlineStr">
+      <c r="C72" s="2" t="inlineStr">
         <is>
           <t>Uncategorised</t>
         </is>
       </c>
-      <c r="D65" s="2" t="inlineStr"/>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="D72" s="2" t="inlineStr"/>
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>Understanding the Foundation Programme: What Awaits After the UKMLA</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>/news#foundation-programme-after-ukmla</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr">
-        <is>
-          <t>Informational</t>
-        </is>
-      </c>
-      <c r="H65" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="I65" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
         <is>
           <t>Needs More Support (1 post)</t>
         </is>
       </c>
-      <c r="J65" s="2" t="inlineStr">
+      <c r="J72" s="2" t="inlineStr">
         <is>
           <t>30 June 2026</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J65"/>
+  <autoFilter ref="A1:J72"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3833,7 +4197,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -3874,7 +4238,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>51</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6">
@@ -3894,7 +4258,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
@@ -3939,7 +4303,7 @@
       <c r="A13" s="9" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Core UKMLA Overview: 7 posts — Established (7 posts)</t>
+          <t>Registration &amp; Eligibility: 7 posts — Established (7 posts)</t>
         </is>
       </c>
     </row>
@@ -3947,7 +4311,7 @@
       <c r="A14" s="9" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Registration &amp; Eligibility: 6 posts — Established (6 posts)</t>
+          <t>Core UKMLA Overview: 7 posts — Established (7 posts)</t>
         </is>
       </c>
     </row>
@@ -3963,7 +4327,7 @@
       <c r="A16" s="9" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Exam Preparation: 5 posts — Established (5 posts)</t>
+          <t>IMG Country Routes &amp; Global Comparisons: 6 posts — Established (6 posts)</t>
         </is>
       </c>
     </row>
@@ -3971,7 +4335,7 @@
       <c r="A17" s="9" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Professional Practice &amp; Safety: 3 posts — Growing (3 posts)</t>
+          <t>Exam Preparation: 5 posts — Established (5 posts)</t>
         </is>
       </c>
     </row>
@@ -3979,7 +4343,7 @@
       <c r="A18" s="9" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Uncategorised: 1 posts — Needs More Support (1 post)</t>
+          <t>Professional Practice &amp; Safety: 3 posts — Growing (3 posts)</t>
         </is>
       </c>
     </row>
@@ -3987,31 +4351,39 @@
       <c r="A19" s="9" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
+          <t>Uncategorised: 1 posts — Needs More Support (1 post)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
           <t>Results &amp; Scoring: 1 posts — Needs More Support (1 post)</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="9" t="n"/>
-    </row>
     <row r="21">
-      <c r="A21" s="10" t="inlineStr">
+      <c r="A21" s="9" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
         <is>
           <t>Potential keyword cannibalization — same primary keyword used by multiple pages:</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="9" t="inlineStr"/>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>"ukmla akt": UKMLA AKT: Format, Question Types, and How to Prepare, AKT Exam Pattern</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="9" t="inlineStr"/>
       <c r="B23" t="inlineStr">
+        <is>
+          <t>"ukmla akt": UKMLA AKT: Format, Question Types, and How to Prepare, AKT Exam Pattern</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
         <is>
           <t>"ukmla cpsa": UKMLA CPSA: What the Clinical Exam Really Tests, CPSA Exam Pattern</t>
         </is>

--- a/UKMLA_Keyword_Cluster_Sheet.xlsx
+++ b/UKMLA_Keyword_Cluster_Sheet.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Keyword Cluster Sheet'!$A$1:$J$72</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Keyword Cluster Sheet'!$A$1:$J$95</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -470,7 +470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J72"/>
+  <dimension ref="A1:J95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -580,7 +580,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Established (22 posts)</t>
+          <t>Established (23 posts)</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -632,7 +632,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Established (22 posts)</t>
+          <t>Established (23 posts)</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Established (22 posts)</t>
+          <t>Established (23 posts)</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Established (22 posts)</t>
+          <t>Established (23 posts)</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Established (22 posts)</t>
+          <t>Established (23 posts)</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>Established (22 posts)</t>
+          <t>Established (23 posts)</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Established (22 posts)</t>
+          <t>Established (23 posts)</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Established (22 posts)</t>
+          <t>Established (23 posts)</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Established (22 posts)</t>
+          <t>Established (23 posts)</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>Established (22 posts)</t>
+          <t>Established (23 posts)</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1100,7 +1100,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Established (22 posts)</t>
+          <t>Established (23 posts)</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>Established (22 posts)</t>
+          <t>Established (23 posts)</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Established (22 posts)</t>
+          <t>Established (23 posts)</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>Established (22 posts)</t>
+          <t>Established (23 posts)</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Established (22 posts)</t>
+          <t>Established (23 posts)</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>Established (22 posts)</t>
+          <t>Established (23 posts)</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Established (22 posts)</t>
+          <t>Established (23 posts)</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -1420,12 +1420,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>radiology AKT UKMLA</t>
+          <t>UKMLA pharmacology revision</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>UKMLA AKT; ms akt; What is the UKMLA AKT?; AKT exam; AKT Details</t>
+          <t>ukmla guide; UKMLA revision notes tips; AKT Revision Strategy; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Safeguarding Adults and Children: A UKMLA Revision Guide</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Radiology and Imaging Interpretation in the AKT</t>
+          <t>Pharmacology and Prescribing Safety in the UKMLA: A Revision Guide</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>/news#radiology-imaging-akt-ukmla</t>
+          <t>/news#pharmacology-prescribing-safety-ukmla</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1460,24 +1460,24 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>Established (22 posts)</t>
+          <t>Established (23 posts)</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>30 June 2026</t>
+          <t>01 July 2026</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>respiratory medicine UKMLA</t>
+          <t>radiology AKT UKMLA</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>how to practice medicine in UK; practising medicine in UK requirements; how to practice medicine in UK from Philippines; Emergency Medicine and Acute Presentations in the UKMLA</t>
+          <t>UKMLA AKT; ms akt; What is the UKMLA AKT?; AKT exam; AKT Details</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1492,12 +1492,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Respiratory Medicine for the UKMLA: What to Focus On</t>
+          <t>Radiology and Imaging Interpretation in the AKT</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>/news#respiratory-medicine-ukmla-revision</t>
+          <t>/news#radiology-imaging-akt-ukmla</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1512,7 +1512,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>Established (22 posts)</t>
+          <t>Established (23 posts)</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -1524,10 +1524,14 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>rheumatology UKMLA</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr"/>
+          <t>respiratory medicine UKMLA</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>how to practice medicine in UK; practising medicine in UK requirements; how to practice medicine in UK from Philippines; Emergency Medicine and Acute Presentations in the UKMLA</t>
+        </is>
+      </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
           <t>Clinical Systems Revision</t>
@@ -1540,12 +1544,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity</t>
+          <t>Respiratory Medicine for the UKMLA: What to Focus On</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>/news#rheumatology-ukmla-revision</t>
+          <t>/news#respiratory-medicine-ukmla-revision</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -1560,7 +1564,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>Established (22 posts)</t>
+          <t>Established (23 posts)</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -1572,14 +1576,10 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>social determinants health UKMLA</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Mental Health Presentations in the UKMLA: What to Revise; Palliative Care and End-of-Life Decisions in the UKMLA</t>
-        </is>
-      </c>
+          <t>rheumatology UKMLA</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr"/>
       <c r="C22" s="2" t="inlineStr">
         <is>
           <t>Clinical Systems Revision</t>
@@ -1592,17 +1592,17 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Social Determinants of Health in the UKMLA: Person-Centred Care</t>
+          <t>Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>/news#social-determinants-health-ukmla</t>
+          <t>/news#rheumatology-ukmla-revision</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Transactional</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Established (22 posts)</t>
+          <t>Established (23 posts)</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -1624,114 +1624,118 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>social determinants health UKMLA</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Mental Health Presentations in the UKMLA: What to Revise; Palliative Care and End-of-Life Decisions in the UKMLA</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Clinical Systems Revision</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>MLA Content Map / Syllabus</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Social Determinants of Health in the UKMLA: Person-Centred Care</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>/news#social-determinants-health-ukmla</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>Transactional</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>Established (23 posts)</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>30 June 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
           <t>surgical presentations UKMLA</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>1. Patient Presentations; how to become a doctor in UK; Emergency Medicine and Acute Presentations in the UKMLA; Mental Health Presentations in the UKMLA: What to Revise; UK doctor salary 2026</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>Clinical Systems Revision</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>MLA Content Map / Syllabus</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>/news#surgical-presentations-ukmla-revision</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>Informational</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>Established (22 posts)</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>Established (23 posts)</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
         <is>
           <t>30 June 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>UKMLA syllabus</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>UKMLA content map; MLA content map; UKMLA syllabus pdf download; UKMLA content map 430 conditions</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>Core UKMLA Overview</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>MLA Content Map / Syllabus</t>
-        </is>
-      </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>MLA Content Map / Syllabus</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
-          <t>/syllabus</t>
-        </is>
-      </c>
-      <c r="G24" s="4" t="inlineStr">
-        <is>
-          <t>Informational</t>
-        </is>
-      </c>
-      <c r="H24" s="4" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="I24" s="4" t="inlineStr">
-        <is>
-          <t>Established (7 posts)</t>
-        </is>
-      </c>
-      <c r="J24" s="4" t="inlineStr">
-        <is>
-          <t>N/A (static page)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>Official Resources</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="inlineStr"/>
+          <t>UKMLA syllabus</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>UKMLA content map; MLA content map; UKMLA syllabus pdf download; UKMLA content map 430 conditions</t>
+        </is>
+      </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
           <t>Core UKMLA Overview</t>
@@ -1739,17 +1743,17 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>Official Resources</t>
+          <t>MLA Content Map / Syllabus</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>Official Resources</t>
+          <t>MLA Content Map / Syllabus</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>/official-resources</t>
+          <t>/syllabus</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr">
@@ -1776,14 +1780,10 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>PLAB vs UKMLA</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>difference between PLAB and UKMLA; is UKMLA replacing PLAB; UKMLA vs PLAB which is harder</t>
-        </is>
-      </c>
+          <t>Official Resources</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr"/>
       <c r="C26" s="4" t="inlineStr">
         <is>
           <t>Core UKMLA Overview</t>
@@ -1791,22 +1791,22 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>UKMLA vs PLAB</t>
+          <t>Official Resources</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>UKMLA vs PLAB</t>
+          <t>Official Resources</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>/ukmla-vs-plab</t>
+          <t>/official-resources</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
@@ -1828,112 +1828,112 @@
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
+          <t>PLAB vs UKMLA</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>difference between PLAB and UKMLA; is UKMLA replacing PLAB; UKMLA vs PLAB which is harder</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>Core UKMLA Overview</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>UKMLA vs PLAB</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>UKMLA vs PLAB</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>/ukmla-vs-plab</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>Commercial</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>Established (7 posts)</t>
+        </is>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>N/A (static page)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
           <t>What Is the UKMLA?</t>
         </is>
       </c>
-      <c r="B27" s="5" t="inlineStr"/>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="B28" s="5" t="inlineStr"/>
+      <c r="C28" s="4" t="inlineStr">
         <is>
           <t>Core UKMLA Overview</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="D28" s="4" t="inlineStr">
         <is>
           <t>What Is the UKMLA?</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
+      <c r="E28" s="4" t="inlineStr">
         <is>
           <t>What Is the UKMLA?</t>
         </is>
       </c>
-      <c r="F27" s="4" t="inlineStr">
+      <c r="F28" s="4" t="inlineStr">
         <is>
           <t>/what-is-ukmla</t>
         </is>
       </c>
-      <c r="G27" s="4" t="inlineStr">
-        <is>
-          <t>Informational</t>
-        </is>
-      </c>
-      <c r="H27" s="4" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="I27" s="4" t="inlineStr">
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I28" s="4" t="inlineStr">
         <is>
           <t>Established (7 posts)</t>
         </is>
       </c>
-      <c r="J27" s="4" t="inlineStr">
+      <c r="J28" s="4" t="inlineStr">
         <is>
           <t>N/A (static page)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>UK medical schools UKMLA implementation</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>medical acronyms; medical students; UKMLA for international medical graduates; UKMLA syllabus for medical students; UK visa for medical professionals</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>Core UKMLA Overview</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>What Is the UKMLA?</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>How UK Medical Schools Implement the UKMLA: An Overview</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>/news#uk-medical-schools-ukmla-implementation</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>Informational</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>Established (7 posts)</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>30 June 2026</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>MLA content map</t>
+          <t>UK medical schools UKMLA implementation</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>UKMLA content map; The MLA Content Map; The MLA Content Map Framework; UKMLA Syllabus &amp; Content Map; Syllabus &amp; Content Map</t>
+          <t>medical acronyms; medical students; UKMLA for international medical graduates; UKMLA syllabus for medical students; UK visa for medical professionals</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -1943,17 +1943,17 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>MLA Content Map / Syllabus</t>
+          <t>What Is the UKMLA?</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>MLA Content Map: The Blueprint Behind Every UKMLA Question</t>
+          <t>How UK Medical Schools Implement the UKMLA: An Overview</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>/news#mla-content-map-explained</t>
+          <t>/news#uk-medical-schools-ukmla-implementation</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -1980,12 +1980,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>PLAB 2 preparation</t>
+          <t>MLA content map</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>PLAB vs UKMLA; UKMLA preparation; plab 1; plab 2; UKMLA vs PLAB</t>
+          <t>UKMLA content map; The MLA Content Map; The MLA Content Map Framework; UKMLA Syllabus &amp; Content Map; Syllabus &amp; Content Map</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -1995,17 +1995,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>UKMLA vs PLAB</t>
+          <t>MLA Content Map / Syllabus</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>PLAB 2 Preparation: How to Excel in the Clinical Assessment</t>
+          <t>MLA Content Map: The Blueprint Behind Every UKMLA Question</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>/news#plab-2-preparation-guide</t>
+          <t>/news#mla-content-map-explained</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -2032,12 +2032,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>UKMLA preparation for IMGs</t>
+          <t>PLAB 2 preparation</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>UKMLA preparation; Preparation; Preparation Guide; UKMLA Preparation Guide; UKMLA OSCE preparation</t>
+          <t>PLAB vs UKMLA; UKMLA preparation; plab 1; plab 2; UKMLA vs PLAB</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2052,12 +2052,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>UKMLA Preparation for IMG Candidates: A Tailored Guide</t>
+          <t>PLAB 2 Preparation: How to Excel in the Clinical Assessment</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-preparation-for-imgs</t>
+          <t>/news#plab-2-preparation-guide</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -2084,12 +2084,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>UKMLA graduate entry</t>
+          <t>UKMLA preparation for IMGs</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>medical students; UKMLA syllabus for medical students; UKMLA exam for UK medical students; Eligibility for UK Medical Students; UKMLA pass rate medical students</t>
+          <t>UKMLA preparation; Preparation; Preparation Guide; UKMLA Preparation Guide; UKMLA OSCE preparation</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2099,17 +2099,17 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Eligibility</t>
+          <t>UKMLA vs PLAB</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>UKMLA for Graduate-Entry Medical Students: What Is Different?</t>
+          <t>UKMLA Preparation for IMG Candidates: A Tailored Guide</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-graduate-entry-medical-students</t>
+          <t>/news#ukmla-preparation-for-imgs</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>UKMLA vs PLAB</t>
+          <t>UKMLA graduate entry</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>PLAB vs UKMLA; plab 1; plab 2; difference between PLAB and UKMLA; is UKMLA replacing PLAB</t>
+          <t>medical students; UKMLA syllabus for medical students; UKMLA exam for UK medical students; Eligibility for UK Medical Students; UKMLA pass rate medical students</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2151,17 +2151,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>UKMLA vs PLAB</t>
+          <t>Eligibility</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>UKMLA vs PLAB: What Is the Difference?</t>
+          <t>UKMLA for Graduate-Entry Medical Students: What Is Different?</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-vs-plab-difference</t>
+          <t>/news#ukmla-graduate-entry-medical-students</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -2188,220 +2188,220 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>UKMLA vs PLAB</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>PLAB vs UKMLA; plab 1; plab 2; difference between PLAB and UKMLA; is UKMLA replacing PLAB</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Core UKMLA Overview</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA vs PLAB</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA vs PLAB: What Is the Difference?</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-vs-plab-difference</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>Established (7 posts)</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>30 June 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
           <t>what is UKMLA</t>
         </is>
       </c>
-      <c r="B34" s="3" t="inlineStr">
+      <c r="B35" s="3" t="inlineStr">
         <is>
           <t>ukmla guide; about ukmla guide; contact ukmla guide; img guide; Preparation Guide</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
         <is>
           <t>Core UKMLA Overview</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>What Is the UKMLA?</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>What Is the UKMLA? A Complete Beginner's Guide</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>/news#what-is-ukmla-complete-guide</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>Informational</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
         <is>
           <t>Established (7 posts)</t>
         </is>
       </c>
-      <c r="J34" s="2" t="inlineStr">
+      <c r="J35" s="2" t="inlineStr">
         <is>
           <t>30 June 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="6" t="inlineStr">
-        <is>
-          <t>UKMLA AKT</t>
-        </is>
-      </c>
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>AKT exam; UKMLA AKT pass mark; how many questions in UKMLA AKT; UKMLA AKT exam preparation tips; UKMLA AKT vs CPSA difference</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="inlineStr">
-        <is>
-          <t>Exam Format</t>
-        </is>
-      </c>
-      <c r="D35" s="4" t="inlineStr">
-        <is>
-          <t>AKT Exam Pattern</t>
-        </is>
-      </c>
-      <c r="E35" s="4" t="inlineStr">
-        <is>
-          <t>AKT Exam Pattern</t>
-        </is>
-      </c>
-      <c r="F35" s="4" t="inlineStr">
-        <is>
-          <t>/exam-pattern/akt</t>
-        </is>
-      </c>
-      <c r="G35" s="4" t="inlineStr">
-        <is>
-          <t>Informational</t>
-        </is>
-      </c>
-      <c r="H35" s="4" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="I35" s="4" t="inlineStr">
-        <is>
-          <t>Established (6 posts)</t>
-        </is>
-      </c>
-      <c r="J35" s="4" t="inlineStr">
-        <is>
-          <t>N/A (static page)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
+          <t>UKMLA AKT</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>AKT exam; UKMLA AKT pass mark; how many questions in UKMLA AKT; UKMLA AKT exam preparation tips; UKMLA AKT vs CPSA difference</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>Exam Format</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>AKT Exam Pattern</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>AKT Exam Pattern</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>/exam-pattern/akt</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I36" s="4" t="inlineStr">
+        <is>
+          <t>Established (6 posts)</t>
+        </is>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>N/A (static page)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
           <t>UKMLA CPSA</t>
         </is>
       </c>
-      <c r="B36" s="5" t="inlineStr">
+      <c r="B37" s="5" t="inlineStr">
         <is>
           <t>CPSA exam; UKMLA CPSA stations examples; UKMLA CPSA centre Manchester</t>
         </is>
       </c>
-      <c r="C36" s="4" t="inlineStr">
+      <c r="C37" s="4" t="inlineStr">
         <is>
           <t>Exam Format</t>
         </is>
       </c>
-      <c r="D36" s="4" t="inlineStr">
+      <c r="D37" s="4" t="inlineStr">
         <is>
           <t>CPSA Exam Pattern</t>
         </is>
       </c>
-      <c r="E36" s="4" t="inlineStr">
+      <c r="E37" s="4" t="inlineStr">
         <is>
           <t>CPSA Exam Pattern</t>
         </is>
       </c>
-      <c r="F36" s="4" t="inlineStr">
+      <c r="F37" s="4" t="inlineStr">
         <is>
           <t>/exam-pattern/cpsa</t>
         </is>
       </c>
-      <c r="G36" s="4" t="inlineStr">
-        <is>
-          <t>Informational</t>
-        </is>
-      </c>
-      <c r="H36" s="4" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="I36" s="4" t="inlineStr">
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I37" s="4" t="inlineStr">
         <is>
           <t>Established (6 posts)</t>
         </is>
       </c>
-      <c r="J36" s="4" t="inlineStr">
+      <c r="J37" s="4" t="inlineStr">
         <is>
           <t>N/A (static page)</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>CPSA clinical examination stations</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>UKMLA CPSA; What is the UKMLA CPSA?; UKMLA CPSA stations list; UKMLA clinical examination tips; UKMLA CPSA stations examples</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>Exam Format</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>CPSA Exam Pattern</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>Clinical Examination Stations in the CPSA: A Practical Guide</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>/news#clinical-examination-cpsa-guide</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>Informational</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>Established (6 posts)</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>30 June 2026</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>how to read AKT stem</t>
+          <t>CPSA clinical examination stations</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>UKMLA AKT; ms akt; What is the UKMLA AKT?; AKT exam; AKT Details</t>
+          <t>UKMLA CPSA; What is the UKMLA CPSA?; UKMLA CPSA stations list; UKMLA clinical examination tips; UKMLA CPSA stations examples</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2411,17 +2411,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern</t>
+          <t>CPSA Exam Pattern</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>How to Read an AKT Stem: Avoiding Common Traps</t>
+          <t>Clinical Examination Stations in the CPSA: A Practical Guide</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>/news#how-to-read-akt-stem</t>
+          <t>/news#clinical-examination-cpsa-guide</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -2448,84 +2448,84 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>how to read AKT stem</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA AKT; ms akt; What is the UKMLA AKT?; AKT exam; AKT Details</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Exam Format</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>AKT Exam Pattern</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>How to Read an AKT Stem: Avoiding Common Traps</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>/news#how-to-read-akt-stem</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>Established (6 posts)</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>30 June 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
           <t>psychiatry communication CPSA</t>
         </is>
       </c>
-      <c r="B39" s="3" t="inlineStr">
+      <c r="B40" s="3" t="inlineStr">
         <is>
           <t>UKMLA CPSA; What is the UKMLA CPSA?; UKMLA CPSA stations list; CPSA exam; UKMLA CPSA stations examples</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t>Exam Format</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>CPSA Exam Pattern</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>Psychiatry Communication Stations: Handling Difficult Conversations</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>/news#psychiatry-communication-cpsa-stations</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>Informational</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>Established (6 posts)</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>30 June 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="6" t="inlineStr">
-        <is>
-          <t>UKMLA AKT</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>ms akt; What is the UKMLA AKT?; AKT exam; how to prepare for UKMLA; AKT Details</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>Exam Format</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>AKT Exam Pattern</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>UKMLA AKT: Format, Question Types, and How to Prepare</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>/news#ukmla-akt-format-preparation</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -2552,220 +2552,220 @@
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
+          <t>UKMLA AKT</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>ms akt; What is the UKMLA AKT?; AKT exam; how to prepare for UKMLA; AKT Details</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Exam Format</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>AKT Exam Pattern</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA AKT: Format, Question Types, and How to Prepare</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-akt-format-preparation</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>Established (6 posts)</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>30 June 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
           <t>UKMLA CPSA</t>
         </is>
       </c>
-      <c r="B41" s="3" t="inlineStr">
+      <c r="B42" s="3" t="inlineStr">
         <is>
           <t>What is the UKMLA CPSA?; CPSA exam; UKMLA exam; what is the UKMLA exam; Clinical Skills (CPSA)</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
         <is>
           <t>Exam Format</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>CPSA Exam Pattern</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>UKMLA CPSA: What the Clinical Exam Really Tests</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>/news#ukmla-cpsa-what-it-tests</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>Informational</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
         <is>
           <t>Established (6 posts)</t>
         </is>
       </c>
-      <c r="J41" s="2" t="inlineStr">
+      <c r="J42" s="2" t="inlineStr">
         <is>
           <t>30 June 2026</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>Angoff standard setting UKMLA</t>
         </is>
       </c>
-      <c r="B42" s="3" t="inlineStr">
+      <c r="B43" s="3" t="inlineStr">
         <is>
           <t>AKT Standard Setting: The Angoff Method; UKMLA AKT standard setting explained; UKMLA Results, Scoring &amp; Standard Setting; angoff definition; angoff method</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
         <is>
           <t>Exam Format</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Results and Scoring</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>What Is an Angoff Standard Setting and Why Does It Matter?</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>/news#angoff-standard-setting-explained</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>Informational</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
         <is>
           <t>Established (6 posts)</t>
         </is>
       </c>
-      <c r="J42" s="2" t="inlineStr">
+      <c r="J43" s="2" t="inlineStr">
         <is>
           <t>30 June 2026</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="4" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
         <is>
           <t>UKMLA preparation</t>
         </is>
       </c>
-      <c r="B43" s="5" t="inlineStr">
+      <c r="B44" s="5" t="inlineStr">
         <is>
           <t>how to prepare for UKMLA; UKMLA study plan; how long to study for UKMLA; UKMLA preparation 6 weeks</t>
         </is>
       </c>
-      <c r="C43" s="4" t="inlineStr">
+      <c r="C44" s="4" t="inlineStr">
         <is>
           <t>Exam Preparation</t>
         </is>
       </c>
-      <c r="D43" s="4" t="inlineStr">
+      <c r="D44" s="4" t="inlineStr">
         <is>
           <t>Preparation</t>
         </is>
       </c>
-      <c r="E43" s="4" t="inlineStr">
+      <c r="E44" s="4" t="inlineStr">
         <is>
           <t>Preparation</t>
         </is>
       </c>
-      <c r="F43" s="4" t="inlineStr">
+      <c r="F44" s="4" t="inlineStr">
         <is>
           <t>/preparation</t>
         </is>
       </c>
-      <c r="G43" s="4" t="inlineStr">
+      <c r="G44" s="4" t="inlineStr">
         <is>
           <t>Commercial</t>
         </is>
       </c>
-      <c r="H43" s="4" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="I43" s="4" t="inlineStr">
-        <is>
-          <t>Established (5 posts)</t>
-        </is>
-      </c>
-      <c r="J43" s="4" t="inlineStr">
+      <c r="H44" s="4" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I44" s="4" t="inlineStr">
+        <is>
+          <t>Established (6 posts)</t>
+        </is>
+      </c>
+      <c r="J44" s="4" t="inlineStr">
         <is>
           <t>N/A (static page)</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>UKMLA group study solo</t>
-        </is>
-      </c>
-      <c r="B44" s="3" t="inlineStr">
-        <is>
-          <t>UKMLA group study vs solo study; how long to study for UKMLA; UKMLA study plan; study plan; UKMLA study plan 12 weeks</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>Exam Preparation</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>Preparation</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>Group Study vs Solo Study for the UKMLA: What Works Best?</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>/news#group-study-vs-solo-ukmla</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>Informational</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>Established (5 posts)</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>30 June 2026</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>UKMLA revision notes</t>
+          <t>UKMLA group study solo</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>UKMLA revision notes tips; UKMLA pharmacology revision; AKT Revision Strategy; CPSA / OSCE Revision Strategy; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide</t>
+          <t>UKMLA group study vs solo study; how long to study for UKMLA; UKMLA study plan; study plan; UKMLA study plan 12 weeks</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -2780,12 +2780,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>How to Write UKMLA Revision Notes That Actually Work</t>
+          <t>Group Study vs Solo Study for the UKMLA: What Works Best?</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-revision-notes-strategy</t>
+          <t>/news#group-study-vs-solo-ukmla</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>Established (5 posts)</t>
+          <t>Established (6 posts)</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>UKMLA mock exams</t>
+          <t>UKMLA revision notes</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>UKMLA mock; UKMLA preparation; Preparation; UKMLA mock exam practice; free UKMLA mock test</t>
+          <t>UKMLA revision notes tips; UKMLA pharmacology revision; AKT Revision Strategy; CPSA / OSCE Revision Strategy; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -2832,12 +2832,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>The Role of Mock Exams in UKMLA Preparation</t>
+          <t>How to Write UKMLA Revision Notes That Actually Work</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>/news#mock-exams-ukmla-preparation</t>
+          <t>/news#ukmla-revision-notes-strategy</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -2852,7 +2852,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>Established (5 posts)</t>
+          <t>Established (6 posts)</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>UKMLA AKT preparation countdown</t>
+          <t>UKMLA exam anxiety tips</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>UKMLA AKT; UKMLA preparation; ms akt; What is the UKMLA AKT?; Preparation</t>
+          <t>UKMLA exam; what is the UKMLA exam; The Exam; UKMLA exam in Dubai; AKT exam</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -2884,12 +2884,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Three Months to the UKMLA AKT: A Final Preparation Countdown</t>
+          <t>Managing UKMLA Exam Anxiety: Practical Strategies for Candidates</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>/news#three-months-ukmla-akt-countdown</t>
+          <t>/news#managing-ukmla-exam-anxiety</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -2904,24 +2904,24 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>Established (5 posts)</t>
+          <t>Established (6 posts)</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>30 June 2026</t>
+          <t>01 July 2026</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>time management UKMLA AKT</t>
+          <t>UKMLA mock exams</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>UKMLA AKT; ms akt; What is the UKMLA AKT?; AKT exam; AKT Details</t>
+          <t>UKMLA mock; UKMLA preparation; Preparation; UKMLA mock exam practice; free UKMLA mock test</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Time Management in the UKMLA AKT: Strategies That Work</t>
+          <t>The Role of Mock Exams in UKMLA Preparation</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>/news#time-management-akt-ukmla</t>
+          <t>/news#mock-exams-ukmla-preparation</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -2956,7 +2956,7 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>Established (5 posts)</t>
+          <t>Established (6 posts)</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -2968,32 +2968,32 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>how to become a doctor in UK from India</t>
+          <t>UKMLA AKT preparation countdown</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>how to become a doctor in UK; UKMLA India; how to become a doctor in UK from Nigeria; how to become a doctor in UK from Pakistan; how to apply for UKMLA from India</t>
+          <t>UKMLA AKT; UKMLA preparation; ms akt; What is the UKMLA AKT?; Preparation</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
+          <t>Exam Preparation</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Eligibility</t>
+          <t>Preparation</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>How to Become a Doctor in the UK from India: The Complete UKMLA Route</t>
+          <t>Three Months to the UKMLA AKT: A Final Preparation Countdown</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>/news#how-to-become-a-doctor-in-uk-from-india</t>
+          <t>/news#three-months-ukmla-akt-countdown</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -3013,24 +3013,24 @@
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>01 July 2026</t>
+          <t>30 June 2026</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>UKMLA question bank</t>
+          <t>time management UKMLA AKT</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>best question bank for UKMLA; best question bank for UKMLA UK students; UKMLA question bank free for students; UKMLA AKT question bank free; UKMLA mock</t>
+          <t>UKMLA AKT; ms akt; What is the UKMLA AKT?; AKT exam; AKT Details</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
+          <t>Exam Preparation</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources</t>
+          <t>Time Management in the UKMLA AKT: Strategies That Work</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-question-bank-and-mock-tests</t>
+          <t>/news#time-management-akt-ukmla</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -3065,19 +3065,19 @@
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>01 July 2026</t>
+          <t>30 June 2026</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>UKMLA for Nigerian doctors</t>
+          <t>English language requirement for UKMLA India</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>UKMLA for GP doctors in UK; UKMLA eligibility for Indian doctors; UKMLA fees for doctors 2026; UKMLA for Indian doctors; UKMLA for Pakistani doctors</t>
+          <t>UKMLA India; English language requirement for UKMLA; English requirement for UKMLA India (IELTS/OET); UKMLA OET or IELTS requirement; Step 2: English Language Proficiency</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC</t>
+          <t>English Language Requirements for the UKMLA: IELTS and OET Scores Explained</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-for-nigerian-doctors</t>
+          <t>/news#english-language-requirement-for-ukmla-india</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>Established (6 posts)</t>
+          <t>Established (25 posts)</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -3124,12 +3124,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>UKMLA for Pakistani doctors</t>
+          <t>GMC registration requirements for international doctors</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>UKMLA for GP doctors in UK; UKMLA eligibility for Indian doctors; UKMLA fees for doctors 2026; UKMLA for Indian doctors; UKMLA for Nigerian doctors</t>
+          <t>UKMLA for GP doctors in UK; UKMLA registration; GMC registration process for doctors; UKMLA registration process GMC; GMC registration requirements IMG</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -3139,17 +3139,17 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Eligibility</t>
+          <t>Registration Guide</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK</t>
+          <t>GMC Registration Requirements for International Doctors: The Complete Process</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-for-pakistani-doctors</t>
+          <t>/news#gmc-registration-requirements-for-international-doctors</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>Established (6 posts)</t>
+          <t>Established (25 posts)</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>UKMLA vs NEET PG</t>
+          <t>GMC registration from India</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>UKMLA exam for Indian medical graduates; UKMLA for international medical graduates; UKMLA for Caribbean medical graduates; international medical graduates; UKMLA for Indian doctors</t>
+          <t>UKMLA India; UKMLA registration; gmc registration guide; how to apply for UKMLA from India; UKMLA GMC registration for graduates</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -3191,17 +3191,17 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>UKMLA vs PLAB</t>
+          <t>Registration Guide</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?</t>
+          <t>GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-vs-neet-pg</t>
+          <t>/news#gmc-registration-and-epic-verification-india</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>Established (6 posts)</t>
+          <t>Established (25 posts)</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -3228,12 +3228,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>UKMLA vs USMLE</t>
+          <t>how to become a doctor in UK from India</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>UKMLA vs USMLE which is easier; UKMLA exam; what is the UKMLA exam; The Exam; UKMLA vs USMLE cost and difficulty</t>
+          <t>how to become a doctor in UK; UKMLA India; how to become a doctor in UK from Nigeria; how to become a doctor in UK from Pakistan; how to apply for UKMLA from India</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -3243,17 +3243,17 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>UKMLA vs PLAB</t>
+          <t>Eligibility</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
+          <t>How to Become a Doctor in the UK from India: The Complete UKMLA Route</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-vs-usmle-comparison</t>
+          <t>/news#how-to-become-a-doctor-in-uk-from-india</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -3268,7 +3268,7 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>Established (6 posts)</t>
+          <t>Established (25 posts)</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -3280,28 +3280,32 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>Good Medical Practice UKMLA</t>
+          <t>how to become a doctor in UK</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>how to practice medicine in UK; medical acronyms; medical students; UKMLA for international medical graduates; UKMLA mock exam practice</t>
+          <t>how to become a doctor in UK from India; how to become a doctor in UK from Nigeria; how to become a doctor in UK from Pakistan; UKMLA registration; gmc registration guide</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Professional Practice &amp; Safety</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr"/>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Good Medical Practice and the UKMLA: What the GMC Expects</t>
+          <t>How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>/news#good-medical-practice-ukmla</t>
+          <t>/news#how-to-become-a-doctor-in-the-uk-gmc-registration-guide</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -3316,40 +3320,44 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>Growing (3 posts)</t>
+          <t>Established (25 posts)</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>30 June 2026</t>
+          <t>01 July 2026</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>patient safety UKMLA</t>
+          <t>is Indian MBBS valid in UK</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>1. Patient Presentations; The official GMC MLA Content Map listing core patient presentations, conditions, and practical procedures</t>
+          <t>MBBS in UK for Indian students; UKMLA after MBBS; UKMLA for Indian doctors; UKMLA after MBBS in India; UKMLA eligibility for Indian doctors</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Professional Practice &amp; Safety</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr"/>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting</t>
+          <t>Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>/news#patient-safety-ukmla-prescribing-errors</t>
+          <t>/news#is-indian-mbbs-valid-in-uk</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -3364,40 +3372,44 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>Growing (3 posts)</t>
+          <t>Established (25 posts)</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>30 June 2026</t>
+          <t>01 July 2026</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>safeguarding UKMLA</t>
+          <t>MBBS in UK for Indian students</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>ukmla guide; UKMLA pharmacology revision; about ukmla guide; contact ukmla guide; img guide</t>
+          <t>is Indian MBBS valid in UK; UKMLA after MBBS; UKMLA for Indian doctors; UKMLA for IMG; medical students</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Professional Practice &amp; Safety</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr"/>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Safeguarding Adults and Children: A UKMLA Revision Guide</t>
+          <t>MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>/news#safeguarding-ukmla-revision</t>
+          <t>/news#mbbs-in-uk-for-indian-students</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -3412,244 +3424,252 @@
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>Growing (3 posts)</t>
+          <t>Established (25 posts)</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>30 June 2026</t>
+          <t>01 July 2026</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="4" t="inlineStr">
-        <is>
-          <t>UKMLA for IMG</t>
-        </is>
-      </c>
-      <c r="B58" s="5" t="inlineStr">
-        <is>
-          <t>UKMLA for international medical graduates; UKMLA eligibility; UKMLA exam for UK medical students; UKMLA eligibility for international medical graduates</t>
-        </is>
-      </c>
-      <c r="C58" s="4" t="inlineStr">
-        <is>
-          <t>Registration &amp; Eligibility</t>
-        </is>
-      </c>
-      <c r="D58" s="4" t="inlineStr">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>UK doctor salary for Indian doctors</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA for Indian doctors; salary of doctor in UK for Indian; UKMLA for GP doctors in UK; UK doctor salary 2026; UKMLA eligibility for Indian doctors</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Eligibility</t>
         </is>
       </c>
-      <c r="E58" s="4" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>/news#uk-doctor-salary-guide-for-indian-doctors</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>Established (25 posts)</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>01 July 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>UK visa for international doctors</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA for GP doctors in UK; how to get UK visa for doctors; UK medical registration for international doctors; UKMLA for Indian doctors; UKMLA for Nigerian doctors</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Eligibility</t>
         </is>
       </c>
-      <c r="F58" s="4" t="inlineStr">
-        <is>
-          <t>/eligibility</t>
-        </is>
-      </c>
-      <c r="G58" s="4" t="inlineStr">
-        <is>
-          <t>Informational</t>
-        </is>
-      </c>
-      <c r="H58" s="4" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="I58" s="4" t="inlineStr">
-        <is>
-          <t>Established (7 posts)</t>
-        </is>
-      </c>
-      <c r="J58" s="4" t="inlineStr">
-        <is>
-          <t>N/A (static page)</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="4" t="inlineStr">
-        <is>
-          <t>Fees</t>
-        </is>
-      </c>
-      <c r="B59" s="5" t="inlineStr"/>
-      <c r="C59" s="4" t="inlineStr">
-        <is>
-          <t>Registration &amp; Eligibility</t>
-        </is>
-      </c>
-      <c r="D59" s="4" t="inlineStr">
-        <is>
-          <t>Fees</t>
-        </is>
-      </c>
-      <c r="E59" s="4" t="inlineStr">
-        <is>
-          <t>Fees</t>
-        </is>
-      </c>
-      <c r="F59" s="4" t="inlineStr">
-        <is>
-          <t>/fees</t>
-        </is>
-      </c>
-      <c r="G59" s="4" t="inlineStr">
-        <is>
-          <t>Commercial</t>
-        </is>
-      </c>
-      <c r="H59" s="4" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="I59" s="4" t="inlineStr">
-        <is>
-          <t>Established (7 posts)</t>
-        </is>
-      </c>
-      <c r="J59" s="4" t="inlineStr">
-        <is>
-          <t>N/A (static page)</t>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>UK Visa Guide for International Doctors: Health and Care Worker Visa Explained</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>/news#uk-visa-guide-for-international-doctors</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>Established (25 posts)</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>01 July 2026</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="4" t="inlineStr">
-        <is>
-          <t>UKMLA dates</t>
-        </is>
-      </c>
-      <c r="B60" s="5" t="inlineStr"/>
-      <c r="C60" s="4" t="inlineStr">
-        <is>
-          <t>Registration &amp; Eligibility</t>
-        </is>
-      </c>
-      <c r="D60" s="4" t="inlineStr">
-        <is>
-          <t>Key Dates</t>
-        </is>
-      </c>
-      <c r="E60" s="4" t="inlineStr">
-        <is>
-          <t>Key Dates</t>
-        </is>
-      </c>
-      <c r="F60" s="4" t="inlineStr">
-        <is>
-          <t>/key-dates</t>
-        </is>
-      </c>
-      <c r="G60" s="4" t="inlineStr">
-        <is>
-          <t>Transactional</t>
-        </is>
-      </c>
-      <c r="H60" s="4" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="I60" s="4" t="inlineStr">
-        <is>
-          <t>Established (7 posts)</t>
-        </is>
-      </c>
-      <c r="J60" s="4" t="inlineStr">
-        <is>
-          <t>N/A (static page)</t>
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA AKT test centres</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA AKT; ms akt; What is the UKMLA AKT?; UKMLA AKT test centres in India; UKMLA AKT test centres in Pakistan</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>AKT Exam Pattern</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-akt-test-centres-guide</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>Established (25 posts)</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>01 July 2026</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="4" t="inlineStr">
-        <is>
-          <t>UKMLA registration</t>
-        </is>
-      </c>
-      <c r="B61" s="5" t="inlineStr">
-        <is>
-          <t>UKMLA booking; English language requirement for UKMLA; UKMLA registration process GMC</t>
-        </is>
-      </c>
-      <c r="C61" s="4" t="inlineStr">
-        <is>
-          <t>Registration &amp; Eligibility</t>
-        </is>
-      </c>
-      <c r="D61" s="4" t="inlineStr">
-        <is>
-          <t>Registration Guide</t>
-        </is>
-      </c>
-      <c r="E61" s="4" t="inlineStr">
-        <is>
-          <t>Registration Guide</t>
-        </is>
-      </c>
-      <c r="F61" s="4" t="inlineStr">
-        <is>
-          <t>/registration-guide</t>
-        </is>
-      </c>
-      <c r="G61" s="4" t="inlineStr">
-        <is>
-          <t>Informational</t>
-        </is>
-      </c>
-      <c r="H61" s="4" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="I61" s="4" t="inlineStr">
-        <is>
-          <t>Established (7 posts)</t>
-        </is>
-      </c>
-      <c r="J61" s="4" t="inlineStr">
-        <is>
-          <t>N/A (static page)</t>
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA question bank</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>best question bank for UKMLA; best question bank for UKMLA UK students; UKMLA question bank free for students; UKMLA AKT question bank free; UKMLA mock</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>Preparation</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-question-bank-and-mock-tests</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>Established (25 posts)</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>01 July 2026</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>UKMLA disability access adjustments</t>
+          <t>UKMLA for Bangladeshi doctors</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>ukmla guide; Reasonable Adjustments; reasonable adjustments gmc; about ukmla guide; contact ukmla guide</t>
+          <t>UKMLA for GP doctors in UK; GMC registration process for doctors; UKMLA eligibility for Indian doctors; UKMLA fees for doctors 2026; UKMLA for Indian doctors</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Registration &amp; Eligibility</t>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Appeals and Resits</t>
+          <t>Eligibility</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide</t>
+          <t>UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>/news#disability-access-ukmla-guide</t>
+          <t>/news#ukmla-for-bangladeshi-doctors</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -3664,44 +3684,44 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>Established (7 posts)</t>
+          <t>Established (25 posts)</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>30 June 2026</t>
+          <t>01 July 2026</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>how to register for PLAB 1</t>
+          <t>UKMLA for Egyptian doctors</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>PLAB vs UKMLA; plab 1; plab 2; UKMLA vs PLAB; is UKMLA replacing PLAB</t>
+          <t>UKMLA for GP doctors in UK; GMC registration process for doctors; UKMLA eligibility for Indian doctors; UKMLA fees for doctors 2026; UKMLA for Indian doctors</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Registration &amp; Eligibility</t>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Registration Guide</t>
+          <t>Eligibility</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>How to Register for PLAB 1: A Step-by-Step Guide for IMGs</t>
+          <t>UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>/news#how-to-register-plab-1</t>
+          <t>/news#ukmla-for-egyptian-doctors</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -3716,29 +3736,29 @@
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>Established (7 posts)</t>
+          <t>Established (25 posts)</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>30 June 2026</t>
+          <t>01 July 2026</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>UKMLA eligibility</t>
+          <t>UKMLA for Filipino doctors</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>Eligibility; UKMLA exam; what is the UKMLA exam; The Exam; UKMLA Eligibility Pathways</t>
+          <t>UKMLA for GP doctors in UK; GMC registration process for doctors; UKMLA eligibility for Indian doctors; UKMLA fees for doctors 2026; UKMLA for Indian doctors</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Registration &amp; Eligibility</t>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -3748,12 +3768,12 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>UKMLA Eligibility: Who Can Sit the Exam?</t>
+          <t>UKMLA for Filipino Doctors: Eligibility, Fees and the Route to GMC Registration</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-eligibility-who-can-sit</t>
+          <t>/news#ukmla-for-filipino-doctors</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -3768,44 +3788,44 @@
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>Established (7 posts)</t>
+          <t>Established (25 posts)</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>30 June 2026</t>
+          <t>01 July 2026</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>UKMLA exam fees for IMG</t>
+          <t>UKMLA for Gulf and Saudi doctors</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>UKMLA exam; UKMLA fees; UKMLA for IMG; what is the UKMLA exam; The Exam</t>
+          <t>UKMLA for GP doctors in UK; UKMLA for Saudi / Gulf doctors; UKMLA for Saudi doctors; GMC registration process for doctors; UKMLA eligibility for Indian doctors</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Registration &amp; Eligibility</t>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Fees</t>
+          <t>Eligibility</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide</t>
+          <t>UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-fees-for-img-2026</t>
+          <t>/news#ukmla-for-gulf-doctors</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -3820,7 +3840,7 @@
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>Established (7 posts)</t>
+          <t>Established (25 posts)</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -3832,32 +3852,32 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>UKMLA fees</t>
+          <t>UKMLA for international medical graduates</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>UKMLA fees for doctors 2026; UKMLA cost; UKMLA Fees and Costs 2026; UKMLA exam fees for IMG; UKMLA fees in Indian rupees</t>
+          <t>international medical graduates; UKMLA eligibility for international medical graduates; UKMLA for Caribbean medical graduates; Eligibility for International Medical Graduates (IMGs); For International Medical Graduates (PLAB Route)</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Registration &amp; Eligibility</t>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Fees</t>
+          <t>Eligibility</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>UKMLA Fees: The Complete 2026 Cost Breakdown</t>
+          <t>UKMLA for International Medical Graduates: Country-by-Country Quick Reference</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-fees-explained</t>
+          <t>/news#ukmla-for-international-medical-graduates-country-routes</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -3872,49 +3892,49 @@
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>Established (7 posts)</t>
+          <t>Established (25 posts)</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>30 June 2026</t>
+          <t>01 July 2026</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>UKMLA key dates</t>
+          <t>UKMLA for Nigerian doctors</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>UKMLA dates; Key Dates; Key Dates &amp; Timeline; UKMLA exam dates 2026; UKMLA exam dates and fees</t>
+          <t>UKMLA for GP doctors in UK; UKMLA eligibility for Indian doctors; UKMLA fees for doctors 2026; UKMLA for Indian doctors; UKMLA for Pakistani doctors</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Registration &amp; Eligibility</t>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Key Dates</t>
+          <t>Eligibility</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>UKMLA Key Dates and Sitting Schedule: What to Know</t>
+          <t>UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-key-dates-sitting-schedule</t>
+          <t>/news#ukmla-for-nigerian-doctors</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>Transactional</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -3924,44 +3944,44 @@
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>Established (7 posts)</t>
+          <t>Established (25 posts)</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>30 June 2026</t>
+          <t>01 July 2026</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>UKMLA resits</t>
+          <t>UKMLA for Pakistani doctors</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>Appeals &amp; Resits; UKMLA Appeals, Resits &amp; Reasonable Adjustments; Appeals, Resits &amp; Reasonable Adjustments; Attempt Limits and Retake Rules; plab attempt limits</t>
+          <t>UKMLA for GP doctors in UK; UKMLA eligibility for Indian doctors; UKMLA fees for doctors 2026; UKMLA for Indian doctors; UKMLA for Nigerian doctors</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Registration &amp; Eligibility</t>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Appeals and Resits</t>
+          <t>Eligibility</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>UKMLA Resits: Rules, Limits, and How to Bounce Back</t>
+          <t>UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-resits-rules-limits</t>
+          <t>/news#ukmla-for-pakistani-doctors</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -3976,144 +3996,148 @@
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>Established (7 posts)</t>
+          <t>Established (25 posts)</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>30 June 2026</t>
+          <t>01 July 2026</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="4" t="inlineStr">
-        <is>
-          <t>Appeals and Resits</t>
-        </is>
-      </c>
-      <c r="B69" s="5" t="inlineStr"/>
-      <c r="C69" s="4" t="inlineStr">
-        <is>
-          <t>Results &amp; Scoring</t>
-        </is>
-      </c>
-      <c r="D69" s="4" t="inlineStr">
-        <is>
-          <t>Appeals and Resits</t>
-        </is>
-      </c>
-      <c r="E69" s="4" t="inlineStr">
-        <is>
-          <t>Appeals and Resits</t>
-        </is>
-      </c>
-      <c r="F69" s="4" t="inlineStr">
-        <is>
-          <t>/appeals-and-resits</t>
-        </is>
-      </c>
-      <c r="G69" s="4" t="inlineStr">
-        <is>
-          <t>Informational</t>
-        </is>
-      </c>
-      <c r="H69" s="4" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="I69" s="4" t="inlineStr">
-        <is>
-          <t>Needs More Support (1 post)</t>
-        </is>
-      </c>
-      <c r="J69" s="4" t="inlineStr">
-        <is>
-          <t>N/A (static page)</t>
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA for refugee doctors</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA for GP doctors in UK; UKMLA fees for refugee doctors; UKMLA for Indian doctors; UKMLA for Nigerian doctors; UKMLA for Pakistani doctors</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA for Refugee Doctors: The GMC Assistance Programme and Fee Support</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-for-refugee-doctors</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>Established (25 posts)</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>01 July 2026</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="4" t="inlineStr">
-        <is>
-          <t>UKMLA results</t>
-        </is>
-      </c>
-      <c r="B70" s="5" t="inlineStr">
-        <is>
-          <t>UKMLA pass mark; UKMLA pass rate for IMG; UKMLA results release date</t>
-        </is>
-      </c>
-      <c r="C70" s="4" t="inlineStr">
-        <is>
-          <t>Results &amp; Scoring</t>
-        </is>
-      </c>
-      <c r="D70" s="4" t="inlineStr">
-        <is>
-          <t>Results and Scoring</t>
-        </is>
-      </c>
-      <c r="E70" s="4" t="inlineStr">
-        <is>
-          <t>Results and Scoring</t>
-        </is>
-      </c>
-      <c r="F70" s="4" t="inlineStr">
-        <is>
-          <t>/results-and-scoring</t>
-        </is>
-      </c>
-      <c r="G70" s="4" t="inlineStr">
-        <is>
-          <t>Informational</t>
-        </is>
-      </c>
-      <c r="H70" s="4" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="I70" s="4" t="inlineStr">
-        <is>
-          <t>Needs More Support (1 post)</t>
-        </is>
-      </c>
-      <c r="J70" s="4" t="inlineStr">
-        <is>
-          <t>N/A (static page)</t>
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA for South African doctors</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA for GP doctors in UK; GMC registration process for doctors; UKMLA eligibility for Indian doctors; UKMLA fees for doctors 2026; UKMLA for Indian doctors</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-for-south-african-doctors</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>Established (25 posts)</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>01 July 2026</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>UKMLA results feedback</t>
+          <t>UKMLA for Sri Lankan doctors</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>UKMLA results; Results &amp; Data; Results &amp; Scoring; UKMLA results timeline 2026; UKMLA results release date</t>
+          <t>UKMLA for GP doctors in UK; GMC registration process for doctors; UKMLA eligibility for Indian doctors; UKMLA fees for doctors 2026; UKMLA for Indian doctors</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Results &amp; Scoring</t>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Results and Scoring</t>
+          <t>Eligibility</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>UKMLA Results: How to Interpret Your Feedback Report</t>
+          <t>UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-results-feedback-report</t>
+          <t>/news#ukmla-for-sri-lankan-doctors</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -4128,65 +4152,1237 @@
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>Needs More Support (1 post)</t>
+          <t>Established (25 posts)</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>30 June 2026</t>
+          <t>01 July 2026</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>UKMLA NHS job after exam</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA exam; what is the UKMLA exam; The Exam; gmc exam; NHS jobs after GMC registration</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-to-nhs-job-pathway</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>Established (25 posts)</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>01 July 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA vs AMC exam comparison</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA exam; what is the UKMLA exam; The Exam; Exam Pattern Comparison; UKMLA vs MCCQE Canada</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA vs PLAB</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA vs AMC and MCCQE: Comparing the UK Route to Australia and Canada</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-vs-amc-and-mccqe-comparison</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>Established (25 posts)</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>01 July 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA vs NEET PG</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA exam for Indian medical graduates; UKMLA for international medical graduates; UKMLA for Caribbean medical graduates; international medical graduates; UKMLA for Indian doctors</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA vs PLAB</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-vs-neet-pg</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>Established (25 posts)</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>01 July 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA vs USMLE</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA vs USMLE which is easier; UKMLA exam; what is the UKMLA exam; The Exam; UKMLA vs USMLE cost and difficulty</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA vs PLAB</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-vs-usmle-comparison</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>Established (25 posts)</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>01 July 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>Good Medical Practice UKMLA</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>how to practice medicine in UK; medical acronyms; medical students; UKMLA for international medical graduates; UKMLA mock exam practice</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Professional Practice &amp; Safety</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr"/>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>Good Medical Practice and the UKMLA: What the GMC Expects</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>/news#good-medical-practice-ukmla</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>Growing (3 posts)</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>30 June 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>patient safety UKMLA</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>1. Patient Presentations; The official GMC MLA Content Map listing core patient presentations, conditions, and practical procedures</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Professional Practice &amp; Safety</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr"/>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>/news#patient-safety-ukmla-prescribing-errors</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>Growing (3 posts)</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>30 June 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>safeguarding UKMLA</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>ukmla guide; UKMLA pharmacology revision; about ukmla guide; contact ukmla guide; img guide</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Professional Practice &amp; Safety</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr"/>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>Safeguarding Adults and Children: A UKMLA Revision Guide</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>/news#safeguarding-ukmla-revision</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>Growing (3 posts)</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>30 June 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="4" t="inlineStr">
+        <is>
+          <t>UKMLA for IMG</t>
+        </is>
+      </c>
+      <c r="B79" s="5" t="inlineStr">
+        <is>
+          <t>UKMLA for international medical graduates; UKMLA eligibility; UKMLA exam for UK medical students; UKMLA eligibility for international medical graduates</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t>Registration &amp; Eligibility</t>
+        </is>
+      </c>
+      <c r="D79" s="4" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
+      <c r="E79" s="4" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
+      <c r="F79" s="4" t="inlineStr">
+        <is>
+          <t>/eligibility</t>
+        </is>
+      </c>
+      <c r="G79" s="4" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H79" s="4" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I79" s="4" t="inlineStr">
+        <is>
+          <t>Established (8 posts)</t>
+        </is>
+      </c>
+      <c r="J79" s="4" t="inlineStr">
+        <is>
+          <t>N/A (static page)</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t>Fees</t>
+        </is>
+      </c>
+      <c r="B80" s="5" t="inlineStr"/>
+      <c r="C80" s="4" t="inlineStr">
+        <is>
+          <t>Registration &amp; Eligibility</t>
+        </is>
+      </c>
+      <c r="D80" s="4" t="inlineStr">
+        <is>
+          <t>Fees</t>
+        </is>
+      </c>
+      <c r="E80" s="4" t="inlineStr">
+        <is>
+          <t>Fees</t>
+        </is>
+      </c>
+      <c r="F80" s="4" t="inlineStr">
+        <is>
+          <t>/fees</t>
+        </is>
+      </c>
+      <c r="G80" s="4" t="inlineStr">
+        <is>
+          <t>Commercial</t>
+        </is>
+      </c>
+      <c r="H80" s="4" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I80" s="4" t="inlineStr">
+        <is>
+          <t>Established (8 posts)</t>
+        </is>
+      </c>
+      <c r="J80" s="4" t="inlineStr">
+        <is>
+          <t>N/A (static page)</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="4" t="inlineStr">
+        <is>
+          <t>UKMLA dates</t>
+        </is>
+      </c>
+      <c r="B81" s="5" t="inlineStr"/>
+      <c r="C81" s="4" t="inlineStr">
+        <is>
+          <t>Registration &amp; Eligibility</t>
+        </is>
+      </c>
+      <c r="D81" s="4" t="inlineStr">
+        <is>
+          <t>Key Dates</t>
+        </is>
+      </c>
+      <c r="E81" s="4" t="inlineStr">
+        <is>
+          <t>Key Dates</t>
+        </is>
+      </c>
+      <c r="F81" s="4" t="inlineStr">
+        <is>
+          <t>/key-dates</t>
+        </is>
+      </c>
+      <c r="G81" s="4" t="inlineStr">
+        <is>
+          <t>Transactional</t>
+        </is>
+      </c>
+      <c r="H81" s="4" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I81" s="4" t="inlineStr">
+        <is>
+          <t>Established (8 posts)</t>
+        </is>
+      </c>
+      <c r="J81" s="4" t="inlineStr">
+        <is>
+          <t>N/A (static page)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="4" t="inlineStr">
+        <is>
+          <t>UKMLA registration</t>
+        </is>
+      </c>
+      <c r="B82" s="5" t="inlineStr">
+        <is>
+          <t>UKMLA booking; English language requirement for UKMLA; UKMLA registration process GMC</t>
+        </is>
+      </c>
+      <c r="C82" s="4" t="inlineStr">
+        <is>
+          <t>Registration &amp; Eligibility</t>
+        </is>
+      </c>
+      <c r="D82" s="4" t="inlineStr">
+        <is>
+          <t>Registration Guide</t>
+        </is>
+      </c>
+      <c r="E82" s="4" t="inlineStr">
+        <is>
+          <t>Registration Guide</t>
+        </is>
+      </c>
+      <c r="F82" s="4" t="inlineStr">
+        <is>
+          <t>/registration-guide</t>
+        </is>
+      </c>
+      <c r="G82" s="4" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H82" s="4" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I82" s="4" t="inlineStr">
+        <is>
+          <t>Established (8 posts)</t>
+        </is>
+      </c>
+      <c r="J82" s="4" t="inlineStr">
+        <is>
+          <t>N/A (static page)</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA disability access adjustments</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>ukmla guide; Reasonable Adjustments; reasonable adjustments gmc; about ukmla guide; contact ukmla guide</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Registration &amp; Eligibility</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Appeals and Resits</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>/news#disability-access-ukmla-guide</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>Established (8 posts)</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>30 June 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA exemptions for specialist doctors</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA for GP doctors in UK; do all doctors need to take UKMLA; is UKMLA required for experienced doctors; UKMLA for Indian doctors; UKMLA for Nigerian doctors</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Registration &amp; Eligibility</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-exemptions-for-specialist-and-gp-doctors</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>Established (8 posts)</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>01 July 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>how to register for PLAB 1</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>PLAB vs UKMLA; plab 1; plab 2; UKMLA vs PLAB; is UKMLA replacing PLAB</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Registration &amp; Eligibility</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Registration Guide</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>How to Register for PLAB 1: A Step-by-Step Guide for IMGs</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>/news#how-to-register-plab-1</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>Established (8 posts)</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>30 June 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA eligibility</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>Eligibility; UKMLA exam; what is the UKMLA exam; The Exam; UKMLA Eligibility Pathways</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Registration &amp; Eligibility</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA Eligibility: Who Can Sit the Exam?</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-eligibility-who-can-sit</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>Established (8 posts)</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>30 June 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA exam fees for IMG</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA exam; UKMLA fees; UKMLA for IMG; what is the UKMLA exam; The Exam</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>Registration &amp; Eligibility</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>Fees</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-fees-for-img-2026</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>Established (8 posts)</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>01 July 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA fees</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA fees for doctors 2026; UKMLA cost; UKMLA Fees and Costs 2026; UKMLA exam fees for IMG; UKMLA fees in Indian rupees</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Registration &amp; Eligibility</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>Fees</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA Fees: The Complete 2026 Cost Breakdown</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-fees-explained</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>Established (8 posts)</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>30 June 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA key dates</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA dates; Key Dates; Key Dates &amp; Timeline; UKMLA exam dates 2026; UKMLA exam dates and fees</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>Registration &amp; Eligibility</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>Key Dates</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA Key Dates and Sitting Schedule: What to Know</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-key-dates-sitting-schedule</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>Transactional</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>Established (8 posts)</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>30 June 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA resits</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t>Appeals &amp; Resits; UKMLA Appeals, Resits &amp; Reasonable Adjustments; Appeals, Resits &amp; Reasonable Adjustments; Attempt Limits and Retake Rules; plab attempt limits</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>Registration &amp; Eligibility</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>Appeals and Resits</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA Resits: Rules, Limits, and How to Bounce Back</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-resits-rules-limits</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>Established (8 posts)</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>30 June 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="4" t="inlineStr">
+        <is>
+          <t>Appeals and Resits</t>
+        </is>
+      </c>
+      <c r="B91" s="5" t="inlineStr"/>
+      <c r="C91" s="4" t="inlineStr">
+        <is>
+          <t>Results &amp; Scoring</t>
+        </is>
+      </c>
+      <c r="D91" s="4" t="inlineStr">
+        <is>
+          <t>Appeals and Resits</t>
+        </is>
+      </c>
+      <c r="E91" s="4" t="inlineStr">
+        <is>
+          <t>Appeals and Resits</t>
+        </is>
+      </c>
+      <c r="F91" s="4" t="inlineStr">
+        <is>
+          <t>/appeals-and-resits</t>
+        </is>
+      </c>
+      <c r="G91" s="4" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H91" s="4" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I91" s="4" t="inlineStr">
+        <is>
+          <t>Growing (2 posts)</t>
+        </is>
+      </c>
+      <c r="J91" s="4" t="inlineStr">
+        <is>
+          <t>N/A (static page)</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="4" t="inlineStr">
+        <is>
+          <t>UKMLA results</t>
+        </is>
+      </c>
+      <c r="B92" s="5" t="inlineStr">
+        <is>
+          <t>UKMLA pass mark; UKMLA pass rate for IMG; UKMLA results release date</t>
+        </is>
+      </c>
+      <c r="C92" s="4" t="inlineStr">
+        <is>
+          <t>Results &amp; Scoring</t>
+        </is>
+      </c>
+      <c r="D92" s="4" t="inlineStr">
+        <is>
+          <t>Results and Scoring</t>
+        </is>
+      </c>
+      <c r="E92" s="4" t="inlineStr">
+        <is>
+          <t>Results and Scoring</t>
+        </is>
+      </c>
+      <c r="F92" s="4" t="inlineStr">
+        <is>
+          <t>/results-and-scoring</t>
+        </is>
+      </c>
+      <c r="G92" s="4" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H92" s="4" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I92" s="4" t="inlineStr">
+        <is>
+          <t>Growing (2 posts)</t>
+        </is>
+      </c>
+      <c r="J92" s="4" t="inlineStr">
+        <is>
+          <t>N/A (static page)</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA AKT pass mark</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA AKT; UKMLA pass mark; how to pass ukmla; ms akt; What is the UKMLA AKT?</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>Results &amp; Scoring</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>Results and Scoring</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA AKT Pass Mark and Pass Rate Explained</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-akt-pass-mark-and-pass-rate-explained</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>Growing (2 posts)</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>01 July 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA results feedback</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA results; Results &amp; Data; Results &amp; Scoring; UKMLA results timeline 2026; UKMLA results release date</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>Results &amp; Scoring</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>Results and Scoring</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA Results: How to Interpret Your Feedback Report</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-results-feedback-report</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>Growing (2 posts)</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>30 June 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
           <t>Foundation Programme after UKMLA</t>
         </is>
       </c>
-      <c r="B72" s="3" t="inlineStr">
+      <c r="B95" s="3" t="inlineStr">
         <is>
           <t>UKMLA for academic foundation programme; UKMLA after MBBS; UKMLA after MBBS in India; UKMLA and foundation year application; UKMLA fail foundation year impact</t>
         </is>
       </c>
-      <c r="C72" s="2" t="inlineStr">
+      <c r="C95" s="2" t="inlineStr">
         <is>
           <t>Uncategorised</t>
         </is>
       </c>
-      <c r="D72" s="2" t="inlineStr"/>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="D95" s="2" t="inlineStr"/>
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>Understanding the Foundation Programme: What Awaits After the UKMLA</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>/news#foundation-programme-after-ukmla</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr">
-        <is>
-          <t>Informational</t>
-        </is>
-      </c>
-      <c r="H72" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="I72" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
         <is>
           <t>Needs More Support (1 post)</t>
         </is>
       </c>
-      <c r="J72" s="2" t="inlineStr">
+      <c r="J95" s="2" t="inlineStr">
         <is>
           <t>30 June 2026</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J72"/>
+  <autoFilter ref="A1:J95"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4238,7 +5434,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>58</v>
+        <v>81</v>
       </c>
     </row>
     <row r="6">
@@ -4268,7 +5464,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -4295,7 +5491,7 @@
       <c r="A12" s="9" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Clinical Systems Revision: 22 posts — Established (22 posts)</t>
+          <t>IMG Country Routes &amp; Global Comparisons: 25 posts — Established (25 posts)</t>
         </is>
       </c>
     </row>
@@ -4303,7 +5499,7 @@
       <c r="A13" s="9" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Registration &amp; Eligibility: 7 posts — Established (7 posts)</t>
+          <t>Clinical Systems Revision: 23 posts — Established (23 posts)</t>
         </is>
       </c>
     </row>
@@ -4311,7 +5507,7 @@
       <c r="A14" s="9" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Core UKMLA Overview: 7 posts — Established (7 posts)</t>
+          <t>Registration &amp; Eligibility: 8 posts — Established (8 posts)</t>
         </is>
       </c>
     </row>
@@ -4319,7 +5515,7 @@
       <c r="A15" s="9" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Exam Format: 6 posts — Established (6 posts)</t>
+          <t>Core UKMLA Overview: 7 posts — Established (7 posts)</t>
         </is>
       </c>
     </row>
@@ -4327,7 +5523,7 @@
       <c r="A16" s="9" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons: 6 posts — Established (6 posts)</t>
+          <t>Exam Format: 6 posts — Established (6 posts)</t>
         </is>
       </c>
     </row>
@@ -4335,7 +5531,7 @@
       <c r="A17" s="9" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Exam Preparation: 5 posts — Established (5 posts)</t>
+          <t>Exam Preparation: 6 posts — Established (6 posts)</t>
         </is>
       </c>
     </row>
@@ -4351,7 +5547,7 @@
       <c r="A19" s="9" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Uncategorised: 1 posts — Needs More Support (1 post)</t>
+          <t>Results &amp; Scoring: 2 posts — Growing (2 posts)</t>
         </is>
       </c>
     </row>
@@ -4359,7 +5555,7 @@
       <c r="A20" s="9" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Results &amp; Scoring: 1 posts — Needs More Support (1 post)</t>
+          <t>Uncategorised: 1 posts — Needs More Support (1 post)</t>
         </is>
       </c>
     </row>

--- a/UKMLA_Keyword_Cluster_Sheet.xlsx
+++ b/UKMLA_Keyword_Cluster_Sheet.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Keyword Cluster Sheet'!$A$1:$J$95</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Keyword Cluster Sheet'!$A$1:$J$121</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -470,7 +470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J95"/>
+  <dimension ref="A1:J121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1768,7 +1768,7 @@
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>Established (7 posts)</t>
+          <t>Established (11 posts)</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>Established (7 posts)</t>
+          <t>Established (11 posts)</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
@@ -1868,7 +1868,7 @@
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>Established (7 posts)</t>
+          <t>Established (11 posts)</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
@@ -1916,7 +1916,7 @@
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>Established (7 posts)</t>
+          <t>Established (11 posts)</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
@@ -1928,12 +1928,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>UK medical schools UKMLA implementation</t>
+          <t>Foundation Programme 2026 recruitment changes</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>medical acronyms; medical students; UKMLA for international medical graduates; UKMLA syllabus for medical students; UK visa for medical professionals</t>
+          <t>UKMLA syllabus 2026 changes; UKMLA for academic foundation programme; ukmla syllabus 2026; Understanding the Foundation Programme: What Awaits After the UKMLA; UK doctor salary 2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -1943,17 +1943,17 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>What Is the UKMLA?</t>
+          <t>Eligibility</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>How UK Medical Schools Implement the UKMLA: An Overview</t>
+          <t>Foundation Programme 2026 Recruitment Changes: What's New for Applicants</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>/news#uk-medical-schools-ukmla-implementation</t>
+          <t>/news#foundation-programme-2026-recruitment-changes</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -1968,24 +1968,24 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>Established (7 posts)</t>
+          <t>Established (11 posts)</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>30 June 2026</t>
+          <t>02 July 2026</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>MLA content map</t>
+          <t>UK medical schools UKMLA implementation</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>UKMLA content map; The MLA Content Map; The MLA Content Map Framework; UKMLA Syllabus &amp; Content Map; Syllabus &amp; Content Map</t>
+          <t>medical acronyms; medical students; UKMLA for international medical graduates; UKMLA syllabus for medical students; UK visa for medical professionals</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -1995,17 +1995,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>MLA Content Map / Syllabus</t>
+          <t>What Is the UKMLA?</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>MLA Content Map: The Blueprint Behind Every UKMLA Question</t>
+          <t>How UK Medical Schools Implement the UKMLA: An Overview</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>/news#mla-content-map-explained</t>
+          <t>/news#uk-medical-schools-ukmla-implementation</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -2020,7 +2020,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>Established (7 posts)</t>
+          <t>Established (11 posts)</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -2032,12 +2032,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>PLAB 2 preparation</t>
+          <t>is UKMLA replacing PLAB</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>PLAB vs UKMLA; UKMLA preparation; plab 1; plab 2; UKMLA vs PLAB</t>
+          <t>PLAB vs UKMLA; plab 1; plab 2; UKMLA vs PLAB; plab pathway</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2052,12 +2052,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>PLAB 2 Preparation: How to Excel in the Clinical Assessment</t>
+          <t>Is UKMLA Replacing PLAB? The Real Relationship, Explained</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>/news#plab-2-preparation-guide</t>
+          <t>/news#is-ukmla-replacing-plab-explained</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -2072,24 +2072,24 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>Established (7 posts)</t>
+          <t>Established (11 posts)</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>30 June 2026</t>
+          <t>02 July 2026</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>UKMLA preparation for IMGs</t>
+          <t>MLA content map</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>UKMLA preparation; Preparation; Preparation Guide; UKMLA Preparation Guide; UKMLA OSCE preparation</t>
+          <t>UKMLA content map; The MLA Content Map; The MLA Content Map Framework; UKMLA Syllabus &amp; Content Map; Syllabus &amp; Content Map</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2099,17 +2099,17 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>UKMLA vs PLAB</t>
+          <t>MLA Content Map / Syllabus</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>UKMLA Preparation for IMG Candidates: A Tailored Guide</t>
+          <t>MLA Content Map: The Blueprint Behind Every UKMLA Question</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-preparation-for-imgs</t>
+          <t>/news#mla-content-map-explained</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>Established (7 posts)</t>
+          <t>Established (11 posts)</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>UKMLA graduate entry</t>
+          <t>PLAB 2 preparation</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>medical students; UKMLA syllabus for medical students; UKMLA exam for UK medical students; Eligibility for UK Medical Students; UKMLA pass rate medical students</t>
+          <t>PLAB vs UKMLA; UKMLA preparation; plab 1; plab 2; UKMLA vs PLAB</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2151,17 +2151,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Eligibility</t>
+          <t>UKMLA vs PLAB</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>UKMLA for Graduate-Entry Medical Students: What Is Different?</t>
+          <t>PLAB 2 Preparation: How to Excel in the Clinical Assessment</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-graduate-entry-medical-students</t>
+          <t>/news#plab-2-preparation-guide</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>Established (7 posts)</t>
+          <t>Established (11 posts)</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -2188,32 +2188,32 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>UKMLA preparation for IMGs</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA preparation; Preparation; Preparation Guide; UKMLA Preparation Guide; UKMLA OSCE preparation</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Core UKMLA Overview</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
           <t>UKMLA vs PLAB</t>
         </is>
       </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>PLAB vs UKMLA; plab 1; plab 2; difference between PLAB and UKMLA; is UKMLA replacing PLAB</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>Core UKMLA Overview</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>UKMLA vs PLAB</t>
-        </is>
-      </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>UKMLA vs PLAB: What Is the Difference?</t>
+          <t>UKMLA Preparation for IMG Candidates: A Tailored Guide</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-vs-plab-difference</t>
+          <t>/news#ukmla-preparation-for-imgs</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>Established (7 posts)</t>
+          <t>Established (11 posts)</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -2240,12 +2240,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>what is UKMLA</t>
+          <t>UKMLA syllabus 2026 changes</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>ukmla guide; about ukmla guide; contact ukmla guide; img guide; Preparation Guide</t>
+          <t>UKMLA syllabus; ukmla syllabus 2026; Syllabus; Content &amp; Syllabus; UKMLA exam syllabus 2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2255,17 +2255,17 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>What Is the UKMLA?</t>
+          <t>MLA Content Map / Syllabus</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>UKMLA Syllabus 2026 Changes: What's New in the Updated MLA Content Map</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>/news#what-is-ukmla-complete-guide</t>
+          <t>/news#ukmla-syllabus-2026-changes</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -2280,148 +2280,148 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>Established (7 posts)</t>
+          <t>Established (11 posts)</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
+          <t>02 July 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA for academic foundation programme</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>Understanding the Foundation Programme: What Awaits After the UKMLA; UKMLA and foundation year application; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; UKMLA fail foundation year impact; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Core UKMLA Overview</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA and the Academic Foundation Programme: What Research-Minded Students Need to Know</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-and-academic-foundation-programme</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>Established (11 posts)</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>02 July 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA graduate entry</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>medical students; UKMLA syllabus for medical students; UKMLA exam for UK medical students; Eligibility for UK Medical Students; UKMLA pass rate medical students</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Core UKMLA Overview</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA for Graduate-Entry Medical Students: What Is Different?</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-graduate-entry-medical-students</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>Established (11 posts)</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
           <t>30 June 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="6" t="inlineStr">
-        <is>
-          <t>UKMLA AKT</t>
-        </is>
-      </c>
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>AKT exam; UKMLA AKT pass mark; how many questions in UKMLA AKT; UKMLA AKT exam preparation tips; UKMLA AKT vs CPSA difference</t>
-        </is>
-      </c>
-      <c r="C36" s="4" t="inlineStr">
-        <is>
-          <t>Exam Format</t>
-        </is>
-      </c>
-      <c r="D36" s="4" t="inlineStr">
-        <is>
-          <t>AKT Exam Pattern</t>
-        </is>
-      </c>
-      <c r="E36" s="4" t="inlineStr">
-        <is>
-          <t>AKT Exam Pattern</t>
-        </is>
-      </c>
-      <c r="F36" s="4" t="inlineStr">
-        <is>
-          <t>/exam-pattern/akt</t>
-        </is>
-      </c>
-      <c r="G36" s="4" t="inlineStr">
-        <is>
-          <t>Informational</t>
-        </is>
-      </c>
-      <c r="H36" s="4" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="I36" s="4" t="inlineStr">
-        <is>
-          <t>Established (6 posts)</t>
-        </is>
-      </c>
-      <c r="J36" s="4" t="inlineStr">
-        <is>
-          <t>N/A (static page)</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="6" t="inlineStr">
-        <is>
-          <t>UKMLA CPSA</t>
-        </is>
-      </c>
-      <c r="B37" s="5" t="inlineStr">
-        <is>
-          <t>CPSA exam; UKMLA CPSA stations examples; UKMLA CPSA centre Manchester</t>
-        </is>
-      </c>
-      <c r="C37" s="4" t="inlineStr">
-        <is>
-          <t>Exam Format</t>
-        </is>
-      </c>
-      <c r="D37" s="4" t="inlineStr">
-        <is>
-          <t>CPSA Exam Pattern</t>
-        </is>
-      </c>
-      <c r="E37" s="4" t="inlineStr">
-        <is>
-          <t>CPSA Exam Pattern</t>
-        </is>
-      </c>
-      <c r="F37" s="4" t="inlineStr">
-        <is>
-          <t>/exam-pattern/cpsa</t>
-        </is>
-      </c>
-      <c r="G37" s="4" t="inlineStr">
-        <is>
-          <t>Informational</t>
-        </is>
-      </c>
-      <c r="H37" s="4" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="I37" s="4" t="inlineStr">
-        <is>
-          <t>Established (6 posts)</t>
-        </is>
-      </c>
-      <c r="J37" s="4" t="inlineStr">
-        <is>
-          <t>N/A (static page)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>CPSA clinical examination stations</t>
+          <t>UKMLA vs PLAB</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>UKMLA CPSA; What is the UKMLA CPSA?; UKMLA CPSA stations list; UKMLA clinical examination tips; UKMLA CPSA stations examples</t>
+          <t>PLAB vs UKMLA; plab 1; plab 2; difference between PLAB and UKMLA; is UKMLA replacing PLAB</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Exam Format</t>
+          <t>Core UKMLA Overview</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>CPSA Exam Pattern</t>
+          <t>UKMLA vs PLAB</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Clinical Examination Stations in the CPSA: A Practical Guide</t>
+          <t>UKMLA vs PLAB: What Is the Difference?</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>/news#clinical-examination-cpsa-guide</t>
+          <t>/news#ukmla-vs-plab-difference</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -2436,7 +2436,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>Established (6 posts)</t>
+          <t>Established (11 posts)</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -2448,168 +2448,168 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>how to read AKT stem</t>
+          <t>what is UKMLA</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>UKMLA AKT; ms akt; What is the UKMLA AKT?; AKT exam; AKT Details</t>
+          <t>ukmla guide; about ukmla guide; contact ukmla guide; img guide; Preparation Guide</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
+          <t>Core UKMLA Overview</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>What Is the UKMLA?</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>What Is the UKMLA? A Complete Beginner's Guide</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>/news#what-is-ukmla-complete-guide</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>Established (11 posts)</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>30 June 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>UKMLA AKT</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>AKT exam; UKMLA AKT pass mark; how many questions in UKMLA AKT; UKMLA AKT exam preparation tips; UKMLA AKT vs CPSA difference</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
           <t>Exam Format</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="D40" s="4" t="inlineStr">
         <is>
           <t>AKT Exam Pattern</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>How to Read an AKT Stem: Avoiding Common Traps</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>/news#how-to-read-akt-stem</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>Informational</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>AKT Exam Pattern</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>/exam-pattern/akt</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I40" s="4" t="inlineStr">
         <is>
           <t>Established (6 posts)</t>
         </is>
       </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>30 June 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>psychiatry communication CPSA</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>UKMLA CPSA; What is the UKMLA CPSA?; UKMLA CPSA stations list; CPSA exam; UKMLA CPSA stations examples</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>Exam Format</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>CPSA Exam Pattern</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>Psychiatry Communication Stations: Handling Difficult Conversations</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>/news#psychiatry-communication-cpsa-stations</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>Informational</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>Established (6 posts)</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>30 June 2026</t>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>N/A (static page)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>UKMLA AKT</t>
-        </is>
-      </c>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>ms akt; What is the UKMLA AKT?; AKT exam; how to prepare for UKMLA; AKT Details</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
+          <t>UKMLA CPSA</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>CPSA exam; UKMLA CPSA stations examples; UKMLA CPSA centre Manchester</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
         <is>
           <t>Exam Format</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>AKT Exam Pattern</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>UKMLA AKT: Format, Question Types, and How to Prepare</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>/news#ukmla-akt-format-preparation</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>Informational</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>CPSA Exam Pattern</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>CPSA Exam Pattern</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>/exam-pattern/cpsa</t>
+        </is>
+      </c>
+      <c r="G41" s="4" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I41" s="4" t="inlineStr">
         <is>
           <t>Established (6 posts)</t>
         </is>
       </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>30 June 2026</t>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>N/A (static page)</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="6" t="inlineStr">
-        <is>
-          <t>UKMLA CPSA</t>
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>CPSA clinical examination stations</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>What is the UKMLA CPSA?; CPSA exam; UKMLA exam; what is the UKMLA exam; Clinical Skills (CPSA)</t>
+          <t>UKMLA CPSA; What is the UKMLA CPSA?; UKMLA CPSA stations list; UKMLA clinical examination tips; UKMLA CPSA stations examples</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -2624,12 +2624,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>UKMLA CPSA: What the Clinical Exam Really Tests</t>
+          <t>Clinical Examination Stations in the CPSA: A Practical Guide</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-cpsa-what-it-tests</t>
+          <t>/news#clinical-examination-cpsa-guide</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -2656,12 +2656,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Angoff standard setting UKMLA</t>
+          <t>how to read AKT stem</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>AKT Standard Setting: The Angoff Method; UKMLA AKT standard setting explained; UKMLA Results, Scoring &amp; Standard Setting; angoff definition; angoff method</t>
+          <t>UKMLA AKT; ms akt; What is the UKMLA AKT?; AKT exam; AKT Details</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -2671,17 +2671,17 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Results and Scoring</t>
+          <t>AKT Exam Pattern</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>What Is an Angoff Standard Setting and Why Does It Matter?</t>
+          <t>How to Read an AKT Stem: Avoiding Common Traps</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>/news#angoff-standard-setting-explained</t>
+          <t>/news#how-to-read-akt-stem</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -2706,86 +2706,86 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="4" t="inlineStr">
-        <is>
-          <t>UKMLA preparation</t>
-        </is>
-      </c>
-      <c r="B44" s="5" t="inlineStr">
-        <is>
-          <t>how to prepare for UKMLA; UKMLA study plan; how long to study for UKMLA; UKMLA preparation 6 weeks</t>
-        </is>
-      </c>
-      <c r="C44" s="4" t="inlineStr">
-        <is>
-          <t>Exam Preparation</t>
-        </is>
-      </c>
-      <c r="D44" s="4" t="inlineStr">
-        <is>
-          <t>Preparation</t>
-        </is>
-      </c>
-      <c r="E44" s="4" t="inlineStr">
-        <is>
-          <t>Preparation</t>
-        </is>
-      </c>
-      <c r="F44" s="4" t="inlineStr">
-        <is>
-          <t>/preparation</t>
-        </is>
-      </c>
-      <c r="G44" s="4" t="inlineStr">
-        <is>
-          <t>Commercial</t>
-        </is>
-      </c>
-      <c r="H44" s="4" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="I44" s="4" t="inlineStr">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>psychiatry communication CPSA</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA CPSA; What is the UKMLA CPSA?; UKMLA CPSA stations list; CPSA exam; UKMLA CPSA stations examples</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Exam Format</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>CPSA Exam Pattern</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Psychiatry Communication Stations: Handling Difficult Conversations</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>/news#psychiatry-communication-cpsa-stations</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
         <is>
           <t>Established (6 posts)</t>
         </is>
       </c>
-      <c r="J44" s="4" t="inlineStr">
-        <is>
-          <t>N/A (static page)</t>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>30 June 2026</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>UKMLA group study solo</t>
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>UKMLA AKT</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>UKMLA group study vs solo study; how long to study for UKMLA; UKMLA study plan; study plan; UKMLA study plan 12 weeks</t>
+          <t>ms akt; What is the UKMLA AKT?; AKT exam; how to prepare for UKMLA; AKT Details</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Exam Preparation</t>
+          <t>Exam Format</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Preparation</t>
+          <t>AKT Exam Pattern</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Group Study vs Solo Study for the UKMLA: What Works Best?</t>
+          <t>UKMLA AKT: Format, Question Types, and How to Prepare</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>/news#group-study-vs-solo-ukmla</t>
+          <t>/news#ukmla-akt-format-preparation</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -2810,34 +2810,34 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>UKMLA revision notes</t>
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>UKMLA CPSA</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>UKMLA revision notes tips; UKMLA pharmacology revision; AKT Revision Strategy; CPSA / OSCE Revision Strategy; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide</t>
+          <t>What is the UKMLA CPSA?; CPSA exam; UKMLA exam; what is the UKMLA exam; Clinical Skills (CPSA)</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Exam Preparation</t>
+          <t>Exam Format</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Preparation</t>
+          <t>CPSA Exam Pattern</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>How to Write UKMLA Revision Notes That Actually Work</t>
+          <t>UKMLA CPSA: What the Clinical Exam Really Tests</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-revision-notes-strategy</t>
+          <t>/news#ukmla-cpsa-what-it-tests</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -2864,116 +2864,116 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>UKMLA exam anxiety tips</t>
+          <t>Angoff standard setting UKMLA</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>UKMLA exam; what is the UKMLA exam; The Exam; UKMLA exam in Dubai; AKT exam</t>
+          <t>AKT Standard Setting: The Angoff Method; UKMLA AKT standard setting explained; UKMLA Results, Scoring &amp; Standard Setting; angoff definition; angoff method</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
+          <t>Exam Format</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Results and Scoring</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>What Is an Angoff Standard Setting and Why Does It Matter?</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>/news#angoff-standard-setting-explained</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>Established (6 posts)</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>30 June 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>UKMLA preparation</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>how to prepare for UKMLA; UKMLA study plan; how long to study for UKMLA; UKMLA preparation 6 weeks</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
           <t>Exam Preparation</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="D48" s="4" t="inlineStr">
         <is>
           <t>Preparation</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>Managing UKMLA Exam Anxiety: Practical Strategies for Candidates</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>/news#managing-ukmla-exam-anxiety</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>Informational</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>Established (6 posts)</t>
-        </is>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>01 July 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>UKMLA mock exams</t>
-        </is>
-      </c>
-      <c r="B48" s="3" t="inlineStr">
-        <is>
-          <t>UKMLA mock; UKMLA preparation; Preparation; UKMLA mock exam practice; free UKMLA mock test</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>Exam Preparation</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="E48" s="4" t="inlineStr">
         <is>
           <t>Preparation</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>The Role of Mock Exams in UKMLA Preparation</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>/news#mock-exams-ukmla-preparation</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>Informational</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>Established (6 posts)</t>
-        </is>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>30 June 2026</t>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>/preparation</t>
+        </is>
+      </c>
+      <c r="G48" s="4" t="inlineStr">
+        <is>
+          <t>Commercial</t>
+        </is>
+      </c>
+      <c r="H48" s="4" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I48" s="4" t="inlineStr">
+        <is>
+          <t>Established (8 posts)</t>
+        </is>
+      </c>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>N/A (static page)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>UKMLA AKT preparation countdown</t>
+          <t>UKMLA group study solo</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>UKMLA AKT; UKMLA preparation; ms akt; What is the UKMLA AKT?; Preparation</t>
+          <t>UKMLA group study vs solo study; how long to study for UKMLA; UKMLA study plan; study plan; UKMLA study plan 12 weeks</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Three Months to the UKMLA AKT: A Final Preparation Countdown</t>
+          <t>Group Study vs Solo Study for the UKMLA: What Works Best?</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>/news#three-months-ukmla-akt-countdown</t>
+          <t>/news#group-study-vs-solo-ukmla</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>Established (6 posts)</t>
+          <t>Established (8 posts)</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>time management UKMLA AKT</t>
+          <t>how to pass UKMLA on first attempt</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>UKMLA AKT; ms akt; What is the UKMLA AKT?; AKT exam; AKT Details</t>
+          <t>how to pass ukmla; UKMLA pass mark; UKMLA pass mark for IMG; UKMLA attempt limit for doctors; UKMLA AKT pass mark</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Time Management in the UKMLA AKT: Strategies That Work</t>
+          <t>How to Pass the UKMLA on Your First Attempt</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>/news#time-management-akt-ukmla</t>
+          <t>/news#how-to-pass-ukmla-on-first-attempt</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -3060,44 +3060,44 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>Established (6 posts)</t>
+          <t>Established (8 posts)</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>30 June 2026</t>
+          <t>02 July 2026</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>English language requirement for UKMLA India</t>
+          <t>UKMLA revision notes</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>UKMLA India; English language requirement for UKMLA; English requirement for UKMLA India (IELTS/OET); UKMLA OET or IELTS requirement; Step 2: English Language Proficiency</t>
+          <t>UKMLA revision notes tips; UKMLA pharmacology revision; AKT Revision Strategy; CPSA / OSCE Revision Strategy; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
+          <t>Exam Preparation</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Eligibility</t>
+          <t>Preparation</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>English Language Requirements for the UKMLA: IELTS and OET Scores Explained</t>
+          <t>How to Write UKMLA Revision Notes That Actually Work</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>/news#english-language-requirement-for-ukmla-india</t>
+          <t>/news#ukmla-revision-notes-strategy</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -3112,44 +3112,44 @@
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>Established (25 posts)</t>
+          <t>Established (8 posts)</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>01 July 2026</t>
+          <t>30 June 2026</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>GMC registration requirements for international doctors</t>
+          <t>UKMLA exam anxiety tips</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>UKMLA for GP doctors in UK; UKMLA registration; GMC registration process for doctors; UKMLA registration process GMC; GMC registration requirements IMG</t>
+          <t>UKMLA exam; what is the UKMLA exam; The Exam; UKMLA exam in Dubai; AKT exam</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
+          <t>Exam Preparation</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Registration Guide</t>
+          <t>Preparation</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>GMC Registration Requirements for International Doctors: The Complete Process</t>
+          <t>Managing UKMLA Exam Anxiety: Practical Strategies for Candidates</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>/news#gmc-registration-requirements-for-international-doctors</t>
+          <t>/news#managing-ukmla-exam-anxiety</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>Established (25 posts)</t>
+          <t>Established (8 posts)</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -3176,32 +3176,32 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>GMC registration from India</t>
+          <t>UKMLA mock exams</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>UKMLA India; UKMLA registration; gmc registration guide; how to apply for UKMLA from India; UKMLA GMC registration for graduates</t>
+          <t>UKMLA mock; UKMLA preparation; Preparation; UKMLA mock exam practice; free UKMLA mock test</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
+          <t>Exam Preparation</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Registration Guide</t>
+          <t>Preparation</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide</t>
+          <t>The Role of Mock Exams in UKMLA Preparation</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>/news#gmc-registration-and-epic-verification-india</t>
+          <t>/news#mock-exams-ukmla-preparation</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -3216,44 +3216,44 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>Established (25 posts)</t>
+          <t>Established (8 posts)</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>01 July 2026</t>
+          <t>30 June 2026</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>how to become a doctor in UK from India</t>
+          <t>UKMLA AKT preparation countdown</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>how to become a doctor in UK; UKMLA India; how to become a doctor in UK from Nigeria; how to become a doctor in UK from Pakistan; how to apply for UKMLA from India</t>
+          <t>UKMLA AKT; UKMLA preparation; ms akt; What is the UKMLA AKT?; Preparation</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
+          <t>Exam Preparation</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Eligibility</t>
+          <t>Preparation</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>How to Become a Doctor in the UK from India: The Complete UKMLA Route</t>
+          <t>Three Months to the UKMLA AKT: A Final Preparation Countdown</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>/news#how-to-become-a-doctor-in-uk-from-india</t>
+          <t>/news#three-months-ukmla-akt-countdown</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -3268,44 +3268,44 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>Established (25 posts)</t>
+          <t>Established (8 posts)</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>01 July 2026</t>
+          <t>30 June 2026</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>how to become a doctor in UK</t>
+          <t>time management UKMLA AKT</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>how to become a doctor in UK from India; how to become a doctor in UK from Nigeria; how to become a doctor in UK from Pakistan; UKMLA registration; gmc registration guide</t>
+          <t>UKMLA AKT; ms akt; What is the UKMLA AKT?; AKT exam; AKT Details</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
+          <t>Exam Preparation</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Eligibility</t>
+          <t>Preparation</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs</t>
+          <t>Time Management in the UKMLA AKT: Strategies That Work</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>/news#how-to-become-a-doctor-in-the-uk-gmc-registration-guide</t>
+          <t>/news#time-management-akt-ukmla</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -3320,44 +3320,44 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>Established (25 posts)</t>
+          <t>Established (8 posts)</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>01 July 2026</t>
+          <t>30 June 2026</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>is Indian MBBS valid in UK</t>
+          <t>UKMLA Anki deck download</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>MBBS in UK for Indian students; UKMLA after MBBS; UKMLA for Indian doctors; UKMLA after MBBS in India; UKMLA eligibility for Indian doctors</t>
+          <t>ukmla guide; UKMLA syllabus pdf download; What Is the UKMLA? A Complete Beginner's Guide; UKMLA pharmacology revision; about ukmla guide</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
+          <t>Exam Preparation</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Eligibility</t>
+          <t>Preparation</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained</t>
+          <t>UKMLA Anki Deck and Flashcard Revision: The Complete Guide</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>/news#is-indian-mbbs-valid-in-uk</t>
+          <t>/news#ukmla-anki-deck-and-flashcard-revision-guide</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -3372,24 +3372,24 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>Established (25 posts)</t>
+          <t>Established (8 posts)</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>01 July 2026</t>
+          <t>02 July 2026</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>MBBS in UK for Indian students</t>
+          <t>English language requirement for UKMLA India</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>is Indian MBBS valid in UK; UKMLA after MBBS; UKMLA for Indian doctors; UKMLA for IMG; medical students</t>
+          <t>UKMLA India; English language requirement for UKMLA; English requirement for UKMLA India (IELTS/OET); UKMLA OET or IELTS requirement; Step 2: English Language Proficiency</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -3404,12 +3404,12 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path</t>
+          <t>English Language Requirements for the UKMLA: IELTS and OET Scores Explained</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>/news#mbbs-in-uk-for-indian-students</t>
+          <t>/news#english-language-requirement-for-ukmla-india</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>Established (25 posts)</t>
+          <t>Established (30 posts)</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>UK doctor salary for Indian doctors</t>
+          <t>foundation year vs specialty training IMG</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>UKMLA for Indian doctors; salary of doctor in UK for Indian; UKMLA for GP doctors in UK; UK doctor salary 2026; UKMLA eligibility for Indian doctors</t>
+          <t>UKMLA for IMG; UKMLA and foundation year application; UKMLA fail foundation year impact; img guide; IMG Pathway</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -3456,12 +3456,12 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home</t>
+          <t>Foundation Year vs Specialty Training for IMGs: Which Route After the UKMLA?</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>/news#uk-doctor-salary-guide-for-indian-doctors</t>
+          <t>/news#foundation-year-vs-specialty-training-for-imgs</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -3476,24 +3476,24 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>Established (25 posts)</t>
+          <t>Established (30 posts)</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>01 July 2026</t>
+          <t>02 July 2026</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>UK visa for international doctors</t>
+          <t>GMC registration requirements for international doctors</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>UKMLA for GP doctors in UK; how to get UK visa for doctors; UK medical registration for international doctors; UKMLA for Indian doctors; UKMLA for Nigerian doctors</t>
+          <t>UKMLA for GP doctors in UK; UKMLA registration; GMC registration process for doctors; UKMLA registration process GMC; GMC registration requirements IMG</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -3503,17 +3503,17 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Eligibility</t>
+          <t>Registration Guide</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>UK Visa Guide for International Doctors: Health and Care Worker Visa Explained</t>
+          <t>GMC Registration Requirements for International Doctors: The Complete Process</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>/news#uk-visa-guide-for-international-doctors</t>
+          <t>/news#gmc-registration-requirements-for-international-doctors</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -3528,7 +3528,7 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>Established (25 posts)</t>
+          <t>Established (30 posts)</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>UKMLA AKT test centres</t>
+          <t>GMC registration from India</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>UKMLA AKT; ms akt; What is the UKMLA AKT?; UKMLA AKT test centres in India; UKMLA AKT test centres in Pakistan</t>
+          <t>UKMLA India; UKMLA registration; gmc registration guide; how to apply for UKMLA from India; UKMLA GMC registration for graduates</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -3555,17 +3555,17 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern</t>
+          <t>Registration Guide</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide</t>
+          <t>GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-akt-test-centres-guide</t>
+          <t>/news#gmc-registration-and-epic-verification-india</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -3580,7 +3580,7 @@
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>Established (25 posts)</t>
+          <t>Established (30 posts)</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -3592,12 +3592,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>UKMLA question bank</t>
+          <t>how to become a doctor in UK from India</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>best question bank for UKMLA; best question bank for UKMLA UK students; UKMLA question bank free for students; UKMLA AKT question bank free; UKMLA mock</t>
+          <t>how to become a doctor in UK; UKMLA India; how to become a doctor in UK from Nigeria; how to become a doctor in UK from Pakistan; how to apply for UKMLA from India</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -3607,17 +3607,17 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Preparation</t>
+          <t>Eligibility</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources</t>
+          <t>How to Become a Doctor in the UK from India: The Complete UKMLA Route</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-question-bank-and-mock-tests</t>
+          <t>/news#how-to-become-a-doctor-in-uk-from-india</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>Established (25 posts)</t>
+          <t>Established (30 posts)</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -3644,12 +3644,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>UKMLA for Bangladeshi doctors</t>
+          <t>how to become a doctor in UK</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>UKMLA for GP doctors in UK; GMC registration process for doctors; UKMLA eligibility for Indian doctors; UKMLA fees for doctors 2026; UKMLA for Indian doctors</t>
+          <t>how to become a doctor in UK from India; how to become a doctor in UK from Nigeria; how to become a doctor in UK from Pakistan; UKMLA registration; gmc registration guide</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+          <t>How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-for-bangladeshi-doctors</t>
+          <t>/news#how-to-become-a-doctor-in-the-uk-gmc-registration-guide</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -3684,7 +3684,7 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>Established (25 posts)</t>
+          <t>Established (30 posts)</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -3696,12 +3696,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>UKMLA for Egyptian doctors</t>
+          <t>is Indian MBBS valid in UK</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>UKMLA for GP doctors in UK; GMC registration process for doctors; UKMLA eligibility for Indian doctors; UKMLA fees for doctors 2026; UKMLA for Indian doctors</t>
+          <t>MBBS in UK for Indian students; UKMLA after MBBS; UKMLA for Indian doctors; UKMLA after MBBS in India; UKMLA eligibility for Indian doctors</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -3716,12 +3716,12 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+          <t>Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-for-egyptian-doctors</t>
+          <t>/news#is-indian-mbbs-valid-in-uk</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>Established (25 posts)</t>
+          <t>Established (30 posts)</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
@@ -3748,12 +3748,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>UKMLA for Filipino doctors</t>
+          <t>MBBS in UK for Indian students</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>UKMLA for GP doctors in UK; GMC registration process for doctors; UKMLA eligibility for Indian doctors; UKMLA fees for doctors 2026; UKMLA for Indian doctors</t>
+          <t>is Indian MBBS valid in UK; UKMLA after MBBS; UKMLA for Indian doctors; UKMLA for IMG; medical students</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -3768,12 +3768,12 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>UKMLA for Filipino Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+          <t>MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-for-filipino-doctors</t>
+          <t>/news#mbbs-in-uk-for-indian-students</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -3788,7 +3788,7 @@
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>Established (25 posts)</t>
+          <t>Established (30 posts)</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -3800,12 +3800,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>UKMLA for Gulf and Saudi doctors</t>
+          <t>Medical Training Initiative scheme closure 2026</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>UKMLA for GP doctors in UK; UKMLA for Saudi / Gulf doctors; UKMLA for Saudi doctors; GMC registration process for doctors; UKMLA eligibility for Indian doctors</t>
+          <t>medical licence UK for doctors 2026; UK medical licence requirements 2026; ukmla syllabus 2026; medical acronyms; medical students</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -3820,12 +3820,12 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+          <t>Medical Training Initiative Scheme Closure 2026: What IMGs Need to Know</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-for-gulf-doctors</t>
+          <t>/news#medical-training-initiative-scheme-closure-2026</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -3840,24 +3840,24 @@
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>Established (25 posts)</t>
+          <t>Established (30 posts)</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>01 July 2026</t>
+          <t>02 July 2026</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>UKMLA for international medical graduates</t>
+          <t>Medical Training Prioritisation Act 2026</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>international medical graduates; UKMLA eligibility for international medical graduates; UKMLA for Caribbean medical graduates; Eligibility for International Medical Graduates (IMGs); For International Medical Graduates (PLAB Route)</t>
+          <t>medical licence UK for doctors 2026; UK medical licence requirements 2026; ukmla syllabus 2026; medical acronyms; medical students</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>UKMLA for International Medical Graduates: Country-by-Country Quick Reference</t>
+          <t>The Medical Training Prioritisation Act 2026: What It Means for IMGs</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-for-international-medical-graduates-country-routes</t>
+          <t>/news#medical-training-prioritisation-act-2026-imgs</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -3892,24 +3892,24 @@
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>Established (25 posts)</t>
+          <t>Established (30 posts)</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>01 July 2026</t>
+          <t>02 July 2026</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>UKMLA for Nigerian doctors</t>
+          <t>UK doctor salary for Indian doctors</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>UKMLA for GP doctors in UK; UKMLA eligibility for Indian doctors; UKMLA fees for doctors 2026; UKMLA for Indian doctors; UKMLA for Pakistani doctors</t>
+          <t>UKMLA for Indian doctors; salary of doctor in UK for Indian; UKMLA for GP doctors in UK; UK doctor salary 2026; UKMLA eligibility for Indian doctors</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -3924,12 +3924,12 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC</t>
+          <t>UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-for-nigerian-doctors</t>
+          <t>/news#uk-doctor-salary-guide-for-indian-doctors</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>Established (25 posts)</t>
+          <t>Established (30 posts)</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
@@ -3956,12 +3956,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>UKMLA for Pakistani doctors</t>
+          <t>UK visa for international doctors</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>UKMLA for GP doctors in UK; UKMLA eligibility for Indian doctors; UKMLA fees for doctors 2026; UKMLA for Indian doctors; UKMLA for Nigerian doctors</t>
+          <t>UKMLA for GP doctors in UK; how to get UK visa for doctors; UK medical registration for international doctors; UKMLA for Indian doctors; UKMLA for Nigerian doctors</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -3976,12 +3976,12 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK</t>
+          <t>UK Visa Guide for International Doctors: Health and Care Worker Visa Explained</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-for-pakistani-doctors</t>
+          <t>/news#uk-visa-guide-for-international-doctors</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>Established (25 posts)</t>
+          <t>Established (30 posts)</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
@@ -4008,12 +4008,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>UKMLA for refugee doctors</t>
+          <t>UK visa salary threshold 2026</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>UKMLA for GP doctors in UK; UKMLA fees for refugee doctors; UKMLA for Indian doctors; UKMLA for Nigerian doctors; UKMLA for Pakistani doctors</t>
+          <t>UK doctor salary 2026; UKMLA fees for doctors 2026; UKMLA syllabus 2026 changes; how to get UK visa for doctors; UKMLA for GP doctors in UK</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -4028,12 +4028,12 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>UKMLA for Refugee Doctors: The GMC Assistance Programme and Fee Support</t>
+          <t>UK Visa Salary Threshold Changes 2026: What Doctors Need to Know</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-for-refugee-doctors</t>
+          <t>/news#uk-visa-salary-threshold-changes-2026-for-doctors</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -4048,24 +4048,24 @@
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>Established (25 posts)</t>
+          <t>Established (30 posts)</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>01 July 2026</t>
+          <t>02 July 2026</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>UKMLA for South African doctors</t>
+          <t>UKMLA AKT test centres</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>UKMLA for GP doctors in UK; GMC registration process for doctors; UKMLA eligibility for Indian doctors; UKMLA fees for doctors 2026; UKMLA for Indian doctors</t>
+          <t>UKMLA AKT; ms akt; What is the UKMLA AKT?; UKMLA AKT test centres in India; UKMLA AKT test centres in Pakistan</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -4075,17 +4075,17 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Eligibility</t>
+          <t>AKT Exam Pattern</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+          <t>UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-for-south-african-doctors</t>
+          <t>/news#ukmla-akt-test-centres-guide</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>Established (25 posts)</t>
+          <t>Established (30 posts)</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
@@ -4112,12 +4112,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>UKMLA for Sri Lankan doctors</t>
+          <t>UKMLA crash course for doctors</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>UKMLA for GP doctors in UK; GMC registration process for doctors; UKMLA eligibility for Indian doctors; UKMLA fees for doctors 2026; UKMLA for Indian doctors</t>
+          <t>UKMLA for GP doctors in UK; UKMLA for Indian doctors; UKMLA for Nigerian doctors; UKMLA for Pakistani doctors; UKMLA for Bangladeshi doctors</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -4127,17 +4127,17 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Eligibility</t>
+          <t>Preparation</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+          <t>UKMLA Crash Course for Doctors: How to Choose the Right Intensive Course</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-for-sri-lankan-doctors</t>
+          <t>/news#ukmla-crash-course-for-doctors</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -4152,24 +4152,24 @@
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>Established (25 posts)</t>
+          <t>Established (30 posts)</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>01 July 2026</t>
+          <t>02 July 2026</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>UKMLA NHS job after exam</t>
+          <t>UKMLA question bank</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>UKMLA exam; what is the UKMLA exam; The Exam; gmc exam; NHS jobs after GMC registration</t>
+          <t>best question bank for UKMLA; best question bank for UKMLA UK students; UKMLA question bank free for students; UKMLA AKT question bank free; UKMLA mock</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -4179,17 +4179,17 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Eligibility</t>
+          <t>Preparation</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
+          <t>UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-to-nhs-job-pathway</t>
+          <t>/news#ukmla-question-bank-and-mock-tests</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -4204,7 +4204,7 @@
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>Established (25 posts)</t>
+          <t>Established (30 posts)</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
@@ -4216,12 +4216,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>UKMLA vs AMC exam comparison</t>
+          <t>UKMLA for Bangladeshi doctors</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>UKMLA exam; what is the UKMLA exam; The Exam; Exam Pattern Comparison; UKMLA vs MCCQE Canada</t>
+          <t>UKMLA for GP doctors in UK; GMC registration process for doctors; UKMLA eligibility for Indian doctors; UKMLA fees for doctors 2026; UKMLA for Indian doctors</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -4231,17 +4231,17 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>UKMLA vs PLAB</t>
+          <t>Eligibility</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>UKMLA vs AMC and MCCQE: Comparing the UK Route to Australia and Canada</t>
+          <t>UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-vs-amc-and-mccqe-comparison</t>
+          <t>/news#ukmla-for-bangladeshi-doctors</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -4256,7 +4256,7 @@
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>Established (25 posts)</t>
+          <t>Established (30 posts)</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
@@ -4268,12 +4268,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>UKMLA vs NEET PG</t>
+          <t>UKMLA for Egyptian doctors</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>UKMLA exam for Indian medical graduates; UKMLA for international medical graduates; UKMLA for Caribbean medical graduates; international medical graduates; UKMLA for Indian doctors</t>
+          <t>UKMLA for GP doctors in UK; GMC registration process for doctors; UKMLA eligibility for Indian doctors; UKMLA fees for doctors 2026; UKMLA for Indian doctors</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -4283,17 +4283,17 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>UKMLA vs PLAB</t>
+          <t>Eligibility</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?</t>
+          <t>UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-vs-neet-pg</t>
+          <t>/news#ukmla-for-egyptian-doctors</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -4308,7 +4308,7 @@
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>Established (25 posts)</t>
+          <t>Established (30 posts)</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -4320,12 +4320,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>UKMLA vs USMLE</t>
+          <t>UKMLA for Filipino doctors</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>UKMLA vs USMLE which is easier; UKMLA exam; what is the UKMLA exam; The Exam; UKMLA vs USMLE cost and difficulty</t>
+          <t>UKMLA for GP doctors in UK; GMC registration process for doctors; UKMLA eligibility for Indian doctors; UKMLA fees for doctors 2026; UKMLA for Indian doctors</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -4335,17 +4335,17 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>UKMLA vs PLAB</t>
+          <t>Eligibility</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
+          <t>UKMLA for Filipino Doctors: Eligibility, Fees and the Route to GMC Registration</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-vs-usmle-comparison</t>
+          <t>/news#ukmla-for-filipino-doctors</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -4360,7 +4360,7 @@
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>Established (25 posts)</t>
+          <t>Established (30 posts)</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
@@ -4372,28 +4372,32 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>Good Medical Practice UKMLA</t>
+          <t>UKMLA for Gulf and Saudi doctors</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>how to practice medicine in UK; medical acronyms; medical students; UKMLA for international medical graduates; UKMLA mock exam practice</t>
+          <t>UKMLA for GP doctors in UK; UKMLA for Saudi / Gulf doctors; UKMLA for Saudi doctors; GMC registration process for doctors; UKMLA eligibility for Indian doctors</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Professional Practice &amp; Safety</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr"/>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Good Medical Practice and the UKMLA: What the GMC Expects</t>
+          <t>UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>/news#good-medical-practice-ukmla</t>
+          <t>/news#ukmla-for-gulf-doctors</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -4408,40 +4412,44 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>Growing (3 posts)</t>
+          <t>Established (30 posts)</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>30 June 2026</t>
+          <t>01 July 2026</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>patient safety UKMLA</t>
+          <t>UKMLA for international medical graduates</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>1. Patient Presentations; The official GMC MLA Content Map listing core patient presentations, conditions, and practical procedures</t>
+          <t>international medical graduates; UKMLA eligibility for international medical graduates; UKMLA for Caribbean medical graduates; Eligibility for International Medical Graduates (IMGs); For International Medical Graduates (PLAB Route)</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Professional Practice &amp; Safety</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr"/>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting</t>
+          <t>UKMLA for International Medical Graduates: Country-by-Country Quick Reference</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>/news#patient-safety-ukmla-prescribing-errors</t>
+          <t>/news#ukmla-for-international-medical-graduates-country-routes</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -4456,40 +4464,44 @@
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>Growing (3 posts)</t>
+          <t>Established (30 posts)</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>30 June 2026</t>
+          <t>01 July 2026</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>safeguarding UKMLA</t>
+          <t>UKMLA for Nigerian doctors</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>ukmla guide; UKMLA pharmacology revision; about ukmla guide; contact ukmla guide; img guide</t>
+          <t>UKMLA for GP doctors in UK; UKMLA eligibility for Indian doctors; UKMLA fees for doctors 2026; UKMLA for Indian doctors; UKMLA for Pakistani doctors</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Professional Practice &amp; Safety</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr"/>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Safeguarding Adults and Children: A UKMLA Revision Guide</t>
+          <t>UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>/news#safeguarding-ukmla-revision</t>
+          <t>/news#ukmla-for-nigerian-doctors</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
@@ -4504,244 +4516,252 @@
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>Growing (3 posts)</t>
+          <t>Established (30 posts)</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>30 June 2026</t>
+          <t>01 July 2026</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="4" t="inlineStr">
-        <is>
-          <t>UKMLA for IMG</t>
-        </is>
-      </c>
-      <c r="B79" s="5" t="inlineStr">
-        <is>
-          <t>UKMLA for international medical graduates; UKMLA eligibility; UKMLA exam for UK medical students; UKMLA eligibility for international medical graduates</t>
-        </is>
-      </c>
-      <c r="C79" s="4" t="inlineStr">
-        <is>
-          <t>Registration &amp; Eligibility</t>
-        </is>
-      </c>
-      <c r="D79" s="4" t="inlineStr">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA for Pakistani doctors</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA for GP doctors in UK; UKMLA eligibility for Indian doctors; UKMLA fees for doctors 2026; UKMLA for Indian doctors; UKMLA for Nigerian doctors</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Eligibility</t>
         </is>
       </c>
-      <c r="E79" s="4" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-for-pakistani-doctors</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>Established (30 posts)</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>01 July 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA for refugee doctors</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA for GP doctors in UK; UKMLA fees for refugee doctors; UKMLA for Indian doctors; UKMLA for Nigerian doctors; UKMLA for Pakistani doctors</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Eligibility</t>
         </is>
       </c>
-      <c r="F79" s="4" t="inlineStr">
-        <is>
-          <t>/eligibility</t>
-        </is>
-      </c>
-      <c r="G79" s="4" t="inlineStr">
-        <is>
-          <t>Informational</t>
-        </is>
-      </c>
-      <c r="H79" s="4" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="I79" s="4" t="inlineStr">
-        <is>
-          <t>Established (8 posts)</t>
-        </is>
-      </c>
-      <c r="J79" s="4" t="inlineStr">
-        <is>
-          <t>N/A (static page)</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="4" t="inlineStr">
-        <is>
-          <t>Fees</t>
-        </is>
-      </c>
-      <c r="B80" s="5" t="inlineStr"/>
-      <c r="C80" s="4" t="inlineStr">
-        <is>
-          <t>Registration &amp; Eligibility</t>
-        </is>
-      </c>
-      <c r="D80" s="4" t="inlineStr">
-        <is>
-          <t>Fees</t>
-        </is>
-      </c>
-      <c r="E80" s="4" t="inlineStr">
-        <is>
-          <t>Fees</t>
-        </is>
-      </c>
-      <c r="F80" s="4" t="inlineStr">
-        <is>
-          <t>/fees</t>
-        </is>
-      </c>
-      <c r="G80" s="4" t="inlineStr">
-        <is>
-          <t>Commercial</t>
-        </is>
-      </c>
-      <c r="H80" s="4" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="I80" s="4" t="inlineStr">
-        <is>
-          <t>Established (8 posts)</t>
-        </is>
-      </c>
-      <c r="J80" s="4" t="inlineStr">
-        <is>
-          <t>N/A (static page)</t>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA for Refugee Doctors: The GMC Assistance Programme and Fee Support</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-for-refugee-doctors</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>Established (30 posts)</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>01 July 2026</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="4" t="inlineStr">
-        <is>
-          <t>UKMLA dates</t>
-        </is>
-      </c>
-      <c r="B81" s="5" t="inlineStr"/>
-      <c r="C81" s="4" t="inlineStr">
-        <is>
-          <t>Registration &amp; Eligibility</t>
-        </is>
-      </c>
-      <c r="D81" s="4" t="inlineStr">
-        <is>
-          <t>Key Dates</t>
-        </is>
-      </c>
-      <c r="E81" s="4" t="inlineStr">
-        <is>
-          <t>Key Dates</t>
-        </is>
-      </c>
-      <c r="F81" s="4" t="inlineStr">
-        <is>
-          <t>/key-dates</t>
-        </is>
-      </c>
-      <c r="G81" s="4" t="inlineStr">
-        <is>
-          <t>Transactional</t>
-        </is>
-      </c>
-      <c r="H81" s="4" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="I81" s="4" t="inlineStr">
-        <is>
-          <t>Established (8 posts)</t>
-        </is>
-      </c>
-      <c r="J81" s="4" t="inlineStr">
-        <is>
-          <t>N/A (static page)</t>
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA for South African doctors</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA for GP doctors in UK; GMC registration process for doctors; UKMLA eligibility for Indian doctors; UKMLA fees for doctors 2026; UKMLA for Indian doctors</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-for-south-african-doctors</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>Established (30 posts)</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>01 July 2026</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="4" t="inlineStr">
-        <is>
-          <t>UKMLA registration</t>
-        </is>
-      </c>
-      <c r="B82" s="5" t="inlineStr">
-        <is>
-          <t>UKMLA booking; English language requirement for UKMLA; UKMLA registration process GMC</t>
-        </is>
-      </c>
-      <c r="C82" s="4" t="inlineStr">
-        <is>
-          <t>Registration &amp; Eligibility</t>
-        </is>
-      </c>
-      <c r="D82" s="4" t="inlineStr">
-        <is>
-          <t>Registration Guide</t>
-        </is>
-      </c>
-      <c r="E82" s="4" t="inlineStr">
-        <is>
-          <t>Registration Guide</t>
-        </is>
-      </c>
-      <c r="F82" s="4" t="inlineStr">
-        <is>
-          <t>/registration-guide</t>
-        </is>
-      </c>
-      <c r="G82" s="4" t="inlineStr">
-        <is>
-          <t>Informational</t>
-        </is>
-      </c>
-      <c r="H82" s="4" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="I82" s="4" t="inlineStr">
-        <is>
-          <t>Established (8 posts)</t>
-        </is>
-      </c>
-      <c r="J82" s="4" t="inlineStr">
-        <is>
-          <t>N/A (static page)</t>
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA for Sri Lankan doctors</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA for GP doctors in UK; GMC registration process for doctors; UKMLA eligibility for Indian doctors; UKMLA fees for doctors 2026; UKMLA for Indian doctors</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-for-sri-lankan-doctors</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>Established (30 posts)</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>01 July 2026</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>UKMLA disability access adjustments</t>
+          <t>UKMLA NHS job after exam</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>ukmla guide; Reasonable Adjustments; reasonable adjustments gmc; about ukmla guide; contact ukmla guide</t>
+          <t>UKMLA exam; what is the UKMLA exam; The Exam; gmc exam; NHS jobs after GMC registration</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Registration &amp; Eligibility</t>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Appeals and Resits</t>
+          <t>Eligibility</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide</t>
+          <t>UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>/news#disability-access-ukmla-guide</t>
+          <t>/news#ukmla-to-nhs-job-pathway</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
@@ -4756,44 +4776,44 @@
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>Established (8 posts)</t>
+          <t>Established (30 posts)</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>30 June 2026</t>
+          <t>01 July 2026</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>UKMLA exemptions for specialist doctors</t>
+          <t>UKMLA vs AMC exam comparison</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>UKMLA for GP doctors in UK; do all doctors need to take UKMLA; is UKMLA required for experienced doctors; UKMLA for Indian doctors; UKMLA for Nigerian doctors</t>
+          <t>UKMLA exam; what is the UKMLA exam; The Exam; Exam Pattern Comparison; UKMLA vs MCCQE Canada</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Registration &amp; Eligibility</t>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Eligibility</t>
+          <t>UKMLA vs PLAB</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs</t>
+          <t>UKMLA vs AMC and MCCQE: Comparing the UK Route to Australia and Canada</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-exemptions-for-specialist-and-gp-doctors</t>
+          <t>/news#ukmla-vs-amc-and-mccqe-comparison</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
@@ -4808,7 +4828,7 @@
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>Established (8 posts)</t>
+          <t>Established (30 posts)</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
@@ -4820,32 +4840,32 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>how to register for PLAB 1</t>
+          <t>UKMLA vs NEET PG</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>PLAB vs UKMLA; plab 1; plab 2; UKMLA vs PLAB; is UKMLA replacing PLAB</t>
+          <t>UKMLA exam for Indian medical graduates; UKMLA for international medical graduates; UKMLA for Caribbean medical graduates; international medical graduates; UKMLA for Indian doctors</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Registration &amp; Eligibility</t>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Registration Guide</t>
+          <t>UKMLA vs PLAB</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>How to Register for PLAB 1: A Step-by-Step Guide for IMGs</t>
+          <t>UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>/news#how-to-register-plab-1</t>
+          <t>/news#ukmla-vs-neet-pg</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
@@ -4860,44 +4880,44 @@
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>Established (8 posts)</t>
+          <t>Established (30 posts)</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>30 June 2026</t>
+          <t>01 July 2026</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>UKMLA eligibility</t>
+          <t>UKMLA vs USMLE</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>Eligibility; UKMLA exam; what is the UKMLA exam; The Exam; UKMLA Eligibility Pathways</t>
+          <t>UKMLA vs USMLE which is easier; UKMLA exam; what is the UKMLA exam; The Exam; UKMLA vs USMLE cost and difficulty</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Registration &amp; Eligibility</t>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Eligibility</t>
+          <t>UKMLA vs PLAB</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>UKMLA Eligibility: Who Can Sit the Exam?</t>
+          <t>UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-eligibility-who-can-sit</t>
+          <t>/news#ukmla-vs-usmle-comparison</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
@@ -4912,44 +4932,44 @@
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>Established (8 posts)</t>
+          <t>Established (30 posts)</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>30 June 2026</t>
+          <t>01 July 2026</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>UKMLA exam fees for IMG</t>
+          <t>GMC fitness to practise</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>UKMLA exam; UKMLA fees; UKMLA for IMG; what is the UKMLA exam; The Exam</t>
+          <t>UKMLA for GP doctors in UK; gmc exam; gmc licensing; gmc Manchester; gmc updates</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Registration &amp; Eligibility</t>
+          <t>Professional Practice &amp; Safety</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Fees</t>
+          <t>Registration Guide</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide</t>
+          <t>GMC Fitness to Practise Explained: What New Doctors Need to Know</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-fees-for-img-2026</t>
+          <t>/news#gmc-fitness-to-practise-explained-for-new-doctors</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
@@ -4964,44 +4984,44 @@
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>Established (8 posts)</t>
+          <t>Established (6 posts)</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>01 July 2026</t>
+          <t>02 July 2026</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>UKMLA fees</t>
+          <t>GMC regulation of physician associates</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>UKMLA fees for doctors 2026; UKMLA cost; UKMLA Fees and Costs 2026; UKMLA exam fees for IMG; UKMLA fees in Indian rupees</t>
+          <t>UKMLA for GP doctors in UK; gmc exam; gmc licensing; gmc Manchester; gmc updates</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Registration &amp; Eligibility</t>
+          <t>Professional Practice &amp; Safety</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Fees</t>
+          <t>Registration Guide</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>UKMLA Fees: The Complete 2026 Cost Breakdown</t>
+          <t>GMC Regulation of Physician Associates: What Doctors Need to Know</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-fees-explained</t>
+          <t>/news#gmc-regulation-of-physician-associates-what-doctors-need-to-know</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
@@ -5016,49 +5036,45 @@
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>Established (8 posts)</t>
+          <t>Established (6 posts)</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>30 June 2026</t>
+          <t>02 July 2026</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>UKMLA key dates</t>
+          <t>Good Medical Practice UKMLA</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>UKMLA dates; Key Dates; Key Dates &amp; Timeline; UKMLA exam dates 2026; UKMLA exam dates and fees</t>
+          <t>how to practice medicine in UK; medical acronyms; medical students; UKMLA for international medical graduates; UKMLA mock exam practice</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Registration &amp; Eligibility</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
-        <is>
-          <t>Key Dates</t>
-        </is>
-      </c>
+          <t>Professional Practice &amp; Safety</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr"/>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>UKMLA Key Dates and Sitting Schedule: What to Know</t>
+          <t>Good Medical Practice and the UKMLA: What the GMC Expects</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-key-dates-sitting-schedule</t>
+          <t>/news#good-medical-practice-ukmla</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>Transactional</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -5068,7 +5084,7 @@
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>Established (8 posts)</t>
+          <t>Established (6 posts)</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
@@ -5080,309 +5096,1645 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
+          <t>patient safety UKMLA</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t>1. Patient Presentations; The official GMC MLA Content Map listing core patient presentations, conditions, and practical procedures</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>Professional Practice &amp; Safety</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr"/>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>/news#patient-safety-ukmla-prescribing-errors</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>Established (6 posts)</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>30 June 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>safeguarding UKMLA</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t>ukmla guide; UKMLA pharmacology revision; about ukmla guide; contact ukmla guide; img guide</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>Professional Practice &amp; Safety</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr"/>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>Safeguarding Adults and Children: A UKMLA Revision Guide</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>/news#safeguarding-ukmla-revision</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>Established (6 posts)</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>30 June 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>GMC revalidation process</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA registration process GMC; GMC registration process for doctors; GMC EPIC verification process; UKMLA for GP doctors in UK; gmc exam</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Professional Practice &amp; Safety</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>Registration Guide</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>The GMC Revalidation Process, Explained for New Doctors</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>/news#gmc-revalidation-process-explained</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>Established (6 posts)</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>02 July 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="4" t="inlineStr">
+        <is>
+          <t>UKMLA for IMG</t>
+        </is>
+      </c>
+      <c r="B93" s="5" t="inlineStr">
+        <is>
+          <t>UKMLA for international medical graduates; UKMLA eligibility; UKMLA exam for UK medical students; UKMLA eligibility for international medical graduates</t>
+        </is>
+      </c>
+      <c r="C93" s="4" t="inlineStr">
+        <is>
+          <t>Registration &amp; Eligibility</t>
+        </is>
+      </c>
+      <c r="D93" s="4" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
+      <c r="E93" s="4" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
+      <c r="F93" s="4" t="inlineStr">
+        <is>
+          <t>/eligibility</t>
+        </is>
+      </c>
+      <c r="G93" s="4" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H93" s="4" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I93" s="4" t="inlineStr">
+        <is>
+          <t>Established (19 posts)</t>
+        </is>
+      </c>
+      <c r="J93" s="4" t="inlineStr">
+        <is>
+          <t>N/A (static page)</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="4" t="inlineStr">
+        <is>
+          <t>Fees</t>
+        </is>
+      </c>
+      <c r="B94" s="5" t="inlineStr"/>
+      <c r="C94" s="4" t="inlineStr">
+        <is>
+          <t>Registration &amp; Eligibility</t>
+        </is>
+      </c>
+      <c r="D94" s="4" t="inlineStr">
+        <is>
+          <t>Fees</t>
+        </is>
+      </c>
+      <c r="E94" s="4" t="inlineStr">
+        <is>
+          <t>Fees</t>
+        </is>
+      </c>
+      <c r="F94" s="4" t="inlineStr">
+        <is>
+          <t>/fees</t>
+        </is>
+      </c>
+      <c r="G94" s="4" t="inlineStr">
+        <is>
+          <t>Commercial</t>
+        </is>
+      </c>
+      <c r="H94" s="4" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I94" s="4" t="inlineStr">
+        <is>
+          <t>Established (19 posts)</t>
+        </is>
+      </c>
+      <c r="J94" s="4" t="inlineStr">
+        <is>
+          <t>N/A (static page)</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="4" t="inlineStr">
+        <is>
+          <t>UKMLA dates</t>
+        </is>
+      </c>
+      <c r="B95" s="5" t="inlineStr"/>
+      <c r="C95" s="4" t="inlineStr">
+        <is>
+          <t>Registration &amp; Eligibility</t>
+        </is>
+      </c>
+      <c r="D95" s="4" t="inlineStr">
+        <is>
+          <t>Key Dates</t>
+        </is>
+      </c>
+      <c r="E95" s="4" t="inlineStr">
+        <is>
+          <t>Key Dates</t>
+        </is>
+      </c>
+      <c r="F95" s="4" t="inlineStr">
+        <is>
+          <t>/key-dates</t>
+        </is>
+      </c>
+      <c r="G95" s="4" t="inlineStr">
+        <is>
+          <t>Transactional</t>
+        </is>
+      </c>
+      <c r="H95" s="4" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I95" s="4" t="inlineStr">
+        <is>
+          <t>Established (19 posts)</t>
+        </is>
+      </c>
+      <c r="J95" s="4" t="inlineStr">
+        <is>
+          <t>N/A (static page)</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="4" t="inlineStr">
+        <is>
+          <t>UKMLA registration</t>
+        </is>
+      </c>
+      <c r="B96" s="5" t="inlineStr">
+        <is>
+          <t>UKMLA booking; English language requirement for UKMLA; UKMLA registration process GMC</t>
+        </is>
+      </c>
+      <c r="C96" s="4" t="inlineStr">
+        <is>
+          <t>Registration &amp; Eligibility</t>
+        </is>
+      </c>
+      <c r="D96" s="4" t="inlineStr">
+        <is>
+          <t>Registration Guide</t>
+        </is>
+      </c>
+      <c r="E96" s="4" t="inlineStr">
+        <is>
+          <t>Registration Guide</t>
+        </is>
+      </c>
+      <c r="F96" s="4" t="inlineStr">
+        <is>
+          <t>/registration-guide</t>
+        </is>
+      </c>
+      <c r="G96" s="4" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H96" s="4" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I96" s="4" t="inlineStr">
+        <is>
+          <t>Established (19 posts)</t>
+        </is>
+      </c>
+      <c r="J96" s="4" t="inlineStr">
+        <is>
+          <t>N/A (static page)</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA disability access adjustments</t>
+        </is>
+      </c>
+      <c r="B97" s="3" t="inlineStr">
+        <is>
+          <t>ukmla guide; Reasonable Adjustments; reasonable adjustments gmc; about ukmla guide; contact ukmla guide</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>Registration &amp; Eligibility</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>Appeals and Resits</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>/news#disability-access-ukmla-guide</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>Established (19 posts)</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>30 June 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA exemptions for specialist doctors</t>
+        </is>
+      </c>
+      <c r="B98" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA for GP doctors in UK; do all doctors need to take UKMLA; is UKMLA required for experienced doctors; UKMLA for Indian doctors; UKMLA for Nigerian doctors</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>Registration &amp; Eligibility</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-exemptions-for-specialist-and-gp-doctors</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>Established (19 posts)</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>01 July 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>GMC English language exemption</t>
+        </is>
+      </c>
+      <c r="B99" s="3" t="inlineStr">
+        <is>
+          <t>English language requirement for UKMLA; OET vs IELTS for GMC registration; UKMLA exemption for specialists; gmc exam; gmc licensing</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>Registration &amp; Eligibility</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>GMC English Language Exemption: Do You Need to Sit IELTS or OET?</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>/news#gmc-english-language-exemption-for-imgs</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>Established (19 posts)</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>02 July 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>GMC Order reform 2026</t>
+        </is>
+      </c>
+      <c r="B100" s="3" t="inlineStr">
+        <is>
+          <t>cost of GMC registration 2026; gmc exam; gmc licensing; gmc Manchester; gmc updates</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>Registration &amp; Eligibility</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>Registration Guide</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>GMC Order Reform 2026: The Consultation on Protected Medical Titles</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>/news#gmc-order-reform-2026-protected-medical-titles</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>Established (19 posts)</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>02 July 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>GMC registration refund policy</t>
+        </is>
+      </c>
+      <c r="B101" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA registration; UKMLA GMC registration for graduates; UKMLA vs specialist registration GMC; UKMLA registration process GMC; gmc registration guide</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>Registration &amp; Eligibility</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>Fees</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>GMC Registration Refund Policy: When You Can (and Can't) Get Your Fee Back</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>/news#gmc-registration-refund-policy</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>Established (19 posts)</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>02 July 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>GMC Welcome to UK Practice</t>
+        </is>
+      </c>
+      <c r="B102" s="3" t="inlineStr">
+        <is>
+          <t>how to practice medicine in UK; UKMLA practice questions free; gmc exam; gmc licensing; gmc Manchester</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>Registration &amp; Eligibility</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>Registration Guide</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>GMC Welcome to UK Practice: A Guide to the Free Induction Workshop</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>/news#gmc-welcome-to-uk-practice-induction-guide</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>Established (19 posts)</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>02 July 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>how long does GMC registration take</t>
+        </is>
+      </c>
+      <c r="B103" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA registration; GMC registration timeline how long; UKMLA GMC registration for graduates; UKMLA vs specialist registration GMC; UKMLA registration process GMC</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>Registration &amp; Eligibility</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Registration Guide</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>How Long Does GMC Registration Take? A Realistic Timeline</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>/news#how-long-does-gmc-registration-take</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>Established (19 posts)</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>02 July 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>how to register for PLAB 1</t>
+        </is>
+      </c>
+      <c r="B104" s="3" t="inlineStr">
+        <is>
+          <t>PLAB vs UKMLA; plab 1; plab 2; UKMLA vs PLAB; is UKMLA replacing PLAB</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>Registration &amp; Eligibility</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>Registration Guide</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>How to Register for PLAB 1: A Step-by-Step Guide for IMGs</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>/news#how-to-register-plab-1</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>Established (19 posts)</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>30 June 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>locally employed doctors GMC registration</t>
+        </is>
+      </c>
+      <c r="B105" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA for GP doctors in UK; UKMLA registration; UKMLA vs specialist registration GMC; GMC registration process for doctors; UKMLA GMC registration for graduates</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>Registration &amp; Eligibility</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>Registration Guide</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>Locally Employed Doctors: The Route to Full and Specialist GMC Registration</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>/news#locally-employed-doctors-route-to-gmc-registration</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>Established (19 posts)</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr">
+        <is>
+          <t>02 July 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>OET vs IELTS for GMC registration</t>
+        </is>
+      </c>
+      <c r="B106" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA registration; UKMLA GMC registration for graduates; UKMLA OET or IELTS requirement; UKMLA vs specialist registration GMC; UKMLA registration process GMC</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>Registration &amp; Eligibility</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>OET vs IELTS for GMC Registration: Which Should You Take?</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>/news#oet-vs-ielts-for-gmc-registration-comparison</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>Established (19 posts)</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr">
+        <is>
+          <t>02 July 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>internship requirement for GMC registration</t>
+        </is>
+      </c>
+      <c r="B107" s="3" t="inlineStr">
+        <is>
+          <t>internship requirement for GMC; UKMLA registration; UKMLA GMC registration for graduates; UKMLA vs specialist registration GMC; UKMLA registration process GMC</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>Registration &amp; Eligibility</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>The Internship Requirement for GMC Registration, Explained</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>/news#internship-requirement-for-gmc-registration</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>Established (19 posts)</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t>02 July 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA exam booking process</t>
+        </is>
+      </c>
+      <c r="B108" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA booking; UKMLA exam; what is the UKMLA exam; The Exam; UKMLA booking process for students</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>Registration &amp; Eligibility</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>Registration Guide</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>The UKMLA Exam Booking Process: A Step-by-Step Walkthrough</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-exam-booking-process-gmc-online</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>Established (19 posts)</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="inlineStr">
+        <is>
+          <t>02 July 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>types of GMC registration</t>
+        </is>
+      </c>
+      <c r="B109" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA registration; UKMLA vs specialist registration GMC; UKMLA GMC registration for graduates; UKMLA registration process GMC; gmc registration guide</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>Registration &amp; Eligibility</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>Registration Guide</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>Types of GMC Registration Explained: Provisional, Full, Specialist and GP</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>/news#types-of-gmc-registration-explained</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>Established (19 posts)</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="inlineStr">
+        <is>
+          <t>02 July 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA eligibility</t>
+        </is>
+      </c>
+      <c r="B110" s="3" t="inlineStr">
+        <is>
+          <t>Eligibility; UKMLA exam; what is the UKMLA exam; The Exam; UKMLA Eligibility Pathways</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>Registration &amp; Eligibility</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA Eligibility: Who Can Sit the Exam?</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-eligibility-who-can-sit</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>Established (19 posts)</t>
+        </is>
+      </c>
+      <c r="J110" s="2" t="inlineStr">
+        <is>
+          <t>30 June 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA exam fees for IMG</t>
+        </is>
+      </c>
+      <c r="B111" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA exam; UKMLA fees; UKMLA for IMG; what is the UKMLA exam; The Exam</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>Registration &amp; Eligibility</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>Fees</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-fees-for-img-2026</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t>Established (19 posts)</t>
+        </is>
+      </c>
+      <c r="J111" s="2" t="inlineStr">
+        <is>
+          <t>01 July 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA fees</t>
+        </is>
+      </c>
+      <c r="B112" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA fees for doctors 2026; UKMLA cost; UKMLA Fees and Costs 2026; UKMLA exam fees for IMG; UKMLA fees in Indian rupees</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>Registration &amp; Eligibility</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>Fees</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA Fees: The Complete 2026 Cost Breakdown</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-fees-explained</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="inlineStr">
+        <is>
+          <t>Established (19 posts)</t>
+        </is>
+      </c>
+      <c r="J112" s="2" t="inlineStr">
+        <is>
+          <t>30 June 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA key dates</t>
+        </is>
+      </c>
+      <c r="B113" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA dates; Key Dates; Key Dates &amp; Timeline; UKMLA exam dates 2026; UKMLA exam dates and fees</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>Registration &amp; Eligibility</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>Key Dates</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA Key Dates and Sitting Schedule: What to Know</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-key-dates-sitting-schedule</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>Transactional</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t>Established (19 posts)</t>
+        </is>
+      </c>
+      <c r="J113" s="2" t="inlineStr">
+        <is>
+          <t>30 June 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
           <t>UKMLA resits</t>
         </is>
       </c>
-      <c r="B90" s="3" t="inlineStr">
+      <c r="B114" s="3" t="inlineStr">
         <is>
           <t>Appeals &amp; Resits; UKMLA Appeals, Resits &amp; Reasonable Adjustments; Appeals, Resits &amp; Reasonable Adjustments; Attempt Limits and Retake Rules; plab attempt limits</t>
         </is>
       </c>
-      <c r="C90" s="2" t="inlineStr">
+      <c r="C114" s="2" t="inlineStr">
         <is>
           <t>Registration &amp; Eligibility</t>
         </is>
       </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>Appeals and Resits</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>UKMLA Resits: Rules, Limits, and How to Bounce Back</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="F114" s="2" t="inlineStr">
         <is>
           <t>/news#ukmla-resits-rules-limits</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr">
-        <is>
-          <t>Informational</t>
-        </is>
-      </c>
-      <c r="H90" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="I90" s="2" t="inlineStr">
-        <is>
-          <t>Established (8 posts)</t>
-        </is>
-      </c>
-      <c r="J90" s="2" t="inlineStr">
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="inlineStr">
+        <is>
+          <t>Established (19 posts)</t>
+        </is>
+      </c>
+      <c r="J114" s="2" t="inlineStr">
         <is>
           <t>30 June 2026</t>
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="4" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>primary medical qualification GMC accepted</t>
+        </is>
+      </c>
+      <c r="B115" s="3" t="inlineStr">
+        <is>
+          <t>gmc exam; gmc licensing; gmc Manchester; gmc updates; medical acronyms</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>Registration &amp; Eligibility</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>Which Medical Qualifications Does the GMC Accept? PMQ Recognition Explained</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>/news#gmc-recognised-primary-medical-qualifications</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="inlineStr">
+        <is>
+          <t>Established (19 posts)</t>
+        </is>
+      </c>
+      <c r="J115" s="2" t="inlineStr">
+        <is>
+          <t>02 July 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="4" t="inlineStr">
         <is>
           <t>Appeals and Resits</t>
         </is>
       </c>
-      <c r="B91" s="5" t="inlineStr"/>
-      <c r="C91" s="4" t="inlineStr">
+      <c r="B116" s="5" t="inlineStr"/>
+      <c r="C116" s="4" t="inlineStr">
         <is>
           <t>Results &amp; Scoring</t>
         </is>
       </c>
-      <c r="D91" s="4" t="inlineStr">
+      <c r="D116" s="4" t="inlineStr">
         <is>
           <t>Appeals and Resits</t>
         </is>
       </c>
-      <c r="E91" s="4" t="inlineStr">
+      <c r="E116" s="4" t="inlineStr">
         <is>
           <t>Appeals and Resits</t>
         </is>
       </c>
-      <c r="F91" s="4" t="inlineStr">
+      <c r="F116" s="4" t="inlineStr">
         <is>
           <t>/appeals-and-resits</t>
         </is>
       </c>
-      <c r="G91" s="4" t="inlineStr">
-        <is>
-          <t>Informational</t>
-        </is>
-      </c>
-      <c r="H91" s="4" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="I91" s="4" t="inlineStr">
-        <is>
-          <t>Growing (2 posts)</t>
-        </is>
-      </c>
-      <c r="J91" s="4" t="inlineStr">
+      <c r="G116" s="4" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H116" s="4" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I116" s="4" t="inlineStr">
+        <is>
+          <t>Growing (3 posts)</t>
+        </is>
+      </c>
+      <c r="J116" s="4" t="inlineStr">
         <is>
           <t>N/A (static page)</t>
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="4" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="4" t="inlineStr">
         <is>
           <t>UKMLA results</t>
         </is>
       </c>
-      <c r="B92" s="5" t="inlineStr">
+      <c r="B117" s="5" t="inlineStr">
         <is>
           <t>UKMLA pass mark; UKMLA pass rate for IMG; UKMLA results release date</t>
         </is>
       </c>
-      <c r="C92" s="4" t="inlineStr">
+      <c r="C117" s="4" t="inlineStr">
         <is>
           <t>Results &amp; Scoring</t>
         </is>
       </c>
-      <c r="D92" s="4" t="inlineStr">
+      <c r="D117" s="4" t="inlineStr">
         <is>
           <t>Results and Scoring</t>
         </is>
       </c>
-      <c r="E92" s="4" t="inlineStr">
+      <c r="E117" s="4" t="inlineStr">
         <is>
           <t>Results and Scoring</t>
         </is>
       </c>
-      <c r="F92" s="4" t="inlineStr">
+      <c r="F117" s="4" t="inlineStr">
         <is>
           <t>/results-and-scoring</t>
         </is>
       </c>
-      <c r="G92" s="4" t="inlineStr">
-        <is>
-          <t>Informational</t>
-        </is>
-      </c>
-      <c r="H92" s="4" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="I92" s="4" t="inlineStr">
-        <is>
-          <t>Growing (2 posts)</t>
-        </is>
-      </c>
-      <c r="J92" s="4" t="inlineStr">
+      <c r="G117" s="4" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H117" s="4" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I117" s="4" t="inlineStr">
+        <is>
+          <t>Growing (3 posts)</t>
+        </is>
+      </c>
+      <c r="J117" s="4" t="inlineStr">
         <is>
           <t>N/A (static page)</t>
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>UKMLA AKT pass mark</t>
         </is>
       </c>
-      <c r="B93" s="3" t="inlineStr">
+      <c r="B118" s="3" t="inlineStr">
         <is>
           <t>UKMLA AKT; UKMLA pass mark; how to pass ukmla; ms akt; What is the UKMLA AKT?</t>
         </is>
       </c>
-      <c r="C93" s="2" t="inlineStr">
+      <c r="C118" s="2" t="inlineStr">
         <is>
           <t>Results &amp; Scoring</t>
         </is>
       </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="D118" s="2" t="inlineStr">
         <is>
           <t>Results and Scoring</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E118" s="2" t="inlineStr">
         <is>
           <t>UKMLA AKT Pass Mark and Pass Rate Explained</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F118" s="2" t="inlineStr">
         <is>
           <t>/news#ukmla-akt-pass-mark-and-pass-rate-explained</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr">
-        <is>
-          <t>Informational</t>
-        </is>
-      </c>
-      <c r="H93" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="I93" s="2" t="inlineStr">
-        <is>
-          <t>Growing (2 posts)</t>
-        </is>
-      </c>
-      <c r="J93" s="2" t="inlineStr">
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="inlineStr">
+        <is>
+          <t>Growing (3 posts)</t>
+        </is>
+      </c>
+      <c r="J118" s="2" t="inlineStr">
         <is>
           <t>01 July 2026</t>
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>UKMLA results feedback</t>
         </is>
       </c>
-      <c r="B94" s="3" t="inlineStr">
+      <c r="B119" s="3" t="inlineStr">
         <is>
           <t>UKMLA results; Results &amp; Data; Results &amp; Scoring; UKMLA results timeline 2026; UKMLA results release date</t>
         </is>
       </c>
-      <c r="C94" s="2" t="inlineStr">
+      <c r="C119" s="2" t="inlineStr">
         <is>
           <t>Results &amp; Scoring</t>
         </is>
       </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>Results and Scoring</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>UKMLA Results: How to Interpret Your Feedback Report</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="F119" s="2" t="inlineStr">
         <is>
           <t>/news#ukmla-results-feedback-report</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr">
-        <is>
-          <t>Informational</t>
-        </is>
-      </c>
-      <c r="H94" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="I94" s="2" t="inlineStr">
-        <is>
-          <t>Growing (2 posts)</t>
-        </is>
-      </c>
-      <c r="J94" s="2" t="inlineStr">
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I119" s="2" t="inlineStr">
+        <is>
+          <t>Growing (3 posts)</t>
+        </is>
+      </c>
+      <c r="J119" s="2" t="inlineStr">
         <is>
           <t>30 June 2026</t>
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>what happens if you fail UKMLA</t>
+        </is>
+      </c>
+      <c r="B120" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA fail foundation year impact; UKMLA and foundation year application; foundation year vs specialty training IMG; how to prepare for UKMLA final year; UKMLA for academic foundation programme</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>Results &amp; Scoring</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>Appeals and Resits</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>What Happens If You Fail the UKMLA? The Impact on Your Foundation Year</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>/news#what-happens-if-you-fail-ukmla-foundation-year-impact</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="inlineStr">
+        <is>
+          <t>Growing (3 posts)</t>
+        </is>
+      </c>
+      <c r="J120" s="2" t="inlineStr">
+        <is>
+          <t>02 July 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>Foundation Programme after UKMLA</t>
         </is>
       </c>
-      <c r="B95" s="3" t="inlineStr">
+      <c r="B121" s="3" t="inlineStr">
         <is>
           <t>UKMLA for academic foundation programme; UKMLA after MBBS; UKMLA after MBBS in India; UKMLA and foundation year application; UKMLA fail foundation year impact</t>
         </is>
       </c>
-      <c r="C95" s="2" t="inlineStr">
+      <c r="C121" s="2" t="inlineStr">
         <is>
           <t>Uncategorised</t>
         </is>
       </c>
-      <c r="D95" s="2" t="inlineStr"/>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="D121" s="2" t="inlineStr"/>
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>Understanding the Foundation Programme: What Awaits After the UKMLA</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
+      <c r="F121" s="2" t="inlineStr">
         <is>
           <t>/news#foundation-programme-after-ukmla</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr">
-        <is>
-          <t>Informational</t>
-        </is>
-      </c>
-      <c r="H95" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="I95" s="2" t="inlineStr">
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I121" s="2" t="inlineStr">
         <is>
           <t>Needs More Support (1 post)</t>
         </is>
       </c>
-      <c r="J95" s="2" t="inlineStr">
+      <c r="J121" s="2" t="inlineStr">
         <is>
           <t>30 June 2026</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J95"/>
+  <autoFilter ref="A1:J121"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5434,7 +6786,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>81</v>
+        <v>107</v>
       </c>
     </row>
     <row r="6">
@@ -5491,7 +6843,7 @@
       <c r="A12" s="9" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons: 25 posts — Established (25 posts)</t>
+          <t>IMG Country Routes &amp; Global Comparisons: 30 posts — Established (30 posts)</t>
         </is>
       </c>
     </row>
@@ -5507,7 +6859,7 @@
       <c r="A14" s="9" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Registration &amp; Eligibility: 8 posts — Established (8 posts)</t>
+          <t>Registration &amp; Eligibility: 19 posts — Established (19 posts)</t>
         </is>
       </c>
     </row>
@@ -5515,7 +6867,7 @@
       <c r="A15" s="9" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Core UKMLA Overview: 7 posts — Established (7 posts)</t>
+          <t>Core UKMLA Overview: 11 posts — Established (11 posts)</t>
         </is>
       </c>
     </row>
@@ -5523,7 +6875,7 @@
       <c r="A16" s="9" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Exam Format: 6 posts — Established (6 posts)</t>
+          <t>Exam Preparation: 8 posts — Established (8 posts)</t>
         </is>
       </c>
     </row>
@@ -5531,7 +6883,7 @@
       <c r="A17" s="9" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Exam Preparation: 6 posts — Established (6 posts)</t>
+          <t>Exam Format: 6 posts — Established (6 posts)</t>
         </is>
       </c>
     </row>
@@ -5539,7 +6891,7 @@
       <c r="A18" s="9" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Professional Practice &amp; Safety: 3 posts — Growing (3 posts)</t>
+          <t>Professional Practice &amp; Safety: 6 posts — Established (6 posts)</t>
         </is>
       </c>
     </row>
@@ -5547,7 +6899,7 @@
       <c r="A19" s="9" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Results &amp; Scoring: 2 posts — Growing (2 posts)</t>
+          <t>Results &amp; Scoring: 3 posts — Growing (3 posts)</t>
         </is>
       </c>
     </row>

--- a/UKMLA_Keyword_Cluster_Sheet.xlsx
+++ b/UKMLA_Keyword_Cluster_Sheet.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Keyword Cluster Sheet'!$A$1:$J$121</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Keyword Cluster Sheet'!$A$1:$J$171</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -470,7 +470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J121"/>
+  <dimension ref="A1:J171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -540,12 +540,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>data interpretation AKT UKMLA</t>
+          <t>anaesthesia UKMLA</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>UKMLA AKT; ms akt; What is the UKMLA AKT?; AKT exam; AKT Details</t>
+          <t>ukmla guide; how to become a doctor in UK; how to practice medicine in UK; about ukmla guide; contact ukmla guide</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -560,12 +560,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Blood Tests and Investigations in the AKT: Data Interpretation Guide</t>
+          <t>Anaesthesia and Perioperative Medicine in the UKMLA: A Foundation Doctor's Guide</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>/news#blood-tests-data-interpretation-akt</t>
+          <t>/news#anaesthesia-and-perioperative-medicine-ukmla</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -580,24 +580,24 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Established (23 posts)</t>
+          <t>Established (46 posts)</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>30 June 2026</t>
+          <t>02 July 2026</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>cardiology UKMLA AKT</t>
+          <t>data interpretation AKT UKMLA</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>UKMLA AKT; ms akt; What is the UKMLA AKT?; UKMLA AKT high yield topics; AKT exam</t>
+          <t>UKMLA AKT; ms akt; What is the UKMLA AKT?; AKT exam; AKT Details</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -612,17 +612,17 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Cardiology High-Yield Topics for the UKMLA AKT</t>
+          <t>Blood Tests and Investigations in the AKT: Data Interpretation Guide</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>/news#cardiology-ukmla-akt-revision</t>
+          <t>/news#blood-tests-data-interpretation-akt</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -632,7 +632,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Established (23 posts)</t>
+          <t>Established (46 posts)</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -644,12 +644,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>dermatology UKMLA</t>
+          <t>cardiology UKMLA AKT</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>UKMLA Key Dates and Sitting Schedule: What to Know; NICE Guidelines and the AKT: What You Actually Need to Know; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
+          <t>UKMLA AKT; ms akt; What is the UKMLA AKT?; UKMLA AKT high yield topics; AKT exam</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -664,17 +664,17 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Dermatology in the UKMLA: Rashes, Lesions, and What to Know</t>
+          <t>Cardiology High-Yield Topics for the UKMLA AKT</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>/news#dermatology-ukmla-revision</t>
+          <t>/news#cardiology-ukmla-akt-revision</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Established (23 posts)</t>
+          <t>Established (46 posts)</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -696,12 +696,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>ECG interpretation UKMLA</t>
+          <t>care of the elderly UKMLA</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Radiology and Imaging Interpretation in the AKT; Blood Tests and Investigations in the AKT: Data Interpretation Guide</t>
+          <t>Palliative Care and End-of-Life Decisions in the UKMLA; Social Determinants of Health in the UKMLA: Person-Centred Care; Mental Health Presentations in the UKMLA: What to Revise; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -716,12 +716,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>ECG Interpretation for the UKMLA: The Findings You Must Recognise</t>
+          <t>Care of the Elderly and Frailty in the UKMLA: What to Revise</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>/news#ecg-interpretation-ukmla</t>
+          <t>/news#care-of-the-elderly-and-frailty-ukmla</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -736,24 +736,24 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Established (23 posts)</t>
+          <t>Established (46 posts)</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>30 June 2026</t>
+          <t>02 July 2026</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>emergency medicine UKMLA</t>
+          <t>chronic pain UKMLA</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>how to practice medicine in UK; practising medicine in UK requirements; Respiratory Medicine for the UKMLA: What to Focus On; how to practice medicine in UK from Philippines; 1. Patient Presentations</t>
+          <t>Mental Health Presentations in the UKMLA: What to Revise; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Time Management in the UKMLA AKT: Strategies That Work</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Emergency Medicine and Acute Presentations in the UKMLA</t>
+          <t>Chronic Pain Management in the UKMLA: What to Revise</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>/news#emergency-medicine-ukmla-revision</t>
+          <t>/news#chronic-pain-management-ukmla</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -788,24 +788,24 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Established (23 posts)</t>
+          <t>Established (46 posts)</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>30 June 2026</t>
+          <t>02 July 2026</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>endocrinology diabetes UKMLA</t>
+          <t>consent and mental capacity UKMLA</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>ukmla guide; UKMLA pharmacology revision; about ukmla guide; contact ukmla guide; img guide</t>
+          <t>ukmla guide; What Is the UKMLA? A Complete Beginner's Guide; about ukmla guide; contact ukmla guide; img guide</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -820,12 +820,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide</t>
+          <t>Consent and Mental Capacity in the UKMLA: The Complete Guide</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>/news#endocrinology-diabetes-ukmla-revision</t>
+          <t>/news#consent-and-mental-capacity-ukmla</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -840,24 +840,24 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>Established (23 posts)</t>
+          <t>Established (46 posts)</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>30 June 2026</t>
+          <t>02 July 2026</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>gastroenterology UKMLA AKT</t>
+          <t>contraception UKMLA</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>UKMLA AKT; ms akt; What is the UKMLA AKT?; AKT exam; AKT Details</t>
+          <t>ukmla guide; What Is the UKMLA? A Complete Beginner's Guide; UKMLA pharmacology revision; about ukmla guide; contact ukmla guide</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -872,12 +872,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Gastroenterology and Hepatology in the UKMLA AKT</t>
+          <t>Contraception Counselling in the UKMLA: A Complete Revision Guide</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>/news#gastroenterology-ukmla-akt-revision</t>
+          <t>/news#contraception-counselling-ukmla</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -892,24 +892,24 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Established (23 posts)</t>
+          <t>Established (46 posts)</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>30 June 2026</t>
+          <t>02 July 2026</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>haematology UKMLA</t>
+          <t>critical care UKMLA</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Blood Tests and Investigations in the AKT: Data Interpretation Guide</t>
+          <t>1. Patient Presentations; Palliative Care and End-of-Life Decisions in the UKMLA; Social Determinants of Health in the UKMLA: Person-Centred Care; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; The official GMC MLA Content Map listing core patient presentations, conditions, and practical procedures</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -924,12 +924,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers</t>
+          <t>Critical Care Basics in the UKMLA: Recognising the Deteriorating Patient</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>/news#haematology-ukmla-revision</t>
+          <t>/news#critical-care-and-intensive-care-basics-ukmla</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -944,24 +944,24 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Established (23 posts)</t>
+          <t>Established (46 posts)</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>30 June 2026</t>
+          <t>02 July 2026</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>infection microbiology UKMLA</t>
+          <t>dermatology UKMLA</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>More than 75 comprehensive answers regarding UKMLA, PLAB transition, eligibility, and formatting</t>
+          <t>UKMLA Key Dates and Sitting Schedule: What to Know; NICE Guidelines and the AKT: What You Actually Need to Know; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -976,12 +976,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More</t>
+          <t>Dermatology in the UKMLA: Rashes, Lesions, and What to Know</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>/news#infection-microbiology-ukmla-revision</t>
+          <t>/news#dermatology-ukmla-revision</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Established (23 posts)</t>
+          <t>Established (46 posts)</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>mental health UKMLA</t>
+          <t>domestic abuse UKMLA</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>1. Patient Presentations; Social Determinants of Health in the UKMLA: Person-Centred Care; Emergency Medicine and Acute Presentations in the UKMLA; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
+          <t>Safeguarding Adults and Children: A UKMLA Revision Guide</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Mental Health Presentations in the UKMLA: What to Revise</t>
+          <t>Domestic Abuse and Adult Safeguarding in the UKMLA</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>/news#mental-health-ukmla-revision</t>
+          <t>/news#domestic-abuse-and-safeguarding-adults-ukmla</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1048,24 +1048,24 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>Established (23 posts)</t>
+          <t>Established (46 posts)</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>30 June 2026</t>
+          <t>02 July 2026</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>NICE guidelines AKT</t>
+          <t>ECG interpretation UKMLA</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>UKMLA AKT; ms akt; What is the UKMLA AKT?; UKMLA NICE guidelines topics; UKMLA NICE guidelines questions</t>
+          <t>Radiology and Imaging Interpretation in the AKT; Blood Tests and Investigations in the AKT: Data Interpretation Guide</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1080,12 +1080,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>NICE Guidelines and the AKT: What You Actually Need to Know</t>
+          <t>ECG Interpretation for the UKMLA: The Findings You Must Recognise</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>/news#nice-guidelines-akt-revision</t>
+          <t>/news#ecg-interpretation-ukmla</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1100,7 +1100,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Established (23 posts)</t>
+          <t>Established (46 posts)</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1112,10 +1112,14 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>nephrology UKMLA AKI CKD</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr"/>
+          <t>early pregnancy complications UKMLA</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>ukmla guide; about ukmla guide; contact ukmla guide; img guide; Preparation Guide</t>
+        </is>
+      </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
           <t>Clinical Systems Revision</t>
@@ -1128,12 +1132,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Nephrology in the UKMLA: AKI, CKD, and Electrolyte Disorders</t>
+          <t>Early Pregnancy Complications in the UKMLA: The Essential Guide</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>/news#nephrology-ukmla-revision</t>
+          <t>/news#early-pregnancy-complications-ukmla</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1148,24 +1152,24 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>Established (23 posts)</t>
+          <t>Established (46 posts)</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>30 June 2026</t>
+          <t>02 July 2026</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>neurology UKMLA</t>
+          <t>emergency medicine UKMLA</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>UKMLA AKT high yield topics; UKMLA revision notes tips; Cardiology High-Yield Topics for the UKMLA AKT; UKMLA pharmacology revision; UKMLA CPSA preparation tips</t>
+          <t>how to practice medicine in UK; practising medicine in UK requirements; Respiratory Medicine for the UKMLA: What to Focus On; how to practice medicine in UK from Philippines; 1. Patient Presentations</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1180,17 +1184,17 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Neurology in the UKMLA: High-Yield Topics and Revision Tips</t>
+          <t>Emergency Medicine and Acute Presentations in the UKMLA</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>/news#neurology-ukmla-revision</t>
+          <t>/news#emergency-medicine-ukmla-revision</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1200,7 +1204,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Established (23 posts)</t>
+          <t>Established (46 posts)</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1212,12 +1216,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>obstetrics gynaecology UKMLA</t>
+          <t>endocrinology diabetes UKMLA</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Key Dates; UKMLA ethics and professionalism topics; UKMLA NICE guidelines topics; Key Dates &amp; Timeline; UKMLA AKT high yield topics</t>
+          <t>ukmla guide; UKMLA pharmacology revision; about ukmla guide; contact ukmla guide; img guide</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1232,17 +1236,17 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise</t>
+          <t>Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>/news#obstetrics-gynaecology-ukmla-revision</t>
+          <t>/news#endocrinology-diabetes-ukmla-revision</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1252,7 +1256,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>Established (23 posts)</t>
+          <t>Established (46 posts)</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1264,12 +1268,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>ophthalmology ENT UKMLA</t>
+          <t>gastroenterology UKMLA AKT</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>UKMLA for GP doctors in UK; do all doctors need to take UKMLA; UKMLA for Indian doctors; UKMLA for Nigerian doctors; UKMLA for Pakistani doctors</t>
+          <t>UKMLA AKT; ms akt; What is the UKMLA AKT?; AKT exam; AKT Details</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1284,12 +1288,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know</t>
+          <t>Gastroenterology and Hepatology in the UKMLA AKT</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>/news#ophthalmology-ent-ukmla-revision</t>
+          <t>/news#gastroenterology-ukmla-akt-revision</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1304,7 +1308,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Established (23 posts)</t>
+          <t>Established (46 posts)</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -1316,12 +1320,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>paediatrics UKMLA</t>
+          <t>genetics UKMLA</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>UKMLA AKT; UKMLA CPSA; ms akt; ukmla guide; What is the UKMLA AKT?</t>
+          <t>NICE Guidelines and the AKT: What You Actually Need to Know; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; do all doctors need to take UKMLA; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; UKMLA Key Dates and Sitting Schedule: What to Know</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1336,12 +1340,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Paediatrics in the AKT and CPSA: A Focused Revision Guide</t>
+          <t>Genetics and Genomics in the UKMLA: What You Need to Know</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>/news#paediatrics-ukmla-revision</t>
+          <t>/news#genetics-and-genomics-in-the-ukmla</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1356,24 +1360,24 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>Established (23 posts)</t>
+          <t>Established (46 posts)</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>30 June 2026</t>
+          <t>02 July 2026</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>palliative care UKMLA</t>
+          <t>gynaecological cancers UKMLA</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Social Determinants of Health in the UKMLA: Person-Centred Care</t>
+          <t>Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1388,12 +1392,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Palliative Care and End-of-Life Decisions in the UKMLA</t>
+          <t>Gynaecological Cancers in the UKMLA: Red Flags and Referral</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>/news#palliative-care-ukmla-revision</t>
+          <t>/news#gynaecological-cancers-ukmla</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1408,24 +1412,24 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Established (23 posts)</t>
+          <t>Established (46 posts)</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>30 June 2026</t>
+          <t>02 July 2026</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>UKMLA pharmacology revision</t>
+          <t>haematology UKMLA</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>ukmla guide; UKMLA revision notes tips; AKT Revision Strategy; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Safeguarding Adults and Children: A UKMLA Revision Guide</t>
+          <t>Blood Tests and Investigations in the AKT: Data Interpretation Guide</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1440,12 +1444,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Pharmacology and Prescribing Safety in the UKMLA: A Revision Guide</t>
+          <t>Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>/news#pharmacology-prescribing-safety-ukmla</t>
+          <t>/news#haematology-ukmla-revision</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1460,24 +1464,24 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>Established (23 posts)</t>
+          <t>Established (46 posts)</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>01 July 2026</t>
+          <t>30 June 2026</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>radiology AKT UKMLA</t>
+          <t>immunology UKMLA</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>UKMLA AKT; ms akt; What is the UKMLA AKT?; AKT exam; AKT Details</t>
+          <t>UKMLA AKT high yield topics; UKMLA pharmacology revision; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Cardiology High-Yield Topics for the UKMLA AKT; UKMLA revision notes tips</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1492,12 +1496,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Radiology and Imaging Interpretation in the AKT</t>
+          <t>Immunology and Allergy in the UKMLA: High-Yield Revision</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>/news#radiology-imaging-akt-ukmla</t>
+          <t>/news#immunology-and-allergy-ukmla</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1512,24 +1516,24 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>Established (23 posts)</t>
+          <t>Established (46 posts)</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>30 June 2026</t>
+          <t>02 July 2026</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>respiratory medicine UKMLA</t>
+          <t>infection microbiology UKMLA</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>how to practice medicine in UK; practising medicine in UK requirements; how to practice medicine in UK from Philippines; Emergency Medicine and Acute Presentations in the UKMLA</t>
+          <t>More than 75 comprehensive answers regarding UKMLA, PLAB transition, eligibility, and formatting</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1544,12 +1548,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Respiratory Medicine for the UKMLA: What to Focus On</t>
+          <t>Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>/news#respiratory-medicine-ukmla-revision</t>
+          <t>/news#infection-microbiology-ukmla-revision</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -1564,7 +1568,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>Established (23 posts)</t>
+          <t>Established (46 posts)</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -1576,10 +1580,14 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>rheumatology UKMLA</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr"/>
+          <t>medical statistics UKMLA</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>medical acronyms; medical students; UKMLA for international medical graduates; UKMLA syllabus for medical students; UK visa for medical professionals</t>
+        </is>
+      </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
           <t>Clinical Systems Revision</t>
@@ -1592,12 +1600,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity</t>
+          <t>Medical Statistics and Evidence-Based Medicine in the UKMLA</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>/news#rheumatology-ukmla-revision</t>
+          <t>/news#medical-statistics-and-evidence-based-medicine-ukmla</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1612,24 +1620,24 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Established (23 posts)</t>
+          <t>Established (46 posts)</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>30 June 2026</t>
+          <t>02 July 2026</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>social determinants health UKMLA</t>
+          <t>medically unexplained symptoms UKMLA</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Mental Health Presentations in the UKMLA: What to Revise; Palliative Care and End-of-Life Decisions in the UKMLA</t>
+          <t>Mental Health Presentations in the UKMLA: What to Revise; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1644,17 +1652,17 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Social Determinants of Health in the UKMLA: Person-Centred Care</t>
+          <t>Medically Unexplained Symptoms in the UKMLA: What to Revise</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>/news#social-determinants-health-ukmla</t>
+          <t>/news#medically-unexplained-symptoms-ukmla</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Transactional</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -1664,24 +1672,24 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>Established (23 posts)</t>
+          <t>Established (46 posts)</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>30 June 2026</t>
+          <t>02 July 2026</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>surgical presentations UKMLA</t>
+          <t>menopause UKMLA</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>1. Patient Presentations; how to become a doctor in UK; Emergency Medicine and Acute Presentations in the UKMLA; Mental Health Presentations in the UKMLA: What to Revise; UK doctor salary 2026</t>
+          <t>NICE Guidelines and the AKT: What You Actually Need to Know; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; do all doctors need to take UKMLA; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; Time Management in the UKMLA AKT: Strategies That Work</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1696,12 +1704,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
+          <t>Menopause Management in the UKMLA: What You Need to Know</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>/news#surgical-presentations-ukmla-revision</t>
+          <t>/news#menopause-management-ukmla</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1716,244 +1724,248 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>Established (23 posts)</t>
+          <t>Established (46 posts)</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
+          <t>02 July 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>mental health UKMLA</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>1. Patient Presentations; Social Determinants of Health in the UKMLA: Person-Centred Care; Emergency Medicine and Acute Presentations in the UKMLA; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Clinical Systems Revision</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>MLA Content Map / Syllabus</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Mental Health Presentations in the UKMLA: What to Revise</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>/news#mental-health-ukmla-revision</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>Established (46 posts)</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>30 June 2026</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>UKMLA syllabus</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>UKMLA content map; MLA content map; UKMLA syllabus pdf download; UKMLA content map 430 conditions</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>Core UKMLA Overview</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>NICE guidelines AKT</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA AKT; ms akt; What is the UKMLA AKT?; UKMLA NICE guidelines topics; UKMLA NICE guidelines questions</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Clinical Systems Revision</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>MLA Content Map / Syllabus</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>NICE Guidelines and the AKT: What You Actually Need to Know</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>/news#nice-guidelines-akt-revision</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>Established (46 posts)</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>30 June 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>nephrology UKMLA AKI CKD</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr"/>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Clinical Systems Revision</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>MLA Content Map / Syllabus</t>
         </is>
       </c>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>/syllabus</t>
-        </is>
-      </c>
-      <c r="G25" s="4" t="inlineStr">
-        <is>
-          <t>Informational</t>
-        </is>
-      </c>
-      <c r="H25" s="4" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="I25" s="4" t="inlineStr">
-        <is>
-          <t>Established (11 posts)</t>
-        </is>
-      </c>
-      <c r="J25" s="4" t="inlineStr">
-        <is>
-          <t>N/A (static page)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>Official Resources</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="inlineStr"/>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>Core UKMLA Overview</t>
-        </is>
-      </c>
-      <c r="D26" s="4" t="inlineStr">
-        <is>
-          <t>Official Resources</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>Official Resources</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>/official-resources</t>
-        </is>
-      </c>
-      <c r="G26" s="4" t="inlineStr">
-        <is>
-          <t>Informational</t>
-        </is>
-      </c>
-      <c r="H26" s="4" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="I26" s="4" t="inlineStr">
-        <is>
-          <t>Established (11 posts)</t>
-        </is>
-      </c>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t>N/A (static page)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>PLAB vs UKMLA</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>difference between PLAB and UKMLA; is UKMLA replacing PLAB; UKMLA vs PLAB which is harder</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>Core UKMLA Overview</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr">
-        <is>
-          <t>UKMLA vs PLAB</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>UKMLA vs PLAB</t>
-        </is>
-      </c>
-      <c r="F27" s="4" t="inlineStr">
-        <is>
-          <t>/ukmla-vs-plab</t>
-        </is>
-      </c>
-      <c r="G27" s="4" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Nephrology in the UKMLA: AKI, CKD, and Electrolyte Disorders</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>/news#nephrology-ukmla-revision</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>Established (46 posts)</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>30 June 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>neurology UKMLA</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA AKT high yield topics; UKMLA revision notes tips; Cardiology High-Yield Topics for the UKMLA AKT; UKMLA pharmacology revision; UKMLA CPSA preparation tips</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Clinical Systems Revision</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>MLA Content Map / Syllabus</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Neurology in the UKMLA: High-Yield Topics and Revision Tips</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>/news#neurology-ukmla-revision</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>Commercial</t>
         </is>
       </c>
-      <c r="H27" s="4" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="I27" s="4" t="inlineStr">
-        <is>
-          <t>Established (11 posts)</t>
-        </is>
-      </c>
-      <c r="J27" s="4" t="inlineStr">
-        <is>
-          <t>N/A (static page)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>What Is the UKMLA?</t>
-        </is>
-      </c>
-      <c r="B28" s="5" t="inlineStr"/>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>Core UKMLA Overview</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t>What Is the UKMLA?</t>
-        </is>
-      </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>What Is the UKMLA?</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="inlineStr">
-        <is>
-          <t>/what-is-ukmla</t>
-        </is>
-      </c>
-      <c r="G28" s="4" t="inlineStr">
-        <is>
-          <t>Informational</t>
-        </is>
-      </c>
-      <c r="H28" s="4" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="I28" s="4" t="inlineStr">
-        <is>
-          <t>Established (11 posts)</t>
-        </is>
-      </c>
-      <c r="J28" s="4" t="inlineStr">
-        <is>
-          <t>N/A (static page)</t>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>Established (46 posts)</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>30 June 2026</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Foundation Programme 2026 recruitment changes</t>
+          <t>nutrition UKMLA</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>UKMLA syllabus 2026 changes; UKMLA for academic foundation programme; ukmla syllabus 2026; Understanding the Foundation Programme: What Awaits After the UKMLA; UK doctor salary 2026</t>
+          <t>Mental Health Presentations in the UKMLA: What to Revise; Nephrology in the UKMLA: AKI, CKD, and Electrolyte Disorders; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Core UKMLA Overview</t>
+          <t>Clinical Systems Revision</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Eligibility</t>
+          <t>MLA Content Map / Syllabus</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Foundation Programme 2026 Recruitment Changes: What's New for Applicants</t>
+          <t>Nutrition and Metabolic Disorders in the UKMLA: What to Revise</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>/news#foundation-programme-2026-recruitment-changes</t>
+          <t>/news#nutrition-and-metabolic-disorders-ukmla</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -1968,7 +1980,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>Established (11 posts)</t>
+          <t>Established (46 posts)</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -1980,37 +1992,37 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>UK medical schools UKMLA implementation</t>
+          <t>obstetrics gynaecology UKMLA</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>medical acronyms; medical students; UKMLA for international medical graduates; UKMLA syllabus for medical students; UK visa for medical professionals</t>
+          <t>Key Dates; UKMLA ethics and professionalism topics; UKMLA NICE guidelines topics; Key Dates &amp; Timeline; UKMLA AKT high yield topics</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Core UKMLA Overview</t>
+          <t>Clinical Systems Revision</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>What Is the UKMLA?</t>
+          <t>MLA Content Map / Syllabus</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>How UK Medical Schools Implement the UKMLA: An Overview</t>
+          <t>Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>/news#uk-medical-schools-ukmla-implementation</t>
+          <t>/news#obstetrics-gynaecology-ukmla-revision</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2020,7 +2032,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>Established (11 posts)</t>
+          <t>Established (46 posts)</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -2032,32 +2044,32 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>is UKMLA replacing PLAB</t>
+          <t>ophthalmology ENT UKMLA</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>PLAB vs UKMLA; plab 1; plab 2; UKMLA vs PLAB; plab pathway</t>
+          <t>UKMLA for GP doctors in UK; do all doctors need to take UKMLA; UKMLA for Indian doctors; UKMLA for Nigerian doctors; UKMLA for Pakistani doctors</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Core UKMLA Overview</t>
+          <t>Clinical Systems Revision</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>UKMLA vs PLAB</t>
+          <t>MLA Content Map / Syllabus</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Is UKMLA Replacing PLAB? The Real Relationship, Explained</t>
+          <t>Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>/news#is-ukmla-replacing-plab-explained</t>
+          <t>/news#ophthalmology-ent-ukmla-revision</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -2072,29 +2084,29 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>Established (11 posts)</t>
+          <t>Established (46 posts)</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>02 July 2026</t>
+          <t>30 June 2026</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>MLA content map</t>
+          <t>paediatrics UKMLA</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>UKMLA content map; The MLA Content Map; The MLA Content Map Framework; UKMLA Syllabus &amp; Content Map; Syllabus &amp; Content Map</t>
+          <t>UKMLA AKT; UKMLA CPSA; ms akt; ukmla guide; What is the UKMLA AKT?</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Core UKMLA Overview</t>
+          <t>Clinical Systems Revision</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -2104,12 +2116,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>MLA Content Map: The Blueprint Behind Every UKMLA Question</t>
+          <t>Paediatrics in the AKT and CPSA: A Focused Revision Guide</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>/news#mla-content-map-explained</t>
+          <t>/news#paediatrics-ukmla-revision</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -2124,7 +2136,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>Established (11 posts)</t>
+          <t>Established (46 posts)</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -2136,32 +2148,32 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>PLAB 2 preparation</t>
+          <t>palliative care UKMLA</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>PLAB vs UKMLA; UKMLA preparation; plab 1; plab 2; UKMLA vs PLAB</t>
+          <t>Social Determinants of Health in the UKMLA: Person-Centred Care</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Core UKMLA Overview</t>
+          <t>Clinical Systems Revision</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>UKMLA vs PLAB</t>
+          <t>MLA Content Map / Syllabus</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>PLAB 2 Preparation: How to Excel in the Clinical Assessment</t>
+          <t>Palliative Care and End-of-Life Decisions in the UKMLA</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>/news#plab-2-preparation-guide</t>
+          <t>/news#palliative-care-ukmla-revision</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -2176,7 +2188,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>Established (11 posts)</t>
+          <t>Established (46 posts)</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -2188,32 +2200,32 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>UKMLA preparation for IMGs</t>
+          <t>UKMLA pharmacology revision</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>UKMLA preparation; Preparation; Preparation Guide; UKMLA Preparation Guide; UKMLA OSCE preparation</t>
+          <t>ukmla guide; UKMLA revision notes tips; AKT Revision Strategy; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Safeguarding Adults and Children: A UKMLA Revision Guide</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Core UKMLA Overview</t>
+          <t>Clinical Systems Revision</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>UKMLA vs PLAB</t>
+          <t>MLA Content Map / Syllabus</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>UKMLA Preparation for IMG Candidates: A Tailored Guide</t>
+          <t>Pharmacology and Prescribing Safety in the UKMLA: A Revision Guide</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-preparation-for-imgs</t>
+          <t>/news#pharmacology-prescribing-safety-ukmla</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -2228,29 +2240,29 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>Established (11 posts)</t>
+          <t>Established (46 posts)</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>30 June 2026</t>
+          <t>01 July 2026</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>UKMLA syllabus 2026 changes</t>
+          <t>prescribing in renal impairment UKMLA</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>UKMLA syllabus; ukmla syllabus 2026; Syllabus; Content &amp; Syllabus; UKMLA exam syllabus 2026</t>
+          <t>ukmla guide; UKMLA pharmacology revision; about ukmla guide; contact ukmla guide; img guide</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Core UKMLA Overview</t>
+          <t>Clinical Systems Revision</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -2260,12 +2272,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>UKMLA Syllabus 2026 Changes: What's New in the Updated MLA Content Map</t>
+          <t>Prescribing in Renal and Hepatic Impairment: A UKMLA Revision Guide</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-syllabus-2026-changes</t>
+          <t>/news#prescribing-in-renal-and-hepatic-impairment-ukmla</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -2280,7 +2292,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>Established (11 posts)</t>
+          <t>Established (46 posts)</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -2292,32 +2304,32 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>UKMLA for academic foundation programme</t>
+          <t>public health UKMLA</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Understanding the Foundation Programme: What Awaits After the UKMLA; UKMLA and foundation year application; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; UKMLA fail foundation year impact; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
+          <t>Mental Health Presentations in the UKMLA: What to Revise; NICE Guidelines and the AKT: What You Actually Need to Know; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Social Determinants of Health in the UKMLA: Person-Centred Care; do all doctors need to take UKMLA</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Core UKMLA Overview</t>
+          <t>Clinical Systems Revision</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Eligibility</t>
+          <t>MLA Content Map / Syllabus</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>UKMLA and the Academic Foundation Programme: What Research-Minded Students Need to Know</t>
+          <t>Public Health and Screening in the UKMLA: What You Need to Know</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-and-academic-foundation-programme</t>
+          <t>/news#public-health-and-screening-ukmla</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -2332,7 +2344,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>Established (11 posts)</t>
+          <t>Established (46 posts)</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -2344,32 +2356,32 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>UKMLA graduate entry</t>
+          <t>radiology AKT UKMLA</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>medical students; UKMLA syllabus for medical students; UKMLA exam for UK medical students; Eligibility for UK Medical Students; UKMLA pass rate medical students</t>
+          <t>UKMLA AKT; ms akt; What is the UKMLA AKT?; AKT exam; AKT Details</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Core UKMLA Overview</t>
+          <t>Clinical Systems Revision</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Eligibility</t>
+          <t>MLA Content Map / Syllabus</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>UKMLA for Graduate-Entry Medical Students: What Is Different?</t>
+          <t>Radiology and Imaging Interpretation in the AKT</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-graduate-entry-medical-students</t>
+          <t>/news#radiology-imaging-akt-ukmla</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -2384,7 +2396,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>Established (11 posts)</t>
+          <t>Established (46 posts)</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -2396,32 +2408,32 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>UKMLA vs PLAB</t>
+          <t>respiratory medicine UKMLA</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>PLAB vs UKMLA; plab 1; plab 2; difference between PLAB and UKMLA; is UKMLA replacing PLAB</t>
+          <t>how to practice medicine in UK; practising medicine in UK requirements; how to practice medicine in UK from Philippines; Emergency Medicine and Acute Presentations in the UKMLA</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Core UKMLA Overview</t>
+          <t>Clinical Systems Revision</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>UKMLA vs PLAB</t>
+          <t>MLA Content Map / Syllabus</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>UKMLA vs PLAB: What Is the Difference?</t>
+          <t>Respiratory Medicine for the UKMLA: What to Focus On</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-vs-plab-difference</t>
+          <t>/news#respiratory-medicine-ukmla-revision</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -2436,7 +2448,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>Established (11 posts)</t>
+          <t>Established (46 posts)</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -2448,188 +2460,184 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>what is UKMLA</t>
-        </is>
-      </c>
-      <c r="B39" s="3" t="inlineStr">
+          <t>rheumatology UKMLA</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr"/>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Clinical Systems Revision</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>MLA Content Map / Syllabus</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>/news#rheumatology-ukmla-revision</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>Established (46 posts)</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>30 June 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>sepsis UKMLA</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
         <is>
           <t>ukmla guide; about ukmla guide; contact ukmla guide; img guide; Preparation Guide</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>Core UKMLA Overview</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>What Is the UKMLA?</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>What Is the UKMLA? A Complete Beginner's Guide</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>/news#what-is-ukmla-complete-guide</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>Informational</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>Established (11 posts)</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Clinical Systems Revision</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>MLA Content Map / Syllabus</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Sepsis Recognition and Management in the UKMLA: The Essential Guide</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>/news#sepsis-recognition-and-management-ukmla</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>Established (46 posts)</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>02 July 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>social determinants health UKMLA</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>Mental Health Presentations in the UKMLA: What to Revise; Palliative Care and End-of-Life Decisions in the UKMLA</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Clinical Systems Revision</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>MLA Content Map / Syllabus</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Social Determinants of Health in the UKMLA: Person-Centred Care</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>/news#social-determinants-health-ukmla</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>Transactional</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>Established (46 posts)</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
         <is>
           <t>30 June 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="6" t="inlineStr">
-        <is>
-          <t>UKMLA AKT</t>
-        </is>
-      </c>
-      <c r="B40" s="5" t="inlineStr">
-        <is>
-          <t>AKT exam; UKMLA AKT pass mark; how many questions in UKMLA AKT; UKMLA AKT exam preparation tips; UKMLA AKT vs CPSA difference</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="inlineStr">
-        <is>
-          <t>Exam Format</t>
-        </is>
-      </c>
-      <c r="D40" s="4" t="inlineStr">
-        <is>
-          <t>AKT Exam Pattern</t>
-        </is>
-      </c>
-      <c r="E40" s="4" t="inlineStr">
-        <is>
-          <t>AKT Exam Pattern</t>
-        </is>
-      </c>
-      <c r="F40" s="4" t="inlineStr">
-        <is>
-          <t>/exam-pattern/akt</t>
-        </is>
-      </c>
-      <c r="G40" s="4" t="inlineStr">
-        <is>
-          <t>Informational</t>
-        </is>
-      </c>
-      <c r="H40" s="4" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="I40" s="4" t="inlineStr">
-        <is>
-          <t>Established (6 posts)</t>
-        </is>
-      </c>
-      <c r="J40" s="4" t="inlineStr">
-        <is>
-          <t>N/A (static page)</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="6" t="inlineStr">
-        <is>
-          <t>UKMLA CPSA</t>
-        </is>
-      </c>
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t>CPSA exam; UKMLA CPSA stations examples; UKMLA CPSA centre Manchester</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="inlineStr">
-        <is>
-          <t>Exam Format</t>
-        </is>
-      </c>
-      <c r="D41" s="4" t="inlineStr">
-        <is>
-          <t>CPSA Exam Pattern</t>
-        </is>
-      </c>
-      <c r="E41" s="4" t="inlineStr">
-        <is>
-          <t>CPSA Exam Pattern</t>
-        </is>
-      </c>
-      <c r="F41" s="4" t="inlineStr">
-        <is>
-          <t>/exam-pattern/cpsa</t>
-        </is>
-      </c>
-      <c r="G41" s="4" t="inlineStr">
-        <is>
-          <t>Informational</t>
-        </is>
-      </c>
-      <c r="H41" s="4" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="I41" s="4" t="inlineStr">
-        <is>
-          <t>Established (6 posts)</t>
-        </is>
-      </c>
-      <c r="J41" s="4" t="inlineStr">
-        <is>
-          <t>N/A (static page)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>CPSA clinical examination stations</t>
+          <t>substance misuse UKMLA</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>UKMLA CPSA; What is the UKMLA CPSA?; UKMLA CPSA stations list; UKMLA clinical examination tips; UKMLA CPSA stations examples</t>
+          <t>Mental Health Presentations in the UKMLA: What to Revise; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Exam Format</t>
+          <t>Clinical Systems Revision</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>CPSA Exam Pattern</t>
+          <t>MLA Content Map / Syllabus</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Clinical Examination Stations in the CPSA: A Practical Guide</t>
+          <t>Substance Misuse and Addiction in the UKMLA: What to Revise</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>/news#clinical-examination-cpsa-guide</t>
+          <t>/news#substance-misuse-and-addiction-ukmla</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -2644,44 +2652,44 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>Established (6 posts)</t>
+          <t>Established (46 posts)</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>30 June 2026</t>
+          <t>02 July 2026</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>how to read AKT stem</t>
+          <t>surgical presentations UKMLA</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>UKMLA AKT; ms akt; What is the UKMLA AKT?; AKT exam; AKT Details</t>
+          <t>1. Patient Presentations; how to become a doctor in UK; Emergency Medicine and Acute Presentations in the UKMLA; Mental Health Presentations in the UKMLA: What to Revise; UK doctor salary 2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Exam Format</t>
+          <t>Clinical Systems Revision</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern</t>
+          <t>MLA Content Map / Syllabus</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>How to Read an AKT Stem: Avoiding Common Traps</t>
+          <t>Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>/news#how-to-read-akt-stem</t>
+          <t>/news#surgical-presentations-ukmla-revision</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -2696,7 +2704,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>Established (6 posts)</t>
+          <t>Established (46 posts)</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -2708,32 +2716,32 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>psychiatry communication CPSA</t>
+          <t>toxicology UKMLA</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>UKMLA CPSA; What is the UKMLA CPSA?; UKMLA CPSA stations list; CPSA exam; UKMLA CPSA stations examples</t>
+          <t>UKMLA AKT high yield topics; Cardiology High-Yield Topics for the UKMLA AKT; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Time Management in the UKMLA AKT: Strategies That Work</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Exam Format</t>
+          <t>Clinical Systems Revision</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>CPSA Exam Pattern</t>
+          <t>MLA Content Map / Syllabus</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Psychiatry Communication Stations: Handling Difficult Conversations</t>
+          <t>Toxicology and Poisoning in the UKMLA: High-Yield Overdose Management</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>/news#psychiatry-communication-cpsa-stations</t>
+          <t>/news#toxicology-and-poisoning-ukmla</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -2748,44 +2756,44 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>Established (6 posts)</t>
+          <t>Established (46 posts)</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>30 June 2026</t>
+          <t>02 July 2026</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="6" t="inlineStr">
-        <is>
-          <t>UKMLA AKT</t>
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>transgender health UKMLA</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>ms akt; What is the UKMLA AKT?; AKT exam; how to prepare for UKMLA; AKT Details</t>
+          <t>UKMLA content map; MLA content map; UKMLA Syllabus &amp; Content Map; Syllabus &amp; Content Map; The MLA Content Map</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Exam Format</t>
+          <t>Clinical Systems Revision</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern</t>
+          <t>MLA Content Map / Syllabus</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>UKMLA AKT: Format, Question Types, and How to Prepare</t>
+          <t>Transgender Health in the UKMLA: What the Content Map Covers</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-akt-format-preparation</t>
+          <t>/news#transgender-health-in-the-ukmla</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -2800,44 +2808,44 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>Established (6 posts)</t>
+          <t>Established (46 posts)</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>30 June 2026</t>
+          <t>02 July 2026</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="6" t="inlineStr">
-        <is>
-          <t>UKMLA CPSA</t>
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>trauma and orthopaedics UKMLA</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>What is the UKMLA CPSA?; CPSA exam; UKMLA exam; what is the UKMLA exam; Clinical Skills (CPSA)</t>
+          <t>UKMLA AKT high yield topics; Cardiology High-Yield Topics for the UKMLA AKT; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Time Management in the UKMLA AKT: Strategies That Work</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Exam Format</t>
+          <t>Clinical Systems Revision</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>CPSA Exam Pattern</t>
+          <t>MLA Content Map / Syllabus</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>UKMLA CPSA: What the Clinical Exam Really Tests</t>
+          <t>Trauma and Orthopaedics in the UKMLA: High-Yield Fracture Management</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-cpsa-what-it-tests</t>
+          <t>/news#trauma-and-orthopaedics-ukmla</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -2852,44 +2860,44 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>Established (6 posts)</t>
+          <t>Established (46 posts)</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>30 June 2026</t>
+          <t>02 July 2026</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Angoff standard setting UKMLA</t>
+          <t>urology UKMLA</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>AKT Standard Setting: The Angoff Method; UKMLA AKT standard setting explained; UKMLA Results, Scoring &amp; Standard Setting; angoff definition; angoff method</t>
+          <t>UKMLA AKT high yield topics; UKMLA AKT; ms akt; What is the UKMLA AKT?; Cardiology High-Yield Topics for the UKMLA AKT</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Exam Format</t>
+          <t>Clinical Systems Revision</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Results and Scoring</t>
+          <t>MLA Content Map / Syllabus</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>What Is an Angoff Standard Setting and Why Does It Matter?</t>
+          <t>Urology in the UKMLA: High-Yield Topics for the AKT</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>/news#angoff-standard-setting-explained</t>
+          <t>/news#urology-ukmla-revision</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -2904,252 +2912,244 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>Established (6 posts)</t>
+          <t>Established (46 posts)</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>30 June 2026</t>
+          <t>02 July 2026</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>UKMLA preparation</t>
+          <t>UKMLA syllabus</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>how to prepare for UKMLA; UKMLA study plan; how long to study for UKMLA; UKMLA preparation 6 weeks</t>
+          <t>UKMLA content map; MLA content map; UKMLA syllabus pdf download; UKMLA content map 430 conditions</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>Exam Preparation</t>
+          <t>Core UKMLA Overview</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>Preparation</t>
+          <t>MLA Content Map / Syllabus</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>Preparation</t>
+          <t>MLA Content Map / Syllabus</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>/preparation</t>
+          <t>/syllabus</t>
         </is>
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H48" s="4" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I48" s="4" t="inlineStr">
+        <is>
+          <t>Established (14 posts)</t>
+        </is>
+      </c>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>N/A (static page)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Official Resources</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr"/>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>Core UKMLA Overview</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>Official Resources</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>Official Resources</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>/official-resources</t>
+        </is>
+      </c>
+      <c r="G49" s="4" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H49" s="4" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I49" s="4" t="inlineStr">
+        <is>
+          <t>Established (14 posts)</t>
+        </is>
+      </c>
+      <c r="J49" s="4" t="inlineStr">
+        <is>
+          <t>N/A (static page)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>PLAB vs UKMLA</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>difference between PLAB and UKMLA; is UKMLA replacing PLAB; UKMLA vs PLAB which is harder</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>Core UKMLA Overview</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>UKMLA vs PLAB</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>UKMLA vs PLAB</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>/ukmla-vs-plab</t>
+        </is>
+      </c>
+      <c r="G50" s="4" t="inlineStr">
+        <is>
           <t>Commercial</t>
         </is>
       </c>
-      <c r="H48" s="4" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="I48" s="4" t="inlineStr">
-        <is>
-          <t>Established (8 posts)</t>
-        </is>
-      </c>
-      <c r="J48" s="4" t="inlineStr">
+      <c r="H50" s="4" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I50" s="4" t="inlineStr">
+        <is>
+          <t>Established (14 posts)</t>
+        </is>
+      </c>
+      <c r="J50" s="4" t="inlineStr">
         <is>
           <t>N/A (static page)</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>UKMLA group study solo</t>
-        </is>
-      </c>
-      <c r="B49" s="3" t="inlineStr">
-        <is>
-          <t>UKMLA group study vs solo study; how long to study for UKMLA; UKMLA study plan; study plan; UKMLA study plan 12 weeks</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>Exam Preparation</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>Preparation</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>Group Study vs Solo Study for the UKMLA: What Works Best?</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>/news#group-study-vs-solo-ukmla</t>
-        </is>
-      </c>
-      <c r="G49" s="2" t="inlineStr">
-        <is>
-          <t>Informational</t>
-        </is>
-      </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t>Established (8 posts)</t>
-        </is>
-      </c>
-      <c r="J49" s="2" t="inlineStr">
-        <is>
-          <t>30 June 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>how to pass UKMLA on first attempt</t>
-        </is>
-      </c>
-      <c r="B50" s="3" t="inlineStr">
-        <is>
-          <t>how to pass ukmla; UKMLA pass mark; UKMLA pass mark for IMG; UKMLA attempt limit for doctors; UKMLA AKT pass mark</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>Exam Preparation</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>Preparation</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>How to Pass the UKMLA on Your First Attempt</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>/news#how-to-pass-ukmla-on-first-attempt</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="inlineStr">
-        <is>
-          <t>Informational</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>Established (8 posts)</t>
-        </is>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>02 July 2026</t>
-        </is>
-      </c>
-    </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>UKMLA revision notes</t>
-        </is>
-      </c>
-      <c r="B51" s="3" t="inlineStr">
-        <is>
-          <t>UKMLA revision notes tips; UKMLA pharmacology revision; AKT Revision Strategy; CPSA / OSCE Revision Strategy; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>Exam Preparation</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>Preparation</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>How to Write UKMLA Revision Notes That Actually Work</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>/news#ukmla-revision-notes-strategy</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="inlineStr">
-        <is>
-          <t>Informational</t>
-        </is>
-      </c>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t>Established (8 posts)</t>
-        </is>
-      </c>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>30 June 2026</t>
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>What Is the UKMLA?</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr"/>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>Core UKMLA Overview</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>What Is the UKMLA?</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>What Is the UKMLA?</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>/what-is-ukmla</t>
+        </is>
+      </c>
+      <c r="G51" s="4" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H51" s="4" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I51" s="4" t="inlineStr">
+        <is>
+          <t>Established (14 posts)</t>
+        </is>
+      </c>
+      <c r="J51" s="4" t="inlineStr">
+        <is>
+          <t>N/A (static page)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>UKMLA exam anxiety tips</t>
+          <t>Foundation Programme 2026 recruitment changes</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>UKMLA exam; what is the UKMLA exam; The Exam; UKMLA exam in Dubai; AKT exam</t>
+          <t>UKMLA syllabus 2026 changes; UKMLA for academic foundation programme; ukmla syllabus 2026; Understanding the Foundation Programme: What Awaits After the UKMLA; UK doctor salary 2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Exam Preparation</t>
+          <t>Core UKMLA Overview</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Preparation</t>
+          <t>Eligibility</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Managing UKMLA Exam Anxiety: Practical Strategies for Candidates</t>
+          <t>Foundation Programme 2026 Recruitment Changes: What's New for Applicants</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>/news#managing-ukmla-exam-anxiety</t>
+          <t>/news#foundation-programme-2026-recruitment-changes</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -3164,44 +3164,44 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>Established (8 posts)</t>
+          <t>Established (14 posts)</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>01 July 2026</t>
+          <t>02 July 2026</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>UKMLA mock exams</t>
+          <t>UK medical schools UKMLA implementation</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>UKMLA mock; UKMLA preparation; Preparation; UKMLA mock exam practice; free UKMLA mock test</t>
+          <t>medical acronyms; medical students; UKMLA for international medical graduates; UKMLA syllabus for medical students; UK visa for medical professionals</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Exam Preparation</t>
+          <t>Core UKMLA Overview</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Preparation</t>
+          <t>What Is the UKMLA?</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>The Role of Mock Exams in UKMLA Preparation</t>
+          <t>How UK Medical Schools Implement the UKMLA: An Overview</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>/news#mock-exams-ukmla-preparation</t>
+          <t>/news#uk-medical-schools-ukmla-implementation</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>Established (8 posts)</t>
+          <t>Established (14 posts)</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -3228,32 +3228,32 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>UKMLA AKT preparation countdown</t>
+          <t>is UKMLA replacing PLAB</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>UKMLA AKT; UKMLA preparation; ms akt; What is the UKMLA AKT?; Preparation</t>
+          <t>PLAB vs UKMLA; plab 1; plab 2; UKMLA vs PLAB; plab pathway</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Exam Preparation</t>
+          <t>Core UKMLA Overview</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Preparation</t>
+          <t>UKMLA vs PLAB</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Three Months to the UKMLA AKT: A Final Preparation Countdown</t>
+          <t>Is UKMLA Replacing PLAB? The Real Relationship, Explained</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>/news#three-months-ukmla-akt-countdown</t>
+          <t>/news#is-ukmla-replacing-plab-explained</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -3268,44 +3268,44 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>Established (8 posts)</t>
+          <t>Established (14 posts)</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>30 June 2026</t>
+          <t>02 July 2026</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>time management UKMLA AKT</t>
+          <t>joining a Royal College after UKMLA</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>UKMLA AKT; ms akt; What is the UKMLA AKT?; AKT exam; AKT Details</t>
+          <t>UKMLA after MBBS; UKMLA after MBBS in India; UKMLA for doctors with MRCP; UKMLA NHS job after exam; NHS jobs after GMC registration</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Exam Preparation</t>
+          <t>Core UKMLA Overview</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Preparation</t>
+          <t>Registration Guide</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Time Management in the UKMLA AKT: Strategies That Work</t>
+          <t>Joining a Royal College After the UKMLA: MRCP, MRCS and MRCGP Explained</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>/news#time-management-akt-ukmla</t>
+          <t>/news#joining-a-royal-college-mrcp-mrcs-mrcgp-overview</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -3320,44 +3320,44 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>Established (8 posts)</t>
+          <t>Established (14 posts)</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>30 June 2026</t>
+          <t>02 July 2026</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>UKMLA Anki deck download</t>
+          <t>MLA content map</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>ukmla guide; UKMLA syllabus pdf download; What Is the UKMLA? A Complete Beginner's Guide; UKMLA pharmacology revision; about ukmla guide</t>
+          <t>UKMLA content map; The MLA Content Map; The MLA Content Map Framework; UKMLA Syllabus &amp; Content Map; Syllabus &amp; Content Map</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Exam Preparation</t>
+          <t>Core UKMLA Overview</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Preparation</t>
+          <t>MLA Content Map / Syllabus</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>UKMLA Anki Deck and Flashcard Revision: The Complete Guide</t>
+          <t>MLA Content Map: The Blueprint Behind Every UKMLA Question</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-anki-deck-and-flashcard-revision-guide</t>
+          <t>/news#mla-content-map-explained</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -3372,44 +3372,44 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>Established (8 posts)</t>
+          <t>Established (14 posts)</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>02 July 2026</t>
+          <t>30 June 2026</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>English language requirement for UKMLA India</t>
+          <t>PLAB 2 preparation</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>UKMLA India; English language requirement for UKMLA; English requirement for UKMLA India (IELTS/OET); UKMLA OET or IELTS requirement; Step 2: English Language Proficiency</t>
+          <t>PLAB vs UKMLA; UKMLA preparation; plab 1; plab 2; UKMLA vs PLAB</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
+          <t>Core UKMLA Overview</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Eligibility</t>
+          <t>UKMLA vs PLAB</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>English Language Requirements for the UKMLA: IELTS and OET Scores Explained</t>
+          <t>PLAB 2 Preparation: How to Excel in the Clinical Assessment</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>/news#english-language-requirement-for-ukmla-india</t>
+          <t>/news#plab-2-preparation-guide</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -3424,44 +3424,44 @@
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>Established (30 posts)</t>
+          <t>Established (14 posts)</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>01 July 2026</t>
+          <t>30 June 2026</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>foundation year vs specialty training IMG</t>
+          <t>history of UKMLA and PLAB transition</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>UKMLA for IMG; UKMLA and foundation year application; UKMLA fail foundation year impact; img guide; IMG Pathway</t>
+          <t>PLAB vs UKMLA; plab 1; plab 2; UKMLA vs PLAB; is UKMLA replacing PLAB</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
+          <t>Core UKMLA Overview</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Eligibility</t>
+          <t>What Is the UKMLA?</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Foundation Year vs Specialty Training for IMGs: Which Route After the UKMLA?</t>
+          <t>The History of the UKMLA and PLAB Transition, Explained</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>/news#foundation-year-vs-specialty-training-for-imgs</t>
+          <t>/news#history-of-ukmla-plab-transition-explained</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>Established (30 posts)</t>
+          <t>Established (14 posts)</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -3488,17 +3488,17 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>GMC registration requirements for international doctors</t>
+          <t>Multi-Specialty Recruitment Assessment</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>UKMLA for GP doctors in UK; UKMLA registration; GMC registration process for doctors; UKMLA registration process GMC; GMC registration requirements IMG</t>
+          <t>Structure of the Assessment; Medical Licensing Assessment; uk medical licensing assessment; UKMLA - UK Medical Licensing Assessment Guide; clinical professional skills assessment</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
+          <t>Core UKMLA Overview</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -3508,12 +3508,12 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>GMC Registration Requirements for International Doctors: The Complete Process</t>
+          <t>The Multi-Specialty Recruitment Assessment (MSRA), Explained</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>/news#gmc-registration-requirements-for-international-doctors</t>
+          <t>/news#multi-specialty-recruitment-assessment-msra-explained</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -3528,44 +3528,44 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>Established (30 posts)</t>
+          <t>Established (14 posts)</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>01 July 2026</t>
+          <t>02 July 2026</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>GMC registration from India</t>
+          <t>UKMLA preparation for IMGs</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>UKMLA India; UKMLA registration; gmc registration guide; how to apply for UKMLA from India; UKMLA GMC registration for graduates</t>
+          <t>UKMLA preparation; Preparation; Preparation Guide; UKMLA Preparation Guide; UKMLA OSCE preparation</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
+          <t>Core UKMLA Overview</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Registration Guide</t>
+          <t>UKMLA vs PLAB</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide</t>
+          <t>UKMLA Preparation for IMG Candidates: A Tailored Guide</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>/news#gmc-registration-and-epic-verification-india</t>
+          <t>/news#ukmla-preparation-for-imgs</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -3580,44 +3580,44 @@
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>Established (30 posts)</t>
+          <t>Established (14 posts)</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>01 July 2026</t>
+          <t>30 June 2026</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>how to become a doctor in UK from India</t>
+          <t>UKMLA syllabus 2026 changes</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>how to become a doctor in UK; UKMLA India; how to become a doctor in UK from Nigeria; how to become a doctor in UK from Pakistan; how to apply for UKMLA from India</t>
+          <t>UKMLA syllabus; ukmla syllabus 2026; Syllabus; Content &amp; Syllabus; UKMLA exam syllabus 2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
+          <t>Core UKMLA Overview</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Eligibility</t>
+          <t>MLA Content Map / Syllabus</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>How to Become a Doctor in the UK from India: The Complete UKMLA Route</t>
+          <t>UKMLA Syllabus 2026 Changes: What's New in the Updated MLA Content Map</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>/news#how-to-become-a-doctor-in-uk-from-india</t>
+          <t>/news#ukmla-syllabus-2026-changes</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -3632,29 +3632,29 @@
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>Established (30 posts)</t>
+          <t>Established (14 posts)</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>01 July 2026</t>
+          <t>02 July 2026</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>how to become a doctor in UK</t>
+          <t>UKMLA for academic foundation programme</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>how to become a doctor in UK from India; how to become a doctor in UK from Nigeria; how to become a doctor in UK from Pakistan; UKMLA registration; gmc registration guide</t>
+          <t>Understanding the Foundation Programme: What Awaits After the UKMLA; UKMLA and foundation year application; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; UKMLA fail foundation year impact; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
+          <t>Core UKMLA Overview</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs</t>
+          <t>UKMLA and the Academic Foundation Programme: What Research-Minded Students Need to Know</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>/news#how-to-become-a-doctor-in-the-uk-gmc-registration-guide</t>
+          <t>/news#ukmla-and-academic-foundation-programme</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -3684,29 +3684,29 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>Established (30 posts)</t>
+          <t>Established (14 posts)</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>01 July 2026</t>
+          <t>02 July 2026</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>is Indian MBBS valid in UK</t>
+          <t>UKMLA graduate entry</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>MBBS in UK for Indian students; UKMLA after MBBS; UKMLA for Indian doctors; UKMLA after MBBS in India; UKMLA eligibility for Indian doctors</t>
+          <t>medical students; UKMLA syllabus for medical students; UKMLA exam for UK medical students; Eligibility for UK Medical Students; UKMLA pass rate medical students</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
+          <t>Core UKMLA Overview</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -3716,12 +3716,12 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained</t>
+          <t>UKMLA for Graduate-Entry Medical Students: What Is Different?</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>/news#is-indian-mbbs-valid-in-uk</t>
+          <t>/news#ukmla-graduate-entry-medical-students</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -3736,44 +3736,44 @@
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>Established (30 posts)</t>
+          <t>Established (14 posts)</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>01 July 2026</t>
+          <t>30 June 2026</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>MBBS in UK for Indian students</t>
+          <t>UKMLA vs PLAB</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>is Indian MBBS valid in UK; UKMLA after MBBS; UKMLA for Indian doctors; UKMLA for IMG; medical students</t>
+          <t>PLAB vs UKMLA; plab 1; plab 2; difference between PLAB and UKMLA; is UKMLA replacing PLAB</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
+          <t>Core UKMLA Overview</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Eligibility</t>
+          <t>UKMLA vs PLAB</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path</t>
+          <t>UKMLA vs PLAB: What Is the Difference?</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>/news#mbbs-in-uk-for-indian-students</t>
+          <t>/news#ukmla-vs-plab-difference</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -3788,44 +3788,44 @@
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>Established (30 posts)</t>
+          <t>Established (14 posts)</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>01 July 2026</t>
+          <t>30 June 2026</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>Medical Training Initiative scheme closure 2026</t>
+          <t>what is UKMLA</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>medical licence UK for doctors 2026; UK medical licence requirements 2026; ukmla syllabus 2026; medical acronyms; medical students</t>
+          <t>ukmla guide; about ukmla guide; contact ukmla guide; img guide; Preparation Guide</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
+          <t>Core UKMLA Overview</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Eligibility</t>
+          <t>What Is the UKMLA?</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Medical Training Initiative Scheme Closure 2026: What IMGs Need to Know</t>
+          <t>What Is the UKMLA? A Complete Beginner's Guide</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>/news#medical-training-initiative-scheme-closure-2026</t>
+          <t>/news#what-is-ukmla-complete-guide</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -3840,148 +3840,148 @@
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>Established (30 posts)</t>
+          <t>Established (14 posts)</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>02 July 2026</t>
+          <t>30 June 2026</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>Medical Training Prioritisation Act 2026</t>
-        </is>
-      </c>
-      <c r="B66" s="3" t="inlineStr">
-        <is>
-          <t>medical licence UK for doctors 2026; UK medical licence requirements 2026; ukmla syllabus 2026; medical acronyms; medical students</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
-        <is>
-          <t>Eligibility</t>
-        </is>
-      </c>
-      <c r="E66" s="2" t="inlineStr">
-        <is>
-          <t>The Medical Training Prioritisation Act 2026: What It Means for IMGs</t>
-        </is>
-      </c>
-      <c r="F66" s="2" t="inlineStr">
-        <is>
-          <t>/news#medical-training-prioritisation-act-2026-imgs</t>
-        </is>
-      </c>
-      <c r="G66" s="2" t="inlineStr">
-        <is>
-          <t>Informational</t>
-        </is>
-      </c>
-      <c r="H66" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="I66" s="2" t="inlineStr">
-        <is>
-          <t>Established (30 posts)</t>
-        </is>
-      </c>
-      <c r="J66" s="2" t="inlineStr">
-        <is>
-          <t>02 July 2026</t>
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>UKMLA AKT</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>AKT exam; UKMLA AKT pass mark; how many questions in UKMLA AKT; UKMLA AKT exam preparation tips; UKMLA AKT vs CPSA difference</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>Exam Format</t>
+        </is>
+      </c>
+      <c r="D66" s="4" t="inlineStr">
+        <is>
+          <t>AKT Exam Pattern</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>AKT Exam Pattern</t>
+        </is>
+      </c>
+      <c r="F66" s="4" t="inlineStr">
+        <is>
+          <t>/exam-pattern/akt</t>
+        </is>
+      </c>
+      <c r="G66" s="4" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H66" s="4" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I66" s="4" t="inlineStr">
+        <is>
+          <t>Established (7 posts)</t>
+        </is>
+      </c>
+      <c r="J66" s="4" t="inlineStr">
+        <is>
+          <t>N/A (static page)</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>UK doctor salary for Indian doctors</t>
-        </is>
-      </c>
-      <c r="B67" s="3" t="inlineStr">
-        <is>
-          <t>UKMLA for Indian doctors; salary of doctor in UK for Indian; UKMLA for GP doctors in UK; UK doctor salary 2026; UKMLA eligibility for Indian doctors</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
-        <is>
-          <t>Eligibility</t>
-        </is>
-      </c>
-      <c r="E67" s="2" t="inlineStr">
-        <is>
-          <t>UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home</t>
-        </is>
-      </c>
-      <c r="F67" s="2" t="inlineStr">
-        <is>
-          <t>/news#uk-doctor-salary-guide-for-indian-doctors</t>
-        </is>
-      </c>
-      <c r="G67" s="2" t="inlineStr">
-        <is>
-          <t>Informational</t>
-        </is>
-      </c>
-      <c r="H67" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="I67" s="2" t="inlineStr">
-        <is>
-          <t>Established (30 posts)</t>
-        </is>
-      </c>
-      <c r="J67" s="2" t="inlineStr">
-        <is>
-          <t>01 July 2026</t>
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t>UKMLA CPSA</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>CPSA exam; UKMLA CPSA stations examples; UKMLA CPSA centre Manchester</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>Exam Format</t>
+        </is>
+      </c>
+      <c r="D67" s="4" t="inlineStr">
+        <is>
+          <t>CPSA Exam Pattern</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>CPSA Exam Pattern</t>
+        </is>
+      </c>
+      <c r="F67" s="4" t="inlineStr">
+        <is>
+          <t>/exam-pattern/cpsa</t>
+        </is>
+      </c>
+      <c r="G67" s="4" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H67" s="4" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I67" s="4" t="inlineStr">
+        <is>
+          <t>Established (7 posts)</t>
+        </is>
+      </c>
+      <c r="J67" s="4" t="inlineStr">
+        <is>
+          <t>N/A (static page)</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>UK visa for international doctors</t>
+          <t>breaking bad news CPSA</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>UKMLA for GP doctors in UK; how to get UK visa for doctors; UK medical registration for international doctors; UKMLA for Indian doctors; UKMLA for Nigerian doctors</t>
+          <t>UKMLA CPSA; ukmla news; What is the UKMLA CPSA?; CPSA exam; CPSA Details</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
+          <t>Exam Format</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Eligibility</t>
+          <t>CPSA Exam Pattern</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>UK Visa Guide for International Doctors: Health and Care Worker Visa Explained</t>
+          <t>Breaking Bad News in the CPSA: A Complete Guide</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>/news#uk-visa-guide-for-international-doctors</t>
+          <t>/news#breaking-bad-news-in-the-cpsa</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -3996,44 +3996,44 @@
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>Established (30 posts)</t>
+          <t>Established (7 posts)</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>01 July 2026</t>
+          <t>02 July 2026</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>UK visa salary threshold 2026</t>
+          <t>CPSA clinical examination stations</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>UK doctor salary 2026; UKMLA fees for doctors 2026; UKMLA syllabus 2026 changes; how to get UK visa for doctors; UKMLA for GP doctors in UK</t>
+          <t>UKMLA CPSA; What is the UKMLA CPSA?; UKMLA CPSA stations list; UKMLA clinical examination tips; UKMLA CPSA stations examples</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
+          <t>Exam Format</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Eligibility</t>
+          <t>CPSA Exam Pattern</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>UK Visa Salary Threshold Changes 2026: What Doctors Need to Know</t>
+          <t>Clinical Examination Stations in the CPSA: A Practical Guide</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>/news#uk-visa-salary-threshold-changes-2026-for-doctors</t>
+          <t>/news#clinical-examination-cpsa-guide</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -4048,29 +4048,29 @@
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>Established (30 posts)</t>
+          <t>Established (7 posts)</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>02 July 2026</t>
+          <t>30 June 2026</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>UKMLA AKT test centres</t>
+          <t>how to read AKT stem</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>UKMLA AKT; ms akt; What is the UKMLA AKT?; UKMLA AKT test centres in India; UKMLA AKT test centres in Pakistan</t>
+          <t>UKMLA AKT; ms akt; What is the UKMLA AKT?; AKT exam; AKT Details</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
+          <t>Exam Format</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide</t>
+          <t>How to Read an AKT Stem: Avoiding Common Traps</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-akt-test-centres-guide</t>
+          <t>/news#how-to-read-akt-stem</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
@@ -4100,44 +4100,44 @@
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>Established (30 posts)</t>
+          <t>Established (7 posts)</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>01 July 2026</t>
+          <t>30 June 2026</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>UKMLA crash course for doctors</t>
+          <t>psychiatry communication CPSA</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>UKMLA for GP doctors in UK; UKMLA for Indian doctors; UKMLA for Nigerian doctors; UKMLA for Pakistani doctors; UKMLA for Bangladeshi doctors</t>
+          <t>UKMLA CPSA; What is the UKMLA CPSA?; UKMLA CPSA stations list; CPSA exam; UKMLA CPSA stations examples</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
+          <t>Exam Format</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Preparation</t>
+          <t>CPSA Exam Pattern</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>UKMLA Crash Course for Doctors: How to Choose the Right Intensive Course</t>
+          <t>Psychiatry Communication Stations: Handling Difficult Conversations</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-crash-course-for-doctors</t>
+          <t>/news#psychiatry-communication-cpsa-stations</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -4152,44 +4152,44 @@
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>Established (30 posts)</t>
+          <t>Established (7 posts)</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>02 July 2026</t>
+          <t>30 June 2026</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>UKMLA question bank</t>
+      <c r="A72" s="6" t="inlineStr">
+        <is>
+          <t>UKMLA AKT</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>best question bank for UKMLA; best question bank for UKMLA UK students; UKMLA question bank free for students; UKMLA AKT question bank free; UKMLA mock</t>
+          <t>ms akt; What is the UKMLA AKT?; AKT exam; how to prepare for UKMLA; AKT Details</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
+          <t>Exam Format</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Preparation</t>
+          <t>AKT Exam Pattern</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources</t>
+          <t>UKMLA AKT: Format, Question Types, and How to Prepare</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-question-bank-and-mock-tests</t>
+          <t>/news#ukmla-akt-format-preparation</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -4204,44 +4204,44 @@
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>Established (30 posts)</t>
+          <t>Established (7 posts)</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>01 July 2026</t>
+          <t>30 June 2026</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>UKMLA for Bangladeshi doctors</t>
+      <c r="A73" s="6" t="inlineStr">
+        <is>
+          <t>UKMLA CPSA</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>UKMLA for GP doctors in UK; GMC registration process for doctors; UKMLA eligibility for Indian doctors; UKMLA fees for doctors 2026; UKMLA for Indian doctors</t>
+          <t>What is the UKMLA CPSA?; CPSA exam; UKMLA exam; what is the UKMLA exam; Clinical Skills (CPSA)</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
+          <t>Exam Format</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Eligibility</t>
+          <t>CPSA Exam Pattern</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+          <t>UKMLA CPSA: What the Clinical Exam Really Tests</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-for-bangladeshi-doctors</t>
+          <t>/news#ukmla-cpsa-what-it-tests</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -4256,44 +4256,44 @@
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>Established (30 posts)</t>
+          <t>Established (7 posts)</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>01 July 2026</t>
+          <t>30 June 2026</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>UKMLA for Egyptian doctors</t>
+          <t>Angoff standard setting UKMLA</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>UKMLA for GP doctors in UK; GMC registration process for doctors; UKMLA eligibility for Indian doctors; UKMLA fees for doctors 2026; UKMLA for Indian doctors</t>
+          <t>AKT Standard Setting: The Angoff Method; UKMLA AKT standard setting explained; UKMLA Results, Scoring &amp; Standard Setting; angoff definition; angoff method</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
+          <t>Exam Format</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Eligibility</t>
+          <t>Results and Scoring</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+          <t>What Is an Angoff Standard Setting and Why Does It Matter?</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-for-egyptian-doctors</t>
+          <t>/news#angoff-standard-setting-explained</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -4308,96 +4308,96 @@
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>Established (30 posts)</t>
+          <t>Established (7 posts)</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>01 July 2026</t>
+          <t>30 June 2026</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="inlineStr">
-        <is>
-          <t>UKMLA for Filipino doctors</t>
-        </is>
-      </c>
-      <c r="B75" s="3" t="inlineStr">
-        <is>
-          <t>UKMLA for GP doctors in UK; GMC registration process for doctors; UKMLA eligibility for Indian doctors; UKMLA fees for doctors 2026; UKMLA for Indian doctors</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
-        <is>
-          <t>Eligibility</t>
-        </is>
-      </c>
-      <c r="E75" s="2" t="inlineStr">
-        <is>
-          <t>UKMLA for Filipino Doctors: Eligibility, Fees and the Route to GMC Registration</t>
-        </is>
-      </c>
-      <c r="F75" s="2" t="inlineStr">
-        <is>
-          <t>/news#ukmla-for-filipino-doctors</t>
-        </is>
-      </c>
-      <c r="G75" s="2" t="inlineStr">
-        <is>
-          <t>Informational</t>
-        </is>
-      </c>
-      <c r="H75" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="I75" s="2" t="inlineStr">
-        <is>
-          <t>Established (30 posts)</t>
-        </is>
-      </c>
-      <c r="J75" s="2" t="inlineStr">
-        <is>
-          <t>01 July 2026</t>
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t>UKMLA preparation</t>
+        </is>
+      </c>
+      <c r="B75" s="5" t="inlineStr">
+        <is>
+          <t>how to prepare for UKMLA; UKMLA study plan; how long to study for UKMLA; UKMLA preparation 6 weeks</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>Exam Preparation</t>
+        </is>
+      </c>
+      <c r="D75" s="4" t="inlineStr">
+        <is>
+          <t>Preparation</t>
+        </is>
+      </c>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t>Preparation</t>
+        </is>
+      </c>
+      <c r="F75" s="4" t="inlineStr">
+        <is>
+          <t>/preparation</t>
+        </is>
+      </c>
+      <c r="G75" s="4" t="inlineStr">
+        <is>
+          <t>Commercial</t>
+        </is>
+      </c>
+      <c r="H75" s="4" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I75" s="4" t="inlineStr">
+        <is>
+          <t>Established (8 posts)</t>
+        </is>
+      </c>
+      <c r="J75" s="4" t="inlineStr">
+        <is>
+          <t>N/A (static page)</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>UKMLA for Gulf and Saudi doctors</t>
+          <t>UKMLA group study solo</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>UKMLA for GP doctors in UK; UKMLA for Saudi / Gulf doctors; UKMLA for Saudi doctors; GMC registration process for doctors; UKMLA eligibility for Indian doctors</t>
+          <t>UKMLA group study vs solo study; how long to study for UKMLA; UKMLA study plan; study plan; UKMLA study plan 12 weeks</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
+          <t>Exam Preparation</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Eligibility</t>
+          <t>Preparation</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+          <t>Group Study vs Solo Study for the UKMLA: What Works Best?</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-for-gulf-doctors</t>
+          <t>/news#group-study-vs-solo-ukmla</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -4412,44 +4412,44 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>Established (30 posts)</t>
+          <t>Established (8 posts)</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>01 July 2026</t>
+          <t>30 June 2026</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>UKMLA for international medical graduates</t>
+          <t>how to pass UKMLA on first attempt</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>international medical graduates; UKMLA eligibility for international medical graduates; UKMLA for Caribbean medical graduates; Eligibility for International Medical Graduates (IMGs); For International Medical Graduates (PLAB Route)</t>
+          <t>how to pass ukmla; UKMLA pass mark; UKMLA pass mark for IMG; UKMLA attempt limit for doctors; UKMLA AKT pass mark</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
+          <t>Exam Preparation</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Eligibility</t>
+          <t>Preparation</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>UKMLA for International Medical Graduates: Country-by-Country Quick Reference</t>
+          <t>How to Pass the UKMLA on Your First Attempt</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-for-international-medical-graduates-country-routes</t>
+          <t>/news#how-to-pass-ukmla-on-first-attempt</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -4464,44 +4464,44 @@
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>Established (30 posts)</t>
+          <t>Established (8 posts)</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>01 July 2026</t>
+          <t>02 July 2026</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>UKMLA for Nigerian doctors</t>
+          <t>UKMLA revision notes</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>UKMLA for GP doctors in UK; UKMLA eligibility for Indian doctors; UKMLA fees for doctors 2026; UKMLA for Indian doctors; UKMLA for Pakistani doctors</t>
+          <t>UKMLA revision notes tips; UKMLA pharmacology revision; AKT Revision Strategy; CPSA / OSCE Revision Strategy; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
+          <t>Exam Preparation</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Eligibility</t>
+          <t>Preparation</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC</t>
+          <t>How to Write UKMLA Revision Notes That Actually Work</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-for-nigerian-doctors</t>
+          <t>/news#ukmla-revision-notes-strategy</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
@@ -4516,44 +4516,44 @@
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>Established (30 posts)</t>
+          <t>Established (8 posts)</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>01 July 2026</t>
+          <t>30 June 2026</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>UKMLA for Pakistani doctors</t>
+          <t>UKMLA exam anxiety tips</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>UKMLA for GP doctors in UK; UKMLA eligibility for Indian doctors; UKMLA fees for doctors 2026; UKMLA for Indian doctors; UKMLA for Nigerian doctors</t>
+          <t>UKMLA exam; what is the UKMLA exam; The Exam; UKMLA exam in Dubai; AKT exam</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
+          <t>Exam Preparation</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Eligibility</t>
+          <t>Preparation</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK</t>
+          <t>Managing UKMLA Exam Anxiety: Practical Strategies for Candidates</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-for-pakistani-doctors</t>
+          <t>/news#managing-ukmla-exam-anxiety</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -4568,7 +4568,7 @@
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>Established (30 posts)</t>
+          <t>Established (8 posts)</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
@@ -4580,32 +4580,32 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>UKMLA for refugee doctors</t>
+          <t>UKMLA mock exams</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>UKMLA for GP doctors in UK; UKMLA fees for refugee doctors; UKMLA for Indian doctors; UKMLA for Nigerian doctors; UKMLA for Pakistani doctors</t>
+          <t>UKMLA mock; UKMLA preparation; Preparation; UKMLA mock exam practice; free UKMLA mock test</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
+          <t>Exam Preparation</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Eligibility</t>
+          <t>Preparation</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>UKMLA for Refugee Doctors: The GMC Assistance Programme and Fee Support</t>
+          <t>The Role of Mock Exams in UKMLA Preparation</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-for-refugee-doctors</t>
+          <t>/news#mock-exams-ukmla-preparation</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -4620,44 +4620,44 @@
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>Established (30 posts)</t>
+          <t>Established (8 posts)</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>01 July 2026</t>
+          <t>30 June 2026</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>UKMLA for South African doctors</t>
+          <t>UKMLA AKT preparation countdown</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>UKMLA for GP doctors in UK; GMC registration process for doctors; UKMLA eligibility for Indian doctors; UKMLA fees for doctors 2026; UKMLA for Indian doctors</t>
+          <t>UKMLA AKT; UKMLA preparation; ms akt; What is the UKMLA AKT?; Preparation</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
+          <t>Exam Preparation</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Eligibility</t>
+          <t>Preparation</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+          <t>Three Months to the UKMLA AKT: A Final Preparation Countdown</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-for-south-african-doctors</t>
+          <t>/news#three-months-ukmla-akt-countdown</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -4672,44 +4672,44 @@
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>Established (30 posts)</t>
+          <t>Established (8 posts)</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>01 July 2026</t>
+          <t>30 June 2026</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>UKMLA for Sri Lankan doctors</t>
+          <t>time management UKMLA AKT</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>UKMLA for GP doctors in UK; GMC registration process for doctors; UKMLA eligibility for Indian doctors; UKMLA fees for doctors 2026; UKMLA for Indian doctors</t>
+          <t>UKMLA AKT; ms akt; What is the UKMLA AKT?; AKT exam; AKT Details</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
+          <t>Exam Preparation</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Eligibility</t>
+          <t>Preparation</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+          <t>Time Management in the UKMLA AKT: Strategies That Work</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-for-sri-lankan-doctors</t>
+          <t>/news#time-management-akt-ukmla</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
@@ -4724,44 +4724,44 @@
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>Established (30 posts)</t>
+          <t>Established (8 posts)</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>01 July 2026</t>
+          <t>30 June 2026</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>UKMLA NHS job after exam</t>
+          <t>UKMLA Anki deck download</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>UKMLA exam; what is the UKMLA exam; The Exam; gmc exam; NHS jobs after GMC registration</t>
+          <t>ukmla guide; UKMLA syllabus pdf download; What Is the UKMLA? A Complete Beginner's Guide; UKMLA pharmacology revision; about ukmla guide</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
+          <t>Exam Preparation</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Eligibility</t>
+          <t>Preparation</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
+          <t>UKMLA Anki Deck and Flashcard Revision: The Complete Guide</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-to-nhs-job-pathway</t>
+          <t>/news#ukmla-anki-deck-and-flashcard-revision-guide</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
@@ -4776,24 +4776,24 @@
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>Established (30 posts)</t>
+          <t>Established (8 posts)</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>01 July 2026</t>
+          <t>02 July 2026</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>UKMLA vs AMC exam comparison</t>
+          <t>dependent visa for doctors' families</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>UKMLA exam; what is the UKMLA exam; The Exam; Exam Pattern Comparison; UKMLA vs MCCQE Canada</t>
+          <t>UKMLA for GP doctors in UK; how to get UK visa for doctors; UKMLA for Indian doctors; UKMLA for Nigerian doctors; UKMLA for Pakistani doctors</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -4803,17 +4803,17 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>UKMLA vs PLAB</t>
+          <t>Eligibility</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>UKMLA vs AMC and MCCQE: Comparing the UK Route to Australia and Canada</t>
+          <t>Bringing Your Family to the UK: A Dependant Visa Guide for Doctors</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-vs-amc-and-mccqe-comparison</t>
+          <t>/news#bringing-family-to-uk-dependent-visa-guide</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
@@ -4828,24 +4828,24 @@
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>Established (30 posts)</t>
+          <t>Established (43 posts)</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>01 July 2026</t>
+          <t>02 July 2026</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>UKMLA vs NEET PG</t>
+          <t>English language requirement for UKMLA India</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>UKMLA exam for Indian medical graduates; UKMLA for international medical graduates; UKMLA for Caribbean medical graduates; international medical graduates; UKMLA for Indian doctors</t>
+          <t>UKMLA India; English language requirement for UKMLA; English requirement for UKMLA India (IELTS/OET); UKMLA OET or IELTS requirement; Step 2: English Language Proficiency</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -4855,17 +4855,17 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>UKMLA vs PLAB</t>
+          <t>Eligibility</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?</t>
+          <t>English Language Requirements for the UKMLA: IELTS and OET Scores Explained</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-vs-neet-pg</t>
+          <t>/news#english-language-requirement-for-ukmla-india</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>Established (30 posts)</t>
+          <t>Established (43 posts)</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
@@ -4892,12 +4892,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>UKMLA vs USMLE</t>
+          <t>foundation year vs specialty training IMG</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>UKMLA vs USMLE which is easier; UKMLA exam; what is the UKMLA exam; The Exam; UKMLA vs USMLE cost and difficulty</t>
+          <t>UKMLA for IMG; UKMLA and foundation year application; UKMLA fail foundation year impact; img guide; IMG Pathway</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -4907,17 +4907,17 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>UKMLA vs PLAB</t>
+          <t>Eligibility</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
+          <t>Foundation Year vs Specialty Training for IMGs: Which Route After the UKMLA?</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-vs-usmle-comparison</t>
+          <t>/news#foundation-year-vs-specialty-training-for-imgs</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
@@ -4932,29 +4932,29 @@
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>Established (30 posts)</t>
+          <t>Established (43 posts)</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>01 July 2026</t>
+          <t>02 July 2026</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>GMC fitness to practise</t>
+          <t>GMC registration requirements for international doctors</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>UKMLA for GP doctors in UK; gmc exam; gmc licensing; gmc Manchester; gmc updates</t>
+          <t>UKMLA for GP doctors in UK; UKMLA registration; GMC registration process for doctors; UKMLA registration process GMC; GMC registration requirements IMG</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Professional Practice &amp; Safety</t>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
@@ -4964,12 +4964,12 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>GMC Fitness to Practise Explained: What New Doctors Need to Know</t>
+          <t>GMC Registration Requirements for International Doctors: The Complete Process</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>/news#gmc-fitness-to-practise-explained-for-new-doctors</t>
+          <t>/news#gmc-registration-requirements-for-international-doctors</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
@@ -4984,29 +4984,29 @@
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>Established (6 posts)</t>
+          <t>Established (43 posts)</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>02 July 2026</t>
+          <t>01 July 2026</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>GMC regulation of physician associates</t>
+          <t>GMC registration from India</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>UKMLA for GP doctors in UK; gmc exam; gmc licensing; gmc Manchester; gmc updates</t>
+          <t>UKMLA India; UKMLA registration; gmc registration guide; how to apply for UKMLA from India; UKMLA GMC registration for graduates</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Professional Practice &amp; Safety</t>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
@@ -5016,12 +5016,12 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>GMC Regulation of Physician Associates: What Doctors Need to Know</t>
+          <t>GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>/news#gmc-regulation-of-physician-associates-what-doctors-need-to-know</t>
+          <t>/news#gmc-registration-and-epic-verification-india</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
@@ -5036,40 +5036,44 @@
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>Established (6 posts)</t>
+          <t>Established (43 posts)</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>02 July 2026</t>
+          <t>01 July 2026</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>Good Medical Practice UKMLA</t>
+          <t>GMC registration for EU and Irish doctors</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>how to practice medicine in UK; medical acronyms; medical students; UKMLA for international medical graduates; UKMLA mock exam practice</t>
+          <t>UKMLA for GP doctors in UK; UKMLA registration; GMC registration process for doctors; UKMLA GMC registration for graduates; UKMLA vs specialist registration GMC</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Professional Practice &amp; Safety</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr"/>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>Good Medical Practice and the UKMLA: What the GMC Expects</t>
+          <t>GMC Registration for EU and Irish Doctors: What Changed After Brexit</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>/news#good-medical-practice-ukmla</t>
+          <t>/news#gmc-registration-for-eu-and-irish-doctors</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
@@ -5084,40 +5088,44 @@
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>Established (6 posts)</t>
+          <t>Established (43 posts)</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>30 June 2026</t>
+          <t>02 July 2026</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>patient safety UKMLA</t>
+          <t>how to become a doctor in UK from India</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>1. Patient Presentations; The official GMC MLA Content Map listing core patient presentations, conditions, and practical procedures</t>
+          <t>how to become a doctor in UK; UKMLA India; how to become a doctor in UK from Nigeria; how to become a doctor in UK from Pakistan; how to apply for UKMLA from India</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Professional Practice &amp; Safety</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr"/>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting</t>
+          <t>How to Become a Doctor in the UK from India: The Complete UKMLA Route</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>/news#patient-safety-ukmla-prescribing-errors</t>
+          <t>/news#how-to-become-a-doctor-in-uk-from-india</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
@@ -5132,40 +5140,44 @@
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>Established (6 posts)</t>
+          <t>Established (43 posts)</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>30 June 2026</t>
+          <t>01 July 2026</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>safeguarding UKMLA</t>
+          <t>how to become a doctor in UK</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>ukmla guide; UKMLA pharmacology revision; about ukmla guide; contact ukmla guide; img guide</t>
+          <t>how to become a doctor in UK from India; how to become a doctor in UK from Nigeria; how to become a doctor in UK from Pakistan; UKMLA registration; gmc registration guide</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Professional Practice &amp; Safety</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr"/>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>Safeguarding Adults and Children: A UKMLA Revision Guide</t>
+          <t>How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>/news#safeguarding-ukmla-revision</t>
+          <t>/news#how-to-become-a-doctor-in-the-uk-gmc-registration-guide</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
@@ -5180,44 +5192,44 @@
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>Established (6 posts)</t>
+          <t>Established (43 posts)</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>30 June 2026</t>
+          <t>01 July 2026</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>GMC revalidation process</t>
+          <t>NHS CV and application</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>UKMLA registration process GMC; GMC registration process for doctors; GMC EPIC verification process; UKMLA for GP doctors in UK; gmc exam</t>
+          <t>UKMLA and foundation year application; UKMLA for doctors already working in NHS; UKMLA NHS job after exam; Step 6: Submit the GMC Application; NHS jobs after GMC registration</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Professional Practice &amp; Safety</t>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Registration Guide</t>
+          <t>Eligibility</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>The GMC Revalidation Process, Explained for New Doctors</t>
+          <t>How to Write an NHS CV and Application That Gets Shortlisted</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>/news#gmc-revalidation-process-explained</t>
+          <t>/news#how-to-write-an-nhs-cv-and-application</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
@@ -5232,7 +5244,7 @@
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>Established (6 posts)</t>
+          <t>Established (43 posts)</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
@@ -5242,234 +5254,242 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="4" t="inlineStr">
-        <is>
-          <t>UKMLA for IMG</t>
-        </is>
-      </c>
-      <c r="B93" s="5" t="inlineStr">
-        <is>
-          <t>UKMLA for international medical graduates; UKMLA eligibility; UKMLA exam for UK medical students; UKMLA eligibility for international medical graduates</t>
-        </is>
-      </c>
-      <c r="C93" s="4" t="inlineStr">
-        <is>
-          <t>Registration &amp; Eligibility</t>
-        </is>
-      </c>
-      <c r="D93" s="4" t="inlineStr">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>is Indian MBBS valid in UK</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>MBBS in UK for Indian students; UKMLA after MBBS; UKMLA for Indian doctors; UKMLA after MBBS in India; UKMLA eligibility for Indian doctors</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>Eligibility</t>
         </is>
       </c>
-      <c r="E93" s="4" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>/news#is-indian-mbbs-valid-in-uk</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>Established (43 posts)</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>01 July 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>locum vs substantive NHS posts</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>Posts; UKMLA for doctors already working in NHS; UKMLA NHS job after exam; NHS jobs after GMC registration; UKMLA vs USMLE which is easier</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>Eligibility</t>
         </is>
       </c>
-      <c r="F93" s="4" t="inlineStr">
-        <is>
-          <t>/eligibility</t>
-        </is>
-      </c>
-      <c r="G93" s="4" t="inlineStr">
-        <is>
-          <t>Informational</t>
-        </is>
-      </c>
-      <c r="H93" s="4" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="I93" s="4" t="inlineStr">
-        <is>
-          <t>Established (19 posts)</t>
-        </is>
-      </c>
-      <c r="J93" s="4" t="inlineStr">
-        <is>
-          <t>N/A (static page)</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="4" t="inlineStr">
-        <is>
-          <t>Fees</t>
-        </is>
-      </c>
-      <c r="B94" s="5" t="inlineStr"/>
-      <c r="C94" s="4" t="inlineStr">
-        <is>
-          <t>Registration &amp; Eligibility</t>
-        </is>
-      </c>
-      <c r="D94" s="4" t="inlineStr">
-        <is>
-          <t>Fees</t>
-        </is>
-      </c>
-      <c r="E94" s="4" t="inlineStr">
-        <is>
-          <t>Fees</t>
-        </is>
-      </c>
-      <c r="F94" s="4" t="inlineStr">
-        <is>
-          <t>/fees</t>
-        </is>
-      </c>
-      <c r="G94" s="4" t="inlineStr">
-        <is>
-          <t>Commercial</t>
-        </is>
-      </c>
-      <c r="H94" s="4" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="I94" s="4" t="inlineStr">
-        <is>
-          <t>Established (19 posts)</t>
-        </is>
-      </c>
-      <c r="J94" s="4" t="inlineStr">
-        <is>
-          <t>N/A (static page)</t>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>Locum vs Substantive NHS Posts: Which Is Right for You?</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>/news#locum-vs-substantive-nhs-posts-explained</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>Established (43 posts)</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>02 July 2026</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="4" t="inlineStr">
-        <is>
-          <t>UKMLA dates</t>
-        </is>
-      </c>
-      <c r="B95" s="5" t="inlineStr"/>
-      <c r="C95" s="4" t="inlineStr">
-        <is>
-          <t>Registration &amp; Eligibility</t>
-        </is>
-      </c>
-      <c r="D95" s="4" t="inlineStr">
-        <is>
-          <t>Key Dates</t>
-        </is>
-      </c>
-      <c r="E95" s="4" t="inlineStr">
-        <is>
-          <t>Key Dates</t>
-        </is>
-      </c>
-      <c r="F95" s="4" t="inlineStr">
-        <is>
-          <t>/key-dates</t>
-        </is>
-      </c>
-      <c r="G95" s="4" t="inlineStr">
-        <is>
-          <t>Transactional</t>
-        </is>
-      </c>
-      <c r="H95" s="4" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="I95" s="4" t="inlineStr">
-        <is>
-          <t>Established (19 posts)</t>
-        </is>
-      </c>
-      <c r="J95" s="4" t="inlineStr">
-        <is>
-          <t>N/A (static page)</t>
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>MBBS in UK for Indian students</t>
+        </is>
+      </c>
+      <c r="B95" s="3" t="inlineStr">
+        <is>
+          <t>is Indian MBBS valid in UK; UKMLA after MBBS; UKMLA for Indian doctors; UKMLA for IMG; medical students</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>/news#mbbs-in-uk-for-indian-students</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>Established (43 posts)</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>01 July 2026</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="4" t="inlineStr">
-        <is>
-          <t>UKMLA registration</t>
-        </is>
-      </c>
-      <c r="B96" s="5" t="inlineStr">
-        <is>
-          <t>UKMLA booking; English language requirement for UKMLA; UKMLA registration process GMC</t>
-        </is>
-      </c>
-      <c r="C96" s="4" t="inlineStr">
-        <is>
-          <t>Registration &amp; Eligibility</t>
-        </is>
-      </c>
-      <c r="D96" s="4" t="inlineStr">
-        <is>
-          <t>Registration Guide</t>
-        </is>
-      </c>
-      <c r="E96" s="4" t="inlineStr">
-        <is>
-          <t>Registration Guide</t>
-        </is>
-      </c>
-      <c r="F96" s="4" t="inlineStr">
-        <is>
-          <t>/registration-guide</t>
-        </is>
-      </c>
-      <c r="G96" s="4" t="inlineStr">
-        <is>
-          <t>Informational</t>
-        </is>
-      </c>
-      <c r="H96" s="4" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="I96" s="4" t="inlineStr">
-        <is>
-          <t>Established (19 posts)</t>
-        </is>
-      </c>
-      <c r="J96" s="4" t="inlineStr">
-        <is>
-          <t>N/A (static page)</t>
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>Medical Training Initiative scheme closure 2026</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t>medical licence UK for doctors 2026; UK medical licence requirements 2026; ukmla syllabus 2026; medical acronyms; medical students</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>Medical Training Initiative Scheme Closure 2026: What IMGs Need to Know</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>/news#medical-training-initiative-scheme-closure-2026</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>Established (43 posts)</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>02 July 2026</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>UKMLA disability access adjustments</t>
+          <t>NHS job interview preparation</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>ukmla guide; Reasonable Adjustments; reasonable adjustments gmc; about ukmla guide; contact ukmla guide</t>
+          <t>UKMLA preparation; Preparation; Preparation Guide; UKMLA Preparation Guide; UKMLA OSCE preparation</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Registration &amp; Eligibility</t>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Appeals and Resits</t>
+          <t>Eligibility</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide</t>
+          <t>NHS Job Interview Preparation: A Complete Guide for IMGs and UK Graduates</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>/news#disability-access-ukmla-guide</t>
+          <t>/news#nhs-job-interview-preparation-guide</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
@@ -5484,29 +5504,29 @@
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>Established (19 posts)</t>
+          <t>Established (43 posts)</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>30 June 2026</t>
+          <t>02 July 2026</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>UKMLA exemptions for specialist doctors</t>
+          <t>relocating to the UK for IMG doctors</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>UKMLA for GP doctors in UK; do all doctors need to take UKMLA; is UKMLA required for experienced doctors; UKMLA for Indian doctors; UKMLA for Nigerian doctors</t>
+          <t>UKMLA for GP doctors in UK; UKMLA for IMG; img guide; UKMLA for Indian doctors; UKMLA for Nigerian doctors</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Registration &amp; Eligibility</t>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
@@ -5516,12 +5536,12 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs</t>
+          <t>Relocating to the UK: A Practical Guide for IMG Doctors</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-exemptions-for-specialist-and-gp-doctors</t>
+          <t>/news#relocating-to-the-uk-a-practical-guide-for-img-doctors</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
@@ -5536,29 +5556,29 @@
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>Established (19 posts)</t>
+          <t>Established (43 posts)</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>01 July 2026</t>
+          <t>02 July 2026</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>GMC English language exemption</t>
+          <t>returning to practise in Gulf countries</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>English language requirement for UKMLA; OET vs IELTS for GMC registration; UKMLA exemption for specialists; gmc exam; gmc licensing</t>
+          <t>ukmla guide; UKMLA for Saudi / Gulf doctors; which countries accept UKMLA; about ukmla guide; contact ukmla guide</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Registration &amp; Eligibility</t>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
@@ -5568,12 +5588,12 @@
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>GMC English Language Exemption: Do You Need to Sit IELTS or OET?</t>
+          <t>Returning to Practise in Gulf Countries: The DataFlow Verification Guide</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>/news#gmc-english-language-exemption-for-imgs</t>
+          <t>/news#returning-to-practise-in-gulf-countries-dataflow-guide</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
@@ -5588,7 +5608,7 @@
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>Established (19 posts)</t>
+          <t>Established (43 posts)</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr">
@@ -5600,32 +5620,32 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>GMC Order reform 2026</t>
+          <t>Medical Training Prioritisation Act 2026</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>cost of GMC registration 2026; gmc exam; gmc licensing; gmc Manchester; gmc updates</t>
+          <t>medical licence UK for doctors 2026; UK medical licence requirements 2026; ukmla syllabus 2026; medical acronyms; medical students</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Registration &amp; Eligibility</t>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Registration Guide</t>
+          <t>Eligibility</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>GMC Order Reform 2026: The Consultation on Protected Medical Titles</t>
+          <t>The Medical Training Prioritisation Act 2026: What It Means for IMGs</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>/news#gmc-order-reform-2026-protected-medical-titles</t>
+          <t>/news#medical-training-prioritisation-act-2026-imgs</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
@@ -5640,7 +5660,7 @@
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>Established (19 posts)</t>
+          <t>Established (43 posts)</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
@@ -5652,32 +5672,32 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>GMC registration refund policy</t>
+          <t>UK doctor salary for Indian doctors</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>UKMLA registration; UKMLA GMC registration for graduates; UKMLA vs specialist registration GMC; UKMLA registration process GMC; gmc registration guide</t>
+          <t>UKMLA for Indian doctors; salary of doctor in UK for Indian; UKMLA for GP doctors in UK; UK doctor salary 2026; UKMLA eligibility for Indian doctors</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Registration &amp; Eligibility</t>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Fees</t>
+          <t>Eligibility</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>GMC Registration Refund Policy: When You Can (and Can't) Get Your Fee Back</t>
+          <t>UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>/news#gmc-registration-refund-policy</t>
+          <t>/news#uk-doctor-salary-guide-for-indian-doctors</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
@@ -5692,44 +5712,44 @@
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>Established (19 posts)</t>
+          <t>Established (43 posts)</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
-          <t>02 July 2026</t>
+          <t>01 July 2026</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>GMC Welcome to UK Practice</t>
+          <t>UK visa for international doctors</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>how to practice medicine in UK; UKMLA practice questions free; gmc exam; gmc licensing; gmc Manchester</t>
+          <t>UKMLA for GP doctors in UK; how to get UK visa for doctors; UK medical registration for international doctors; UKMLA for Indian doctors; UKMLA for Nigerian doctors</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Registration &amp; Eligibility</t>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Registration Guide</t>
+          <t>Eligibility</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>GMC Welcome to UK Practice: A Guide to the Free Induction Workshop</t>
+          <t>UK Visa Guide for International Doctors: Health and Care Worker Visa Explained</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>/news#gmc-welcome-to-uk-practice-induction-guide</t>
+          <t>/news#uk-visa-guide-for-international-doctors</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
@@ -5744,44 +5764,44 @@
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>Established (19 posts)</t>
+          <t>Established (43 posts)</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>02 July 2026</t>
+          <t>01 July 2026</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>how long does GMC registration take</t>
+          <t>UK visa salary threshold 2026</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>UKMLA registration; GMC registration timeline how long; UKMLA GMC registration for graduates; UKMLA vs specialist registration GMC; UKMLA registration process GMC</t>
+          <t>UK doctor salary 2026; UKMLA fees for doctors 2026; UKMLA syllabus 2026 changes; how to get UK visa for doctors; UKMLA for GP doctors in UK</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Registration &amp; Eligibility</t>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Registration Guide</t>
+          <t>Eligibility</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>How Long Does GMC Registration Take? A Realistic Timeline</t>
+          <t>UK Visa Salary Threshold Changes 2026: What Doctors Need to Know</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>/news#how-long-does-gmc-registration-take</t>
+          <t>/news#uk-visa-salary-threshold-changes-2026-for-doctors</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
@@ -5796,7 +5816,7 @@
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>Established (19 posts)</t>
+          <t>Established (43 posts)</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr">
@@ -5808,32 +5828,32 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>how to register for PLAB 1</t>
+          <t>UKMLA AKT test centres</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>PLAB vs UKMLA; plab 1; plab 2; UKMLA vs PLAB; is UKMLA replacing PLAB</t>
+          <t>UKMLA AKT; ms akt; What is the UKMLA AKT?; UKMLA AKT test centres in India; UKMLA AKT test centres in Pakistan</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Registration &amp; Eligibility</t>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Registration Guide</t>
+          <t>AKT Exam Pattern</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>How to Register for PLAB 1: A Step-by-Step Guide for IMGs</t>
+          <t>UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>/news#how-to-register-plab-1</t>
+          <t>/news#ukmla-akt-test-centres-guide</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
@@ -5848,44 +5868,44 @@
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>Established (19 posts)</t>
+          <t>Established (43 posts)</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>30 June 2026</t>
+          <t>01 July 2026</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>locally employed doctors GMC registration</t>
+          <t>UKMLA crash course for doctors</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>UKMLA for GP doctors in UK; UKMLA registration; UKMLA vs specialist registration GMC; GMC registration process for doctors; UKMLA GMC registration for graduates</t>
+          <t>UKMLA for GP doctors in UK; UKMLA for Indian doctors; UKMLA for Nigerian doctors; UKMLA for Pakistani doctors; UKMLA for Bangladeshi doctors</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>Registration &amp; Eligibility</t>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>Registration Guide</t>
+          <t>Preparation</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>Locally Employed Doctors: The Route to Full and Specialist GMC Registration</t>
+          <t>UKMLA Crash Course for Doctors: How to Choose the Right Intensive Course</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>/news#locally-employed-doctors-route-to-gmc-registration</t>
+          <t>/news#ukmla-crash-course-for-doctors</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
@@ -5900,7 +5920,7 @@
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>Established (19 posts)</t>
+          <t>Established (43 posts)</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr">
@@ -5912,32 +5932,32 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>OET vs IELTS for GMC registration</t>
+          <t>UKMLA question bank</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>UKMLA registration; UKMLA GMC registration for graduates; UKMLA OET or IELTS requirement; UKMLA vs specialist registration GMC; UKMLA registration process GMC</t>
+          <t>best question bank for UKMLA; best question bank for UKMLA UK students; UKMLA question bank free for students; UKMLA AKT question bank free; UKMLA mock</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Registration &amp; Eligibility</t>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Eligibility</t>
+          <t>Preparation</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>OET vs IELTS for GMC Registration: Which Should You Take?</t>
+          <t>UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>/news#oet-vs-ielts-for-gmc-registration-comparison</t>
+          <t>/news#ukmla-question-bank-and-mock-tests</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
@@ -5952,29 +5972,29 @@
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>Established (19 posts)</t>
+          <t>Established (43 posts)</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
-          <t>02 July 2026</t>
+          <t>01 July 2026</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>internship requirement for GMC registration</t>
+          <t>UKMLA for Bangladeshi doctors</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>internship requirement for GMC; UKMLA registration; UKMLA GMC registration for graduates; UKMLA vs specialist registration GMC; UKMLA registration process GMC</t>
+          <t>UKMLA for GP doctors in UK; GMC registration process for doctors; UKMLA eligibility for Indian doctors; UKMLA fees for doctors 2026; UKMLA for Indian doctors</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>Registration &amp; Eligibility</t>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
@@ -5984,12 +6004,12 @@
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>The Internship Requirement for GMC Registration, Explained</t>
+          <t>UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>/news#internship-requirement-for-gmc-registration</t>
+          <t>/news#ukmla-for-bangladeshi-doctors</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
@@ -6004,44 +6024,44 @@
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>Established (19 posts)</t>
+          <t>Established (43 posts)</t>
         </is>
       </c>
       <c r="J107" s="2" t="inlineStr">
         <is>
-          <t>02 July 2026</t>
+          <t>01 July 2026</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>UKMLA exam booking process</t>
+          <t>UKMLA for Chinese doctors</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>UKMLA booking; UKMLA exam; what is the UKMLA exam; The Exam; UKMLA booking process for students</t>
+          <t>UKMLA for GP doctors in UK; GMC registration process for doctors; UKMLA eligibility for Indian doctors; UKMLA fees for doctors 2026; UKMLA for Indian doctors</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Registration &amp; Eligibility</t>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Registration Guide</t>
+          <t>Eligibility</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>The UKMLA Exam Booking Process: A Step-by-Step Walkthrough</t>
+          <t>UKMLA for Chinese Doctors: Eligibility, Fees and the Route to GMC Registration</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-exam-booking-process-gmc-online</t>
+          <t>/news#ukmla-for-chinese-doctors</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
@@ -6056,7 +6076,7 @@
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>Established (19 posts)</t>
+          <t>Established (43 posts)</t>
         </is>
       </c>
       <c r="J108" s="2" t="inlineStr">
@@ -6068,32 +6088,32 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>types of GMC registration</t>
+          <t>UKMLA for Egyptian doctors</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t>UKMLA registration; UKMLA vs specialist registration GMC; UKMLA GMC registration for graduates; UKMLA registration process GMC; gmc registration guide</t>
+          <t>UKMLA for GP doctors in UK; GMC registration process for doctors; UKMLA eligibility for Indian doctors; UKMLA fees for doctors 2026; UKMLA for Indian doctors</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>Registration &amp; Eligibility</t>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>Registration Guide</t>
+          <t>Eligibility</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>Types of GMC Registration Explained: Provisional, Full, Specialist and GP</t>
+          <t>UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>/news#types-of-gmc-registration-explained</t>
+          <t>/news#ukmla-for-egyptian-doctors</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
@@ -6108,29 +6128,29 @@
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
-          <t>Established (19 posts)</t>
+          <t>Established (43 posts)</t>
         </is>
       </c>
       <c r="J109" s="2" t="inlineStr">
         <is>
-          <t>02 July 2026</t>
+          <t>01 July 2026</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>UKMLA eligibility</t>
+          <t>UKMLA for Filipino doctors</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>Eligibility; UKMLA exam; what is the UKMLA exam; The Exam; UKMLA Eligibility Pathways</t>
+          <t>UKMLA for GP doctors in UK; GMC registration process for doctors; UKMLA eligibility for Indian doctors; UKMLA fees for doctors 2026; UKMLA for Indian doctors</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Registration &amp; Eligibility</t>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
@@ -6140,12 +6160,12 @@
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>UKMLA Eligibility: Who Can Sit the Exam?</t>
+          <t>UKMLA for Filipino Doctors: Eligibility, Fees and the Route to GMC Registration</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-eligibility-who-can-sit</t>
+          <t>/news#ukmla-for-filipino-doctors</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
@@ -6160,44 +6180,44 @@
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>Established (19 posts)</t>
+          <t>Established (43 posts)</t>
         </is>
       </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
-          <t>30 June 2026</t>
+          <t>01 July 2026</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>UKMLA exam fees for IMG</t>
+          <t>UKMLA for Gulf and Saudi doctors</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>UKMLA exam; UKMLA fees; UKMLA for IMG; what is the UKMLA exam; The Exam</t>
+          <t>UKMLA for GP doctors in UK; UKMLA for Saudi / Gulf doctors; UKMLA for Saudi doctors; GMC registration process for doctors; UKMLA eligibility for Indian doctors</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>Registration &amp; Eligibility</t>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>Fees</t>
+          <t>Eligibility</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide</t>
+          <t>UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-fees-for-img-2026</t>
+          <t>/news#ukmla-for-gulf-doctors</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
@@ -6212,7 +6232,7 @@
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
-          <t>Established (19 posts)</t>
+          <t>Established (43 posts)</t>
         </is>
       </c>
       <c r="J111" s="2" t="inlineStr">
@@ -6224,32 +6244,32 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>UKMLA fees</t>
+          <t>UKMLA for international medical graduates</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
         <is>
-          <t>UKMLA fees for doctors 2026; UKMLA cost; UKMLA Fees and Costs 2026; UKMLA exam fees for IMG; UKMLA fees in Indian rupees</t>
+          <t>international medical graduates; UKMLA eligibility for international medical graduates; UKMLA for Caribbean medical graduates; Eligibility for International Medical Graduates (IMGs); For International Medical Graduates (PLAB Route)</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Registration &amp; Eligibility</t>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>Fees</t>
+          <t>Eligibility</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>UKMLA Fees: The Complete 2026 Cost Breakdown</t>
+          <t>UKMLA for International Medical Graduates: Country-by-Country Quick Reference</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-fees-explained</t>
+          <t>/news#ukmla-for-international-medical-graduates-country-routes</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
@@ -6264,49 +6284,49 @@
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>Established (19 posts)</t>
+          <t>Established (43 posts)</t>
         </is>
       </c>
       <c r="J112" s="2" t="inlineStr">
         <is>
-          <t>30 June 2026</t>
+          <t>01 July 2026</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>UKMLA key dates</t>
+          <t>UKMLA for Jamaican and Trinidadian doctors</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>UKMLA dates; Key Dates; Key Dates &amp; Timeline; UKMLA exam dates 2026; UKMLA exam dates and fees</t>
+          <t>UKMLA for GP doctors in UK; GMC registration process for doctors; UKMLA eligibility for Indian doctors; UKMLA fees for doctors 2026; UKMLA for Indian doctors</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>Registration &amp; Eligibility</t>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>Key Dates</t>
+          <t>Eligibility</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>UKMLA Key Dates and Sitting Schedule: What to Know</t>
+          <t>UKMLA for Jamaican and Trinidadian Doctors: Eligibility, Fees and the Route to GMC Registration</t>
         </is>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-key-dates-sitting-schedule</t>
+          <t>/news#ukmla-for-jamaican-and-trinidadian-doctors</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>Transactional</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
@@ -6316,44 +6336,44 @@
       </c>
       <c r="I113" s="2" t="inlineStr">
         <is>
-          <t>Established (19 posts)</t>
+          <t>Established (43 posts)</t>
         </is>
       </c>
       <c r="J113" s="2" t="inlineStr">
         <is>
-          <t>30 June 2026</t>
+          <t>02 July 2026</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>UKMLA resits</t>
+          <t>UKMLA for Jordanian and Iraqi doctors</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
         <is>
-          <t>Appeals &amp; Resits; UKMLA Appeals, Resits &amp; Reasonable Adjustments; Appeals, Resits &amp; Reasonable Adjustments; Attempt Limits and Retake Rules; plab attempt limits</t>
+          <t>UKMLA for GP doctors in UK; GMC registration process for doctors; UKMLA eligibility for Indian doctors; UKMLA fees for doctors 2026; UKMLA for Indian doctors</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Registration &amp; Eligibility</t>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>Appeals and Resits</t>
+          <t>Eligibility</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>UKMLA Resits: Rules, Limits, and How to Bounce Back</t>
+          <t>UKMLA for Jordanian and Iraqi Doctors: Eligibility, Fees and the Route to GMC Registration</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-resits-rules-limits</t>
+          <t>/news#ukmla-for-jordanian-and-iraqi-doctors</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
@@ -6368,29 +6388,29 @@
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>Established (19 posts)</t>
+          <t>Established (43 posts)</t>
         </is>
       </c>
       <c r="J114" s="2" t="inlineStr">
         <is>
-          <t>30 June 2026</t>
+          <t>02 July 2026</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>primary medical qualification GMC accepted</t>
+          <t>UKMLA for Kenyan and East African doctors</t>
         </is>
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>gmc exam; gmc licensing; gmc Manchester; gmc updates; medical acronyms</t>
+          <t>UKMLA for GP doctors in UK; UKMLA for South African doctors; GMC registration process for doctors; UKMLA eligibility for Indian doctors; UKMLA fees for doctors 2026</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>Registration &amp; Eligibility</t>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
@@ -6400,12 +6420,12 @@
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>Which Medical Qualifications Does the GMC Accept? PMQ Recognition Explained</t>
+          <t>UKMLA for Kenyan and East African Doctors: Eligibility, Fees and the Route to GMC Registration</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>/news#gmc-recognised-primary-medical-qualifications</t>
+          <t>/news#ukmla-for-kenyan-and-east-african-doctors</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
@@ -6420,7 +6440,7 @@
       </c>
       <c r="I115" s="2" t="inlineStr">
         <is>
-          <t>Established (19 posts)</t>
+          <t>Established (43 posts)</t>
         </is>
       </c>
       <c r="J115" s="2" t="inlineStr">
@@ -6430,134 +6450,138 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="4" t="inlineStr">
-        <is>
-          <t>Appeals and Resits</t>
-        </is>
-      </c>
-      <c r="B116" s="5" t="inlineStr"/>
-      <c r="C116" s="4" t="inlineStr">
-        <is>
-          <t>Results &amp; Scoring</t>
-        </is>
-      </c>
-      <c r="D116" s="4" t="inlineStr">
-        <is>
-          <t>Appeals and Resits</t>
-        </is>
-      </c>
-      <c r="E116" s="4" t="inlineStr">
-        <is>
-          <t>Appeals and Resits</t>
-        </is>
-      </c>
-      <c r="F116" s="4" t="inlineStr">
-        <is>
-          <t>/appeals-and-resits</t>
-        </is>
-      </c>
-      <c r="G116" s="4" t="inlineStr">
-        <is>
-          <t>Informational</t>
-        </is>
-      </c>
-      <c r="H116" s="4" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="I116" s="4" t="inlineStr">
-        <is>
-          <t>Growing (3 posts)</t>
-        </is>
-      </c>
-      <c r="J116" s="4" t="inlineStr">
-        <is>
-          <t>N/A (static page)</t>
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA for Nigerian doctors</t>
+        </is>
+      </c>
+      <c r="B116" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA for GP doctors in UK; UKMLA eligibility for Indian doctors; UKMLA fees for doctors 2026; UKMLA for Indian doctors; UKMLA for Pakistani doctors</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-for-nigerian-doctors</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="inlineStr">
+        <is>
+          <t>Established (43 posts)</t>
+        </is>
+      </c>
+      <c r="J116" s="2" t="inlineStr">
+        <is>
+          <t>01 July 2026</t>
         </is>
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="4" t="inlineStr">
-        <is>
-          <t>UKMLA results</t>
-        </is>
-      </c>
-      <c r="B117" s="5" t="inlineStr">
-        <is>
-          <t>UKMLA pass mark; UKMLA pass rate for IMG; UKMLA results release date</t>
-        </is>
-      </c>
-      <c r="C117" s="4" t="inlineStr">
-        <is>
-          <t>Results &amp; Scoring</t>
-        </is>
-      </c>
-      <c r="D117" s="4" t="inlineStr">
-        <is>
-          <t>Results and Scoring</t>
-        </is>
-      </c>
-      <c r="E117" s="4" t="inlineStr">
-        <is>
-          <t>Results and Scoring</t>
-        </is>
-      </c>
-      <c r="F117" s="4" t="inlineStr">
-        <is>
-          <t>/results-and-scoring</t>
-        </is>
-      </c>
-      <c r="G117" s="4" t="inlineStr">
-        <is>
-          <t>Informational</t>
-        </is>
-      </c>
-      <c r="H117" s="4" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="I117" s="4" t="inlineStr">
-        <is>
-          <t>Growing (3 posts)</t>
-        </is>
-      </c>
-      <c r="J117" s="4" t="inlineStr">
-        <is>
-          <t>N/A (static page)</t>
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA for Pakistani doctors</t>
+        </is>
+      </c>
+      <c r="B117" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA for GP doctors in UK; UKMLA eligibility for Indian doctors; UKMLA fees for doctors 2026; UKMLA for Indian doctors; UKMLA for Nigerian doctors</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-for-pakistani-doctors</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I117" s="2" t="inlineStr">
+        <is>
+          <t>Established (43 posts)</t>
+        </is>
+      </c>
+      <c r="J117" s="2" t="inlineStr">
+        <is>
+          <t>01 July 2026</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>UKMLA AKT pass mark</t>
+          <t>UKMLA for refugee doctors</t>
         </is>
       </c>
       <c r="B118" s="3" t="inlineStr">
         <is>
-          <t>UKMLA AKT; UKMLA pass mark; how to pass ukmla; ms akt; What is the UKMLA AKT?</t>
+          <t>UKMLA for GP doctors in UK; UKMLA fees for refugee doctors; UKMLA for Indian doctors; UKMLA for Nigerian doctors; UKMLA for Pakistani doctors</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>Results &amp; Scoring</t>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>Results and Scoring</t>
+          <t>Eligibility</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>UKMLA AKT Pass Mark and Pass Rate Explained</t>
+          <t>UKMLA for Refugee Doctors: The GMC Assistance Programme and Fee Support</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-akt-pass-mark-and-pass-rate-explained</t>
+          <t>/news#ukmla-for-refugee-doctors</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
@@ -6572,7 +6596,7 @@
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>Growing (3 posts)</t>
+          <t>Established (43 posts)</t>
         </is>
       </c>
       <c r="J118" s="2" t="inlineStr">
@@ -6584,32 +6608,32 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>UKMLA results feedback</t>
+          <t>UKMLA for South African doctors</t>
         </is>
       </c>
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t>UKMLA results; Results &amp; Data; Results &amp; Scoring; UKMLA results timeline 2026; UKMLA results release date</t>
+          <t>UKMLA for GP doctors in UK; GMC registration process for doctors; UKMLA eligibility for Indian doctors; UKMLA fees for doctors 2026; UKMLA for Indian doctors</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>Results &amp; Scoring</t>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>Results and Scoring</t>
+          <t>Eligibility</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>UKMLA Results: How to Interpret Your Feedback Report</t>
+          <t>UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration</t>
         </is>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-results-feedback-report</t>
+          <t>/news#ukmla-for-south-african-doctors</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
@@ -6624,44 +6648,44 @@
       </c>
       <c r="I119" s="2" t="inlineStr">
         <is>
-          <t>Growing (3 posts)</t>
+          <t>Established (43 posts)</t>
         </is>
       </c>
       <c r="J119" s="2" t="inlineStr">
         <is>
-          <t>30 June 2026</t>
+          <t>01 July 2026</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>what happens if you fail UKMLA</t>
+          <t>UKMLA for Sri Lankan doctors</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
         <is>
-          <t>UKMLA fail foundation year impact; UKMLA and foundation year application; foundation year vs specialty training IMG; how to prepare for UKMLA final year; UKMLA for academic foundation programme</t>
+          <t>UKMLA for GP doctors in UK; GMC registration process for doctors; UKMLA eligibility for Indian doctors; UKMLA fees for doctors 2026; UKMLA for Indian doctors</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>Results &amp; Scoring</t>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>Appeals and Resits</t>
+          <t>Eligibility</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>What Happens If You Fail the UKMLA? The Impact on Your Foundation Year</t>
+          <t>UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>/news#what-happens-if-you-fail-ukmla-foundation-year-impact</t>
+          <t>/news#ukmla-for-sri-lankan-doctors</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
@@ -6676,65 +6700,2641 @@
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>Growing (3 posts)</t>
+          <t>Established (43 posts)</t>
         </is>
       </c>
       <c r="J120" s="2" t="inlineStr">
         <is>
-          <t>02 July 2026</t>
+          <t>01 July 2026</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
+          <t>UKMLA for Vietnamese and Indonesian doctors</t>
+        </is>
+      </c>
+      <c r="B121" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA for GP doctors in UK; GMC registration process for doctors; UKMLA eligibility for Indian doctors; UKMLA fees for doctors 2026; UKMLA for Indian doctors</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA for Vietnamese and Indonesian Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-for-vietnamese-and-indonesian-doctors</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I121" s="2" t="inlineStr">
+        <is>
+          <t>Established (43 posts)</t>
+        </is>
+      </c>
+      <c r="J121" s="2" t="inlineStr">
+        <is>
+          <t>02 July 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA NHS job after exam</t>
+        </is>
+      </c>
+      <c r="B122" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA exam; what is the UKMLA exam; The Exam; gmc exam; NHS jobs after GMC registration</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-to-nhs-job-pathway</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="inlineStr">
+        <is>
+          <t>Established (43 posts)</t>
+        </is>
+      </c>
+      <c r="J122" s="2" t="inlineStr">
+        <is>
+          <t>01 July 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA vs AMC exam comparison</t>
+        </is>
+      </c>
+      <c r="B123" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA exam; what is the UKMLA exam; The Exam; Exam Pattern Comparison; UKMLA vs MCCQE Canada</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA vs PLAB</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA vs AMC and MCCQE: Comparing the UK Route to Australia and Canada</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-vs-amc-and-mccqe-comparison</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I123" s="2" t="inlineStr">
+        <is>
+          <t>Established (43 posts)</t>
+        </is>
+      </c>
+      <c r="J123" s="2" t="inlineStr">
+        <is>
+          <t>01 July 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA vs NEET PG</t>
+        </is>
+      </c>
+      <c r="B124" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA exam for Indian medical graduates; UKMLA for international medical graduates; UKMLA for Caribbean medical graduates; international medical graduates; UKMLA for Indian doctors</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA vs PLAB</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-vs-neet-pg</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="inlineStr">
+        <is>
+          <t>Established (43 posts)</t>
+        </is>
+      </c>
+      <c r="J124" s="2" t="inlineStr">
+        <is>
+          <t>01 July 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA vs USMLE</t>
+        </is>
+      </c>
+      <c r="B125" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA vs USMLE which is easier; UKMLA exam; what is the UKMLA exam; The Exam; UKMLA vs USMLE cost and difficulty</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA vs PLAB</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-vs-usmle-comparison</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I125" s="2" t="inlineStr">
+        <is>
+          <t>Established (43 posts)</t>
+        </is>
+      </c>
+      <c r="J125" s="2" t="inlineStr">
+        <is>
+          <t>01 July 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>NHS pay scales and banding</t>
+        </is>
+      </c>
+      <c r="B126" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA for GP doctors in UK; UKMLA for doctors already working in NHS; UKMLA for Indian doctors; UKMLA for Nigerian doctors; UKMLA for Pakistani doctors</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>Fees</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>Understanding NHS Pay Scales and Banding for Doctors</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>/news#understanding-nhs-pay-scales-and-banding-for-doctors</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I126" s="2" t="inlineStr">
+        <is>
+          <t>Established (43 posts)</t>
+        </is>
+      </c>
+      <c r="J126" s="2" t="inlineStr">
+        <is>
+          <t>02 July 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>GMC fitness to practise</t>
+        </is>
+      </c>
+      <c r="B127" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA for GP doctors in UK; gmc exam; gmc licensing; gmc Manchester; gmc updates</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>Professional Practice &amp; Safety</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>Registration Guide</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>GMC Fitness to Practise Explained: What New Doctors Need to Know</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>/news#gmc-fitness-to-practise-explained-for-new-doctors</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="inlineStr">
+        <is>
+          <t>Established (6 posts)</t>
+        </is>
+      </c>
+      <c r="J127" s="2" t="inlineStr">
+        <is>
+          <t>02 July 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>GMC regulation of physician associates</t>
+        </is>
+      </c>
+      <c r="B128" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA for GP doctors in UK; gmc exam; gmc licensing; gmc Manchester; gmc updates</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>Professional Practice &amp; Safety</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>Registration Guide</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>GMC Regulation of Physician Associates: What Doctors Need to Know</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>/news#gmc-regulation-of-physician-associates-what-doctors-need-to-know</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I128" s="2" t="inlineStr">
+        <is>
+          <t>Established (6 posts)</t>
+        </is>
+      </c>
+      <c r="J128" s="2" t="inlineStr">
+        <is>
+          <t>02 July 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>Good Medical Practice UKMLA</t>
+        </is>
+      </c>
+      <c r="B129" s="3" t="inlineStr">
+        <is>
+          <t>how to practice medicine in UK; medical acronyms; medical students; UKMLA for international medical graduates; UKMLA mock exam practice</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>Professional Practice &amp; Safety</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr"/>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>Good Medical Practice and the UKMLA: What the GMC Expects</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>/news#good-medical-practice-ukmla</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I129" s="2" t="inlineStr">
+        <is>
+          <t>Established (6 posts)</t>
+        </is>
+      </c>
+      <c r="J129" s="2" t="inlineStr">
+        <is>
+          <t>30 June 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>patient safety UKMLA</t>
+        </is>
+      </c>
+      <c r="B130" s="3" t="inlineStr">
+        <is>
+          <t>1. Patient Presentations; The official GMC MLA Content Map listing core patient presentations, conditions, and practical procedures</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>Professional Practice &amp; Safety</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr"/>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>/news#patient-safety-ukmla-prescribing-errors</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I130" s="2" t="inlineStr">
+        <is>
+          <t>Established (6 posts)</t>
+        </is>
+      </c>
+      <c r="J130" s="2" t="inlineStr">
+        <is>
+          <t>30 June 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>safeguarding UKMLA</t>
+        </is>
+      </c>
+      <c r="B131" s="3" t="inlineStr">
+        <is>
+          <t>ukmla guide; UKMLA pharmacology revision; about ukmla guide; contact ukmla guide; img guide</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>Professional Practice &amp; Safety</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr"/>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>Safeguarding Adults and Children: A UKMLA Revision Guide</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>/news#safeguarding-ukmla-revision</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I131" s="2" t="inlineStr">
+        <is>
+          <t>Established (6 posts)</t>
+        </is>
+      </c>
+      <c r="J131" s="2" t="inlineStr">
+        <is>
+          <t>30 June 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>GMC revalidation process</t>
+        </is>
+      </c>
+      <c r="B132" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA registration process GMC; GMC registration process for doctors; GMC EPIC verification process; UKMLA for GP doctors in UK; gmc exam</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>Professional Practice &amp; Safety</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>Registration Guide</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>The GMC Revalidation Process, Explained for New Doctors</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>/news#gmc-revalidation-process-explained</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I132" s="2" t="inlineStr">
+        <is>
+          <t>Established (6 posts)</t>
+        </is>
+      </c>
+      <c r="J132" s="2" t="inlineStr">
+        <is>
+          <t>02 July 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="4" t="inlineStr">
+        <is>
+          <t>UKMLA for IMG</t>
+        </is>
+      </c>
+      <c r="B133" s="5" t="inlineStr">
+        <is>
+          <t>UKMLA for international medical graduates; UKMLA eligibility; UKMLA exam for UK medical students; UKMLA eligibility for international medical graduates</t>
+        </is>
+      </c>
+      <c r="C133" s="4" t="inlineStr">
+        <is>
+          <t>Registration &amp; Eligibility</t>
+        </is>
+      </c>
+      <c r="D133" s="4" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
+      <c r="E133" s="4" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
+      <c r="F133" s="4" t="inlineStr">
+        <is>
+          <t>/eligibility</t>
+        </is>
+      </c>
+      <c r="G133" s="4" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H133" s="4" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I133" s="4" t="inlineStr">
+        <is>
+          <t>Established (29 posts)</t>
+        </is>
+      </c>
+      <c r="J133" s="4" t="inlineStr">
+        <is>
+          <t>N/A (static page)</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="4" t="inlineStr">
+        <is>
+          <t>Fees</t>
+        </is>
+      </c>
+      <c r="B134" s="5" t="inlineStr"/>
+      <c r="C134" s="4" t="inlineStr">
+        <is>
+          <t>Registration &amp; Eligibility</t>
+        </is>
+      </c>
+      <c r="D134" s="4" t="inlineStr">
+        <is>
+          <t>Fees</t>
+        </is>
+      </c>
+      <c r="E134" s="4" t="inlineStr">
+        <is>
+          <t>Fees</t>
+        </is>
+      </c>
+      <c r="F134" s="4" t="inlineStr">
+        <is>
+          <t>/fees</t>
+        </is>
+      </c>
+      <c r="G134" s="4" t="inlineStr">
+        <is>
+          <t>Commercial</t>
+        </is>
+      </c>
+      <c r="H134" s="4" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I134" s="4" t="inlineStr">
+        <is>
+          <t>Established (29 posts)</t>
+        </is>
+      </c>
+      <c r="J134" s="4" t="inlineStr">
+        <is>
+          <t>N/A (static page)</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="4" t="inlineStr">
+        <is>
+          <t>UKMLA dates</t>
+        </is>
+      </c>
+      <c r="B135" s="5" t="inlineStr"/>
+      <c r="C135" s="4" t="inlineStr">
+        <is>
+          <t>Registration &amp; Eligibility</t>
+        </is>
+      </c>
+      <c r="D135" s="4" t="inlineStr">
+        <is>
+          <t>Key Dates</t>
+        </is>
+      </c>
+      <c r="E135" s="4" t="inlineStr">
+        <is>
+          <t>Key Dates</t>
+        </is>
+      </c>
+      <c r="F135" s="4" t="inlineStr">
+        <is>
+          <t>/key-dates</t>
+        </is>
+      </c>
+      <c r="G135" s="4" t="inlineStr">
+        <is>
+          <t>Transactional</t>
+        </is>
+      </c>
+      <c r="H135" s="4" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I135" s="4" t="inlineStr">
+        <is>
+          <t>Established (29 posts)</t>
+        </is>
+      </c>
+      <c r="J135" s="4" t="inlineStr">
+        <is>
+          <t>N/A (static page)</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="4" t="inlineStr">
+        <is>
+          <t>UKMLA registration</t>
+        </is>
+      </c>
+      <c r="B136" s="5" t="inlineStr">
+        <is>
+          <t>UKMLA booking; English language requirement for UKMLA; UKMLA registration process GMC</t>
+        </is>
+      </c>
+      <c r="C136" s="4" t="inlineStr">
+        <is>
+          <t>Registration &amp; Eligibility</t>
+        </is>
+      </c>
+      <c r="D136" s="4" t="inlineStr">
+        <is>
+          <t>Registration Guide</t>
+        </is>
+      </c>
+      <c r="E136" s="4" t="inlineStr">
+        <is>
+          <t>Registration Guide</t>
+        </is>
+      </c>
+      <c r="F136" s="4" t="inlineStr">
+        <is>
+          <t>/registration-guide</t>
+        </is>
+      </c>
+      <c r="G136" s="4" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H136" s="4" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I136" s="4" t="inlineStr">
+        <is>
+          <t>Established (29 posts)</t>
+        </is>
+      </c>
+      <c r="J136" s="4" t="inlineStr">
+        <is>
+          <t>N/A (static page)</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>Annual Review of Competence Progression</t>
+        </is>
+      </c>
+      <c r="B137" s="3" t="inlineStr">
+        <is>
+          <t>GMC annual retention fee; The Biggest Confusion Explained; UKMLA AKT standard setting explained</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>Registration &amp; Eligibility</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>Registration Guide</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>ARCP: The Annual Review of Competence Progression, Explained</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>/news#arcp-annual-review-of-competence-progression-explained</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I137" s="2" t="inlineStr">
+        <is>
+          <t>Established (29 posts)</t>
+        </is>
+      </c>
+      <c r="J137" s="2" t="inlineStr">
+        <is>
+          <t>02 July 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA disability access adjustments</t>
+        </is>
+      </c>
+      <c r="B138" s="3" t="inlineStr">
+        <is>
+          <t>ukmla guide; Reasonable Adjustments; reasonable adjustments gmc; about ukmla guide; contact ukmla guide</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>Registration &amp; Eligibility</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>Appeals and Resits</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>/news#disability-access-ukmla-guide</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I138" s="2" t="inlineStr">
+        <is>
+          <t>Established (29 posts)</t>
+        </is>
+      </c>
+      <c r="J138" s="2" t="inlineStr">
+        <is>
+          <t>30 June 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA exemptions for specialist doctors</t>
+        </is>
+      </c>
+      <c r="B139" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA for GP doctors in UK; do all doctors need to take UKMLA; is UKMLA required for experienced doctors; UKMLA for Indian doctors; UKMLA for Nigerian doctors</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>Registration &amp; Eligibility</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-exemptions-for-specialist-and-gp-doctors</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I139" s="2" t="inlineStr">
+        <is>
+          <t>Established (29 posts)</t>
+        </is>
+      </c>
+      <c r="J139" s="2" t="inlineStr">
+        <is>
+          <t>01 July 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>GMC English language exemption</t>
+        </is>
+      </c>
+      <c r="B140" s="3" t="inlineStr">
+        <is>
+          <t>English language requirement for UKMLA; OET vs IELTS for GMC registration; UKMLA exemption for specialists; gmc exam; gmc licensing</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>Registration &amp; Eligibility</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>GMC English Language Exemption: Do You Need to Sit IELTS or OET?</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>/news#gmc-english-language-exemption-for-imgs</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I140" s="2" t="inlineStr">
+        <is>
+          <t>Established (29 posts)</t>
+        </is>
+      </c>
+      <c r="J140" s="2" t="inlineStr">
+        <is>
+          <t>02 July 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>GMC Order reform 2026</t>
+        </is>
+      </c>
+      <c r="B141" s="3" t="inlineStr">
+        <is>
+          <t>cost of GMC registration 2026; gmc exam; gmc licensing; gmc Manchester; gmc updates</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>Registration &amp; Eligibility</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>Registration Guide</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>GMC Order Reform 2026: The Consultation on Protected Medical Titles</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>/news#gmc-order-reform-2026-protected-medical-titles</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I141" s="2" t="inlineStr">
+        <is>
+          <t>Established (29 posts)</t>
+        </is>
+      </c>
+      <c r="J141" s="2" t="inlineStr">
+        <is>
+          <t>02 July 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>GMC registration refund policy</t>
+        </is>
+      </c>
+      <c r="B142" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA registration; UKMLA GMC registration for graduates; UKMLA vs specialist registration GMC; UKMLA registration process GMC; gmc registration guide</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>Registration &amp; Eligibility</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>Fees</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>GMC Registration Refund Policy: When You Can (and Can't) Get Your Fee Back</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>/news#gmc-registration-refund-policy</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="inlineStr">
+        <is>
+          <t>Established (29 posts)</t>
+        </is>
+      </c>
+      <c r="J142" s="2" t="inlineStr">
+        <is>
+          <t>02 July 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>GMC Welcome to UK Practice</t>
+        </is>
+      </c>
+      <c r="B143" s="3" t="inlineStr">
+        <is>
+          <t>how to practice medicine in UK; UKMLA practice questions free; gmc exam; gmc licensing; gmc Manchester</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>Registration &amp; Eligibility</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>Registration Guide</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>GMC Welcome to UK Practice: A Guide to the Free Induction Workshop</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>/news#gmc-welcome-to-uk-practice-induction-guide</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H143" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I143" s="2" t="inlineStr">
+        <is>
+          <t>Established (29 posts)</t>
+        </is>
+      </c>
+      <c r="J143" s="2" t="inlineStr">
+        <is>
+          <t>02 July 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>how long does GMC registration take</t>
+        </is>
+      </c>
+      <c r="B144" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA registration; GMC registration timeline how long; UKMLA GMC registration for graduates; UKMLA vs specialist registration GMC; UKMLA registration process GMC</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>Registration &amp; Eligibility</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>Registration Guide</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>How Long Does GMC Registration Take? A Realistic Timeline</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>/news#how-long-does-gmc-registration-take</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I144" s="2" t="inlineStr">
+        <is>
+          <t>Established (29 posts)</t>
+        </is>
+      </c>
+      <c r="J144" s="2" t="inlineStr">
+        <is>
+          <t>02 July 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>how to register for PLAB 1</t>
+        </is>
+      </c>
+      <c r="B145" s="3" t="inlineStr">
+        <is>
+          <t>PLAB vs UKMLA; plab 1; plab 2; UKMLA vs PLAB; is UKMLA replacing PLAB</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>Registration &amp; Eligibility</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>Registration Guide</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>How to Register for PLAB 1: A Step-by-Step Guide for IMGs</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>/news#how-to-register-plab-1</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I145" s="2" t="inlineStr">
+        <is>
+          <t>Established (29 posts)</t>
+        </is>
+      </c>
+      <c r="J145" s="2" t="inlineStr">
+        <is>
+          <t>30 June 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>indemnity insurance for doctors</t>
+        </is>
+      </c>
+      <c r="B146" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA for GP doctors in UK; UKMLA for Indian doctors; UKMLA for Nigerian doctors; UKMLA for Pakistani doctors; UKMLA for Bangladeshi doctors</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>Registration &amp; Eligibility</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>Fees</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>Indemnity Insurance for Doctors, Explained</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>/news#indemnity-insurance-for-doctors-explained</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I146" s="2" t="inlineStr">
+        <is>
+          <t>Established (29 posts)</t>
+        </is>
+      </c>
+      <c r="J146" s="2" t="inlineStr">
+        <is>
+          <t>02 July 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>locally employed doctors GMC registration</t>
+        </is>
+      </c>
+      <c r="B147" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA for GP doctors in UK; UKMLA registration; UKMLA vs specialist registration GMC; GMC registration process for doctors; UKMLA GMC registration for graduates</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>Registration &amp; Eligibility</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>Registration Guide</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>Locally Employed Doctors: The Route to Full and Specialist GMC Registration</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>/news#locally-employed-doctors-route-to-gmc-registration</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H147" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I147" s="2" t="inlineStr">
+        <is>
+          <t>Established (29 posts)</t>
+        </is>
+      </c>
+      <c r="J147" s="2" t="inlineStr">
+        <is>
+          <t>02 July 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>OET vs IELTS for GMC registration</t>
+        </is>
+      </c>
+      <c r="B148" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA registration; UKMLA GMC registration for graduates; UKMLA OET or IELTS requirement; UKMLA vs specialist registration GMC; UKMLA registration process GMC</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>Registration &amp; Eligibility</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>OET vs IELTS for GMC Registration: Which Should You Take?</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>/news#oet-vs-ielts-for-gmc-registration-comparison</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I148" s="2" t="inlineStr">
+        <is>
+          <t>Established (29 posts)</t>
+        </is>
+      </c>
+      <c r="J148" s="2" t="inlineStr">
+        <is>
+          <t>02 July 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>practising medicine in Scotland Wales Northern Ireland</t>
+        </is>
+      </c>
+      <c r="B149" s="3" t="inlineStr">
+        <is>
+          <t>practising medicine in UK requirements; how to practice medicine in UK; Respiratory Medicine for the UKMLA: What to Focus On; how to practice medicine in UK from Philippines; Emergency Medicine and Acute Presentations in the UKMLA</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>Registration &amp; Eligibility</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>Registration Guide</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>Practising Medicine in Scotland, Wales and Northern Ireland: What's Different?</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>/news#scotland-wales-northern-ireland-registration-differences</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H149" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I149" s="2" t="inlineStr">
+        <is>
+          <t>Established (29 posts)</t>
+        </is>
+      </c>
+      <c r="J149" s="2" t="inlineStr">
+        <is>
+          <t>02 July 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>Certificate of Completion of Training</t>
+        </is>
+      </c>
+      <c r="B150" s="3" t="inlineStr">
+        <is>
+          <t>foundation year vs specialty training IMG; The Biggest Confusion Explained; UKMLA AKT standard setting explained</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>Registration &amp; Eligibility</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>Registration Guide</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>The Certificate of Completion of Training (CCT), Explained</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>/news#certificate-of-completion-of-training-cct-explained</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I150" s="2" t="inlineStr">
+        <is>
+          <t>Established (29 posts)</t>
+        </is>
+      </c>
+      <c r="J150" s="2" t="inlineStr">
+        <is>
+          <t>02 July 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>GMC annual retention fee</t>
+        </is>
+      </c>
+      <c r="B151" s="3" t="inlineStr">
+        <is>
+          <t>gmc exam; gmc licensing; gmc Manchester; gmc updates; UKMLA GMC registration for graduates</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>Registration &amp; Eligibility</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>Fees</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>The GMC Annual Retention Fee, Explained</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>/news#gmc-annual-retention-fee-explained</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H151" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I151" s="2" t="inlineStr">
+        <is>
+          <t>Established (29 posts)</t>
+        </is>
+      </c>
+      <c r="J151" s="2" t="inlineStr">
+        <is>
+          <t>02 July 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>internship requirement for GMC registration</t>
+        </is>
+      </c>
+      <c r="B152" s="3" t="inlineStr">
+        <is>
+          <t>internship requirement for GMC; UKMLA registration; UKMLA GMC registration for graduates; UKMLA vs specialist registration GMC; UKMLA registration process GMC</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>Registration &amp; Eligibility</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>The Internship Requirement for GMC Registration, Explained</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>/news#internship-requirement-for-gmc-registration</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I152" s="2" t="inlineStr">
+        <is>
+          <t>Established (29 posts)</t>
+        </is>
+      </c>
+      <c r="J152" s="2" t="inlineStr">
+        <is>
+          <t>02 July 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>NHS Pension Scheme for doctors</t>
+        </is>
+      </c>
+      <c r="B153" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA for GP doctors in UK; UKMLA for Indian doctors; UKMLA for Nigerian doctors; UKMLA for Pakistani doctors; UKMLA for Bangladeshi doctors</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>Registration &amp; Eligibility</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>Fees</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>The NHS Pension Scheme for Doctors, Explained</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>/news#nhs-pension-scheme-for-doctors-explained</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H153" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I153" s="2" t="inlineStr">
+        <is>
+          <t>Established (29 posts)</t>
+        </is>
+      </c>
+      <c r="J153" s="2" t="inlineStr">
+        <is>
+          <t>02 July 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>NHS e-Portfolio guide</t>
+        </is>
+      </c>
+      <c r="B154" s="3" t="inlineStr">
+        <is>
+          <t>ukmla guide; UKMLA for GP doctors in UK; about ukmla guide; contact ukmla guide; img guide</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>Registration &amp; Eligibility</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>Registration Guide</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>The NHS e-Portfolio: A Practical Guide for Doctors</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>/news#nhs-eportfolio-guide-for-doctors</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I154" s="2" t="inlineStr">
+        <is>
+          <t>Established (29 posts)</t>
+        </is>
+      </c>
+      <c r="J154" s="2" t="inlineStr">
+        <is>
+          <t>02 July 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA exam booking process</t>
+        </is>
+      </c>
+      <c r="B155" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA booking; UKMLA exam; what is the UKMLA exam; The Exam; UKMLA booking process for students</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>Registration &amp; Eligibility</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>Registration Guide</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>The UKMLA Exam Booking Process: A Step-by-Step Walkthrough</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-exam-booking-process-gmc-online</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H155" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I155" s="2" t="inlineStr">
+        <is>
+          <t>Established (29 posts)</t>
+        </is>
+      </c>
+      <c r="J155" s="2" t="inlineStr">
+        <is>
+          <t>02 July 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>types of GMC registration</t>
+        </is>
+      </c>
+      <c r="B156" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA registration; UKMLA vs specialist registration GMC; UKMLA GMC registration for graduates; UKMLA registration process GMC; gmc registration guide</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>Registration &amp; Eligibility</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>Registration Guide</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>Types of GMC Registration Explained: Provisional, Full, Specialist and GP</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>/news#types-of-gmc-registration-explained</t>
+        </is>
+      </c>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I156" s="2" t="inlineStr">
+        <is>
+          <t>Established (29 posts)</t>
+        </is>
+      </c>
+      <c r="J156" s="2" t="inlineStr">
+        <is>
+          <t>02 July 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA eligibility</t>
+        </is>
+      </c>
+      <c r="B157" s="3" t="inlineStr">
+        <is>
+          <t>Eligibility; UKMLA exam; what is the UKMLA exam; The Exam; UKMLA Eligibility Pathways</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>Registration &amp; Eligibility</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA Eligibility: Who Can Sit the Exam?</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-eligibility-who-can-sit</t>
+        </is>
+      </c>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H157" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I157" s="2" t="inlineStr">
+        <is>
+          <t>Established (29 posts)</t>
+        </is>
+      </c>
+      <c r="J157" s="2" t="inlineStr">
+        <is>
+          <t>30 June 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA exam day what to expect</t>
+        </is>
+      </c>
+      <c r="B158" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA exam; what is the UKMLA exam; The Exam; AKT exam; CPSA exam</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>Registration &amp; Eligibility</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>Registration Guide</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA Exam Day: What to Expect at the AKT and CPSA</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-exam-day-what-to-expect</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I158" s="2" t="inlineStr">
+        <is>
+          <t>Established (29 posts)</t>
+        </is>
+      </c>
+      <c r="J158" s="2" t="inlineStr">
+        <is>
+          <t>02 July 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA exam fees for IMG</t>
+        </is>
+      </c>
+      <c r="B159" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA exam; UKMLA fees; UKMLA for IMG; what is the UKMLA exam; The Exam</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>Registration &amp; Eligibility</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>Fees</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-fees-for-img-2026</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H159" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I159" s="2" t="inlineStr">
+        <is>
+          <t>Established (29 posts)</t>
+        </is>
+      </c>
+      <c r="J159" s="2" t="inlineStr">
+        <is>
+          <t>01 July 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA fees</t>
+        </is>
+      </c>
+      <c r="B160" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA fees for doctors 2026; UKMLA cost; UKMLA Fees and Costs 2026; UKMLA exam fees for IMG; UKMLA fees in Indian rupees</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>Registration &amp; Eligibility</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>Fees</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA Fees: The Complete 2026 Cost Breakdown</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-fees-explained</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H160" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I160" s="2" t="inlineStr">
+        <is>
+          <t>Established (29 posts)</t>
+        </is>
+      </c>
+      <c r="J160" s="2" t="inlineStr">
+        <is>
+          <t>30 June 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA key dates</t>
+        </is>
+      </c>
+      <c r="B161" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA dates; Key Dates; Key Dates &amp; Timeline; UKMLA exam dates 2026; UKMLA exam dates and fees</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>Registration &amp; Eligibility</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>Key Dates</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA Key Dates and Sitting Schedule: What to Know</t>
+        </is>
+      </c>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-key-dates-sitting-schedule</t>
+        </is>
+      </c>
+      <c r="G161" s="2" t="inlineStr">
+        <is>
+          <t>Transactional</t>
+        </is>
+      </c>
+      <c r="H161" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I161" s="2" t="inlineStr">
+        <is>
+          <t>Established (29 posts)</t>
+        </is>
+      </c>
+      <c r="J161" s="2" t="inlineStr">
+        <is>
+          <t>30 June 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA resits</t>
+        </is>
+      </c>
+      <c r="B162" s="3" t="inlineStr">
+        <is>
+          <t>Appeals &amp; Resits; UKMLA Appeals, Resits &amp; Reasonable Adjustments; Appeals, Resits &amp; Reasonable Adjustments; Attempt Limits and Retake Rules; plab attempt limits</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>Registration &amp; Eligibility</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>Appeals and Resits</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA Resits: Rules, Limits, and How to Bounce Back</t>
+        </is>
+      </c>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-resits-rules-limits</t>
+        </is>
+      </c>
+      <c r="G162" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H162" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I162" s="2" t="inlineStr">
+        <is>
+          <t>Established (29 posts)</t>
+        </is>
+      </c>
+      <c r="J162" s="2" t="inlineStr">
+        <is>
+          <t>30 June 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA special circumstances</t>
+        </is>
+      </c>
+      <c r="B163" s="3" t="inlineStr">
+        <is>
+          <t>Mitigating Circumstances; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Attempt limits, mitigating circumstances, reasonable adjustments, and how to appeal a licensing decision</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>Registration &amp; Eligibility</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>Registration Guide</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA Special Circumstances: Accommodations Beyond Disability Access</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-special-circumstances-and-accommodations</t>
+        </is>
+      </c>
+      <c r="G163" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H163" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I163" s="2" t="inlineStr">
+        <is>
+          <t>Established (29 posts)</t>
+        </is>
+      </c>
+      <c r="J163" s="2" t="inlineStr">
+        <is>
+          <t>02 July 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>primary medical qualification GMC accepted</t>
+        </is>
+      </c>
+      <c r="B164" s="3" t="inlineStr">
+        <is>
+          <t>gmc exam; gmc licensing; gmc Manchester; gmc updates; medical acronyms</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>Registration &amp; Eligibility</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>Which Medical Qualifications Does the GMC Accept? PMQ Recognition Explained</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>/news#gmc-recognised-primary-medical-qualifications</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H164" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I164" s="2" t="inlineStr">
+        <is>
+          <t>Established (29 posts)</t>
+        </is>
+      </c>
+      <c r="J164" s="2" t="inlineStr">
+        <is>
+          <t>02 July 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>working hours and rest rules for doctors</t>
+        </is>
+      </c>
+      <c r="B165" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA for GP doctors in UK; UKMLA preparation for working doctors; UKMLA for Indian doctors; UKMLA for Nigerian doctors; UKMLA for Pakistani doctors</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>Registration &amp; Eligibility</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>Registration Guide</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>Working Hours and Rest Rules for Doctors: The EWTD Explained</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>/news#ewtd-working-hours-and-rest-rules-for-doctors</t>
+        </is>
+      </c>
+      <c r="G165" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H165" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I165" s="2" t="inlineStr">
+        <is>
+          <t>Established (29 posts)</t>
+        </is>
+      </c>
+      <c r="J165" s="2" t="inlineStr">
+        <is>
+          <t>02 July 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="4" t="inlineStr">
+        <is>
+          <t>Appeals and Resits</t>
+        </is>
+      </c>
+      <c r="B166" s="5" t="inlineStr"/>
+      <c r="C166" s="4" t="inlineStr">
+        <is>
+          <t>Results &amp; Scoring</t>
+        </is>
+      </c>
+      <c r="D166" s="4" t="inlineStr">
+        <is>
+          <t>Appeals and Resits</t>
+        </is>
+      </c>
+      <c r="E166" s="4" t="inlineStr">
+        <is>
+          <t>Appeals and Resits</t>
+        </is>
+      </c>
+      <c r="F166" s="4" t="inlineStr">
+        <is>
+          <t>/appeals-and-resits</t>
+        </is>
+      </c>
+      <c r="G166" s="4" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H166" s="4" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I166" s="4" t="inlineStr">
+        <is>
+          <t>Growing (3 posts)</t>
+        </is>
+      </c>
+      <c r="J166" s="4" t="inlineStr">
+        <is>
+          <t>N/A (static page)</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="4" t="inlineStr">
+        <is>
+          <t>UKMLA results</t>
+        </is>
+      </c>
+      <c r="B167" s="5" t="inlineStr">
+        <is>
+          <t>UKMLA pass mark; UKMLA pass rate for IMG; UKMLA results release date</t>
+        </is>
+      </c>
+      <c r="C167" s="4" t="inlineStr">
+        <is>
+          <t>Results &amp; Scoring</t>
+        </is>
+      </c>
+      <c r="D167" s="4" t="inlineStr">
+        <is>
+          <t>Results and Scoring</t>
+        </is>
+      </c>
+      <c r="E167" s="4" t="inlineStr">
+        <is>
+          <t>Results and Scoring</t>
+        </is>
+      </c>
+      <c r="F167" s="4" t="inlineStr">
+        <is>
+          <t>/results-and-scoring</t>
+        </is>
+      </c>
+      <c r="G167" s="4" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H167" s="4" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I167" s="4" t="inlineStr">
+        <is>
+          <t>Growing (3 posts)</t>
+        </is>
+      </c>
+      <c r="J167" s="4" t="inlineStr">
+        <is>
+          <t>N/A (static page)</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA AKT pass mark</t>
+        </is>
+      </c>
+      <c r="B168" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA AKT; UKMLA pass mark; how to pass ukmla; ms akt; What is the UKMLA AKT?</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>Results &amp; Scoring</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>Results and Scoring</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA AKT Pass Mark and Pass Rate Explained</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-akt-pass-mark-and-pass-rate-explained</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H168" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I168" s="2" t="inlineStr">
+        <is>
+          <t>Growing (3 posts)</t>
+        </is>
+      </c>
+      <c r="J168" s="2" t="inlineStr">
+        <is>
+          <t>01 July 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA results feedback</t>
+        </is>
+      </c>
+      <c r="B169" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA results; Results &amp; Data; Results &amp; Scoring; UKMLA results timeline 2026; UKMLA results release date</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>Results &amp; Scoring</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>Results and Scoring</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA Results: How to Interpret Your Feedback Report</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-results-feedback-report</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H169" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I169" s="2" t="inlineStr">
+        <is>
+          <t>Growing (3 posts)</t>
+        </is>
+      </c>
+      <c r="J169" s="2" t="inlineStr">
+        <is>
+          <t>30 June 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>what happens if you fail UKMLA</t>
+        </is>
+      </c>
+      <c r="B170" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA fail foundation year impact; UKMLA and foundation year application; foundation year vs specialty training IMG; how to prepare for UKMLA final year; UKMLA for academic foundation programme</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>Results &amp; Scoring</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>Appeals and Resits</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>What Happens If You Fail the UKMLA? The Impact on Your Foundation Year</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>/news#what-happens-if-you-fail-ukmla-foundation-year-impact</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H170" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I170" s="2" t="inlineStr">
+        <is>
+          <t>Growing (3 posts)</t>
+        </is>
+      </c>
+      <c r="J170" s="2" t="inlineStr">
+        <is>
+          <t>02 July 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
           <t>Foundation Programme after UKMLA</t>
         </is>
       </c>
-      <c r="B121" s="3" t="inlineStr">
+      <c r="B171" s="3" t="inlineStr">
         <is>
           <t>UKMLA for academic foundation programme; UKMLA after MBBS; UKMLA after MBBS in India; UKMLA and foundation year application; UKMLA fail foundation year impact</t>
         </is>
       </c>
-      <c r="C121" s="2" t="inlineStr">
+      <c r="C171" s="2" t="inlineStr">
         <is>
           <t>Uncategorised</t>
         </is>
       </c>
-      <c r="D121" s="2" t="inlineStr"/>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="D171" s="2" t="inlineStr"/>
+      <c r="E171" s="2" t="inlineStr">
         <is>
           <t>Understanding the Foundation Programme: What Awaits After the UKMLA</t>
         </is>
       </c>
-      <c r="F121" s="2" t="inlineStr">
+      <c r="F171" s="2" t="inlineStr">
         <is>
           <t>/news#foundation-programme-after-ukmla</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr">
-        <is>
-          <t>Informational</t>
-        </is>
-      </c>
-      <c r="H121" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="I121" s="2" t="inlineStr">
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I171" s="2" t="inlineStr">
         <is>
           <t>Needs More Support (1 post)</t>
         </is>
       </c>
-      <c r="J121" s="2" t="inlineStr">
+      <c r="J171" s="2" t="inlineStr">
         <is>
           <t>30 June 2026</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J121"/>
+  <autoFilter ref="A1:J171"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6786,7 +9386,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>107</v>
+        <v>157</v>
       </c>
     </row>
     <row r="6">
@@ -6843,7 +9443,7 @@
       <c r="A12" s="9" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons: 30 posts — Established (30 posts)</t>
+          <t>Clinical Systems Revision: 46 posts — Established (46 posts)</t>
         </is>
       </c>
     </row>
@@ -6851,7 +9451,7 @@
       <c r="A13" s="9" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Clinical Systems Revision: 23 posts — Established (23 posts)</t>
+          <t>IMG Country Routes &amp; Global Comparisons: 43 posts — Established (43 posts)</t>
         </is>
       </c>
     </row>
@@ -6859,7 +9459,7 @@
       <c r="A14" s="9" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Registration &amp; Eligibility: 19 posts — Established (19 posts)</t>
+          <t>Registration &amp; Eligibility: 29 posts — Established (29 posts)</t>
         </is>
       </c>
     </row>
@@ -6867,7 +9467,7 @@
       <c r="A15" s="9" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Core UKMLA Overview: 11 posts — Established (11 posts)</t>
+          <t>Core UKMLA Overview: 14 posts — Established (14 posts)</t>
         </is>
       </c>
     </row>
@@ -6883,7 +9483,7 @@
       <c r="A17" s="9" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Exam Format: 6 posts — Established (6 posts)</t>
+          <t>Exam Format: 7 posts — Established (7 posts)</t>
         </is>
       </c>
     </row>

--- a/UKMLA_Keyword_Cluster_Sheet.xlsx
+++ b/UKMLA_Keyword_Cluster_Sheet.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Keyword Cluster Sheet'!$A$1:$J$171</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Keyword Cluster Sheet'!$A$1:$J$183</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -470,7 +470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J171"/>
+  <dimension ref="A1:J183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -4360,7 +4360,7 @@
       </c>
       <c r="I75" s="4" t="inlineStr">
         <is>
-          <t>Established (8 posts)</t>
+          <t>Established (10 posts)</t>
         </is>
       </c>
       <c r="J75" s="4" t="inlineStr">
@@ -4372,12 +4372,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>UKMLA group study solo</t>
+          <t>best question bank for UKMLA</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>UKMLA group study vs solo study; how long to study for UKMLA; UKMLA study plan; study plan; UKMLA study plan 12 weeks</t>
+          <t>UKMLA question bank; best question bank for UKMLA UK students; UKMLA question bank free for students; UKMLA AKT question bank free; Anatomy of an SBA Question</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -4392,12 +4392,12 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Group Study vs Solo Study for the UKMLA: What Works Best?</t>
+          <t>Best Question Bank for UKMLA: The 2026 Head-to-Head Comparison</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>/news#group-study-vs-solo-ukmla</t>
+          <t>/news#best-ukmla-question-banks-compared</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -4412,24 +4412,24 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>Established (8 posts)</t>
+          <t>Established (10 posts)</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>30 June 2026</t>
+          <t>03 July 2026</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>how to pass UKMLA on first attempt</t>
+          <t>UKMLA group study solo</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>how to pass ukmla; UKMLA pass mark; UKMLA pass mark for IMG; UKMLA attempt limit for doctors; UKMLA AKT pass mark</t>
+          <t>UKMLA group study vs solo study; how long to study for UKMLA; UKMLA study plan; study plan; UKMLA study plan 12 weeks</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>How to Pass the UKMLA on Your First Attempt</t>
+          <t>Group Study vs Solo Study for the UKMLA: What Works Best?</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>/news#how-to-pass-ukmla-on-first-attempt</t>
+          <t>/news#group-study-vs-solo-ukmla</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -4464,24 +4464,24 @@
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>Established (8 posts)</t>
+          <t>Established (10 posts)</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>02 July 2026</t>
+          <t>30 June 2026</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>UKMLA revision notes</t>
+          <t>how to pass UKMLA on first attempt</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>UKMLA revision notes tips; UKMLA pharmacology revision; AKT Revision Strategy; CPSA / OSCE Revision Strategy; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide</t>
+          <t>how to pass ukmla; UKMLA pass mark; UKMLA pass mark for IMG; UKMLA attempt limit for doctors; UKMLA AKT pass mark</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -4496,12 +4496,12 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>How to Write UKMLA Revision Notes That Actually Work</t>
+          <t>How to Pass the UKMLA on Your First Attempt</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-revision-notes-strategy</t>
+          <t>/news#how-to-pass-ukmla-on-first-attempt</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
@@ -4516,24 +4516,24 @@
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>Established (8 posts)</t>
+          <t>Established (10 posts)</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>30 June 2026</t>
+          <t>02 July 2026</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>UKMLA exam anxiety tips</t>
+          <t>UKMLA final year</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>UKMLA exam; what is the UKMLA exam; The Exam; UKMLA exam in Dubai; AKT exam</t>
+          <t>how to prepare for UKMLA final year; UKMLA AKT format for final year; when is UKMLA exam for final year; how to prepare for UKMLA; Prepare</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -4548,12 +4548,12 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>Managing UKMLA Exam Anxiety: Practical Strategies for Candidates</t>
+          <t>How to Prepare for the UKMLA as a UK Final-Year Student</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>/news#managing-ukmla-exam-anxiety</t>
+          <t>/news#ukmla-preparation-for-uk-final-year-students</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -4568,24 +4568,24 @@
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>Established (8 posts)</t>
+          <t>Established (10 posts)</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>01 July 2026</t>
+          <t>03 July 2026</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>UKMLA mock exams</t>
+          <t>UKMLA revision notes</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>UKMLA mock; UKMLA preparation; Preparation; UKMLA mock exam practice; free UKMLA mock test</t>
+          <t>UKMLA revision notes tips; UKMLA pharmacology revision; AKT Revision Strategy; CPSA / OSCE Revision Strategy; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>The Role of Mock Exams in UKMLA Preparation</t>
+          <t>How to Write UKMLA Revision Notes That Actually Work</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>/news#mock-exams-ukmla-preparation</t>
+          <t>/news#ukmla-revision-notes-strategy</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -4620,7 +4620,7 @@
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>Established (8 posts)</t>
+          <t>Established (10 posts)</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
@@ -4632,12 +4632,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>UKMLA AKT preparation countdown</t>
+          <t>UKMLA exam anxiety tips</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>UKMLA AKT; UKMLA preparation; ms akt; What is the UKMLA AKT?; Preparation</t>
+          <t>UKMLA exam; what is the UKMLA exam; The Exam; UKMLA exam in Dubai; AKT exam</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -4652,12 +4652,12 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>Three Months to the UKMLA AKT: A Final Preparation Countdown</t>
+          <t>Managing UKMLA Exam Anxiety: Practical Strategies for Candidates</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>/news#three-months-ukmla-akt-countdown</t>
+          <t>/news#managing-ukmla-exam-anxiety</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -4672,24 +4672,24 @@
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>Established (8 posts)</t>
+          <t>Established (10 posts)</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>30 June 2026</t>
+          <t>01 July 2026</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>time management UKMLA AKT</t>
+          <t>UKMLA mock exams</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>UKMLA AKT; ms akt; What is the UKMLA AKT?; AKT exam; AKT Details</t>
+          <t>UKMLA mock; UKMLA preparation; Preparation; UKMLA mock exam practice; free UKMLA mock test</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -4704,12 +4704,12 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Time Management in the UKMLA AKT: Strategies That Work</t>
+          <t>The Role of Mock Exams in UKMLA Preparation</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>/news#time-management-akt-ukmla</t>
+          <t>/news#mock-exams-ukmla-preparation</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
@@ -4724,7 +4724,7 @@
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>Established (8 posts)</t>
+          <t>Established (10 posts)</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
@@ -4736,12 +4736,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>UKMLA Anki deck download</t>
+          <t>UKMLA AKT preparation countdown</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>ukmla guide; UKMLA syllabus pdf download; What Is the UKMLA? A Complete Beginner's Guide; UKMLA pharmacology revision; about ukmla guide</t>
+          <t>UKMLA AKT; UKMLA preparation; ms akt; What is the UKMLA AKT?; Preparation</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>UKMLA Anki Deck and Flashcard Revision: The Complete Guide</t>
+          <t>Three Months to the UKMLA AKT: A Final Preparation Countdown</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-anki-deck-and-flashcard-revision-guide</t>
+          <t>/news#three-months-ukmla-akt-countdown</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
@@ -4776,44 +4776,44 @@
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>Established (8 posts)</t>
+          <t>Established (10 posts)</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>02 July 2026</t>
+          <t>30 June 2026</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>dependent visa for doctors' families</t>
+          <t>time management UKMLA AKT</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>UKMLA for GP doctors in UK; how to get UK visa for doctors; UKMLA for Indian doctors; UKMLA for Nigerian doctors; UKMLA for Pakistani doctors</t>
+          <t>UKMLA AKT; ms akt; What is the UKMLA AKT?; AKT exam; AKT Details</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
+          <t>Exam Preparation</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Eligibility</t>
+          <t>Preparation</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Bringing Your Family to the UK: A Dependant Visa Guide for Doctors</t>
+          <t>Time Management in the UKMLA AKT: Strategies That Work</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>/news#bringing-family-to-uk-dependent-visa-guide</t>
+          <t>/news#time-management-akt-ukmla</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
@@ -4828,44 +4828,44 @@
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>Established (43 posts)</t>
+          <t>Established (10 posts)</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>02 July 2026</t>
+          <t>30 June 2026</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>English language requirement for UKMLA India</t>
+          <t>UKMLA Anki deck download</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>UKMLA India; English language requirement for UKMLA; English requirement for UKMLA India (IELTS/OET); UKMLA OET or IELTS requirement; Step 2: English Language Proficiency</t>
+          <t>ukmla guide; UKMLA syllabus pdf download; What Is the UKMLA? A Complete Beginner's Guide; UKMLA pharmacology revision; about ukmla guide</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
+          <t>Exam Preparation</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Eligibility</t>
+          <t>Preparation</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>English Language Requirements for the UKMLA: IELTS and OET Scores Explained</t>
+          <t>UKMLA Anki Deck and Flashcard Revision: The Complete Guide</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>/news#english-language-requirement-for-ukmla-india</t>
+          <t>/news#ukmla-anki-deck-and-flashcard-revision-guide</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
@@ -4880,24 +4880,24 @@
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>Established (43 posts)</t>
+          <t>Established (10 posts)</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>01 July 2026</t>
+          <t>02 July 2026</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>foundation year vs specialty training IMG</t>
+          <t>dependent visa for doctors' families</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>UKMLA for IMG; UKMLA and foundation year application; UKMLA fail foundation year impact; img guide; IMG Pathway</t>
+          <t>UKMLA for GP doctors in UK; how to get UK visa for doctors; UKMLA for Indian doctors; UKMLA for Nigerian doctors; UKMLA for Pakistani doctors</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Foundation Year vs Specialty Training for IMGs: Which Route After the UKMLA?</t>
+          <t>Bringing Your Family to the UK: A Dependant Visa Guide for Doctors</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>/news#foundation-year-vs-specialty-training-for-imgs</t>
+          <t>/news#bringing-family-to-uk-dependent-visa-guide</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
@@ -4932,7 +4932,7 @@
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>Established (43 posts)</t>
+          <t>Established (51 posts)</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
@@ -4944,12 +4944,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>GMC registration requirements for international doctors</t>
+          <t>English language requirement for UKMLA India</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>UKMLA for GP doctors in UK; UKMLA registration; GMC registration process for doctors; UKMLA registration process GMC; GMC registration requirements IMG</t>
+          <t>UKMLA India; English language requirement for UKMLA; English requirement for UKMLA India (IELTS/OET); UKMLA OET or IELTS requirement; Step 2: English Language Proficiency</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -4959,17 +4959,17 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Registration Guide</t>
+          <t>Eligibility</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>GMC Registration Requirements for International Doctors: The Complete Process</t>
+          <t>English Language Requirements for the UKMLA: IELTS and OET Scores Explained</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>/news#gmc-registration-requirements-for-international-doctors</t>
+          <t>/news#english-language-requirement-for-ukmla-india</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
@@ -4984,7 +4984,7 @@
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>Established (43 posts)</t>
+          <t>Established (51 posts)</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
@@ -4996,12 +4996,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>GMC registration from India</t>
+          <t>foundation year vs specialty training IMG</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>UKMLA India; UKMLA registration; gmc registration guide; how to apply for UKMLA from India; UKMLA GMC registration for graduates</t>
+          <t>UKMLA for IMG; UKMLA and foundation year application; UKMLA fail foundation year impact; img guide; IMG Pathway</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -5011,17 +5011,17 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Registration Guide</t>
+          <t>Eligibility</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide</t>
+          <t>Foundation Year vs Specialty Training for IMGs: Which Route After the UKMLA?</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>/news#gmc-registration-and-epic-verification-india</t>
+          <t>/news#foundation-year-vs-specialty-training-for-imgs</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
@@ -5036,24 +5036,24 @@
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>Established (43 posts)</t>
+          <t>Established (51 posts)</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>01 July 2026</t>
+          <t>02 July 2026</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>GMC registration for EU and Irish doctors</t>
+          <t>GMC registration requirements for international doctors</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>UKMLA for GP doctors in UK; UKMLA registration; GMC registration process for doctors; UKMLA GMC registration for graduates; UKMLA vs specialist registration GMC</t>
+          <t>UKMLA for GP doctors in UK; UKMLA registration; GMC registration process for doctors; UKMLA registration process GMC; GMC registration requirements IMG</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -5063,17 +5063,17 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>Eligibility</t>
+          <t>Registration Guide</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>GMC Registration for EU and Irish Doctors: What Changed After Brexit</t>
+          <t>GMC Registration Requirements for International Doctors: The Complete Process</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>/news#gmc-registration-for-eu-and-irish-doctors</t>
+          <t>/news#gmc-registration-requirements-for-international-doctors</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
@@ -5088,24 +5088,24 @@
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>Established (43 posts)</t>
+          <t>Established (51 posts)</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>02 July 2026</t>
+          <t>01 July 2026</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>how to become a doctor in UK from India</t>
+          <t>GMC registration from India</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>how to become a doctor in UK; UKMLA India; how to become a doctor in UK from Nigeria; how to become a doctor in UK from Pakistan; how to apply for UKMLA from India</t>
+          <t>UKMLA India; UKMLA registration; gmc registration guide; how to apply for UKMLA from India; UKMLA GMC registration for graduates</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -5115,17 +5115,17 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>Eligibility</t>
+          <t>Registration Guide</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>How to Become a Doctor in the UK from India: The Complete UKMLA Route</t>
+          <t>GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>/news#how-to-become-a-doctor-in-uk-from-india</t>
+          <t>/news#gmc-registration-and-epic-verification-india</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
@@ -5140,7 +5140,7 @@
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>Established (43 posts)</t>
+          <t>Established (51 posts)</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>how to become a doctor in UK</t>
+          <t>GMC registration for EU and Irish doctors</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>how to become a doctor in UK from India; how to become a doctor in UK from Nigeria; how to become a doctor in UK from Pakistan; UKMLA registration; gmc registration guide</t>
+          <t>UKMLA for GP doctors in UK; UKMLA registration; GMC registration process for doctors; UKMLA GMC registration for graduates; UKMLA vs specialist registration GMC</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -5172,12 +5172,12 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs</t>
+          <t>GMC Registration for EU and Irish Doctors: What Changed After Brexit</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>/news#how-to-become-a-doctor-in-the-uk-gmc-registration-guide</t>
+          <t>/news#gmc-registration-for-eu-and-irish-doctors</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
@@ -5192,24 +5192,24 @@
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>Established (43 posts)</t>
+          <t>Established (51 posts)</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>01 July 2026</t>
+          <t>02 July 2026</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>NHS CV and application</t>
+          <t>how to become a doctor in UK from India</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>UKMLA and foundation year application; UKMLA for doctors already working in NHS; UKMLA NHS job after exam; Step 6: Submit the GMC Application; NHS jobs after GMC registration</t>
+          <t>how to become a doctor in UK; UKMLA India; how to become a doctor in UK from Nigeria; how to become a doctor in UK from Pakistan; how to apply for UKMLA from India</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -5224,12 +5224,12 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>How to Write an NHS CV and Application That Gets Shortlisted</t>
+          <t>How to Become a Doctor in the UK from India: The Complete UKMLA Route</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>/news#how-to-write-an-nhs-cv-and-application</t>
+          <t>/news#how-to-become-a-doctor-in-uk-from-india</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
@@ -5244,24 +5244,24 @@
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>Established (43 posts)</t>
+          <t>Established (51 posts)</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>02 July 2026</t>
+          <t>01 July 2026</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>is Indian MBBS valid in UK</t>
+          <t>how to become a doctor in UK</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>MBBS in UK for Indian students; UKMLA after MBBS; UKMLA for Indian doctors; UKMLA after MBBS in India; UKMLA eligibility for Indian doctors</t>
+          <t>how to become a doctor in UK from India; how to become a doctor in UK from Nigeria; how to become a doctor in UK from Pakistan; UKMLA registration; gmc registration guide</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -5276,12 +5276,12 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained</t>
+          <t>How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>/news#is-indian-mbbs-valid-in-uk</t>
+          <t>/news#how-to-become-a-doctor-in-the-uk-gmc-registration-guide</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>Established (43 posts)</t>
+          <t>Established (51 posts)</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
@@ -5308,12 +5308,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>locum vs substantive NHS posts</t>
+          <t>NHS CV and application</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>Posts; UKMLA for doctors already working in NHS; UKMLA NHS job after exam; NHS jobs after GMC registration; UKMLA vs USMLE which is easier</t>
+          <t>UKMLA and foundation year application; UKMLA for doctors already working in NHS; UKMLA NHS job after exam; Step 6: Submit the GMC Application; NHS jobs after GMC registration</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>Locum vs Substantive NHS Posts: Which Is Right for You?</t>
+          <t>How to Write an NHS CV and Application That Gets Shortlisted</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>/news#locum-vs-substantive-nhs-posts-explained</t>
+          <t>/news#how-to-write-an-nhs-cv-and-application</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
@@ -5348,7 +5348,7 @@
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>Established (43 posts)</t>
+          <t>Established (51 posts)</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
@@ -5360,12 +5360,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>MBBS in UK for Indian students</t>
+          <t>is Indian MBBS valid in UK</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>is Indian MBBS valid in UK; UKMLA after MBBS; UKMLA for Indian doctors; UKMLA for IMG; medical students</t>
+          <t>MBBS in UK for Indian students; UKMLA after MBBS; UKMLA for Indian doctors; UKMLA after MBBS in India; UKMLA eligibility for Indian doctors</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -5380,12 +5380,12 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path</t>
+          <t>Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>/news#mbbs-in-uk-for-indian-students</t>
+          <t>/news#is-indian-mbbs-valid-in-uk</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
@@ -5400,7 +5400,7 @@
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>Established (43 posts)</t>
+          <t>Established (51 posts)</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
@@ -5412,12 +5412,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>Medical Training Initiative scheme closure 2026</t>
+          <t>locum vs substantive NHS posts</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>medical licence UK for doctors 2026; UK medical licence requirements 2026; ukmla syllabus 2026; medical acronyms; medical students</t>
+          <t>Posts; UKMLA for doctors already working in NHS; UKMLA NHS job after exam; NHS jobs after GMC registration; UKMLA vs USMLE which is easier</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -5432,12 +5432,12 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>Medical Training Initiative Scheme Closure 2026: What IMGs Need to Know</t>
+          <t>Locum vs Substantive NHS Posts: Which Is Right for You?</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>/news#medical-training-initiative-scheme-closure-2026</t>
+          <t>/news#locum-vs-substantive-nhs-posts-explained</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
@@ -5452,7 +5452,7 @@
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>Established (43 posts)</t>
+          <t>Established (51 posts)</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
@@ -5464,12 +5464,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>NHS job interview preparation</t>
+          <t>MBBS in UK for Indian students</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>UKMLA preparation; Preparation; Preparation Guide; UKMLA Preparation Guide; UKMLA OSCE preparation</t>
+          <t>is Indian MBBS valid in UK; UKMLA after MBBS; UKMLA for Indian doctors; UKMLA for IMG; medical students</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -5484,12 +5484,12 @@
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>NHS Job Interview Preparation: A Complete Guide for IMGs and UK Graduates</t>
+          <t>MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>/news#nhs-job-interview-preparation-guide</t>
+          <t>/news#mbbs-in-uk-for-indian-students</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
@@ -5504,24 +5504,24 @@
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>Established (43 posts)</t>
+          <t>Established (51 posts)</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>02 July 2026</t>
+          <t>01 July 2026</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>relocating to the UK for IMG doctors</t>
+          <t>Medical Training Initiative scheme closure 2026</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>UKMLA for GP doctors in UK; UKMLA for IMG; img guide; UKMLA for Indian doctors; UKMLA for Nigerian doctors</t>
+          <t>medical licence UK for doctors 2026; UK medical licence requirements 2026; ukmla syllabus 2026; medical acronyms; medical students</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -5536,12 +5536,12 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>Relocating to the UK: A Practical Guide for IMG Doctors</t>
+          <t>Medical Training Initiative Scheme Closure 2026: What IMGs Need to Know</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>/news#relocating-to-the-uk-a-practical-guide-for-img-doctors</t>
+          <t>/news#medical-training-initiative-scheme-closure-2026</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
@@ -5556,7 +5556,7 @@
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>Established (43 posts)</t>
+          <t>Established (51 posts)</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
@@ -5568,12 +5568,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>returning to practise in Gulf countries</t>
+          <t>NHS job interview preparation</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>ukmla guide; UKMLA for Saudi / Gulf doctors; which countries accept UKMLA; about ukmla guide; contact ukmla guide</t>
+          <t>UKMLA preparation; Preparation; Preparation Guide; UKMLA Preparation Guide; UKMLA OSCE preparation</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -5588,12 +5588,12 @@
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>Returning to Practise in Gulf Countries: The DataFlow Verification Guide</t>
+          <t>NHS Job Interview Preparation: A Complete Guide for IMGs and UK Graduates</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>/news#returning-to-practise-in-gulf-countries-dataflow-guide</t>
+          <t>/news#nhs-job-interview-preparation-guide</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
@@ -5608,7 +5608,7 @@
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>Established (43 posts)</t>
+          <t>Established (51 posts)</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr">
@@ -5620,12 +5620,12 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>Medical Training Prioritisation Act 2026</t>
+          <t>relocating to the UK for IMG doctors</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>medical licence UK for doctors 2026; UK medical licence requirements 2026; ukmla syllabus 2026; medical acronyms; medical students</t>
+          <t>UKMLA for GP doctors in UK; UKMLA for IMG; img guide; UKMLA for Indian doctors; UKMLA for Nigerian doctors</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -5640,12 +5640,12 @@
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>The Medical Training Prioritisation Act 2026: What It Means for IMGs</t>
+          <t>Relocating to the UK: A Practical Guide for IMG Doctors</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>/news#medical-training-prioritisation-act-2026-imgs</t>
+          <t>/news#relocating-to-the-uk-a-practical-guide-for-img-doctors</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
@@ -5660,7 +5660,7 @@
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>Established (43 posts)</t>
+          <t>Established (51 posts)</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
@@ -5672,12 +5672,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>UK doctor salary for Indian doctors</t>
+          <t>returning to practise in Gulf countries</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>UKMLA for Indian doctors; salary of doctor in UK for Indian; UKMLA for GP doctors in UK; UK doctor salary 2026; UKMLA eligibility for Indian doctors</t>
+          <t>ukmla guide; UKMLA for Saudi / Gulf doctors; which countries accept UKMLA; about ukmla guide; contact ukmla guide</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -5692,12 +5692,12 @@
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home</t>
+          <t>Returning to Practise in Gulf Countries: The DataFlow Verification Guide</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>/news#uk-doctor-salary-guide-for-indian-doctors</t>
+          <t>/news#returning-to-practise-in-gulf-countries-dataflow-guide</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
@@ -5712,24 +5712,24 @@
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>Established (43 posts)</t>
+          <t>Established (51 posts)</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
-          <t>01 July 2026</t>
+          <t>02 July 2026</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>UK visa for international doctors</t>
+          <t>Medical Training Prioritisation Act 2026</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>UKMLA for GP doctors in UK; how to get UK visa for doctors; UK medical registration for international doctors; UKMLA for Indian doctors; UKMLA for Nigerian doctors</t>
+          <t>medical licence UK for doctors 2026; UK medical licence requirements 2026; ukmla syllabus 2026; medical acronyms; medical students</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -5744,12 +5744,12 @@
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>UK Visa Guide for International Doctors: Health and Care Worker Visa Explained</t>
+          <t>The Medical Training Prioritisation Act 2026: What It Means for IMGs</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>/news#uk-visa-guide-for-international-doctors</t>
+          <t>/news#medical-training-prioritisation-act-2026-imgs</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
@@ -5764,24 +5764,24 @@
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>Established (43 posts)</t>
+          <t>Established (51 posts)</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>01 July 2026</t>
+          <t>02 July 2026</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>UK visa salary threshold 2026</t>
+          <t>UK doctor salary for Indian doctors</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>UK doctor salary 2026; UKMLA fees for doctors 2026; UKMLA syllabus 2026 changes; how to get UK visa for doctors; UKMLA for GP doctors in UK</t>
+          <t>UKMLA for Indian doctors; salary of doctor in UK for Indian; UKMLA for GP doctors in UK; UK doctor salary 2026; UKMLA eligibility for Indian doctors</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -5796,12 +5796,12 @@
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>UK Visa Salary Threshold Changes 2026: What Doctors Need to Know</t>
+          <t>UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>/news#uk-visa-salary-threshold-changes-2026-for-doctors</t>
+          <t>/news#uk-doctor-salary-guide-for-indian-doctors</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
@@ -5816,24 +5816,24 @@
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>Established (43 posts)</t>
+          <t>Established (51 posts)</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr">
         <is>
-          <t>02 July 2026</t>
+          <t>01 July 2026</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>UKMLA AKT test centres</t>
+          <t>UK visa for international doctors</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>UKMLA AKT; ms akt; What is the UKMLA AKT?; UKMLA AKT test centres in India; UKMLA AKT test centres in Pakistan</t>
+          <t>UKMLA for GP doctors in UK; how to get UK visa for doctors; UK medical registration for international doctors; UKMLA for Indian doctors; UKMLA for Nigerian doctors</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -5843,17 +5843,17 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern</t>
+          <t>Eligibility</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide</t>
+          <t>UK Visa Guide for International Doctors: Health and Care Worker Visa Explained</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-akt-test-centres-guide</t>
+          <t>/news#uk-visa-guide-for-international-doctors</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
@@ -5868,7 +5868,7 @@
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>Established (43 posts)</t>
+          <t>Established (51 posts)</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr">
@@ -5880,12 +5880,12 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>UKMLA crash course for doctors</t>
+          <t>UK visa salary threshold 2026</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>UKMLA for GP doctors in UK; UKMLA for Indian doctors; UKMLA for Nigerian doctors; UKMLA for Pakistani doctors; UKMLA for Bangladeshi doctors</t>
+          <t>UK doctor salary 2026; UKMLA fees for doctors 2026; UKMLA syllabus 2026 changes; how to get UK visa for doctors; UKMLA for GP doctors in UK</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -5895,17 +5895,17 @@
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>Preparation</t>
+          <t>Eligibility</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>UKMLA Crash Course for Doctors: How to Choose the Right Intensive Course</t>
+          <t>UK Visa Salary Threshold Changes 2026: What Doctors Need to Know</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-crash-course-for-doctors</t>
+          <t>/news#uk-visa-salary-threshold-changes-2026-for-doctors</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
@@ -5920,7 +5920,7 @@
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>Established (43 posts)</t>
+          <t>Established (51 posts)</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr">
@@ -5932,12 +5932,12 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>UKMLA question bank</t>
+          <t>UKMLA AKT test centres</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>best question bank for UKMLA; best question bank for UKMLA UK students; UKMLA question bank free for students; UKMLA AKT question bank free; UKMLA mock</t>
+          <t>UKMLA AKT; ms akt; What is the UKMLA AKT?; UKMLA AKT test centres in India; UKMLA AKT test centres in Pakistan</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -5947,17 +5947,17 @@
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Preparation</t>
+          <t>AKT Exam Pattern</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources</t>
+          <t>UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-question-bank-and-mock-tests</t>
+          <t>/news#ukmla-akt-test-centres-guide</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
@@ -5972,7 +5972,7 @@
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>Established (43 posts)</t>
+          <t>Established (51 posts)</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr">
@@ -5984,12 +5984,12 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>UKMLA for Bangladeshi doctors</t>
+          <t>UKMLA after MBBS in India</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>UKMLA for GP doctors in UK; GMC registration process for doctors; UKMLA eligibility for Indian doctors; UKMLA fees for doctors 2026; UKMLA for Indian doctors</t>
+          <t>UKMLA after MBBS; UKMLA India; how to apply for UKMLA from India; UKMLA exam cost in India; is Indian MBBS valid in UK</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -6004,12 +6004,12 @@
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+          <t>UKMLA After MBBS in India: What to Do Next</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-for-bangladeshi-doctors</t>
+          <t>/news#ukmla-after-mbbs-in-india</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
@@ -6024,24 +6024,24 @@
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>Established (43 posts)</t>
+          <t>Established (51 posts)</t>
         </is>
       </c>
       <c r="J107" s="2" t="inlineStr">
         <is>
-          <t>01 July 2026</t>
+          <t>03 July 2026</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>UKMLA for Chinese doctors</t>
+          <t>UKMLA crash course for doctors</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>UKMLA for GP doctors in UK; GMC registration process for doctors; UKMLA eligibility for Indian doctors; UKMLA fees for doctors 2026; UKMLA for Indian doctors</t>
+          <t>UKMLA for GP doctors in UK; UKMLA for Indian doctors; UKMLA for Nigerian doctors; UKMLA for Pakistani doctors; UKMLA for Bangladeshi doctors</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -6051,17 +6051,17 @@
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Eligibility</t>
+          <t>Preparation</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>UKMLA for Chinese Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+          <t>UKMLA Crash Course for Doctors: How to Choose the Right Intensive Course</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-for-chinese-doctors</t>
+          <t>/news#ukmla-crash-course-for-doctors</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
@@ -6076,7 +6076,7 @@
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>Established (43 posts)</t>
+          <t>Established (51 posts)</t>
         </is>
       </c>
       <c r="J108" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>UKMLA for Egyptian doctors</t>
+          <t>UKMLA question bank</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t>UKMLA for GP doctors in UK; GMC registration process for doctors; UKMLA eligibility for Indian doctors; UKMLA fees for doctors 2026; UKMLA for Indian doctors</t>
+          <t>best question bank for UKMLA; best question bank for UKMLA UK students; UKMLA question bank free for students; UKMLA AKT question bank free; UKMLA mock</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -6103,17 +6103,17 @@
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>Eligibility</t>
+          <t>Preparation</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+          <t>UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-for-egyptian-doctors</t>
+          <t>/news#ukmla-question-bank-and-mock-tests</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
@@ -6128,7 +6128,7 @@
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
-          <t>Established (43 posts)</t>
+          <t>Established (51 posts)</t>
         </is>
       </c>
       <c r="J109" s="2" t="inlineStr">
@@ -6140,7 +6140,7 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>UKMLA for Filipino doctors</t>
+          <t>UKMLA for Bangladeshi doctors</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
@@ -6160,12 +6160,12 @@
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>UKMLA for Filipino Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+          <t>UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-for-filipino-doctors</t>
+          <t>/news#ukmla-for-bangladeshi-doctors</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
@@ -6180,7 +6180,7 @@
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>Established (43 posts)</t>
+          <t>Established (51 posts)</t>
         </is>
       </c>
       <c r="J110" s="2" t="inlineStr">
@@ -6192,12 +6192,12 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>UKMLA for Gulf and Saudi doctors</t>
+          <t>UKMLA for Chinese doctors</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>UKMLA for GP doctors in UK; UKMLA for Saudi / Gulf doctors; UKMLA for Saudi doctors; GMC registration process for doctors; UKMLA eligibility for Indian doctors</t>
+          <t>UKMLA for GP doctors in UK; GMC registration process for doctors; UKMLA eligibility for Indian doctors; UKMLA fees for doctors 2026; UKMLA for Indian doctors</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -6212,12 +6212,12 @@
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+          <t>UKMLA for Chinese Doctors: Eligibility, Fees and the Route to GMC Registration</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-for-gulf-doctors</t>
+          <t>/news#ukmla-for-chinese-doctors</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
@@ -6232,24 +6232,24 @@
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
-          <t>Established (43 posts)</t>
+          <t>Established (51 posts)</t>
         </is>
       </c>
       <c r="J111" s="2" t="inlineStr">
         <is>
-          <t>01 July 2026</t>
+          <t>02 July 2026</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>UKMLA for international medical graduates</t>
+          <t>UKMLA for Egyptian doctors</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
         <is>
-          <t>international medical graduates; UKMLA eligibility for international medical graduates; UKMLA for Caribbean medical graduates; Eligibility for International Medical Graduates (IMGs); For International Medical Graduates (PLAB Route)</t>
+          <t>UKMLA for GP doctors in UK; GMC registration process for doctors; UKMLA eligibility for Indian doctors; UKMLA fees for doctors 2026; UKMLA for Indian doctors</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -6264,12 +6264,12 @@
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>UKMLA for International Medical Graduates: Country-by-Country Quick Reference</t>
+          <t>UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-for-international-medical-graduates-country-routes</t>
+          <t>/news#ukmla-for-egyptian-doctors</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
@@ -6284,7 +6284,7 @@
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>Established (43 posts)</t>
+          <t>Established (51 posts)</t>
         </is>
       </c>
       <c r="J112" s="2" t="inlineStr">
@@ -6296,7 +6296,7 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>UKMLA for Jamaican and Trinidadian doctors</t>
+          <t>UKMLA for Ethiopian doctors</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
@@ -6316,12 +6316,12 @@
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>UKMLA for Jamaican and Trinidadian Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+          <t>UKMLA for Ethiopian Doctors: Eligibility, Fees and the Route to GMC Registration</t>
         </is>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-for-jamaican-and-trinidadian-doctors</t>
+          <t>/news#ukmla-for-ethiopian-doctors</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
@@ -6336,19 +6336,19 @@
       </c>
       <c r="I113" s="2" t="inlineStr">
         <is>
-          <t>Established (43 posts)</t>
+          <t>Established (51 posts)</t>
         </is>
       </c>
       <c r="J113" s="2" t="inlineStr">
         <is>
-          <t>02 July 2026</t>
+          <t>03 July 2026</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>UKMLA for Jordanian and Iraqi doctors</t>
+          <t>UKMLA for Filipino doctors</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
@@ -6368,12 +6368,12 @@
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>UKMLA for Jordanian and Iraqi Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+          <t>UKMLA for Filipino Doctors: Eligibility, Fees and the Route to GMC Registration</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-for-jordanian-and-iraqi-doctors</t>
+          <t>/news#ukmla-for-filipino-doctors</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
@@ -6388,24 +6388,24 @@
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>Established (43 posts)</t>
+          <t>Established (51 posts)</t>
         </is>
       </c>
       <c r="J114" s="2" t="inlineStr">
         <is>
-          <t>02 July 2026</t>
+          <t>01 July 2026</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>UKMLA for Kenyan and East African doctors</t>
+          <t>UKMLA for Ghanaian doctors</t>
         </is>
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>UKMLA for GP doctors in UK; UKMLA for South African doctors; GMC registration process for doctors; UKMLA eligibility for Indian doctors; UKMLA fees for doctors 2026</t>
+          <t>UKMLA for GP doctors in UK; GMC registration process for doctors; UKMLA eligibility for Indian doctors; UKMLA fees for doctors 2026; UKMLA for Indian doctors</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -6420,12 +6420,12 @@
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>UKMLA for Kenyan and East African Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+          <t>UKMLA for Ghanaian Doctors: Eligibility, Fees and the Route to GMC Registration</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-for-kenyan-and-east-african-doctors</t>
+          <t>/news#ukmla-for-ghanaian-doctors</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
@@ -6440,24 +6440,24 @@
       </c>
       <c r="I115" s="2" t="inlineStr">
         <is>
-          <t>Established (43 posts)</t>
+          <t>Established (51 posts)</t>
         </is>
       </c>
       <c r="J115" s="2" t="inlineStr">
         <is>
-          <t>02 July 2026</t>
+          <t>03 July 2026</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>UKMLA for Nigerian doctors</t>
+          <t>UKMLA for Gulf and Saudi doctors</t>
         </is>
       </c>
       <c r="B116" s="3" t="inlineStr">
         <is>
-          <t>UKMLA for GP doctors in UK; UKMLA eligibility for Indian doctors; UKMLA fees for doctors 2026; UKMLA for Indian doctors; UKMLA for Pakistani doctors</t>
+          <t>UKMLA for GP doctors in UK; UKMLA for Saudi / Gulf doctors; UKMLA for Saudi doctors; GMC registration process for doctors; UKMLA eligibility for Indian doctors</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC</t>
+          <t>UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-for-nigerian-doctors</t>
+          <t>/news#ukmla-for-gulf-doctors</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
@@ -6492,7 +6492,7 @@
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>Established (43 posts)</t>
+          <t>Established (51 posts)</t>
         </is>
       </c>
       <c r="J116" s="2" t="inlineStr">
@@ -6504,12 +6504,12 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>UKMLA for Pakistani doctors</t>
+          <t>UKMLA for Indian doctors</t>
         </is>
       </c>
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t>UKMLA for GP doctors in UK; UKMLA eligibility for Indian doctors; UKMLA fees for doctors 2026; UKMLA for Indian doctors; UKMLA for Nigerian doctors</t>
+          <t>UKMLA for GP doctors in UK; UKMLA eligibility for Indian doctors; UKMLA preparation for Indian doctors; UKMLA vs PLAB for Indian doctors; GMC registration process for doctors</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK</t>
+          <t>UKMLA for Indian Doctors: Eligibility, Fees and the Route to GMC Registration</t>
         </is>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-for-pakistani-doctors</t>
+          <t>/news#ukmla-for-indian-doctors</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
@@ -6544,24 +6544,24 @@
       </c>
       <c r="I117" s="2" t="inlineStr">
         <is>
-          <t>Established (43 posts)</t>
+          <t>Established (51 posts)</t>
         </is>
       </c>
       <c r="J117" s="2" t="inlineStr">
         <is>
-          <t>01 July 2026</t>
+          <t>03 July 2026</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>UKMLA for refugee doctors</t>
+          <t>UKMLA for international medical graduates</t>
         </is>
       </c>
       <c r="B118" s="3" t="inlineStr">
         <is>
-          <t>UKMLA for GP doctors in UK; UKMLA fees for refugee doctors; UKMLA for Indian doctors; UKMLA for Nigerian doctors; UKMLA for Pakistani doctors</t>
+          <t>international medical graduates; UKMLA eligibility for international medical graduates; UKMLA for Caribbean medical graduates; Eligibility for International Medical Graduates (IMGs); For International Medical Graduates (PLAB Route)</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>UKMLA for Refugee Doctors: The GMC Assistance Programme and Fee Support</t>
+          <t>UKMLA for International Medical Graduates: Country-by-Country Quick Reference</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-for-refugee-doctors</t>
+          <t>/news#ukmla-for-international-medical-graduates-country-routes</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
@@ -6596,7 +6596,7 @@
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>Established (43 posts)</t>
+          <t>Established (51 posts)</t>
         </is>
       </c>
       <c r="J118" s="2" t="inlineStr">
@@ -6608,7 +6608,7 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>UKMLA for South African doctors</t>
+          <t>UKMLA for Jamaican and Trinidadian doctors</t>
         </is>
       </c>
       <c r="B119" s="3" t="inlineStr">
@@ -6628,12 +6628,12 @@
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+          <t>UKMLA for Jamaican and Trinidadian Doctors: Eligibility, Fees and the Route to GMC Registration</t>
         </is>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-for-south-african-doctors</t>
+          <t>/news#ukmla-for-jamaican-and-trinidadian-doctors</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
@@ -6648,19 +6648,19 @@
       </c>
       <c r="I119" s="2" t="inlineStr">
         <is>
-          <t>Established (43 posts)</t>
+          <t>Established (51 posts)</t>
         </is>
       </c>
       <c r="J119" s="2" t="inlineStr">
         <is>
-          <t>01 July 2026</t>
+          <t>02 July 2026</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>UKMLA for Sri Lankan doctors</t>
+          <t>UKMLA for Jordanian and Iraqi doctors</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
@@ -6680,12 +6680,12 @@
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+          <t>UKMLA for Jordanian and Iraqi Doctors: Eligibility, Fees and the Route to GMC Registration</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-for-sri-lankan-doctors</t>
+          <t>/news#ukmla-for-jordanian-and-iraqi-doctors</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
@@ -6700,24 +6700,24 @@
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>Established (43 posts)</t>
+          <t>Established (51 posts)</t>
         </is>
       </c>
       <c r="J120" s="2" t="inlineStr">
         <is>
-          <t>01 July 2026</t>
+          <t>02 July 2026</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>UKMLA for Vietnamese and Indonesian doctors</t>
+          <t>UKMLA for Kenyan and East African doctors</t>
         </is>
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t>UKMLA for GP doctors in UK; GMC registration process for doctors; UKMLA eligibility for Indian doctors; UKMLA fees for doctors 2026; UKMLA for Indian doctors</t>
+          <t>UKMLA for GP doctors in UK; UKMLA for South African doctors; GMC registration process for doctors; UKMLA eligibility for Indian doctors; UKMLA fees for doctors 2026</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -6732,12 +6732,12 @@
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>UKMLA for Vietnamese and Indonesian Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+          <t>UKMLA for Kenyan and East African Doctors: Eligibility, Fees and the Route to GMC Registration</t>
         </is>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-for-vietnamese-and-indonesian-doctors</t>
+          <t>/news#ukmla-for-kenyan-and-east-african-doctors</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
@@ -6752,7 +6752,7 @@
       </c>
       <c r="I121" s="2" t="inlineStr">
         <is>
-          <t>Established (43 posts)</t>
+          <t>Established (51 posts)</t>
         </is>
       </c>
       <c r="J121" s="2" t="inlineStr">
@@ -6764,12 +6764,12 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>UKMLA NHS job after exam</t>
+          <t>UKMLA for Malaysian doctors</t>
         </is>
       </c>
       <c r="B122" s="3" t="inlineStr">
         <is>
-          <t>UKMLA exam; what is the UKMLA exam; The Exam; gmc exam; NHS jobs after GMC registration</t>
+          <t>UKMLA for GP doctors in UK; GMC registration process for doctors; UKMLA eligibility for Indian doctors; UKMLA fees for doctors 2026; UKMLA for Indian doctors</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -6784,12 +6784,12 @@
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
+          <t>UKMLA for Malaysian Doctors: Eligibility, Fees and the Route to GMC Registration</t>
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-to-nhs-job-pathway</t>
+          <t>/news#ukmla-for-malaysian-doctors</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
@@ -6804,24 +6804,24 @@
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
-          <t>Established (43 posts)</t>
+          <t>Established (51 posts)</t>
         </is>
       </c>
       <c r="J122" s="2" t="inlineStr">
         <is>
-          <t>01 July 2026</t>
+          <t>03 July 2026</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>UKMLA vs AMC exam comparison</t>
+          <t>UKMLA for Nepali doctors</t>
         </is>
       </c>
       <c r="B123" s="3" t="inlineStr">
         <is>
-          <t>UKMLA exam; what is the UKMLA exam; The Exam; Exam Pattern Comparison; UKMLA vs MCCQE Canada</t>
+          <t>UKMLA for GP doctors in UK; GMC registration process for doctors; UKMLA eligibility for Indian doctors; UKMLA fees for doctors 2026; UKMLA for Indian doctors</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -6831,17 +6831,17 @@
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>UKMLA vs PLAB</t>
+          <t>Eligibility</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>UKMLA vs AMC and MCCQE: Comparing the UK Route to Australia and Canada</t>
+          <t>UKMLA for Nepali Doctors: Eligibility, Fees and the Route to GMC Registration</t>
         </is>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-vs-amc-and-mccqe-comparison</t>
+          <t>/news#ukmla-for-nepali-doctors</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
@@ -6856,24 +6856,24 @@
       </c>
       <c r="I123" s="2" t="inlineStr">
         <is>
-          <t>Established (43 posts)</t>
+          <t>Established (51 posts)</t>
         </is>
       </c>
       <c r="J123" s="2" t="inlineStr">
         <is>
-          <t>01 July 2026</t>
+          <t>03 July 2026</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>UKMLA vs NEET PG</t>
+          <t>UKMLA for Nigerian doctors</t>
         </is>
       </c>
       <c r="B124" s="3" t="inlineStr">
         <is>
-          <t>UKMLA exam for Indian medical graduates; UKMLA for international medical graduates; UKMLA for Caribbean medical graduates; international medical graduates; UKMLA for Indian doctors</t>
+          <t>UKMLA for GP doctors in UK; UKMLA eligibility for Indian doctors; UKMLA fees for doctors 2026; UKMLA for Indian doctors; UKMLA for Pakistani doctors</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -6883,17 +6883,17 @@
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>UKMLA vs PLAB</t>
+          <t>Eligibility</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?</t>
+          <t>UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-vs-neet-pg</t>
+          <t>/news#ukmla-for-nigerian-doctors</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
@@ -6908,7 +6908,7 @@
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>Established (43 posts)</t>
+          <t>Established (51 posts)</t>
         </is>
       </c>
       <c r="J124" s="2" t="inlineStr">
@@ -6920,12 +6920,12 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>UKMLA vs USMLE</t>
+          <t>UKMLA for Pakistani doctors</t>
         </is>
       </c>
       <c r="B125" s="3" t="inlineStr">
         <is>
-          <t>UKMLA vs USMLE which is easier; UKMLA exam; what is the UKMLA exam; The Exam; UKMLA vs USMLE cost and difficulty</t>
+          <t>UKMLA for GP doctors in UK; UKMLA eligibility for Indian doctors; UKMLA fees for doctors 2026; UKMLA for Indian doctors; UKMLA for Nigerian doctors</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -6935,17 +6935,17 @@
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>UKMLA vs PLAB</t>
+          <t>Eligibility</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
+          <t>UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK</t>
         </is>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-vs-usmle-comparison</t>
+          <t>/news#ukmla-for-pakistani-doctors</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
@@ -6960,7 +6960,7 @@
       </c>
       <c r="I125" s="2" t="inlineStr">
         <is>
-          <t>Established (43 posts)</t>
+          <t>Established (51 posts)</t>
         </is>
       </c>
       <c r="J125" s="2" t="inlineStr">
@@ -6972,12 +6972,12 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>NHS pay scales and banding</t>
+          <t>UKMLA for refugee doctors</t>
         </is>
       </c>
       <c r="B126" s="3" t="inlineStr">
         <is>
-          <t>UKMLA for GP doctors in UK; UKMLA for doctors already working in NHS; UKMLA for Indian doctors; UKMLA for Nigerian doctors; UKMLA for Pakistani doctors</t>
+          <t>UKMLA for GP doctors in UK; UKMLA fees for refugee doctors; UKMLA for Indian doctors; UKMLA for Nigerian doctors; UKMLA for Pakistani doctors</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -6987,17 +6987,17 @@
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>Fees</t>
+          <t>Eligibility</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>Understanding NHS Pay Scales and Banding for Doctors</t>
+          <t>UKMLA for Refugee Doctors: The GMC Assistance Programme and Fee Support</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>/news#understanding-nhs-pay-scales-and-banding-for-doctors</t>
+          <t>/news#ukmla-for-refugee-doctors</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
@@ -7012,44 +7012,44 @@
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>Established (43 posts)</t>
+          <t>Established (51 posts)</t>
         </is>
       </c>
       <c r="J126" s="2" t="inlineStr">
         <is>
-          <t>02 July 2026</t>
+          <t>01 July 2026</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>GMC fitness to practise</t>
+          <t>UKMLA for South African doctors</t>
         </is>
       </c>
       <c r="B127" s="3" t="inlineStr">
         <is>
-          <t>UKMLA for GP doctors in UK; gmc exam; gmc licensing; gmc Manchester; gmc updates</t>
+          <t>UKMLA for GP doctors in UK; GMC registration process for doctors; UKMLA eligibility for Indian doctors; UKMLA fees for doctors 2026; UKMLA for Indian doctors</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>Professional Practice &amp; Safety</t>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>Registration Guide</t>
+          <t>Eligibility</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>GMC Fitness to Practise Explained: What New Doctors Need to Know</t>
+          <t>UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration</t>
         </is>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>/news#gmc-fitness-to-practise-explained-for-new-doctors</t>
+          <t>/news#ukmla-for-south-african-doctors</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
@@ -7064,44 +7064,44 @@
       </c>
       <c r="I127" s="2" t="inlineStr">
         <is>
-          <t>Established (6 posts)</t>
+          <t>Established (51 posts)</t>
         </is>
       </c>
       <c r="J127" s="2" t="inlineStr">
         <is>
-          <t>02 July 2026</t>
+          <t>01 July 2026</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>GMC regulation of physician associates</t>
+          <t>UKMLA for Sri Lankan doctors</t>
         </is>
       </c>
       <c r="B128" s="3" t="inlineStr">
         <is>
-          <t>UKMLA for GP doctors in UK; gmc exam; gmc licensing; gmc Manchester; gmc updates</t>
+          <t>UKMLA for GP doctors in UK; GMC registration process for doctors; UKMLA eligibility for Indian doctors; UKMLA fees for doctors 2026; UKMLA for Indian doctors</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>Professional Practice &amp; Safety</t>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>Registration Guide</t>
+          <t>Eligibility</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>GMC Regulation of Physician Associates: What Doctors Need to Know</t>
+          <t>UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration</t>
         </is>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>/news#gmc-regulation-of-physician-associates-what-doctors-need-to-know</t>
+          <t>/news#ukmla-for-sri-lankan-doctors</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr">
@@ -7116,40 +7116,44 @@
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>Established (6 posts)</t>
+          <t>Established (51 posts)</t>
         </is>
       </c>
       <c r="J128" s="2" t="inlineStr">
         <is>
-          <t>02 July 2026</t>
+          <t>01 July 2026</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>Good Medical Practice UKMLA</t>
+          <t>UKMLA for Sudanese doctors</t>
         </is>
       </c>
       <c r="B129" s="3" t="inlineStr">
         <is>
-          <t>how to practice medicine in UK; medical acronyms; medical students; UKMLA for international medical graduates; UKMLA mock exam practice</t>
+          <t>UKMLA for GP doctors in UK; GMC registration process for doctors; UKMLA eligibility for Indian doctors; UKMLA fees for doctors 2026; UKMLA for Indian doctors</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>Professional Practice &amp; Safety</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr"/>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>Good Medical Practice and the UKMLA: What the GMC Expects</t>
+          <t>UKMLA for Sudanese Doctors: Eligibility, Fees and the Route to GMC Registration</t>
         </is>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>/news#good-medical-practice-ukmla</t>
+          <t>/news#ukmla-for-sudanese-doctors</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
@@ -7164,40 +7168,44 @@
       </c>
       <c r="I129" s="2" t="inlineStr">
         <is>
-          <t>Established (6 posts)</t>
+          <t>Established (51 posts)</t>
         </is>
       </c>
       <c r="J129" s="2" t="inlineStr">
         <is>
-          <t>30 June 2026</t>
+          <t>03 July 2026</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>patient safety UKMLA</t>
+          <t>UKMLA for Vietnamese and Indonesian doctors</t>
         </is>
       </c>
       <c r="B130" s="3" t="inlineStr">
         <is>
-          <t>1. Patient Presentations; The official GMC MLA Content Map listing core patient presentations, conditions, and practical procedures</t>
+          <t>UKMLA for GP doctors in UK; GMC registration process for doctors; UKMLA eligibility for Indian doctors; UKMLA fees for doctors 2026; UKMLA for Indian doctors</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>Professional Practice &amp; Safety</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr"/>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting</t>
+          <t>UKMLA for Vietnamese and Indonesian Doctors: Eligibility, Fees and the Route to GMC Registration</t>
         </is>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>/news#patient-safety-ukmla-prescribing-errors</t>
+          <t>/news#ukmla-for-vietnamese-and-indonesian-doctors</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
@@ -7212,40 +7220,44 @@
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>Established (6 posts)</t>
+          <t>Established (51 posts)</t>
         </is>
       </c>
       <c r="J130" s="2" t="inlineStr">
         <is>
-          <t>30 June 2026</t>
+          <t>02 July 2026</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>safeguarding UKMLA</t>
+          <t>UKMLA for Zimbabwean doctors</t>
         </is>
       </c>
       <c r="B131" s="3" t="inlineStr">
         <is>
-          <t>ukmla guide; UKMLA pharmacology revision; about ukmla guide; contact ukmla guide; img guide</t>
+          <t>UKMLA for GP doctors in UK; GMC registration process for doctors; UKMLA eligibility for Indian doctors; UKMLA fees for doctors 2026; UKMLA for Indian doctors</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>Professional Practice &amp; Safety</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr"/>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>Safeguarding Adults and Children: A UKMLA Revision Guide</t>
+          <t>UKMLA for Zimbabwean Doctors: Eligibility, Fees and the Route to GMC Registration</t>
         </is>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>/news#safeguarding-ukmla-revision</t>
+          <t>/news#ukmla-for-zimbabwean-doctors</t>
         </is>
       </c>
       <c r="G131" s="2" t="inlineStr">
@@ -7260,44 +7272,44 @@
       </c>
       <c r="I131" s="2" t="inlineStr">
         <is>
-          <t>Established (6 posts)</t>
+          <t>Established (51 posts)</t>
         </is>
       </c>
       <c r="J131" s="2" t="inlineStr">
         <is>
-          <t>30 June 2026</t>
+          <t>03 July 2026</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>GMC revalidation process</t>
+          <t>UKMLA NHS job after exam</t>
         </is>
       </c>
       <c r="B132" s="3" t="inlineStr">
         <is>
-          <t>UKMLA registration process GMC; GMC registration process for doctors; GMC EPIC verification process; UKMLA for GP doctors in UK; gmc exam</t>
+          <t>UKMLA exam; what is the UKMLA exam; The Exam; gmc exam; NHS jobs after GMC registration</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>Professional Practice &amp; Safety</t>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>Registration Guide</t>
+          <t>Eligibility</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>The GMC Revalidation Process, Explained for New Doctors</t>
+          <t>UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>/news#gmc-revalidation-process-explained</t>
+          <t>/news#ukmla-to-nhs-job-pathway</t>
         </is>
       </c>
       <c r="G132" s="2" t="inlineStr">
@@ -7312,229 +7324,237 @@
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>Established (6 posts)</t>
+          <t>Established (51 posts)</t>
         </is>
       </c>
       <c r="J132" s="2" t="inlineStr">
         <is>
+          <t>01 July 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA vs AMC exam comparison</t>
+        </is>
+      </c>
+      <c r="B133" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA exam; what is the UKMLA exam; The Exam; Exam Pattern Comparison; UKMLA vs MCCQE Canada</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA vs PLAB</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA vs AMC and MCCQE: Comparing the UK Route to Australia and Canada</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-vs-amc-and-mccqe-comparison</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I133" s="2" t="inlineStr">
+        <is>
+          <t>Established (51 posts)</t>
+        </is>
+      </c>
+      <c r="J133" s="2" t="inlineStr">
+        <is>
+          <t>01 July 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA vs NEET PG</t>
+        </is>
+      </c>
+      <c r="B134" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA exam for Indian medical graduates; UKMLA for international medical graduates; UKMLA for Caribbean medical graduates; international medical graduates; UKMLA for Indian doctors</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA vs PLAB</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-vs-neet-pg</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I134" s="2" t="inlineStr">
+        <is>
+          <t>Established (51 posts)</t>
+        </is>
+      </c>
+      <c r="J134" s="2" t="inlineStr">
+        <is>
+          <t>01 July 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA vs USMLE</t>
+        </is>
+      </c>
+      <c r="B135" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA vs USMLE which is easier; UKMLA exam; what is the UKMLA exam; The Exam; UKMLA vs USMLE cost and difficulty</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA vs PLAB</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-vs-usmle-comparison</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H135" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I135" s="2" t="inlineStr">
+        <is>
+          <t>Established (51 posts)</t>
+        </is>
+      </c>
+      <c r="J135" s="2" t="inlineStr">
+        <is>
+          <t>01 July 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>NHS pay scales and banding</t>
+        </is>
+      </c>
+      <c r="B136" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA for GP doctors in UK; UKMLA for doctors already working in NHS; UKMLA for Indian doctors; UKMLA for Nigerian doctors; UKMLA for Pakistani doctors</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>Fees</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>Understanding NHS Pay Scales and Banding for Doctors</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>/news#understanding-nhs-pay-scales-and-banding-for-doctors</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I136" s="2" t="inlineStr">
+        <is>
+          <t>Established (51 posts)</t>
+        </is>
+      </c>
+      <c r="J136" s="2" t="inlineStr">
+        <is>
           <t>02 July 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="4" t="inlineStr">
-        <is>
-          <t>UKMLA for IMG</t>
-        </is>
-      </c>
-      <c r="B133" s="5" t="inlineStr">
-        <is>
-          <t>UKMLA for international medical graduates; UKMLA eligibility; UKMLA exam for UK medical students; UKMLA eligibility for international medical graduates</t>
-        </is>
-      </c>
-      <c r="C133" s="4" t="inlineStr">
-        <is>
-          <t>Registration &amp; Eligibility</t>
-        </is>
-      </c>
-      <c r="D133" s="4" t="inlineStr">
-        <is>
-          <t>Eligibility</t>
-        </is>
-      </c>
-      <c r="E133" s="4" t="inlineStr">
-        <is>
-          <t>Eligibility</t>
-        </is>
-      </c>
-      <c r="F133" s="4" t="inlineStr">
-        <is>
-          <t>/eligibility</t>
-        </is>
-      </c>
-      <c r="G133" s="4" t="inlineStr">
-        <is>
-          <t>Informational</t>
-        </is>
-      </c>
-      <c r="H133" s="4" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="I133" s="4" t="inlineStr">
-        <is>
-          <t>Established (29 posts)</t>
-        </is>
-      </c>
-      <c r="J133" s="4" t="inlineStr">
-        <is>
-          <t>N/A (static page)</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="4" t="inlineStr">
-        <is>
-          <t>Fees</t>
-        </is>
-      </c>
-      <c r="B134" s="5" t="inlineStr"/>
-      <c r="C134" s="4" t="inlineStr">
-        <is>
-          <t>Registration &amp; Eligibility</t>
-        </is>
-      </c>
-      <c r="D134" s="4" t="inlineStr">
-        <is>
-          <t>Fees</t>
-        </is>
-      </c>
-      <c r="E134" s="4" t="inlineStr">
-        <is>
-          <t>Fees</t>
-        </is>
-      </c>
-      <c r="F134" s="4" t="inlineStr">
-        <is>
-          <t>/fees</t>
-        </is>
-      </c>
-      <c r="G134" s="4" t="inlineStr">
-        <is>
-          <t>Commercial</t>
-        </is>
-      </c>
-      <c r="H134" s="4" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="I134" s="4" t="inlineStr">
-        <is>
-          <t>Established (29 posts)</t>
-        </is>
-      </c>
-      <c r="J134" s="4" t="inlineStr">
-        <is>
-          <t>N/A (static page)</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="4" t="inlineStr">
-        <is>
-          <t>UKMLA dates</t>
-        </is>
-      </c>
-      <c r="B135" s="5" t="inlineStr"/>
-      <c r="C135" s="4" t="inlineStr">
-        <is>
-          <t>Registration &amp; Eligibility</t>
-        </is>
-      </c>
-      <c r="D135" s="4" t="inlineStr">
-        <is>
-          <t>Key Dates</t>
-        </is>
-      </c>
-      <c r="E135" s="4" t="inlineStr">
-        <is>
-          <t>Key Dates</t>
-        </is>
-      </c>
-      <c r="F135" s="4" t="inlineStr">
-        <is>
-          <t>/key-dates</t>
-        </is>
-      </c>
-      <c r="G135" s="4" t="inlineStr">
-        <is>
-          <t>Transactional</t>
-        </is>
-      </c>
-      <c r="H135" s="4" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="I135" s="4" t="inlineStr">
-        <is>
-          <t>Established (29 posts)</t>
-        </is>
-      </c>
-      <c r="J135" s="4" t="inlineStr">
-        <is>
-          <t>N/A (static page)</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="4" t="inlineStr">
-        <is>
-          <t>UKMLA registration</t>
-        </is>
-      </c>
-      <c r="B136" s="5" t="inlineStr">
-        <is>
-          <t>UKMLA booking; English language requirement for UKMLA; UKMLA registration process GMC</t>
-        </is>
-      </c>
-      <c r="C136" s="4" t="inlineStr">
-        <is>
-          <t>Registration &amp; Eligibility</t>
-        </is>
-      </c>
-      <c r="D136" s="4" t="inlineStr">
-        <is>
-          <t>Registration Guide</t>
-        </is>
-      </c>
-      <c r="E136" s="4" t="inlineStr">
-        <is>
-          <t>Registration Guide</t>
-        </is>
-      </c>
-      <c r="F136" s="4" t="inlineStr">
-        <is>
-          <t>/registration-guide</t>
-        </is>
-      </c>
-      <c r="G136" s="4" t="inlineStr">
-        <is>
-          <t>Informational</t>
-        </is>
-      </c>
-      <c r="H136" s="4" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="I136" s="4" t="inlineStr">
-        <is>
-          <t>Established (29 posts)</t>
-        </is>
-      </c>
-      <c r="J136" s="4" t="inlineStr">
-        <is>
-          <t>N/A (static page)</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>Annual Review of Competence Progression</t>
+          <t>GMC fitness to practise</t>
         </is>
       </c>
       <c r="B137" s="3" t="inlineStr">
         <is>
-          <t>GMC annual retention fee; The Biggest Confusion Explained; UKMLA AKT standard setting explained</t>
+          <t>UKMLA for GP doctors in UK; gmc exam; gmc licensing; gmc Manchester; gmc updates</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>Registration &amp; Eligibility</t>
+          <t>Professional Practice &amp; Safety</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
@@ -7544,12 +7564,12 @@
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>ARCP: The Annual Review of Competence Progression, Explained</t>
+          <t>GMC Fitness to Practise Explained: What New Doctors Need to Know</t>
         </is>
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>/news#arcp-annual-review-of-competence-progression-explained</t>
+          <t>/news#gmc-fitness-to-practise-explained-for-new-doctors</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
@@ -7564,7 +7584,7 @@
       </c>
       <c r="I137" s="2" t="inlineStr">
         <is>
-          <t>Established (29 posts)</t>
+          <t>Established (6 posts)</t>
         </is>
       </c>
       <c r="J137" s="2" t="inlineStr">
@@ -7576,32 +7596,32 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>UKMLA disability access adjustments</t>
+          <t>GMC regulation of physician associates</t>
         </is>
       </c>
       <c r="B138" s="3" t="inlineStr">
         <is>
-          <t>ukmla guide; Reasonable Adjustments; reasonable adjustments gmc; about ukmla guide; contact ukmla guide</t>
+          <t>UKMLA for GP doctors in UK; gmc exam; gmc licensing; gmc Manchester; gmc updates</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>Registration &amp; Eligibility</t>
+          <t>Professional Practice &amp; Safety</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>Appeals and Resits</t>
+          <t>Registration Guide</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide</t>
+          <t>GMC Regulation of Physician Associates: What Doctors Need to Know</t>
         </is>
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>/news#disability-access-ukmla-guide</t>
+          <t>/news#gmc-regulation-of-physician-associates-what-doctors-need-to-know</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
@@ -7616,44 +7636,40 @@
       </c>
       <c r="I138" s="2" t="inlineStr">
         <is>
-          <t>Established (29 posts)</t>
+          <t>Established (6 posts)</t>
         </is>
       </c>
       <c r="J138" s="2" t="inlineStr">
         <is>
-          <t>30 June 2026</t>
+          <t>02 July 2026</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>UKMLA exemptions for specialist doctors</t>
+          <t>Good Medical Practice UKMLA</t>
         </is>
       </c>
       <c r="B139" s="3" t="inlineStr">
         <is>
-          <t>UKMLA for GP doctors in UK; do all doctors need to take UKMLA; is UKMLA required for experienced doctors; UKMLA for Indian doctors; UKMLA for Nigerian doctors</t>
+          <t>how to practice medicine in UK; medical acronyms; medical students; UKMLA for international medical graduates; UKMLA mock exam practice</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>Registration &amp; Eligibility</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="inlineStr">
-        <is>
-          <t>Eligibility</t>
-        </is>
-      </c>
+          <t>Professional Practice &amp; Safety</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr"/>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs</t>
+          <t>Good Medical Practice and the UKMLA: What the GMC Expects</t>
         </is>
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-exemptions-for-specialist-and-gp-doctors</t>
+          <t>/news#good-medical-practice-ukmla</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
@@ -7668,44 +7684,40 @@
       </c>
       <c r="I139" s="2" t="inlineStr">
         <is>
-          <t>Established (29 posts)</t>
+          <t>Established (6 posts)</t>
         </is>
       </c>
       <c r="J139" s="2" t="inlineStr">
         <is>
-          <t>01 July 2026</t>
+          <t>30 June 2026</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>GMC English language exemption</t>
+          <t>patient safety UKMLA</t>
         </is>
       </c>
       <c r="B140" s="3" t="inlineStr">
         <is>
-          <t>English language requirement for UKMLA; OET vs IELTS for GMC registration; UKMLA exemption for specialists; gmc exam; gmc licensing</t>
+          <t>1. Patient Presentations; The official GMC MLA Content Map listing core patient presentations, conditions, and practical procedures</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>Registration &amp; Eligibility</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="inlineStr">
-        <is>
-          <t>Eligibility</t>
-        </is>
-      </c>
+          <t>Professional Practice &amp; Safety</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr"/>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>GMC English Language Exemption: Do You Need to Sit IELTS or OET?</t>
+          <t>Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting</t>
         </is>
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>/news#gmc-english-language-exemption-for-imgs</t>
+          <t>/news#patient-safety-ukmla-prescribing-errors</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr">
@@ -7720,44 +7732,40 @@
       </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
-          <t>Established (29 posts)</t>
+          <t>Established (6 posts)</t>
         </is>
       </c>
       <c r="J140" s="2" t="inlineStr">
         <is>
-          <t>02 July 2026</t>
+          <t>30 June 2026</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>GMC Order reform 2026</t>
+          <t>safeguarding UKMLA</t>
         </is>
       </c>
       <c r="B141" s="3" t="inlineStr">
         <is>
-          <t>cost of GMC registration 2026; gmc exam; gmc licensing; gmc Manchester; gmc updates</t>
+          <t>ukmla guide; UKMLA pharmacology revision; about ukmla guide; contact ukmla guide; img guide</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>Registration &amp; Eligibility</t>
-        </is>
-      </c>
-      <c r="D141" s="2" t="inlineStr">
-        <is>
-          <t>Registration Guide</t>
-        </is>
-      </c>
+          <t>Professional Practice &amp; Safety</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr"/>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>GMC Order Reform 2026: The Consultation on Protected Medical Titles</t>
+          <t>Safeguarding Adults and Children: A UKMLA Revision Guide</t>
         </is>
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>/news#gmc-order-reform-2026-protected-medical-titles</t>
+          <t>/news#safeguarding-ukmla-revision</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr">
@@ -7772,284 +7780,276 @@
       </c>
       <c r="I141" s="2" t="inlineStr">
         <is>
-          <t>Established (29 posts)</t>
+          <t>Established (6 posts)</t>
         </is>
       </c>
       <c r="J141" s="2" t="inlineStr">
         <is>
-          <t>02 July 2026</t>
+          <t>30 June 2026</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>GMC registration refund policy</t>
+          <t>GMC revalidation process</t>
         </is>
       </c>
       <c r="B142" s="3" t="inlineStr">
         <is>
-          <t>UKMLA registration; UKMLA GMC registration for graduates; UKMLA vs specialist registration GMC; UKMLA registration process GMC; gmc registration guide</t>
+          <t>UKMLA registration process GMC; GMC registration process for doctors; GMC EPIC verification process; UKMLA for GP doctors in UK; gmc exam</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
+          <t>Professional Practice &amp; Safety</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>Registration Guide</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>The GMC Revalidation Process, Explained for New Doctors</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>/news#gmc-revalidation-process-explained</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="inlineStr">
+        <is>
+          <t>Established (6 posts)</t>
+        </is>
+      </c>
+      <c r="J142" s="2" t="inlineStr">
+        <is>
+          <t>02 July 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="4" t="inlineStr">
+        <is>
+          <t>UKMLA for IMG</t>
+        </is>
+      </c>
+      <c r="B143" s="5" t="inlineStr">
+        <is>
+          <t>UKMLA for international medical graduates; UKMLA eligibility; UKMLA exam for UK medical students; UKMLA eligibility for international medical graduates</t>
+        </is>
+      </c>
+      <c r="C143" s="4" t="inlineStr">
+        <is>
           <t>Registration &amp; Eligibility</t>
         </is>
       </c>
-      <c r="D142" s="2" t="inlineStr">
+      <c r="D143" s="4" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
+      <c r="E143" s="4" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
+      <c r="F143" s="4" t="inlineStr">
+        <is>
+          <t>/eligibility</t>
+        </is>
+      </c>
+      <c r="G143" s="4" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H143" s="4" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I143" s="4" t="inlineStr">
+        <is>
+          <t>Established (31 posts)</t>
+        </is>
+      </c>
+      <c r="J143" s="4" t="inlineStr">
+        <is>
+          <t>N/A (static page)</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="4" t="inlineStr">
         <is>
           <t>Fees</t>
         </is>
       </c>
-      <c r="E142" s="2" t="inlineStr">
-        <is>
-          <t>GMC Registration Refund Policy: When You Can (and Can't) Get Your Fee Back</t>
-        </is>
-      </c>
-      <c r="F142" s="2" t="inlineStr">
-        <is>
-          <t>/news#gmc-registration-refund-policy</t>
-        </is>
-      </c>
-      <c r="G142" s="2" t="inlineStr">
-        <is>
-          <t>Informational</t>
-        </is>
-      </c>
-      <c r="H142" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="I142" s="2" t="inlineStr">
-        <is>
-          <t>Established (29 posts)</t>
-        </is>
-      </c>
-      <c r="J142" s="2" t="inlineStr">
-        <is>
-          <t>02 July 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
-        <is>
-          <t>GMC Welcome to UK Practice</t>
-        </is>
-      </c>
-      <c r="B143" s="3" t="inlineStr">
-        <is>
-          <t>how to practice medicine in UK; UKMLA practice questions free; gmc exam; gmc licensing; gmc Manchester</t>
-        </is>
-      </c>
-      <c r="C143" s="2" t="inlineStr">
+      <c r="B144" s="5" t="inlineStr"/>
+      <c r="C144" s="4" t="inlineStr">
         <is>
           <t>Registration &amp; Eligibility</t>
         </is>
       </c>
-      <c r="D143" s="2" t="inlineStr">
+      <c r="D144" s="4" t="inlineStr">
+        <is>
+          <t>Fees</t>
+        </is>
+      </c>
+      <c r="E144" s="4" t="inlineStr">
+        <is>
+          <t>Fees</t>
+        </is>
+      </c>
+      <c r="F144" s="4" t="inlineStr">
+        <is>
+          <t>/fees</t>
+        </is>
+      </c>
+      <c r="G144" s="4" t="inlineStr">
+        <is>
+          <t>Commercial</t>
+        </is>
+      </c>
+      <c r="H144" s="4" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I144" s="4" t="inlineStr">
+        <is>
+          <t>Established (31 posts)</t>
+        </is>
+      </c>
+      <c r="J144" s="4" t="inlineStr">
+        <is>
+          <t>N/A (static page)</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="4" t="inlineStr">
+        <is>
+          <t>UKMLA dates</t>
+        </is>
+      </c>
+      <c r="B145" s="5" t="inlineStr"/>
+      <c r="C145" s="4" t="inlineStr">
+        <is>
+          <t>Registration &amp; Eligibility</t>
+        </is>
+      </c>
+      <c r="D145" s="4" t="inlineStr">
+        <is>
+          <t>Key Dates</t>
+        </is>
+      </c>
+      <c r="E145" s="4" t="inlineStr">
+        <is>
+          <t>Key Dates</t>
+        </is>
+      </c>
+      <c r="F145" s="4" t="inlineStr">
+        <is>
+          <t>/key-dates</t>
+        </is>
+      </c>
+      <c r="G145" s="4" t="inlineStr">
+        <is>
+          <t>Transactional</t>
+        </is>
+      </c>
+      <c r="H145" s="4" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I145" s="4" t="inlineStr">
+        <is>
+          <t>Established (31 posts)</t>
+        </is>
+      </c>
+      <c r="J145" s="4" t="inlineStr">
+        <is>
+          <t>N/A (static page)</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="4" t="inlineStr">
+        <is>
+          <t>UKMLA registration</t>
+        </is>
+      </c>
+      <c r="B146" s="5" t="inlineStr">
+        <is>
+          <t>UKMLA booking; English language requirement for UKMLA; UKMLA registration process GMC</t>
+        </is>
+      </c>
+      <c r="C146" s="4" t="inlineStr">
+        <is>
+          <t>Registration &amp; Eligibility</t>
+        </is>
+      </c>
+      <c r="D146" s="4" t="inlineStr">
         <is>
           <t>Registration Guide</t>
         </is>
       </c>
-      <c r="E143" s="2" t="inlineStr">
-        <is>
-          <t>GMC Welcome to UK Practice: A Guide to the Free Induction Workshop</t>
-        </is>
-      </c>
-      <c r="F143" s="2" t="inlineStr">
-        <is>
-          <t>/news#gmc-welcome-to-uk-practice-induction-guide</t>
-        </is>
-      </c>
-      <c r="G143" s="2" t="inlineStr">
-        <is>
-          <t>Informational</t>
-        </is>
-      </c>
-      <c r="H143" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="I143" s="2" t="inlineStr">
-        <is>
-          <t>Established (29 posts)</t>
-        </is>
-      </c>
-      <c r="J143" s="2" t="inlineStr">
-        <is>
-          <t>02 July 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="2" t="inlineStr">
-        <is>
-          <t>how long does GMC registration take</t>
-        </is>
-      </c>
-      <c r="B144" s="3" t="inlineStr">
-        <is>
-          <t>UKMLA registration; GMC registration timeline how long; UKMLA GMC registration for graduates; UKMLA vs specialist registration GMC; UKMLA registration process GMC</t>
-        </is>
-      </c>
-      <c r="C144" s="2" t="inlineStr">
-        <is>
-          <t>Registration &amp; Eligibility</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="inlineStr">
+      <c r="E146" s="4" t="inlineStr">
         <is>
           <t>Registration Guide</t>
         </is>
       </c>
-      <c r="E144" s="2" t="inlineStr">
-        <is>
-          <t>How Long Does GMC Registration Take? A Realistic Timeline</t>
-        </is>
-      </c>
-      <c r="F144" s="2" t="inlineStr">
-        <is>
-          <t>/news#how-long-does-gmc-registration-take</t>
-        </is>
-      </c>
-      <c r="G144" s="2" t="inlineStr">
-        <is>
-          <t>Informational</t>
-        </is>
-      </c>
-      <c r="H144" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="I144" s="2" t="inlineStr">
-        <is>
-          <t>Established (29 posts)</t>
-        </is>
-      </c>
-      <c r="J144" s="2" t="inlineStr">
-        <is>
-          <t>02 July 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="2" t="inlineStr">
-        <is>
-          <t>how to register for PLAB 1</t>
-        </is>
-      </c>
-      <c r="B145" s="3" t="inlineStr">
-        <is>
-          <t>PLAB vs UKMLA; plab 1; plab 2; UKMLA vs PLAB; is UKMLA replacing PLAB</t>
-        </is>
-      </c>
-      <c r="C145" s="2" t="inlineStr">
-        <is>
-          <t>Registration &amp; Eligibility</t>
-        </is>
-      </c>
-      <c r="D145" s="2" t="inlineStr">
-        <is>
-          <t>Registration Guide</t>
-        </is>
-      </c>
-      <c r="E145" s="2" t="inlineStr">
-        <is>
-          <t>How to Register for PLAB 1: A Step-by-Step Guide for IMGs</t>
-        </is>
-      </c>
-      <c r="F145" s="2" t="inlineStr">
-        <is>
-          <t>/news#how-to-register-plab-1</t>
-        </is>
-      </c>
-      <c r="G145" s="2" t="inlineStr">
-        <is>
-          <t>Informational</t>
-        </is>
-      </c>
-      <c r="H145" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="I145" s="2" t="inlineStr">
-        <is>
-          <t>Established (29 posts)</t>
-        </is>
-      </c>
-      <c r="J145" s="2" t="inlineStr">
-        <is>
-          <t>30 June 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="2" t="inlineStr">
-        <is>
-          <t>indemnity insurance for doctors</t>
-        </is>
-      </c>
-      <c r="B146" s="3" t="inlineStr">
-        <is>
-          <t>UKMLA for GP doctors in UK; UKMLA for Indian doctors; UKMLA for Nigerian doctors; UKMLA for Pakistani doctors; UKMLA for Bangladeshi doctors</t>
-        </is>
-      </c>
-      <c r="C146" s="2" t="inlineStr">
-        <is>
-          <t>Registration &amp; Eligibility</t>
-        </is>
-      </c>
-      <c r="D146" s="2" t="inlineStr">
-        <is>
-          <t>Fees</t>
-        </is>
-      </c>
-      <c r="E146" s="2" t="inlineStr">
-        <is>
-          <t>Indemnity Insurance for Doctors, Explained</t>
-        </is>
-      </c>
-      <c r="F146" s="2" t="inlineStr">
-        <is>
-          <t>/news#indemnity-insurance-for-doctors-explained</t>
-        </is>
-      </c>
-      <c r="G146" s="2" t="inlineStr">
-        <is>
-          <t>Informational</t>
-        </is>
-      </c>
-      <c r="H146" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="I146" s="2" t="inlineStr">
-        <is>
-          <t>Established (29 posts)</t>
-        </is>
-      </c>
-      <c r="J146" s="2" t="inlineStr">
-        <is>
-          <t>02 July 2026</t>
+      <c r="F146" s="4" t="inlineStr">
+        <is>
+          <t>/registration-guide</t>
+        </is>
+      </c>
+      <c r="G146" s="4" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H146" s="4" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I146" s="4" t="inlineStr">
+        <is>
+          <t>Established (31 posts)</t>
+        </is>
+      </c>
+      <c r="J146" s="4" t="inlineStr">
+        <is>
+          <t>N/A (static page)</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>locally employed doctors GMC registration</t>
+          <t>Annual Review of Competence Progression</t>
         </is>
       </c>
       <c r="B147" s="3" t="inlineStr">
         <is>
-          <t>UKMLA for GP doctors in UK; UKMLA registration; UKMLA vs specialist registration GMC; GMC registration process for doctors; UKMLA GMC registration for graduates</t>
+          <t>GMC annual retention fee; The Biggest Confusion Explained; UKMLA AKT standard setting explained</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
@@ -8064,12 +8064,12 @@
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>Locally Employed Doctors: The Route to Full and Specialist GMC Registration</t>
+          <t>ARCP: The Annual Review of Competence Progression, Explained</t>
         </is>
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t>/news#locally-employed-doctors-route-to-gmc-registration</t>
+          <t>/news#arcp-annual-review-of-competence-progression-explained</t>
         </is>
       </c>
       <c r="G147" s="2" t="inlineStr">
@@ -8084,7 +8084,7 @@
       </c>
       <c r="I147" s="2" t="inlineStr">
         <is>
-          <t>Established (29 posts)</t>
+          <t>Established (31 posts)</t>
         </is>
       </c>
       <c r="J147" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>OET vs IELTS for GMC registration</t>
+          <t>cost of GMC registration</t>
         </is>
       </c>
       <c r="B148" s="3" t="inlineStr">
         <is>
-          <t>UKMLA registration; UKMLA GMC registration for graduates; UKMLA OET or IELTS requirement; UKMLA vs specialist registration GMC; UKMLA registration process GMC</t>
+          <t>UKMLA cost; UKMLA registration; cost of GMC registration 2026; UKMLA GMC registration for graduates; UKMLA vs specialist registration GMC</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
@@ -8111,17 +8111,17 @@
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>Eligibility</t>
+          <t>Fees</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>OET vs IELTS for GMC Registration: Which Should You Take?</t>
+          <t>Cost of GMC Registration 2026: Full Fee Breakdown</t>
         </is>
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>/news#oet-vs-ielts-for-gmc-registration-comparison</t>
+          <t>/news#cost-of-gmc-registration-2026</t>
         </is>
       </c>
       <c r="G148" s="2" t="inlineStr">
@@ -8136,24 +8136,24 @@
       </c>
       <c r="I148" s="2" t="inlineStr">
         <is>
-          <t>Established (29 posts)</t>
+          <t>Established (31 posts)</t>
         </is>
       </c>
       <c r="J148" s="2" t="inlineStr">
         <is>
-          <t>02 July 2026</t>
+          <t>03 July 2026</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>practising medicine in Scotland Wales Northern Ireland</t>
+          <t>UKMLA disability access adjustments</t>
         </is>
       </c>
       <c r="B149" s="3" t="inlineStr">
         <is>
-          <t>practising medicine in UK requirements; how to practice medicine in UK; Respiratory Medicine for the UKMLA: What to Focus On; how to practice medicine in UK from Philippines; Emergency Medicine and Acute Presentations in the UKMLA</t>
+          <t>ukmla guide; Reasonable Adjustments; reasonable adjustments gmc; about ukmla guide; contact ukmla guide</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
@@ -8163,17 +8163,17 @@
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>Registration Guide</t>
+          <t>Appeals and Resits</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>Practising Medicine in Scotland, Wales and Northern Ireland: What's Different?</t>
+          <t>Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide</t>
         </is>
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
-          <t>/news#scotland-wales-northern-ireland-registration-differences</t>
+          <t>/news#disability-access-ukmla-guide</t>
         </is>
       </c>
       <c r="G149" s="2" t="inlineStr">
@@ -8188,24 +8188,24 @@
       </c>
       <c r="I149" s="2" t="inlineStr">
         <is>
-          <t>Established (29 posts)</t>
+          <t>Established (31 posts)</t>
         </is>
       </c>
       <c r="J149" s="2" t="inlineStr">
         <is>
-          <t>02 July 2026</t>
+          <t>30 June 2026</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>Certificate of Completion of Training</t>
+          <t>UKMLA exemptions for specialist doctors</t>
         </is>
       </c>
       <c r="B150" s="3" t="inlineStr">
         <is>
-          <t>foundation year vs specialty training IMG; The Biggest Confusion Explained; UKMLA AKT standard setting explained</t>
+          <t>UKMLA for GP doctors in UK; do all doctors need to take UKMLA; is UKMLA required for experienced doctors; UKMLA for Indian doctors; UKMLA for Nigerian doctors</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
@@ -8215,17 +8215,17 @@
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>Registration Guide</t>
+          <t>Eligibility</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>The Certificate of Completion of Training (CCT), Explained</t>
+          <t>Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs</t>
         </is>
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>/news#certificate-of-completion-of-training-cct-explained</t>
+          <t>/news#ukmla-exemptions-for-specialist-and-gp-doctors</t>
         </is>
       </c>
       <c r="G150" s="2" t="inlineStr">
@@ -8240,24 +8240,24 @@
       </c>
       <c r="I150" s="2" t="inlineStr">
         <is>
-          <t>Established (29 posts)</t>
+          <t>Established (31 posts)</t>
         </is>
       </c>
       <c r="J150" s="2" t="inlineStr">
         <is>
-          <t>02 July 2026</t>
+          <t>01 July 2026</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>GMC annual retention fee</t>
+          <t>GMC EPIC verification</t>
         </is>
       </c>
       <c r="B151" s="3" t="inlineStr">
         <is>
-          <t>gmc exam; gmc licensing; gmc Manchester; gmc updates; UKMLA GMC registration for graduates</t>
+          <t>epic verification; GMC EPIC verification process; UKMLA EPIC verification India; UKMLA registration process GMC; gmc exam</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
@@ -8267,17 +8267,17 @@
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>Fees</t>
+          <t>Registration Guide</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>The GMC Annual Retention Fee, Explained</t>
+          <t>GMC EPIC/MyIntealth Verification Process Explained</t>
         </is>
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
-          <t>/news#gmc-annual-retention-fee-explained</t>
+          <t>/news#gmc-epic-verification-process-explained</t>
         </is>
       </c>
       <c r="G151" s="2" t="inlineStr">
@@ -8292,24 +8292,24 @@
       </c>
       <c r="I151" s="2" t="inlineStr">
         <is>
-          <t>Established (29 posts)</t>
+          <t>Established (31 posts)</t>
         </is>
       </c>
       <c r="J151" s="2" t="inlineStr">
         <is>
-          <t>02 July 2026</t>
+          <t>03 July 2026</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>internship requirement for GMC registration</t>
+          <t>GMC English language exemption</t>
         </is>
       </c>
       <c r="B152" s="3" t="inlineStr">
         <is>
-          <t>internship requirement for GMC; UKMLA registration; UKMLA GMC registration for graduates; UKMLA vs specialist registration GMC; UKMLA registration process GMC</t>
+          <t>English language requirement for UKMLA; OET vs IELTS for GMC registration; UKMLA exemption for specialists; gmc exam; gmc licensing</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
@@ -8324,12 +8324,12 @@
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>The Internship Requirement for GMC Registration, Explained</t>
+          <t>GMC English Language Exemption: Do You Need to Sit IELTS or OET?</t>
         </is>
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
-          <t>/news#internship-requirement-for-gmc-registration</t>
+          <t>/news#gmc-english-language-exemption-for-imgs</t>
         </is>
       </c>
       <c r="G152" s="2" t="inlineStr">
@@ -8344,7 +8344,7 @@
       </c>
       <c r="I152" s="2" t="inlineStr">
         <is>
-          <t>Established (29 posts)</t>
+          <t>Established (31 posts)</t>
         </is>
       </c>
       <c r="J152" s="2" t="inlineStr">
@@ -8356,12 +8356,12 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>NHS Pension Scheme for doctors</t>
+          <t>GMC Order reform 2026</t>
         </is>
       </c>
       <c r="B153" s="3" t="inlineStr">
         <is>
-          <t>UKMLA for GP doctors in UK; UKMLA for Indian doctors; UKMLA for Nigerian doctors; UKMLA for Pakistani doctors; UKMLA for Bangladeshi doctors</t>
+          <t>cost of GMC registration 2026; gmc exam; gmc licensing; gmc Manchester; gmc updates</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
@@ -8371,17 +8371,17 @@
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>Fees</t>
+          <t>Registration Guide</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>The NHS Pension Scheme for Doctors, Explained</t>
+          <t>GMC Order Reform 2026: The Consultation on Protected Medical Titles</t>
         </is>
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
-          <t>/news#nhs-pension-scheme-for-doctors-explained</t>
+          <t>/news#gmc-order-reform-2026-protected-medical-titles</t>
         </is>
       </c>
       <c r="G153" s="2" t="inlineStr">
@@ -8396,7 +8396,7 @@
       </c>
       <c r="I153" s="2" t="inlineStr">
         <is>
-          <t>Established (29 posts)</t>
+          <t>Established (31 posts)</t>
         </is>
       </c>
       <c r="J153" s="2" t="inlineStr">
@@ -8408,12 +8408,12 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>NHS e-Portfolio guide</t>
+          <t>GMC registration refund policy</t>
         </is>
       </c>
       <c r="B154" s="3" t="inlineStr">
         <is>
-          <t>ukmla guide; UKMLA for GP doctors in UK; about ukmla guide; contact ukmla guide; img guide</t>
+          <t>UKMLA registration; UKMLA GMC registration for graduates; UKMLA vs specialist registration GMC; UKMLA registration process GMC; gmc registration guide</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
@@ -8423,17 +8423,17 @@
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>Registration Guide</t>
+          <t>Fees</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>The NHS e-Portfolio: A Practical Guide for Doctors</t>
+          <t>GMC Registration Refund Policy: When You Can (and Can't) Get Your Fee Back</t>
         </is>
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
-          <t>/news#nhs-eportfolio-guide-for-doctors</t>
+          <t>/news#gmc-registration-refund-policy</t>
         </is>
       </c>
       <c r="G154" s="2" t="inlineStr">
@@ -8448,7 +8448,7 @@
       </c>
       <c r="I154" s="2" t="inlineStr">
         <is>
-          <t>Established (29 posts)</t>
+          <t>Established (31 posts)</t>
         </is>
       </c>
       <c r="J154" s="2" t="inlineStr">
@@ -8460,12 +8460,12 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>UKMLA exam booking process</t>
+          <t>GMC Welcome to UK Practice</t>
         </is>
       </c>
       <c r="B155" s="3" t="inlineStr">
         <is>
-          <t>UKMLA booking; UKMLA exam; what is the UKMLA exam; The Exam; UKMLA booking process for students</t>
+          <t>how to practice medicine in UK; UKMLA practice questions free; gmc exam; gmc licensing; gmc Manchester</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
@@ -8480,12 +8480,12 @@
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>The UKMLA Exam Booking Process: A Step-by-Step Walkthrough</t>
+          <t>GMC Welcome to UK Practice: A Guide to the Free Induction Workshop</t>
         </is>
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-exam-booking-process-gmc-online</t>
+          <t>/news#gmc-welcome-to-uk-practice-induction-guide</t>
         </is>
       </c>
       <c r="G155" s="2" t="inlineStr">
@@ -8500,7 +8500,7 @@
       </c>
       <c r="I155" s="2" t="inlineStr">
         <is>
-          <t>Established (29 posts)</t>
+          <t>Established (31 posts)</t>
         </is>
       </c>
       <c r="J155" s="2" t="inlineStr">
@@ -8512,12 +8512,12 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>types of GMC registration</t>
+          <t>how long does GMC registration take</t>
         </is>
       </c>
       <c r="B156" s="3" t="inlineStr">
         <is>
-          <t>UKMLA registration; UKMLA vs specialist registration GMC; UKMLA GMC registration for graduates; UKMLA registration process GMC; gmc registration guide</t>
+          <t>UKMLA registration; GMC registration timeline how long; UKMLA GMC registration for graduates; UKMLA vs specialist registration GMC; UKMLA registration process GMC</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
@@ -8532,12 +8532,12 @@
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>Types of GMC Registration Explained: Provisional, Full, Specialist and GP</t>
+          <t>How Long Does GMC Registration Take? A Realistic Timeline</t>
         </is>
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
-          <t>/news#types-of-gmc-registration-explained</t>
+          <t>/news#how-long-does-gmc-registration-take</t>
         </is>
       </c>
       <c r="G156" s="2" t="inlineStr">
@@ -8552,7 +8552,7 @@
       </c>
       <c r="I156" s="2" t="inlineStr">
         <is>
-          <t>Established (29 posts)</t>
+          <t>Established (31 posts)</t>
         </is>
       </c>
       <c r="J156" s="2" t="inlineStr">
@@ -8564,12 +8564,12 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>UKMLA eligibility</t>
+          <t>how to register for PLAB 1</t>
         </is>
       </c>
       <c r="B157" s="3" t="inlineStr">
         <is>
-          <t>Eligibility; UKMLA exam; what is the UKMLA exam; The Exam; UKMLA Eligibility Pathways</t>
+          <t>PLAB vs UKMLA; plab 1; plab 2; UKMLA vs PLAB; is UKMLA replacing PLAB</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
@@ -8579,17 +8579,17 @@
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>Eligibility</t>
+          <t>Registration Guide</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>UKMLA Eligibility: Who Can Sit the Exam?</t>
+          <t>How to Register for PLAB 1: A Step-by-Step Guide for IMGs</t>
         </is>
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-eligibility-who-can-sit</t>
+          <t>/news#how-to-register-plab-1</t>
         </is>
       </c>
       <c r="G157" s="2" t="inlineStr">
@@ -8604,7 +8604,7 @@
       </c>
       <c r="I157" s="2" t="inlineStr">
         <is>
-          <t>Established (29 posts)</t>
+          <t>Established (31 posts)</t>
         </is>
       </c>
       <c r="J157" s="2" t="inlineStr">
@@ -8616,12 +8616,12 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>UKMLA exam day what to expect</t>
+          <t>indemnity insurance for doctors</t>
         </is>
       </c>
       <c r="B158" s="3" t="inlineStr">
         <is>
-          <t>UKMLA exam; what is the UKMLA exam; The Exam; AKT exam; CPSA exam</t>
+          <t>UKMLA for GP doctors in UK; UKMLA for Indian doctors; UKMLA for Nigerian doctors; UKMLA for Pakistani doctors; UKMLA for Bangladeshi doctors</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
@@ -8631,17 +8631,17 @@
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>Registration Guide</t>
+          <t>Fees</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>UKMLA Exam Day: What to Expect at the AKT and CPSA</t>
+          <t>Indemnity Insurance for Doctors, Explained</t>
         </is>
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-exam-day-what-to-expect</t>
+          <t>/news#indemnity-insurance-for-doctors-explained</t>
         </is>
       </c>
       <c r="G158" s="2" t="inlineStr">
@@ -8656,7 +8656,7 @@
       </c>
       <c r="I158" s="2" t="inlineStr">
         <is>
-          <t>Established (29 posts)</t>
+          <t>Established (31 posts)</t>
         </is>
       </c>
       <c r="J158" s="2" t="inlineStr">
@@ -8668,12 +8668,12 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>UKMLA exam fees for IMG</t>
+          <t>locally employed doctors GMC registration</t>
         </is>
       </c>
       <c r="B159" s="3" t="inlineStr">
         <is>
-          <t>UKMLA exam; UKMLA fees; UKMLA for IMG; what is the UKMLA exam; The Exam</t>
+          <t>UKMLA for GP doctors in UK; UKMLA registration; UKMLA vs specialist registration GMC; GMC registration process for doctors; UKMLA GMC registration for graduates</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
@@ -8683,17 +8683,17 @@
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>Fees</t>
+          <t>Registration Guide</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide</t>
+          <t>Locally Employed Doctors: The Route to Full and Specialist GMC Registration</t>
         </is>
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-fees-for-img-2026</t>
+          <t>/news#locally-employed-doctors-route-to-gmc-registration</t>
         </is>
       </c>
       <c r="G159" s="2" t="inlineStr">
@@ -8708,24 +8708,24 @@
       </c>
       <c r="I159" s="2" t="inlineStr">
         <is>
-          <t>Established (29 posts)</t>
+          <t>Established (31 posts)</t>
         </is>
       </c>
       <c r="J159" s="2" t="inlineStr">
         <is>
-          <t>01 July 2026</t>
+          <t>02 July 2026</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>UKMLA fees</t>
+          <t>OET vs IELTS for GMC registration</t>
         </is>
       </c>
       <c r="B160" s="3" t="inlineStr">
         <is>
-          <t>UKMLA fees for doctors 2026; UKMLA cost; UKMLA Fees and Costs 2026; UKMLA exam fees for IMG; UKMLA fees in Indian rupees</t>
+          <t>UKMLA registration; UKMLA GMC registration for graduates; UKMLA OET or IELTS requirement; UKMLA vs specialist registration GMC; UKMLA registration process GMC</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
@@ -8735,17 +8735,17 @@
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>Fees</t>
+          <t>Eligibility</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>UKMLA Fees: The Complete 2026 Cost Breakdown</t>
+          <t>OET vs IELTS for GMC Registration: Which Should You Take?</t>
         </is>
       </c>
       <c r="F160" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-fees-explained</t>
+          <t>/news#oet-vs-ielts-for-gmc-registration-comparison</t>
         </is>
       </c>
       <c r="G160" s="2" t="inlineStr">
@@ -8760,24 +8760,24 @@
       </c>
       <c r="I160" s="2" t="inlineStr">
         <is>
-          <t>Established (29 posts)</t>
+          <t>Established (31 posts)</t>
         </is>
       </c>
       <c r="J160" s="2" t="inlineStr">
         <is>
-          <t>30 June 2026</t>
+          <t>02 July 2026</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>UKMLA key dates</t>
+          <t>practising medicine in Scotland Wales Northern Ireland</t>
         </is>
       </c>
       <c r="B161" s="3" t="inlineStr">
         <is>
-          <t>UKMLA dates; Key Dates; Key Dates &amp; Timeline; UKMLA exam dates 2026; UKMLA exam dates and fees</t>
+          <t>practising medicine in UK requirements; how to practice medicine in UK; Respiratory Medicine for the UKMLA: What to Focus On; how to practice medicine in UK from Philippines; Emergency Medicine and Acute Presentations in the UKMLA</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
@@ -8787,22 +8787,22 @@
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>Key Dates</t>
+          <t>Registration Guide</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>UKMLA Key Dates and Sitting Schedule: What to Know</t>
+          <t>Practising Medicine in Scotland, Wales and Northern Ireland: What's Different?</t>
         </is>
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-key-dates-sitting-schedule</t>
+          <t>/news#scotland-wales-northern-ireland-registration-differences</t>
         </is>
       </c>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>Transactional</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="H161" s="2" t="inlineStr">
@@ -8812,24 +8812,24 @@
       </c>
       <c r="I161" s="2" t="inlineStr">
         <is>
-          <t>Established (29 posts)</t>
+          <t>Established (31 posts)</t>
         </is>
       </c>
       <c r="J161" s="2" t="inlineStr">
         <is>
-          <t>30 June 2026</t>
+          <t>02 July 2026</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>UKMLA resits</t>
+          <t>Certificate of Completion of Training</t>
         </is>
       </c>
       <c r="B162" s="3" t="inlineStr">
         <is>
-          <t>Appeals &amp; Resits; UKMLA Appeals, Resits &amp; Reasonable Adjustments; Appeals, Resits &amp; Reasonable Adjustments; Attempt Limits and Retake Rules; plab attempt limits</t>
+          <t>foundation year vs specialty training IMG; The Biggest Confusion Explained; UKMLA AKT standard setting explained</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
@@ -8839,17 +8839,17 @@
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>Appeals and Resits</t>
+          <t>Registration Guide</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>UKMLA Resits: Rules, Limits, and How to Bounce Back</t>
+          <t>The Certificate of Completion of Training (CCT), Explained</t>
         </is>
       </c>
       <c r="F162" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-resits-rules-limits</t>
+          <t>/news#certificate-of-completion-of-training-cct-explained</t>
         </is>
       </c>
       <c r="G162" s="2" t="inlineStr">
@@ -8864,24 +8864,24 @@
       </c>
       <c r="I162" s="2" t="inlineStr">
         <is>
-          <t>Established (29 posts)</t>
+          <t>Established (31 posts)</t>
         </is>
       </c>
       <c r="J162" s="2" t="inlineStr">
         <is>
-          <t>30 June 2026</t>
+          <t>02 July 2026</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>UKMLA special circumstances</t>
+          <t>GMC annual retention fee</t>
         </is>
       </c>
       <c r="B163" s="3" t="inlineStr">
         <is>
-          <t>Mitigating Circumstances; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Attempt limits, mitigating circumstances, reasonable adjustments, and how to appeal a licensing decision</t>
+          <t>gmc exam; gmc licensing; gmc Manchester; gmc updates; UKMLA GMC registration for graduates</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
@@ -8891,17 +8891,17 @@
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>Registration Guide</t>
+          <t>Fees</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>UKMLA Special Circumstances: Accommodations Beyond Disability Access</t>
+          <t>The GMC Annual Retention Fee, Explained</t>
         </is>
       </c>
       <c r="F163" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-special-circumstances-and-accommodations</t>
+          <t>/news#gmc-annual-retention-fee-explained</t>
         </is>
       </c>
       <c r="G163" s="2" t="inlineStr">
@@ -8916,7 +8916,7 @@
       </c>
       <c r="I163" s="2" t="inlineStr">
         <is>
-          <t>Established (29 posts)</t>
+          <t>Established (31 posts)</t>
         </is>
       </c>
       <c r="J163" s="2" t="inlineStr">
@@ -8928,12 +8928,12 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>primary medical qualification GMC accepted</t>
+          <t>internship requirement for GMC registration</t>
         </is>
       </c>
       <c r="B164" s="3" t="inlineStr">
         <is>
-          <t>gmc exam; gmc licensing; gmc Manchester; gmc updates; medical acronyms</t>
+          <t>internship requirement for GMC; UKMLA registration; UKMLA GMC registration for graduates; UKMLA vs specialist registration GMC; UKMLA registration process GMC</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
@@ -8948,12 +8948,12 @@
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>Which Medical Qualifications Does the GMC Accept? PMQ Recognition Explained</t>
+          <t>The Internship Requirement for GMC Registration, Explained</t>
         </is>
       </c>
       <c r="F164" s="2" t="inlineStr">
         <is>
-          <t>/news#gmc-recognised-primary-medical-qualifications</t>
+          <t>/news#internship-requirement-for-gmc-registration</t>
         </is>
       </c>
       <c r="G164" s="2" t="inlineStr">
@@ -8968,7 +8968,7 @@
       </c>
       <c r="I164" s="2" t="inlineStr">
         <is>
-          <t>Established (29 posts)</t>
+          <t>Established (31 posts)</t>
         </is>
       </c>
       <c r="J164" s="2" t="inlineStr">
@@ -8980,12 +8980,12 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>working hours and rest rules for doctors</t>
+          <t>NHS Pension Scheme for doctors</t>
         </is>
       </c>
       <c r="B165" s="3" t="inlineStr">
         <is>
-          <t>UKMLA for GP doctors in UK; UKMLA preparation for working doctors; UKMLA for Indian doctors; UKMLA for Nigerian doctors; UKMLA for Pakistani doctors</t>
+          <t>UKMLA for GP doctors in UK; UKMLA for Indian doctors; UKMLA for Nigerian doctors; UKMLA for Pakistani doctors; UKMLA for Bangladeshi doctors</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
@@ -8995,169 +8995,173 @@
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
+          <t>Fees</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>The NHS Pension Scheme for Doctors, Explained</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>/news#nhs-pension-scheme-for-doctors-explained</t>
+        </is>
+      </c>
+      <c r="G165" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H165" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I165" s="2" t="inlineStr">
+        <is>
+          <t>Established (31 posts)</t>
+        </is>
+      </c>
+      <c r="J165" s="2" t="inlineStr">
+        <is>
+          <t>02 July 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>NHS e-Portfolio guide</t>
+        </is>
+      </c>
+      <c r="B166" s="3" t="inlineStr">
+        <is>
+          <t>ukmla guide; UKMLA for GP doctors in UK; about ukmla guide; contact ukmla guide; img guide</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>Registration &amp; Eligibility</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
           <t>Registration Guide</t>
         </is>
       </c>
-      <c r="E165" s="2" t="inlineStr">
-        <is>
-          <t>Working Hours and Rest Rules for Doctors: The EWTD Explained</t>
-        </is>
-      </c>
-      <c r="F165" s="2" t="inlineStr">
-        <is>
-          <t>/news#ewtd-working-hours-and-rest-rules-for-doctors</t>
-        </is>
-      </c>
-      <c r="G165" s="2" t="inlineStr">
-        <is>
-          <t>Informational</t>
-        </is>
-      </c>
-      <c r="H165" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="I165" s="2" t="inlineStr">
-        <is>
-          <t>Established (29 posts)</t>
-        </is>
-      </c>
-      <c r="J165" s="2" t="inlineStr">
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>The NHS e-Portfolio: A Practical Guide for Doctors</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>/news#nhs-eportfolio-guide-for-doctors</t>
+        </is>
+      </c>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H166" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I166" s="2" t="inlineStr">
+        <is>
+          <t>Established (31 posts)</t>
+        </is>
+      </c>
+      <c r="J166" s="2" t="inlineStr">
         <is>
           <t>02 July 2026</t>
         </is>
       </c>
     </row>
-    <row r="166">
-      <c r="A166" s="4" t="inlineStr">
-        <is>
-          <t>Appeals and Resits</t>
-        </is>
-      </c>
-      <c r="B166" s="5" t="inlineStr"/>
-      <c r="C166" s="4" t="inlineStr">
-        <is>
-          <t>Results &amp; Scoring</t>
-        </is>
-      </c>
-      <c r="D166" s="4" t="inlineStr">
-        <is>
-          <t>Appeals and Resits</t>
-        </is>
-      </c>
-      <c r="E166" s="4" t="inlineStr">
-        <is>
-          <t>Appeals and Resits</t>
-        </is>
-      </c>
-      <c r="F166" s="4" t="inlineStr">
-        <is>
-          <t>/appeals-and-resits</t>
-        </is>
-      </c>
-      <c r="G166" s="4" t="inlineStr">
-        <is>
-          <t>Informational</t>
-        </is>
-      </c>
-      <c r="H166" s="4" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="I166" s="4" t="inlineStr">
-        <is>
-          <t>Growing (3 posts)</t>
-        </is>
-      </c>
-      <c r="J166" s="4" t="inlineStr">
-        <is>
-          <t>N/A (static page)</t>
-        </is>
-      </c>
-    </row>
     <row r="167">
-      <c r="A167" s="4" t="inlineStr">
-        <is>
-          <t>UKMLA results</t>
-        </is>
-      </c>
-      <c r="B167" s="5" t="inlineStr">
-        <is>
-          <t>UKMLA pass mark; UKMLA pass rate for IMG; UKMLA results release date</t>
-        </is>
-      </c>
-      <c r="C167" s="4" t="inlineStr">
-        <is>
-          <t>Results &amp; Scoring</t>
-        </is>
-      </c>
-      <c r="D167" s="4" t="inlineStr">
-        <is>
-          <t>Results and Scoring</t>
-        </is>
-      </c>
-      <c r="E167" s="4" t="inlineStr">
-        <is>
-          <t>Results and Scoring</t>
-        </is>
-      </c>
-      <c r="F167" s="4" t="inlineStr">
-        <is>
-          <t>/results-and-scoring</t>
-        </is>
-      </c>
-      <c r="G167" s="4" t="inlineStr">
-        <is>
-          <t>Informational</t>
-        </is>
-      </c>
-      <c r="H167" s="4" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="I167" s="4" t="inlineStr">
-        <is>
-          <t>Growing (3 posts)</t>
-        </is>
-      </c>
-      <c r="J167" s="4" t="inlineStr">
-        <is>
-          <t>N/A (static page)</t>
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA exam booking process</t>
+        </is>
+      </c>
+      <c r="B167" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA booking; UKMLA exam; what is the UKMLA exam; The Exam; UKMLA booking process for students</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>Registration &amp; Eligibility</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>Registration Guide</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>The UKMLA Exam Booking Process: A Step-by-Step Walkthrough</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-exam-booking-process-gmc-online</t>
+        </is>
+      </c>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H167" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I167" s="2" t="inlineStr">
+        <is>
+          <t>Established (31 posts)</t>
+        </is>
+      </c>
+      <c r="J167" s="2" t="inlineStr">
+        <is>
+          <t>02 July 2026</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>UKMLA AKT pass mark</t>
+          <t>types of GMC registration</t>
         </is>
       </c>
       <c r="B168" s="3" t="inlineStr">
         <is>
-          <t>UKMLA AKT; UKMLA pass mark; how to pass ukmla; ms akt; What is the UKMLA AKT?</t>
+          <t>UKMLA registration; UKMLA vs specialist registration GMC; UKMLA GMC registration for graduates; UKMLA registration process GMC; gmc registration guide</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>Results &amp; Scoring</t>
+          <t>Registration &amp; Eligibility</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>Results and Scoring</t>
+          <t>Registration Guide</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>UKMLA AKT Pass Mark and Pass Rate Explained</t>
+          <t>Types of GMC Registration Explained: Provisional, Full, Specialist and GP</t>
         </is>
       </c>
       <c r="F168" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-akt-pass-mark-and-pass-rate-explained</t>
+          <t>/news#types-of-gmc-registration-explained</t>
         </is>
       </c>
       <c r="G168" s="2" t="inlineStr">
@@ -9172,44 +9176,44 @@
       </c>
       <c r="I168" s="2" t="inlineStr">
         <is>
-          <t>Growing (3 posts)</t>
+          <t>Established (31 posts)</t>
         </is>
       </c>
       <c r="J168" s="2" t="inlineStr">
         <is>
-          <t>01 July 2026</t>
+          <t>02 July 2026</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>UKMLA results feedback</t>
+          <t>UKMLA eligibility</t>
         </is>
       </c>
       <c r="B169" s="3" t="inlineStr">
         <is>
-          <t>UKMLA results; Results &amp; Data; Results &amp; Scoring; UKMLA results timeline 2026; UKMLA results release date</t>
+          <t>Eligibility; UKMLA exam; what is the UKMLA exam; The Exam; UKMLA Eligibility Pathways</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>Results &amp; Scoring</t>
+          <t>Registration &amp; Eligibility</t>
         </is>
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>Results and Scoring</t>
+          <t>Eligibility</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>UKMLA Results: How to Interpret Your Feedback Report</t>
+          <t>UKMLA Eligibility: Who Can Sit the Exam?</t>
         </is>
       </c>
       <c r="F169" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-results-feedback-report</t>
+          <t>/news#ukmla-eligibility-who-can-sit</t>
         </is>
       </c>
       <c r="G169" s="2" t="inlineStr">
@@ -9224,7 +9228,7 @@
       </c>
       <c r="I169" s="2" t="inlineStr">
         <is>
-          <t>Growing (3 posts)</t>
+          <t>Established (31 posts)</t>
         </is>
       </c>
       <c r="J169" s="2" t="inlineStr">
@@ -9236,32 +9240,32 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>what happens if you fail UKMLA</t>
+          <t>UKMLA exam day what to expect</t>
         </is>
       </c>
       <c r="B170" s="3" t="inlineStr">
         <is>
-          <t>UKMLA fail foundation year impact; UKMLA and foundation year application; foundation year vs specialty training IMG; how to prepare for UKMLA final year; UKMLA for academic foundation programme</t>
+          <t>UKMLA exam; what is the UKMLA exam; The Exam; AKT exam; CPSA exam</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>Results &amp; Scoring</t>
+          <t>Registration &amp; Eligibility</t>
         </is>
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>Appeals and Resits</t>
+          <t>Registration Guide</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>What Happens If You Fail the UKMLA? The Impact on Your Foundation Year</t>
+          <t>UKMLA Exam Day: What to Expect at the AKT and CPSA</t>
         </is>
       </c>
       <c r="F170" s="2" t="inlineStr">
         <is>
-          <t>/news#what-happens-if-you-fail-ukmla-foundation-year-impact</t>
+          <t>/news#ukmla-exam-day-what-to-expect</t>
         </is>
       </c>
       <c r="G170" s="2" t="inlineStr">
@@ -9276,7 +9280,7 @@
       </c>
       <c r="I170" s="2" t="inlineStr">
         <is>
-          <t>Growing (3 posts)</t>
+          <t>Established (31 posts)</t>
         </is>
       </c>
       <c r="J170" s="2" t="inlineStr">
@@ -9288,53 +9292,673 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
+          <t>UKMLA exam fees for IMG</t>
+        </is>
+      </c>
+      <c r="B171" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA exam; UKMLA fees; UKMLA for IMG; what is the UKMLA exam; The Exam</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>Registration &amp; Eligibility</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>Fees</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-fees-for-img-2026</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I171" s="2" t="inlineStr">
+        <is>
+          <t>Established (31 posts)</t>
+        </is>
+      </c>
+      <c r="J171" s="2" t="inlineStr">
+        <is>
+          <t>01 July 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA fees</t>
+        </is>
+      </c>
+      <c r="B172" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA fees for doctors 2026; UKMLA cost; UKMLA Fees and Costs 2026; UKMLA exam fees for IMG; UKMLA fees in Indian rupees</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>Registration &amp; Eligibility</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>Fees</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA Fees: The Complete 2026 Cost Breakdown</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-fees-explained</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H172" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I172" s="2" t="inlineStr">
+        <is>
+          <t>Established (31 posts)</t>
+        </is>
+      </c>
+      <c r="J172" s="2" t="inlineStr">
+        <is>
+          <t>30 June 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA key dates</t>
+        </is>
+      </c>
+      <c r="B173" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA dates; Key Dates; Key Dates &amp; Timeline; UKMLA exam dates 2026; UKMLA exam dates and fees</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>Registration &amp; Eligibility</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>Key Dates</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA Key Dates and Sitting Schedule: What to Know</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-key-dates-sitting-schedule</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>Transactional</t>
+        </is>
+      </c>
+      <c r="H173" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I173" s="2" t="inlineStr">
+        <is>
+          <t>Established (31 posts)</t>
+        </is>
+      </c>
+      <c r="J173" s="2" t="inlineStr">
+        <is>
+          <t>30 June 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA resits</t>
+        </is>
+      </c>
+      <c r="B174" s="3" t="inlineStr">
+        <is>
+          <t>Appeals &amp; Resits; UKMLA Appeals, Resits &amp; Reasonable Adjustments; Appeals, Resits &amp; Reasonable Adjustments; Attempt Limits and Retake Rules; plab attempt limits</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>Registration &amp; Eligibility</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>Appeals and Resits</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA Resits: Rules, Limits, and How to Bounce Back</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-resits-rules-limits</t>
+        </is>
+      </c>
+      <c r="G174" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H174" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I174" s="2" t="inlineStr">
+        <is>
+          <t>Established (31 posts)</t>
+        </is>
+      </c>
+      <c r="J174" s="2" t="inlineStr">
+        <is>
+          <t>30 June 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA special circumstances</t>
+        </is>
+      </c>
+      <c r="B175" s="3" t="inlineStr">
+        <is>
+          <t>Mitigating Circumstances; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Attempt limits, mitigating circumstances, reasonable adjustments, and how to appeal a licensing decision</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>Registration &amp; Eligibility</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>Registration Guide</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA Special Circumstances: Accommodations Beyond Disability Access</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-special-circumstances-and-accommodations</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H175" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I175" s="2" t="inlineStr">
+        <is>
+          <t>Established (31 posts)</t>
+        </is>
+      </c>
+      <c r="J175" s="2" t="inlineStr">
+        <is>
+          <t>02 July 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>primary medical qualification GMC accepted</t>
+        </is>
+      </c>
+      <c r="B176" s="3" t="inlineStr">
+        <is>
+          <t>gmc exam; gmc licensing; gmc Manchester; gmc updates; medical acronyms</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>Registration &amp; Eligibility</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>Which Medical Qualifications Does the GMC Accept? PMQ Recognition Explained</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>/news#gmc-recognised-primary-medical-qualifications</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H176" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I176" s="2" t="inlineStr">
+        <is>
+          <t>Established (31 posts)</t>
+        </is>
+      </c>
+      <c r="J176" s="2" t="inlineStr">
+        <is>
+          <t>02 July 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>working hours and rest rules for doctors</t>
+        </is>
+      </c>
+      <c r="B177" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA for GP doctors in UK; UKMLA preparation for working doctors; UKMLA for Indian doctors; UKMLA for Nigerian doctors; UKMLA for Pakistani doctors</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>Registration &amp; Eligibility</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>Registration Guide</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr">
+        <is>
+          <t>Working Hours and Rest Rules for Doctors: The EWTD Explained</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>/news#ewtd-working-hours-and-rest-rules-for-doctors</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H177" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I177" s="2" t="inlineStr">
+        <is>
+          <t>Established (31 posts)</t>
+        </is>
+      </c>
+      <c r="J177" s="2" t="inlineStr">
+        <is>
+          <t>02 July 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="4" t="inlineStr">
+        <is>
+          <t>Appeals and Resits</t>
+        </is>
+      </c>
+      <c r="B178" s="5" t="inlineStr"/>
+      <c r="C178" s="4" t="inlineStr">
+        <is>
+          <t>Results &amp; Scoring</t>
+        </is>
+      </c>
+      <c r="D178" s="4" t="inlineStr">
+        <is>
+          <t>Appeals and Resits</t>
+        </is>
+      </c>
+      <c r="E178" s="4" t="inlineStr">
+        <is>
+          <t>Appeals and Resits</t>
+        </is>
+      </c>
+      <c r="F178" s="4" t="inlineStr">
+        <is>
+          <t>/appeals-and-resits</t>
+        </is>
+      </c>
+      <c r="G178" s="4" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H178" s="4" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I178" s="4" t="inlineStr">
+        <is>
+          <t>Growing (3 posts)</t>
+        </is>
+      </c>
+      <c r="J178" s="4" t="inlineStr">
+        <is>
+          <t>N/A (static page)</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="4" t="inlineStr">
+        <is>
+          <t>UKMLA results</t>
+        </is>
+      </c>
+      <c r="B179" s="5" t="inlineStr">
+        <is>
+          <t>UKMLA pass mark; UKMLA pass rate for IMG; UKMLA results release date</t>
+        </is>
+      </c>
+      <c r="C179" s="4" t="inlineStr">
+        <is>
+          <t>Results &amp; Scoring</t>
+        </is>
+      </c>
+      <c r="D179" s="4" t="inlineStr">
+        <is>
+          <t>Results and Scoring</t>
+        </is>
+      </c>
+      <c r="E179" s="4" t="inlineStr">
+        <is>
+          <t>Results and Scoring</t>
+        </is>
+      </c>
+      <c r="F179" s="4" t="inlineStr">
+        <is>
+          <t>/results-and-scoring</t>
+        </is>
+      </c>
+      <c r="G179" s="4" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H179" s="4" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I179" s="4" t="inlineStr">
+        <is>
+          <t>Growing (3 posts)</t>
+        </is>
+      </c>
+      <c r="J179" s="4" t="inlineStr">
+        <is>
+          <t>N/A (static page)</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA AKT pass mark</t>
+        </is>
+      </c>
+      <c r="B180" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA AKT; UKMLA pass mark; how to pass ukmla; ms akt; What is the UKMLA AKT?</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>Results &amp; Scoring</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>Results and Scoring</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA AKT Pass Mark and Pass Rate Explained</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-akt-pass-mark-and-pass-rate-explained</t>
+        </is>
+      </c>
+      <c r="G180" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H180" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I180" s="2" t="inlineStr">
+        <is>
+          <t>Growing (3 posts)</t>
+        </is>
+      </c>
+      <c r="J180" s="2" t="inlineStr">
+        <is>
+          <t>01 July 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA results feedback</t>
+        </is>
+      </c>
+      <c r="B181" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA results; Results &amp; Data; Results &amp; Scoring; UKMLA results timeline 2026; UKMLA results release date</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>Results &amp; Scoring</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
+        <is>
+          <t>Results and Scoring</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA Results: How to Interpret Your Feedback Report</t>
+        </is>
+      </c>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-results-feedback-report</t>
+        </is>
+      </c>
+      <c r="G181" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H181" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I181" s="2" t="inlineStr">
+        <is>
+          <t>Growing (3 posts)</t>
+        </is>
+      </c>
+      <c r="J181" s="2" t="inlineStr">
+        <is>
+          <t>30 June 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>what happens if you fail UKMLA</t>
+        </is>
+      </c>
+      <c r="B182" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA fail foundation year impact; UKMLA and foundation year application; foundation year vs specialty training IMG; how to prepare for UKMLA final year; UKMLA for academic foundation programme</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>Results &amp; Scoring</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>Appeals and Resits</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>What Happens If You Fail the UKMLA? The Impact on Your Foundation Year</t>
+        </is>
+      </c>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>/news#what-happens-if-you-fail-ukmla-foundation-year-impact</t>
+        </is>
+      </c>
+      <c r="G182" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H182" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I182" s="2" t="inlineStr">
+        <is>
+          <t>Growing (3 posts)</t>
+        </is>
+      </c>
+      <c r="J182" s="2" t="inlineStr">
+        <is>
+          <t>02 July 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
           <t>Foundation Programme after UKMLA</t>
         </is>
       </c>
-      <c r="B171" s="3" t="inlineStr">
+      <c r="B183" s="3" t="inlineStr">
         <is>
           <t>UKMLA for academic foundation programme; UKMLA after MBBS; UKMLA after MBBS in India; UKMLA and foundation year application; UKMLA fail foundation year impact</t>
         </is>
       </c>
-      <c r="C171" s="2" t="inlineStr">
+      <c r="C183" s="2" t="inlineStr">
         <is>
           <t>Uncategorised</t>
         </is>
       </c>
-      <c r="D171" s="2" t="inlineStr"/>
-      <c r="E171" s="2" t="inlineStr">
+      <c r="D183" s="2" t="inlineStr"/>
+      <c r="E183" s="2" t="inlineStr">
         <is>
           <t>Understanding the Foundation Programme: What Awaits After the UKMLA</t>
         </is>
       </c>
-      <c r="F171" s="2" t="inlineStr">
+      <c r="F183" s="2" t="inlineStr">
         <is>
           <t>/news#foundation-programme-after-ukmla</t>
         </is>
       </c>
-      <c r="G171" s="2" t="inlineStr">
-        <is>
-          <t>Informational</t>
-        </is>
-      </c>
-      <c r="H171" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="I171" s="2" t="inlineStr">
+      <c r="G183" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="H183" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="I183" s="2" t="inlineStr">
         <is>
           <t>Needs More Support (1 post)</t>
         </is>
       </c>
-      <c r="J171" s="2" t="inlineStr">
+      <c r="J183" s="2" t="inlineStr">
         <is>
           <t>30 June 2026</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J171"/>
+  <autoFilter ref="A1:J183"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9386,7 +10010,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>157</v>
+        <v>169</v>
       </c>
     </row>
     <row r="6">
@@ -9443,7 +10067,7 @@
       <c r="A12" s="9" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Clinical Systems Revision: 46 posts — Established (46 posts)</t>
+          <t>IMG Country Routes &amp; Global Comparisons: 51 posts — Established (51 posts)</t>
         </is>
       </c>
     </row>
@@ -9451,7 +10075,7 @@
       <c r="A13" s="9" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons: 43 posts — Established (43 posts)</t>
+          <t>Clinical Systems Revision: 46 posts — Established (46 posts)</t>
         </is>
       </c>
     </row>
@@ -9459,7 +10083,7 @@
       <c r="A14" s="9" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Registration &amp; Eligibility: 29 posts — Established (29 posts)</t>
+          <t>Registration &amp; Eligibility: 31 posts — Established (31 posts)</t>
         </is>
       </c>
     </row>
@@ -9475,7 +10099,7 @@
       <c r="A16" s="9" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Exam Preparation: 8 posts — Established (8 posts)</t>
+          <t>Exam Preparation: 10 posts — Established (10 posts)</t>
         </is>
       </c>
     </row>
